--- a/data/searchresults.xlsx
+++ b/data/searchresults.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f0ae25cf28fa736a/Projects/BIAutomations/shipment-schedule/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{293ED245-5B87-43DD-B8A5-39298595C6BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{61969EF7-9912-4B44-8214-4F1B6AE3D726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A390BCB3-8B65-4562-86A4-CCD9BC532A50}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0B368942-8F3B-44B2-8BD1-9F04935E3B49}"/>
   </bookViews>
   <sheets>
     <sheet name="OPTSensiMedicalSalesOpenOrderR" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1311" uniqueCount="380">
   <si>
     <t>Division</t>
   </si>
@@ -103,6 +103,426 @@
     <t>MD</t>
   </si>
   <si>
+    <t>201052</t>
+  </si>
+  <si>
+    <t>MCK : MCKESSON MEDICAL SURGICAL MD PC 201052</t>
+  </si>
+  <si>
+    <t>SO153712</t>
+  </si>
+  <si>
+    <t>36936661</t>
+  </si>
+  <si>
+    <t>SENSI MEDICAL</t>
+  </si>
+  <si>
+    <t>V7871800000</t>
+  </si>
+  <si>
+    <t>20164396C</t>
+  </si>
+  <si>
+    <t>1258911</t>
+  </si>
+  <si>
+    <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>20710 HEMPSTEAD ROAD</t>
+  </si>
+  <si>
+    <t>HOUSTON</t>
+  </si>
+  <si>
+    <t>TX</t>
+  </si>
+  <si>
+    <t>77065</t>
+  </si>
+  <si>
+    <t>SO153713</t>
+  </si>
+  <si>
+    <t>36936662</t>
+  </si>
+  <si>
+    <t>4250 PATRIOT DRIVE</t>
+  </si>
+  <si>
+    <t>GRAPEVINE</t>
+  </si>
+  <si>
+    <t>76051</t>
+  </si>
+  <si>
+    <t>SO153723</t>
+  </si>
+  <si>
+    <t>36936673</t>
+  </si>
+  <si>
+    <t>PHOENIX DC #264</t>
+  </si>
+  <si>
+    <t>TOLLESON</t>
+  </si>
+  <si>
+    <t>AZ</t>
+  </si>
+  <si>
+    <t>85353</t>
+  </si>
+  <si>
+    <t>201001</t>
+  </si>
+  <si>
+    <t>CAH : CARDINAL - MD DS 201001</t>
+  </si>
+  <si>
+    <t>SO153728</t>
+  </si>
+  <si>
+    <t>4231341053</t>
+  </si>
+  <si>
+    <t>7871800002</t>
+  </si>
+  <si>
+    <t>20164395C</t>
+  </si>
+  <si>
+    <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+  </si>
+  <si>
+    <t>1550 FIRST COLONY BLVD</t>
+  </si>
+  <si>
+    <t>SUGAR LAND</t>
+  </si>
+  <si>
+    <t>774794000</t>
+  </si>
+  <si>
+    <t>SO153721</t>
+  </si>
+  <si>
+    <t>36936671</t>
+  </si>
+  <si>
+    <t>SEATTLE  #255</t>
+  </si>
+  <si>
+    <t>KENT</t>
+  </si>
+  <si>
+    <t>WA</t>
+  </si>
+  <si>
+    <t>98032</t>
+  </si>
+  <si>
+    <t>V7871800002</t>
+  </si>
+  <si>
+    <t>20164397C</t>
+  </si>
+  <si>
+    <t>1258913</t>
+  </si>
+  <si>
+    <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+  </si>
+  <si>
+    <t>209200</t>
+  </si>
+  <si>
+    <t>TRI-MED MEDICAL SUPPLIES, INC. 209200</t>
+  </si>
+  <si>
+    <t>SO153725</t>
+  </si>
+  <si>
+    <t>215031026SM</t>
+  </si>
+  <si>
+    <t>4110 BUTLER PIKE, SUITE A-106</t>
+  </si>
+  <si>
+    <t>PLYMOUTH MEETING</t>
+  </si>
+  <si>
+    <t>PA</t>
+  </si>
+  <si>
+    <t>19462</t>
+  </si>
+  <si>
+    <t>209177</t>
+  </si>
+  <si>
+    <t>Indiana University Health Integrated Service Center 209177</t>
+  </si>
+  <si>
+    <t>SO153731</t>
+  </si>
+  <si>
+    <t>PUR1001985775</t>
+  </si>
+  <si>
+    <t>390 Airtech Parkway</t>
+  </si>
+  <si>
+    <t>Plainfield</t>
+  </si>
+  <si>
+    <t>IN</t>
+  </si>
+  <si>
+    <t>46168</t>
+  </si>
+  <si>
+    <t>201067</t>
+  </si>
+  <si>
+    <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+  </si>
+  <si>
+    <t>SO153813</t>
+  </si>
+  <si>
+    <t>03180</t>
+  </si>
+  <si>
+    <t>487471800000</t>
+  </si>
+  <si>
+    <t>2151 COUNTY ROAD H2W</t>
+  </si>
+  <si>
+    <t>MOUNDS VIEW</t>
+  </si>
+  <si>
+    <t>MN</t>
+  </si>
+  <si>
+    <t>55112</t>
+  </si>
+  <si>
+    <t>487471800002</t>
+  </si>
+  <si>
+    <t>SO153817</t>
+  </si>
+  <si>
+    <t>08924</t>
+  </si>
+  <si>
+    <t>48741800002</t>
+  </si>
+  <si>
+    <t>8489 WESTSIDE INDUSTRIAL DRIVE</t>
+  </si>
+  <si>
+    <t>JACKSONVILLE</t>
+  </si>
+  <si>
+    <t>FL</t>
+  </si>
+  <si>
+    <t>32219</t>
+  </si>
+  <si>
+    <t>SO153819</t>
+  </si>
+  <si>
+    <t>15058</t>
+  </si>
+  <si>
+    <t>326 U.S. HIGHWAY 49 SOUTH</t>
+  </si>
+  <si>
+    <t>RICHLAND</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>39218</t>
+  </si>
+  <si>
+    <t>SO153820</t>
+  </si>
+  <si>
+    <t>15997</t>
+  </si>
+  <si>
+    <t>7437 INDUSTRIAL BOULEVARD</t>
+  </si>
+  <si>
+    <t>ALLENTOWN</t>
+  </si>
+  <si>
+    <t>18106</t>
+  </si>
+  <si>
+    <t>SO153824</t>
+  </si>
+  <si>
+    <t>21098</t>
+  </si>
+  <si>
+    <t>1425 MAGELLAN ROAD</t>
+  </si>
+  <si>
+    <t>HANOVER</t>
+  </si>
+  <si>
+    <t>21076</t>
+  </si>
+  <si>
+    <t>SO153825</t>
+  </si>
+  <si>
+    <t>23101</t>
+  </si>
+  <si>
+    <t>14599 NW 8TH STREET</t>
+  </si>
+  <si>
+    <t>SUNRISE</t>
+  </si>
+  <si>
+    <t>33325</t>
+  </si>
+  <si>
+    <t>SO153829</t>
+  </si>
+  <si>
+    <t>37987</t>
+  </si>
+  <si>
+    <t>36663 VAN BORN RD</t>
+  </si>
+  <si>
+    <t>ROMULUS</t>
+  </si>
+  <si>
+    <t>MI</t>
+  </si>
+  <si>
+    <t>48174</t>
+  </si>
+  <si>
+    <t>SO153830</t>
+  </si>
+  <si>
+    <t>38875</t>
+  </si>
+  <si>
+    <t>550 LAKESIDE PARKWAY</t>
+  </si>
+  <si>
+    <t>FLOWER MOUND</t>
+  </si>
+  <si>
+    <t>75028</t>
+  </si>
+  <si>
+    <t>SO153831</t>
+  </si>
+  <si>
+    <t>39664</t>
+  </si>
+  <si>
+    <t>4807 NE 63RD AVENUE</t>
+  </si>
+  <si>
+    <t>GAINESVILLE</t>
+  </si>
+  <si>
+    <t>32609</t>
+  </si>
+  <si>
+    <t>SO153834</t>
+  </si>
+  <si>
+    <t>59613</t>
+  </si>
+  <si>
+    <t>4301 W VALLEY HWY EAST</t>
+  </si>
+  <si>
+    <t>SUMNER</t>
+  </si>
+  <si>
+    <t>98390</t>
+  </si>
+  <si>
+    <t>SO153835</t>
+  </si>
+  <si>
+    <t>60727</t>
+  </si>
+  <si>
+    <t>7871800000</t>
+  </si>
+  <si>
+    <t>20164394C</t>
+  </si>
+  <si>
+    <t>48741800000</t>
+  </si>
+  <si>
+    <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
+  </si>
+  <si>
+    <t>8313 WEST PIERCE STREET, SUITE 100</t>
+  </si>
+  <si>
+    <t>SO153837</t>
+  </si>
+  <si>
+    <t>69574</t>
+  </si>
+  <si>
+    <t>1880 NORTH CORRINGTON AVE</t>
+  </si>
+  <si>
+    <t>KANSAS CITY</t>
+  </si>
+  <si>
+    <t>MO</t>
+  </si>
+  <si>
+    <t>64120</t>
+  </si>
+  <si>
+    <t>SO153838</t>
+  </si>
+  <si>
+    <t>78571</t>
+  </si>
+  <si>
+    <t>27695 S.W. 95th AVENUE</t>
+  </si>
+  <si>
+    <t>WILSONVILLE</t>
+  </si>
+  <si>
+    <t>OR</t>
+  </si>
+  <si>
+    <t>97070</t>
+  </si>
+  <si>
     <t>202033</t>
   </si>
   <si>
@@ -115,27 +535,9 @@
     <t>4519692670</t>
   </si>
   <si>
-    <t>SENSI MEDICAL</t>
-  </si>
-  <si>
-    <t>V7871800000</t>
-  </si>
-  <si>
-    <t>20164396C</t>
-  </si>
-  <si>
     <t>O-T7871800000</t>
   </si>
   <si>
-    <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
-  </si>
-  <si>
-    <t>CA</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
     <t>1040 ENTERPRISE PARKWAY</t>
   </si>
   <si>
@@ -160,15 +562,6 @@
     <t>1042653452</t>
   </si>
   <si>
-    <t>7871800000</t>
-  </si>
-  <si>
-    <t>20164394C</t>
-  </si>
-  <si>
-    <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
-  </si>
-  <si>
     <t>1810 Summit Commerce Pkwy</t>
   </si>
   <si>
@@ -190,27 +583,15 @@
     <t>3584739</t>
   </si>
   <si>
-    <t>V7871800002</t>
-  </si>
-  <si>
-    <t>20164397C</t>
-  </si>
-  <si>
     <t>354866</t>
   </si>
   <si>
-    <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
-  </si>
-  <si>
     <t>500 INDUSTRIAL PARK DRIVE</t>
   </si>
   <si>
     <t>SHELBYVILLE</t>
   </si>
   <si>
-    <t>IN</t>
-  </si>
-  <si>
     <t>46176</t>
   </si>
   <si>
@@ -232,36 +613,6 @@
     <t>37705</t>
   </si>
   <si>
-    <t>SO153649</t>
-  </si>
-  <si>
-    <t>3584738</t>
-  </si>
-  <si>
-    <t>7871800002</t>
-  </si>
-  <si>
-    <t>20164395C</t>
-  </si>
-  <si>
-    <t>354862</t>
-  </si>
-  <si>
-    <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
-  </si>
-  <si>
-    <t>276 ENTERPRISE WAY</t>
-  </si>
-  <si>
-    <t>MOCKSVILLE</t>
-  </si>
-  <si>
-    <t>NC</t>
-  </si>
-  <si>
-    <t>27028</t>
-  </si>
-  <si>
     <t>SO153652</t>
   </si>
   <si>
@@ -277,9 +628,6 @@
     <t>KALAMAZOO</t>
   </si>
   <si>
-    <t>MI</t>
-  </si>
-  <si>
     <t>49048</t>
   </si>
   <si>
@@ -400,15 +748,6 @@
     <t>1401 N. UNIVERSAL AVE.</t>
   </si>
   <si>
-    <t>KANSAS CITY</t>
-  </si>
-  <si>
-    <t>MO</t>
-  </si>
-  <si>
-    <t>64120</t>
-  </si>
-  <si>
     <t>SO153485</t>
   </si>
   <si>
@@ -421,9 +760,6 @@
     <t>ROGERS</t>
   </si>
   <si>
-    <t>MN</t>
-  </si>
-  <si>
     <t>55374</t>
   </si>
   <si>
@@ -457,9 +793,6 @@
     <t>WILMER</t>
   </si>
   <si>
-    <t>TX</t>
-  </si>
-  <si>
     <t>75172</t>
   </si>
   <si>
@@ -472,12 +805,6 @@
     <t>36445 VAN BORN ROAD</t>
   </si>
   <si>
-    <t>ROMULUS</t>
-  </si>
-  <si>
-    <t>48174</t>
-  </si>
-  <si>
     <t>SO153502</t>
   </si>
   <si>
@@ -487,15 +814,6 @@
     <t>8787 W BUCKEYE ROAD</t>
   </si>
   <si>
-    <t>TOLLESON</t>
-  </si>
-  <si>
-    <t>AZ</t>
-  </si>
-  <si>
-    <t>85353</t>
-  </si>
-  <si>
     <t>SO153483</t>
   </si>
   <si>
@@ -508,9 +826,6 @@
     <t>GRESHAM</t>
   </si>
   <si>
-    <t>OR</t>
-  </si>
-  <si>
     <t>97030</t>
   </si>
   <si>
@@ -661,9 +976,6 @@
     <t>Southaven</t>
   </si>
   <si>
-    <t>MS</t>
-  </si>
-  <si>
     <t>38672</t>
   </si>
   <si>
@@ -709,9 +1021,6 @@
     <t>LACEY</t>
   </si>
   <si>
-    <t>WA</t>
-  </si>
-  <si>
     <t>98516</t>
   </si>
   <si>
@@ -797,15 +1106,6 @@
   </si>
   <si>
     <t>8691 JESSE B SMITH COURT</t>
-  </si>
-  <si>
-    <t>JACKSONVILLE</t>
-  </si>
-  <si>
-    <t>FL</t>
-  </si>
-  <si>
-    <t>32219</t>
   </si>
   <si>
     <t>209207</t>
@@ -1731,8 +2031,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{529A2BDD-FECF-4D0F-8404-391D859E2D0E}">
-  <dimension ref="A1:Z57"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E77F3A3-7010-4EAD-87B8-02E76E752B7D}">
+  <dimension ref="A1:Z82"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.2">
@@ -1820,7 +2120,7 @@
         <v>26</v>
       </c>
       <c r="B2" s="2">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="C2" t="s">
         <v>27</v>
@@ -1859,7 +2159,7 @@
         <v>18499</v>
       </c>
       <c r="O2">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="P2" t="s">
         <v>37</v>
@@ -1877,7 +2177,7 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="V2">
         <v>47.46</v>
@@ -1900,46 +2200,46 @@
         <v>26</v>
       </c>
       <c r="B3" s="2">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" t="s">
         <v>42</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>43</v>
-      </c>
-      <c r="E3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F3" t="s">
-        <v>45</v>
       </c>
       <c r="G3" t="s">
         <v>31</v>
       </c>
       <c r="H3" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="I3" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="J3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K3" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="L3" t="s">
         <v>36</v>
       </c>
       <c r="M3">
-        <v>1791</v>
+        <v>18525</v>
       </c>
       <c r="N3">
-        <v>1777</v>
+        <v>18499</v>
       </c>
       <c r="O3">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="P3" t="s">
         <v>37</v>
@@ -1957,22 +2257,22 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="V3">
-        <v>57.33</v>
+        <v>47.46</v>
       </c>
       <c r="W3" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="X3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="Y3" t="s">
         <v>40</v>
       </c>
       <c r="Z3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.2">
@@ -1980,49 +2280,49 @@
         <v>26</v>
       </c>
       <c r="B4" s="2">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="G4" t="s">
         <v>31</v>
       </c>
       <c r="H4" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="I4" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="J4" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="K4" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="L4" t="s">
         <v>36</v>
       </c>
       <c r="M4">
-        <v>37803</v>
+        <v>18525</v>
       </c>
       <c r="N4">
-        <v>37748</v>
+        <v>18499</v>
       </c>
       <c r="O4">
-        <v>15</v>
-      </c>
-      <c r="P4">
-        <v>15</v>
+        <v>1</v>
+      </c>
+      <c r="P4" t="s">
+        <v>37</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -2037,22 +2337,22 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W4" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="X4" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="Y4" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="Z4" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.2">
@@ -2060,31 +2360,31 @@
         <v>26</v>
       </c>
       <c r="B5" s="2">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E5" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="G5" t="s">
         <v>31</v>
       </c>
       <c r="H5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J5" t="s">
         <v>57</v>
-      </c>
-      <c r="J5" t="s">
-        <v>58</v>
       </c>
       <c r="K5" t="s">
         <v>59</v>
@@ -2093,16 +2393,16 @@
         <v>36</v>
       </c>
       <c r="M5">
-        <v>37803</v>
+        <v>12600</v>
       </c>
       <c r="N5">
-        <v>37748</v>
+        <v>11150</v>
       </c>
       <c r="O5">
-        <v>14</v>
-      </c>
-      <c r="P5">
-        <v>14</v>
+        <v>1</v>
+      </c>
+      <c r="P5" t="s">
+        <v>37</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -2117,22 +2417,22 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5">
-        <v>29.4</v>
+        <v>36.86</v>
       </c>
       <c r="W5" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="X5" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="Y5" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="Z5" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.2">
@@ -2140,49 +2440,49 @@
         <v>26</v>
       </c>
       <c r="B6" s="2">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="E6" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="F6" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="G6" t="s">
         <v>31</v>
       </c>
       <c r="H6" t="s">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="I6" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="J6" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="K6" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="L6" t="s">
         <v>36</v>
       </c>
       <c r="M6">
-        <v>12656</v>
+        <v>18525</v>
       </c>
       <c r="N6">
-        <v>12550</v>
+        <v>18499</v>
       </c>
       <c r="O6">
-        <v>56</v>
-      </c>
-      <c r="P6">
-        <v>56</v>
+        <v>19</v>
+      </c>
+      <c r="P6" t="s">
+        <v>37</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -2197,22 +2497,22 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="V6">
-        <v>36.86</v>
+        <v>47.46</v>
       </c>
       <c r="W6" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="X6" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="Y6" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="Z6" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.2">
@@ -2220,49 +2520,49 @@
         <v>26</v>
       </c>
       <c r="B7" s="2">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="E7" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="F7" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="G7" t="s">
         <v>31</v>
       </c>
       <c r="H7" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="I7" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="J7" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="K7" t="s">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="L7" t="s">
         <v>36</v>
       </c>
       <c r="M7">
-        <v>18525</v>
+        <v>37803</v>
       </c>
       <c r="N7">
-        <v>18499</v>
+        <v>37608</v>
       </c>
       <c r="O7">
-        <v>26</v>
-      </c>
-      <c r="P7">
-        <v>26</v>
+        <v>20</v>
+      </c>
+      <c r="P7" t="s">
+        <v>37</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -2277,22 +2577,22 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V7">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W7" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="X7" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="Y7" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="Z7" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.2">
@@ -2300,34 +2600,34 @@
         <v>26</v>
       </c>
       <c r="B8" s="2">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="D8" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="E8" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F8" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G8" t="s">
         <v>31</v>
       </c>
       <c r="H8" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="I8" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="J8" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="K8" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="L8" t="s">
         <v>36</v>
@@ -2336,13 +2636,13 @@
         <v>37803</v>
       </c>
       <c r="N8">
-        <v>37748</v>
+        <v>37608</v>
       </c>
       <c r="O8">
-        <v>26</v>
+        <v>140</v>
       </c>
       <c r="P8">
-        <v>26</v>
+        <v>140</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -2363,66 +2663,66 @@
         <v>29.4</v>
       </c>
       <c r="W8" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="X8" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="Y8" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="Z8" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>87</v>
+        <v>26</v>
       </c>
       <c r="B9" s="2">
-        <v>46086</v>
+        <v>46091</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D9" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E9" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="F9" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="G9" t="s">
         <v>31</v>
       </c>
       <c r="H9" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="I9" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="J9" t="s">
         <v>37</v>
       </c>
       <c r="K9" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="L9" t="s">
         <v>36</v>
       </c>
       <c r="M9">
-        <v>1791</v>
+        <v>37803</v>
       </c>
       <c r="N9">
-        <v>1777</v>
+        <v>37608</v>
       </c>
       <c r="O9">
-        <v>8</v>
-      </c>
-      <c r="P9">
-        <v>8</v>
+        <v>791</v>
+      </c>
+      <c r="P9" t="s">
+        <v>37</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -2437,22 +2737,22 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>791</v>
       </c>
       <c r="V9">
-        <v>57.33</v>
+        <v>29.4</v>
       </c>
       <c r="W9" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="X9" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="Y9" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="Z9" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.2">
@@ -2460,19 +2760,19 @@
         <v>26</v>
       </c>
       <c r="B10" s="2">
-        <v>46086</v>
+        <v>46091</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="D10" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="E10" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F10" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G10" t="s">
         <v>31</v>
@@ -2484,7 +2784,7 @@
         <v>33</v>
       </c>
       <c r="J10" t="s">
-        <v>34</v>
+        <v>93</v>
       </c>
       <c r="K10" t="s">
         <v>35</v>
@@ -2499,7 +2799,7 @@
         <v>18499</v>
       </c>
       <c r="O10">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="P10" t="s">
         <v>37</v>
@@ -2517,22 +2817,22 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="V10">
         <v>47.46</v>
       </c>
       <c r="W10" t="s">
+        <v>94</v>
+      </c>
+      <c r="X10" t="s">
+        <v>95</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z10" t="s">
         <v>97</v>
-      </c>
-      <c r="X10" t="s">
-        <v>98</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>99</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.2">
@@ -2540,46 +2840,46 @@
         <v>26</v>
       </c>
       <c r="B11" s="2">
-        <v>46086</v>
+        <v>46091</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="E11" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="F11" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="G11" t="s">
         <v>31</v>
       </c>
       <c r="H11" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="I11" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="J11" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="K11" t="s">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="L11" t="s">
         <v>36</v>
       </c>
       <c r="M11">
-        <v>18525</v>
+        <v>37803</v>
       </c>
       <c r="N11">
-        <v>18499</v>
+        <v>37608</v>
       </c>
       <c r="O11">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="P11" t="s">
         <v>37</v>
@@ -2597,22 +2897,22 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="V11">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W11" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="X11" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="Y11" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="Z11" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.2">
@@ -2620,46 +2920,46 @@
         <v>26</v>
       </c>
       <c r="B12" s="2">
-        <v>46086</v>
+        <v>46091</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="D12" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="E12" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G12" t="s">
         <v>31</v>
       </c>
       <c r="H12" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="I12" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="J12" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="K12" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="L12" t="s">
         <v>36</v>
       </c>
       <c r="M12">
-        <v>12656</v>
+        <v>12600</v>
       </c>
       <c r="N12">
-        <v>12550</v>
+        <v>11150</v>
       </c>
       <c r="O12">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="P12" t="s">
         <v>37</v>
@@ -2677,22 +2977,22 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="V12">
-        <v>36.86</v>
+        <v>36.8598</v>
       </c>
       <c r="W12" t="s">
+        <v>102</v>
+      </c>
+      <c r="X12" t="s">
         <v>103</v>
       </c>
-      <c r="X12" t="s">
+      <c r="Y12" t="s">
         <v>104</v>
       </c>
-      <c r="Y12" t="s">
+      <c r="Z12" t="s">
         <v>105</v>
-      </c>
-      <c r="Z12" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.2">
@@ -2700,46 +3000,46 @@
         <v>26</v>
       </c>
       <c r="B13" s="2">
-        <v>46086</v>
+        <v>46091</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="D13" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="E13" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G13" t="s">
         <v>31</v>
       </c>
       <c r="H13" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="I13" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="J13" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="K13" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="L13" t="s">
         <v>36</v>
       </c>
       <c r="M13">
-        <v>37803</v>
+        <v>18525</v>
       </c>
       <c r="N13">
-        <v>37748</v>
+        <v>18499</v>
       </c>
       <c r="O13">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="P13" t="s">
         <v>37</v>
@@ -2757,22 +3057,22 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="V13">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W13" t="s">
+        <v>102</v>
+      </c>
+      <c r="X13" t="s">
         <v>103</v>
       </c>
-      <c r="X13" t="s">
+      <c r="Y13" t="s">
         <v>104</v>
       </c>
-      <c r="Y13" t="s">
+      <c r="Z13" t="s">
         <v>105</v>
-      </c>
-      <c r="Z13" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.2">
@@ -2780,46 +3080,46 @@
         <v>26</v>
       </c>
       <c r="B14" s="2">
-        <v>46086</v>
+        <v>46091</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="D14" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="E14" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="F14" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="G14" t="s">
         <v>31</v>
       </c>
       <c r="H14" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="I14" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="J14" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="K14" t="s">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="L14" t="s">
         <v>36</v>
       </c>
       <c r="M14">
-        <v>18525</v>
+        <v>37803</v>
       </c>
       <c r="N14">
-        <v>18499</v>
+        <v>37608</v>
       </c>
       <c r="O14">
-        <v>13</v>
+        <v>231</v>
       </c>
       <c r="P14" t="s">
         <v>37</v>
@@ -2837,22 +3137,22 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>13</v>
+        <v>231</v>
       </c>
       <c r="V14">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W14" t="s">
-        <v>38</v>
+        <v>102</v>
       </c>
       <c r="X14" t="s">
-        <v>39</v>
+        <v>103</v>
       </c>
       <c r="Y14" t="s">
-        <v>40</v>
+        <v>104</v>
       </c>
       <c r="Z14" t="s">
-        <v>41</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.2">
@@ -2860,46 +3160,46 @@
         <v>26</v>
       </c>
       <c r="B15" s="2">
-        <v>46086</v>
+        <v>46091</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="E15" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F15" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="G15" t="s">
         <v>31</v>
       </c>
       <c r="H15" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="I15" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="J15" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="K15" t="s">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="L15" t="s">
         <v>36</v>
       </c>
       <c r="M15">
-        <v>18525</v>
+        <v>37803</v>
       </c>
       <c r="N15">
-        <v>18499</v>
+        <v>37608</v>
       </c>
       <c r="O15">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="P15" t="s">
         <v>37</v>
@@ -2917,22 +3217,22 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="V15">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W15" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="X15" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="Y15" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="Z15" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.2">
@@ -2940,31 +3240,31 @@
         <v>26</v>
       </c>
       <c r="B16" s="2">
-        <v>46086</v>
+        <v>46091</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="D16" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="E16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G16" t="s">
         <v>31</v>
       </c>
       <c r="H16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J16" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="K16" t="s">
         <v>59</v>
@@ -2973,13 +3273,13 @@
         <v>36</v>
       </c>
       <c r="M16">
-        <v>37803</v>
+        <v>12600</v>
       </c>
       <c r="N16">
-        <v>37748</v>
+        <v>11150</v>
       </c>
       <c r="O16">
-        <v>140</v>
+        <v>274</v>
       </c>
       <c r="P16" t="s">
         <v>37</v>
@@ -2997,10 +3297,10 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>140</v>
+        <v>274</v>
       </c>
       <c r="V16">
-        <v>29.4</v>
+        <v>36.8598</v>
       </c>
       <c r="W16" t="s">
         <v>114</v>
@@ -3009,10 +3309,10 @@
         <v>115</v>
       </c>
       <c r="Y16" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z16" t="s">
         <v>116</v>
-      </c>
-      <c r="Z16" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.2">
@@ -3020,46 +3320,46 @@
         <v>26</v>
       </c>
       <c r="B17" s="2">
-        <v>46086</v>
+        <v>46091</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="D17" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="E17" t="s">
+        <v>117</v>
+      </c>
+      <c r="F17" t="s">
         <v>118</v>
-      </c>
-      <c r="F17" t="s">
-        <v>119</v>
       </c>
       <c r="G17" t="s">
         <v>31</v>
       </c>
       <c r="H17" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="I17" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="J17" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="K17" t="s">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="L17" t="s">
         <v>36</v>
       </c>
       <c r="M17">
-        <v>18525</v>
+        <v>37803</v>
       </c>
       <c r="N17">
-        <v>18499</v>
+        <v>37608</v>
       </c>
       <c r="O17">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="P17" t="s">
         <v>37</v>
@@ -3077,22 +3377,22 @@
         <v>0</v>
       </c>
       <c r="U17">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="V17">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W17" t="s">
+        <v>119</v>
+      </c>
+      <c r="X17" t="s">
         <v>120</v>
       </c>
-      <c r="X17" t="s">
+      <c r="Y17" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z17" t="s">
         <v>121</v>
-      </c>
-      <c r="Y17" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z17" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.2">
@@ -3100,46 +3400,46 @@
         <v>26</v>
       </c>
       <c r="B18" s="2">
-        <v>46086</v>
+        <v>46091</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="D18" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="E18" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F18" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G18" t="s">
         <v>31</v>
       </c>
       <c r="H18" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="I18" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="J18" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="K18" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="L18" t="s">
         <v>36</v>
       </c>
       <c r="M18">
-        <v>37803</v>
+        <v>18525</v>
       </c>
       <c r="N18">
-        <v>37748</v>
+        <v>18499</v>
       </c>
       <c r="O18">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="P18" t="s">
         <v>37</v>
@@ -3157,22 +3457,22 @@
         <v>0</v>
       </c>
       <c r="U18">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="V18">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W18" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="X18" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="Y18" t="s">
-        <v>26</v>
+        <v>104</v>
       </c>
       <c r="Z18" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.2">
@@ -3180,19 +3480,19 @@
         <v>26</v>
       </c>
       <c r="B19" s="2">
-        <v>46086</v>
+        <v>46091</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="D19" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="E19" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F19" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G19" t="s">
         <v>31</v>
@@ -3204,7 +3504,7 @@
         <v>33</v>
       </c>
       <c r="J19" t="s">
-        <v>34</v>
+        <v>93</v>
       </c>
       <c r="K19" t="s">
         <v>35</v>
@@ -3219,7 +3519,7 @@
         <v>18499</v>
       </c>
       <c r="O19">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="P19" t="s">
         <v>37</v>
@@ -3237,22 +3537,22 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="V19">
         <v>47.46</v>
       </c>
       <c r="W19" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="X19" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="Y19" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="Z19" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.2">
@@ -3260,34 +3560,34 @@
         <v>26</v>
       </c>
       <c r="B20" s="2">
-        <v>46086</v>
+        <v>46091</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="D20" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="E20" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F20" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G20" t="s">
         <v>31</v>
       </c>
       <c r="H20" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="I20" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="J20" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="K20" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="L20" t="s">
         <v>36</v>
@@ -3296,10 +3596,10 @@
         <v>37803</v>
       </c>
       <c r="N20">
-        <v>37748</v>
+        <v>37608</v>
       </c>
       <c r="O20">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="P20" t="s">
         <v>37</v>
@@ -3317,22 +3617,22 @@
         <v>0</v>
       </c>
       <c r="U20">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="V20">
         <v>29.4</v>
       </c>
       <c r="W20" t="s">
+        <v>129</v>
+      </c>
+      <c r="X20" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y20" t="s">
         <v>131</v>
       </c>
-      <c r="X20" t="s">
+      <c r="Z20" t="s">
         <v>132</v>
-      </c>
-      <c r="Y20" t="s">
-        <v>133</v>
-      </c>
-      <c r="Z20" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.2">
@@ -3340,46 +3640,46 @@
         <v>26</v>
       </c>
       <c r="B21" s="2">
-        <v>46086</v>
+        <v>46091</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="D21" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="E21" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F21" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G21" t="s">
         <v>31</v>
       </c>
       <c r="H21" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="I21" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="J21" t="s">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="K21" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="L21" t="s">
         <v>36</v>
       </c>
       <c r="M21">
-        <v>18525</v>
+        <v>12600</v>
       </c>
       <c r="N21">
-        <v>18499</v>
+        <v>11150</v>
       </c>
       <c r="O21">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="P21" t="s">
         <v>37</v>
@@ -3397,22 +3697,22 @@
         <v>0</v>
       </c>
       <c r="U21">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="V21">
-        <v>47.46</v>
+        <v>36.8598</v>
       </c>
       <c r="W21" t="s">
+        <v>135</v>
+      </c>
+      <c r="X21" t="s">
+        <v>136</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z21" t="s">
         <v>137</v>
-      </c>
-      <c r="X21" t="s">
-        <v>138</v>
-      </c>
-      <c r="Y21" t="s">
-        <v>139</v>
-      </c>
-      <c r="Z21" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.2">
@@ -3420,46 +3720,46 @@
         <v>26</v>
       </c>
       <c r="B22" s="2">
-        <v>46086</v>
+        <v>46091</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="D22" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="E22" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F22" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G22" t="s">
         <v>31</v>
       </c>
       <c r="H22" t="s">
+        <v>69</v>
+      </c>
+      <c r="I22" t="s">
+        <v>70</v>
+      </c>
+      <c r="J22" t="s">
+        <v>98</v>
+      </c>
+      <c r="K22" t="s">
         <v>72</v>
-      </c>
-      <c r="I22" t="s">
-        <v>73</v>
-      </c>
-      <c r="J22" t="s">
-        <v>107</v>
-      </c>
-      <c r="K22" t="s">
-        <v>75</v>
       </c>
       <c r="L22" t="s">
         <v>36</v>
       </c>
       <c r="M22">
-        <v>12656</v>
+        <v>37803</v>
       </c>
       <c r="N22">
-        <v>12550</v>
+        <v>37608</v>
       </c>
       <c r="O22">
-        <v>70</v>
+        <v>362</v>
       </c>
       <c r="P22" t="s">
         <v>37</v>
@@ -3477,22 +3777,22 @@
         <v>0</v>
       </c>
       <c r="U22">
-        <v>70</v>
+        <v>362</v>
       </c>
       <c r="V22">
-        <v>36.86</v>
+        <v>29.4</v>
       </c>
       <c r="W22" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="X22" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="Y22" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="Z22" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.2">
@@ -3500,31 +3800,31 @@
         <v>26</v>
       </c>
       <c r="B23" s="2">
-        <v>46086</v>
+        <v>46091</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="D23" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="E23" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F23" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="G23" t="s">
         <v>31</v>
       </c>
       <c r="H23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J23" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="K23" t="s">
         <v>59</v>
@@ -3533,13 +3833,13 @@
         <v>36</v>
       </c>
       <c r="M23">
-        <v>37803</v>
+        <v>12600</v>
       </c>
       <c r="N23">
-        <v>37748</v>
+        <v>11150</v>
       </c>
       <c r="O23">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="P23" t="s">
         <v>37</v>
@@ -3557,22 +3857,22 @@
         <v>0</v>
       </c>
       <c r="U23">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="V23">
-        <v>29.4</v>
+        <v>36.8598</v>
       </c>
       <c r="W23" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="X23" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="Y23" t="s">
-        <v>139</v>
+        <v>67</v>
       </c>
       <c r="Z23" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.2">
@@ -3580,46 +3880,46 @@
         <v>26</v>
       </c>
       <c r="B24" s="2">
-        <v>46086</v>
+        <v>46091</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="D24" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="E24" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F24" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="G24" t="s">
         <v>31</v>
       </c>
       <c r="H24" t="s">
-        <v>32</v>
+        <v>150</v>
       </c>
       <c r="I24" t="s">
-        <v>33</v>
+        <v>151</v>
       </c>
       <c r="J24" t="s">
-        <v>34</v>
+        <v>152</v>
       </c>
       <c r="K24" t="s">
-        <v>35</v>
+        <v>153</v>
       </c>
       <c r="L24" t="s">
         <v>36</v>
       </c>
       <c r="M24">
-        <v>18525</v>
+        <v>1791</v>
       </c>
       <c r="N24">
-        <v>18499</v>
+        <v>1745</v>
       </c>
       <c r="O24">
-        <v>8</v>
+        <v>112</v>
       </c>
       <c r="P24" t="s">
         <v>37</v>
@@ -3637,22 +3937,22 @@
         <v>0</v>
       </c>
       <c r="U24">
-        <v>8</v>
+        <v>112</v>
       </c>
       <c r="V24">
-        <v>47.46</v>
+        <v>57.33</v>
       </c>
       <c r="W24" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="X24" t="s">
-        <v>144</v>
+        <v>50</v>
       </c>
       <c r="Y24" t="s">
-        <v>145</v>
+        <v>51</v>
       </c>
       <c r="Z24" t="s">
-        <v>146</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.2">
@@ -3660,46 +3960,46 @@
         <v>26</v>
       </c>
       <c r="B25" s="2">
-        <v>46086</v>
+        <v>46091</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="D25" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="E25" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F25" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="G25" t="s">
         <v>31</v>
       </c>
       <c r="H25" t="s">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="I25" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="J25" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="K25" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="L25" t="s">
         <v>36</v>
       </c>
       <c r="M25">
-        <v>12656</v>
+        <v>18525</v>
       </c>
       <c r="N25">
-        <v>12550</v>
+        <v>18499</v>
       </c>
       <c r="O25">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="P25" t="s">
         <v>37</v>
@@ -3717,22 +4017,22 @@
         <v>0</v>
       </c>
       <c r="U25">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="V25">
-        <v>36.86</v>
+        <v>47.46</v>
       </c>
       <c r="W25" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="X25" t="s">
-        <v>144</v>
+        <v>50</v>
       </c>
       <c r="Y25" t="s">
-        <v>145</v>
+        <v>51</v>
       </c>
       <c r="Z25" t="s">
-        <v>146</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.2">
@@ -3740,34 +4040,34 @@
         <v>26</v>
       </c>
       <c r="B26" s="2">
-        <v>46086</v>
+        <v>46091</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="D26" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="E26" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="F26" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="G26" t="s">
         <v>31</v>
       </c>
       <c r="H26" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="I26" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="J26" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="K26" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="L26" t="s">
         <v>36</v>
@@ -3776,10 +4076,10 @@
         <v>37803</v>
       </c>
       <c r="N26">
-        <v>37748</v>
+        <v>37608</v>
       </c>
       <c r="O26">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="P26" t="s">
         <v>37</v>
@@ -3797,22 +4097,22 @@
         <v>0</v>
       </c>
       <c r="U26">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="V26">
         <v>29.4</v>
       </c>
       <c r="W26" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="X26" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="Y26" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="Z26" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
     </row>
     <row r="27" spans="1:26" x14ac:dyDescent="0.2">
@@ -3820,46 +4120,46 @@
         <v>26</v>
       </c>
       <c r="B27" s="2">
-        <v>46086</v>
+        <v>46091</v>
       </c>
       <c r="C27" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="D27" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="E27" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="F27" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="G27" t="s">
         <v>31</v>
       </c>
       <c r="H27" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="I27" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="J27" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="K27" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="L27" t="s">
         <v>36</v>
       </c>
       <c r="M27">
-        <v>12656</v>
+        <v>12600</v>
       </c>
       <c r="N27">
-        <v>12550</v>
+        <v>11150</v>
       </c>
       <c r="O27">
-        <v>42</v>
+        <v>120</v>
       </c>
       <c r="P27" t="s">
         <v>37</v>
@@ -3877,22 +4177,22 @@
         <v>0</v>
       </c>
       <c r="U27">
-        <v>42</v>
+        <v>120</v>
       </c>
       <c r="V27">
-        <v>36.86</v>
+        <v>36.8598</v>
       </c>
       <c r="W27" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="X27" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="Y27" t="s">
-        <v>85</v>
+        <v>165</v>
       </c>
       <c r="Z27" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
     </row>
     <row r="28" spans="1:26" x14ac:dyDescent="0.2">
@@ -3900,19 +4200,19 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="C28" t="s">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="D28" t="s">
-        <v>28</v>
+        <v>168</v>
       </c>
       <c r="E28" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="F28" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="G28" t="s">
         <v>31</v>
@@ -3924,7 +4224,7 @@
         <v>33</v>
       </c>
       <c r="J28" t="s">
-        <v>34</v>
+        <v>171</v>
       </c>
       <c r="K28" t="s">
         <v>35</v>
@@ -3939,7 +4239,7 @@
         <v>18499</v>
       </c>
       <c r="O28">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="P28" t="s">
         <v>37</v>
@@ -3957,22 +4257,22 @@
         <v>0</v>
       </c>
       <c r="U28">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="V28">
         <v>47.46</v>
       </c>
       <c r="W28" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="X28" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="Y28" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="Z28" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.2">
@@ -3980,49 +4280,49 @@
         <v>26</v>
       </c>
       <c r="B29" s="2">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="C29" t="s">
-        <v>27</v>
+        <v>176</v>
       </c>
       <c r="D29" t="s">
-        <v>28</v>
+        <v>177</v>
       </c>
       <c r="E29" t="s">
-        <v>152</v>
+        <v>178</v>
       </c>
       <c r="F29" t="s">
-        <v>153</v>
+        <v>179</v>
       </c>
       <c r="G29" t="s">
         <v>31</v>
       </c>
       <c r="H29" t="s">
-        <v>56</v>
+        <v>150</v>
       </c>
       <c r="I29" t="s">
-        <v>57</v>
+        <v>151</v>
       </c>
       <c r="J29" t="s">
-        <v>108</v>
+        <v>37</v>
       </c>
       <c r="K29" t="s">
-        <v>59</v>
+        <v>153</v>
       </c>
       <c r="L29" t="s">
         <v>36</v>
       </c>
       <c r="M29">
-        <v>37803</v>
+        <v>1791</v>
       </c>
       <c r="N29">
-        <v>37748</v>
+        <v>1745</v>
       </c>
       <c r="O29">
-        <v>60</v>
-      </c>
-      <c r="P29" t="s">
-        <v>37</v>
+        <v>28</v>
+      </c>
+      <c r="P29">
+        <v>28</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -4037,22 +4337,22 @@
         <v>0</v>
       </c>
       <c r="U29">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="V29">
-        <v>29.4</v>
+        <v>57.33</v>
       </c>
       <c r="W29" t="s">
-        <v>154</v>
+        <v>180</v>
       </c>
       <c r="X29" t="s">
-        <v>155</v>
+        <v>181</v>
       </c>
       <c r="Y29" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="Z29" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.2">
@@ -4060,34 +4360,34 @@
         <v>26</v>
       </c>
       <c r="B30" s="2">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="C30" t="s">
-        <v>27</v>
+        <v>183</v>
       </c>
       <c r="D30" t="s">
-        <v>28</v>
+        <v>184</v>
       </c>
       <c r="E30" t="s">
-        <v>158</v>
+        <v>185</v>
       </c>
       <c r="F30" t="s">
-        <v>159</v>
+        <v>186</v>
       </c>
       <c r="G30" t="s">
         <v>31</v>
       </c>
       <c r="H30" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="I30" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="J30" t="s">
-        <v>108</v>
+        <v>187</v>
       </c>
       <c r="K30" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="L30" t="s">
         <v>36</v>
@@ -4096,13 +4396,13 @@
         <v>37803</v>
       </c>
       <c r="N30">
-        <v>37748</v>
+        <v>37608</v>
       </c>
       <c r="O30">
-        <v>30</v>
-      </c>
-      <c r="P30" t="s">
-        <v>37</v>
+        <v>15</v>
+      </c>
+      <c r="P30">
+        <v>15</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -4117,22 +4417,22 @@
         <v>0</v>
       </c>
       <c r="U30">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="V30">
         <v>29.4</v>
       </c>
       <c r="W30" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
       <c r="X30" t="s">
-        <v>161</v>
+        <v>189</v>
       </c>
       <c r="Y30" t="s">
-        <v>162</v>
+        <v>87</v>
       </c>
       <c r="Z30" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.2">
@@ -4140,79 +4440,79 @@
         <v>26</v>
       </c>
       <c r="B31" s="2">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="C31" t="s">
-        <v>27</v>
+        <v>183</v>
       </c>
       <c r="D31" t="s">
-        <v>28</v>
+        <v>184</v>
       </c>
       <c r="E31" t="s">
-        <v>164</v>
+        <v>191</v>
       </c>
       <c r="F31" t="s">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="G31" t="s">
         <v>31</v>
       </c>
       <c r="H31" t="s">
+        <v>69</v>
+      </c>
+      <c r="I31" t="s">
+        <v>70</v>
+      </c>
+      <c r="J31" t="s">
+        <v>187</v>
+      </c>
+      <c r="K31" t="s">
         <v>72</v>
-      </c>
-      <c r="I31" t="s">
-        <v>73</v>
-      </c>
-      <c r="J31" t="s">
-        <v>107</v>
-      </c>
-      <c r="K31" t="s">
-        <v>75</v>
       </c>
       <c r="L31" t="s">
         <v>36</v>
       </c>
       <c r="M31">
-        <v>12656</v>
+        <v>37803</v>
       </c>
       <c r="N31">
-        <v>12550</v>
+        <v>37608</v>
       </c>
       <c r="O31">
-        <v>10</v>
-      </c>
-      <c r="P31" t="s">
-        <v>37</v>
+        <v>14</v>
+      </c>
+      <c r="P31">
+        <v>14</v>
       </c>
       <c r="Q31">
         <v>0</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="T31">
         <v>0</v>
       </c>
       <c r="U31">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V31">
-        <v>36.86</v>
+        <v>29.4</v>
       </c>
       <c r="W31" t="s">
-        <v>166</v>
+        <v>193</v>
       </c>
       <c r="X31" t="s">
-        <v>167</v>
+        <v>194</v>
       </c>
       <c r="Y31" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
       <c r="Z31" t="s">
-        <v>169</v>
+        <v>196</v>
       </c>
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.2">
@@ -4220,49 +4520,49 @@
         <v>26</v>
       </c>
       <c r="B32" s="2">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="C32" t="s">
-        <v>27</v>
+        <v>183</v>
       </c>
       <c r="D32" t="s">
-        <v>28</v>
+        <v>184</v>
       </c>
       <c r="E32" t="s">
-        <v>164</v>
+        <v>197</v>
       </c>
       <c r="F32" t="s">
-        <v>165</v>
+        <v>198</v>
       </c>
       <c r="G32" t="s">
         <v>31</v>
       </c>
       <c r="H32" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="I32" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="J32" t="s">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="K32" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="L32" t="s">
         <v>36</v>
       </c>
       <c r="M32">
-        <v>37803</v>
+        <v>18525</v>
       </c>
       <c r="N32">
-        <v>37748</v>
+        <v>18499</v>
       </c>
       <c r="O32">
-        <v>140</v>
-      </c>
-      <c r="P32" t="s">
-        <v>37</v>
+        <v>26</v>
+      </c>
+      <c r="P32">
+        <v>26</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -4277,22 +4577,22 @@
         <v>0</v>
       </c>
       <c r="U32">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="V32">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W32" t="s">
-        <v>166</v>
+        <v>200</v>
       </c>
       <c r="X32" t="s">
-        <v>167</v>
+        <v>201</v>
       </c>
       <c r="Y32" t="s">
-        <v>168</v>
+        <v>131</v>
       </c>
       <c r="Z32" t="s">
-        <v>169</v>
+        <v>202</v>
       </c>
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.2">
@@ -4300,49 +4600,49 @@
         <v>26</v>
       </c>
       <c r="B33" s="2">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="C33" t="s">
-        <v>27</v>
+        <v>183</v>
       </c>
       <c r="D33" t="s">
-        <v>28</v>
+        <v>184</v>
       </c>
       <c r="E33" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="F33" t="s">
-        <v>171</v>
+        <v>198</v>
       </c>
       <c r="G33" t="s">
         <v>31</v>
       </c>
       <c r="H33" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="I33" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="J33" t="s">
-        <v>34</v>
+        <v>187</v>
       </c>
       <c r="K33" t="s">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="L33" t="s">
         <v>36</v>
       </c>
       <c r="M33">
-        <v>18525</v>
+        <v>37803</v>
       </c>
       <c r="N33">
-        <v>18499</v>
+        <v>37608</v>
       </c>
       <c r="O33">
-        <v>10</v>
-      </c>
-      <c r="P33" t="s">
-        <v>37</v>
+        <v>26</v>
+      </c>
+      <c r="P33">
+        <v>26</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -4357,72 +4657,72 @@
         <v>0</v>
       </c>
       <c r="U33">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V33">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W33" t="s">
-        <v>172</v>
+        <v>200</v>
       </c>
       <c r="X33" t="s">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="Y33" t="s">
-        <v>174</v>
+        <v>131</v>
       </c>
       <c r="Z33" t="s">
-        <v>175</v>
+        <v>202</v>
       </c>
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>26</v>
+        <v>203</v>
       </c>
       <c r="B34" s="2">
         <v>46086</v>
       </c>
       <c r="C34" t="s">
-        <v>27</v>
+        <v>204</v>
       </c>
       <c r="D34" t="s">
-        <v>28</v>
+        <v>205</v>
       </c>
       <c r="E34" t="s">
-        <v>170</v>
+        <v>206</v>
       </c>
       <c r="F34" t="s">
-        <v>171</v>
+        <v>207</v>
       </c>
       <c r="G34" t="s">
         <v>31</v>
       </c>
       <c r="H34" t="s">
-        <v>56</v>
+        <v>150</v>
       </c>
       <c r="I34" t="s">
-        <v>57</v>
+        <v>151</v>
       </c>
       <c r="J34" t="s">
-        <v>108</v>
+        <v>37</v>
       </c>
       <c r="K34" t="s">
-        <v>59</v>
+        <v>153</v>
       </c>
       <c r="L34" t="s">
         <v>36</v>
       </c>
       <c r="M34">
-        <v>37803</v>
+        <v>1791</v>
       </c>
       <c r="N34">
-        <v>37748</v>
+        <v>1745</v>
       </c>
       <c r="O34">
-        <v>70</v>
-      </c>
-      <c r="P34" t="s">
-        <v>37</v>
+        <v>8</v>
+      </c>
+      <c r="P34">
+        <v>8</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -4437,22 +4737,22 @@
         <v>0</v>
       </c>
       <c r="U34">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="V34">
-        <v>29.4</v>
+        <v>57.33</v>
       </c>
       <c r="W34" t="s">
-        <v>172</v>
+        <v>208</v>
       </c>
       <c r="X34" t="s">
-        <v>173</v>
+        <v>209</v>
       </c>
       <c r="Y34" t="s">
-        <v>174</v>
+        <v>87</v>
       </c>
       <c r="Z34" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
     </row>
     <row r="35" spans="1:26" x14ac:dyDescent="0.2">
@@ -4463,43 +4763,43 @@
         <v>46086</v>
       </c>
       <c r="C35" t="s">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="D35" t="s">
-        <v>28</v>
+        <v>168</v>
       </c>
       <c r="E35" t="s">
-        <v>176</v>
+        <v>211</v>
       </c>
       <c r="F35" t="s">
-        <v>177</v>
+        <v>212</v>
       </c>
       <c r="G35" t="s">
         <v>31</v>
       </c>
       <c r="H35" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="I35" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="J35" t="s">
-        <v>108</v>
+        <v>171</v>
       </c>
       <c r="K35" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="L35" t="s">
         <v>36</v>
       </c>
       <c r="M35">
-        <v>37803</v>
+        <v>18525</v>
       </c>
       <c r="N35">
-        <v>37748</v>
+        <v>18499</v>
       </c>
       <c r="O35">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="P35" t="s">
         <v>37</v>
@@ -4517,22 +4817,22 @@
         <v>0</v>
       </c>
       <c r="U35">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="V35">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W35" t="s">
-        <v>178</v>
+        <v>213</v>
       </c>
       <c r="X35" t="s">
-        <v>179</v>
+        <v>214</v>
       </c>
       <c r="Y35" t="s">
-        <v>180</v>
+        <v>215</v>
       </c>
       <c r="Z35" t="s">
-        <v>181</v>
+        <v>216</v>
       </c>
     </row>
     <row r="36" spans="1:26" x14ac:dyDescent="0.2">
@@ -4543,16 +4843,16 @@
         <v>46086</v>
       </c>
       <c r="C36" t="s">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="D36" t="s">
-        <v>28</v>
+        <v>168</v>
       </c>
       <c r="E36" t="s">
-        <v>182</v>
+        <v>217</v>
       </c>
       <c r="F36" t="s">
-        <v>183</v>
+        <v>218</v>
       </c>
       <c r="G36" t="s">
         <v>31</v>
@@ -4564,7 +4864,7 @@
         <v>33</v>
       </c>
       <c r="J36" t="s">
-        <v>34</v>
+        <v>171</v>
       </c>
       <c r="K36" t="s">
         <v>35</v>
@@ -4579,7 +4879,7 @@
         <v>18499</v>
       </c>
       <c r="O36">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="P36" t="s">
         <v>37</v>
@@ -4597,22 +4897,22 @@
         <v>0</v>
       </c>
       <c r="U36">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="V36">
         <v>47.46</v>
       </c>
       <c r="W36" t="s">
-        <v>184</v>
+        <v>219</v>
       </c>
       <c r="X36" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="Y36" t="s">
-        <v>186</v>
+        <v>221</v>
       </c>
       <c r="Z36" t="s">
-        <v>187</v>
+        <v>222</v>
       </c>
     </row>
     <row r="37" spans="1:26" x14ac:dyDescent="0.2">
@@ -4623,43 +4923,43 @@
         <v>46086</v>
       </c>
       <c r="C37" t="s">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="D37" t="s">
-        <v>28</v>
+        <v>168</v>
       </c>
       <c r="E37" t="s">
-        <v>188</v>
+        <v>217</v>
       </c>
       <c r="F37" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="G37" t="s">
         <v>31</v>
       </c>
       <c r="H37" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="I37" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="J37" t="s">
-        <v>34</v>
+        <v>223</v>
       </c>
       <c r="K37" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="L37" t="s">
         <v>36</v>
       </c>
       <c r="M37">
-        <v>18525</v>
+        <v>12600</v>
       </c>
       <c r="N37">
-        <v>18499</v>
+        <v>11150</v>
       </c>
       <c r="O37">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="P37" t="s">
         <v>37</v>
@@ -4677,22 +4977,22 @@
         <v>0</v>
       </c>
       <c r="U37">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="V37">
-        <v>47.46</v>
+        <v>36.86</v>
       </c>
       <c r="W37" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
       <c r="X37" t="s">
-        <v>191</v>
+        <v>220</v>
       </c>
       <c r="Y37" t="s">
-        <v>68</v>
+        <v>221</v>
       </c>
       <c r="Z37" t="s">
-        <v>192</v>
+        <v>222</v>
       </c>
     </row>
     <row r="38" spans="1:26" x14ac:dyDescent="0.2">
@@ -4703,31 +5003,31 @@
         <v>46086</v>
       </c>
       <c r="C38" t="s">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="D38" t="s">
-        <v>28</v>
+        <v>168</v>
       </c>
       <c r="E38" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="F38" t="s">
-        <v>194</v>
+        <v>218</v>
       </c>
       <c r="G38" t="s">
         <v>31</v>
       </c>
       <c r="H38" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="I38" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="J38" t="s">
-        <v>108</v>
+        <v>224</v>
       </c>
       <c r="K38" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="L38" t="s">
         <v>36</v>
@@ -4736,10 +5036,10 @@
         <v>37803</v>
       </c>
       <c r="N38">
-        <v>37748</v>
+        <v>37608</v>
       </c>
       <c r="O38">
-        <v>140</v>
+        <v>70</v>
       </c>
       <c r="P38" t="s">
         <v>37</v>
@@ -4757,22 +5057,22 @@
         <v>0</v>
       </c>
       <c r="U38">
-        <v>140</v>
+        <v>70</v>
       </c>
       <c r="V38">
         <v>29.4</v>
       </c>
       <c r="W38" t="s">
-        <v>195</v>
+        <v>219</v>
       </c>
       <c r="X38" t="s">
-        <v>196</v>
+        <v>220</v>
       </c>
       <c r="Y38" t="s">
-        <v>36</v>
+        <v>221</v>
       </c>
       <c r="Z38" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
     </row>
     <row r="39" spans="1:26" x14ac:dyDescent="0.2">
@@ -4783,43 +5083,43 @@
         <v>46086</v>
       </c>
       <c r="C39" t="s">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="D39" t="s">
-        <v>28</v>
+        <v>168</v>
       </c>
       <c r="E39" t="s">
-        <v>198</v>
+        <v>225</v>
       </c>
       <c r="F39" t="s">
-        <v>199</v>
+        <v>226</v>
       </c>
       <c r="G39" t="s">
         <v>31</v>
       </c>
       <c r="H39" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="I39" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="J39" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="K39" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="L39" t="s">
         <v>36</v>
       </c>
       <c r="M39">
-        <v>1791</v>
+        <v>18525</v>
       </c>
       <c r="N39">
-        <v>1777</v>
+        <v>18499</v>
       </c>
       <c r="O39">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="P39" t="s">
         <v>37</v>
@@ -4837,22 +5137,22 @@
         <v>0</v>
       </c>
       <c r="U39">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="V39">
-        <v>57.33</v>
+        <v>47.46</v>
       </c>
       <c r="W39" t="s">
-        <v>201</v>
+        <v>172</v>
       </c>
       <c r="X39" t="s">
-        <v>202</v>
+        <v>173</v>
       </c>
       <c r="Y39" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="Z39" t="s">
-        <v>203</v>
+        <v>175</v>
       </c>
     </row>
     <row r="40" spans="1:26" x14ac:dyDescent="0.2">
@@ -4863,16 +5163,16 @@
         <v>46086</v>
       </c>
       <c r="C40" t="s">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="D40" t="s">
-        <v>28</v>
+        <v>168</v>
       </c>
       <c r="E40" t="s">
-        <v>198</v>
+        <v>227</v>
       </c>
       <c r="F40" t="s">
-        <v>199</v>
+        <v>228</v>
       </c>
       <c r="G40" t="s">
         <v>31</v>
@@ -4884,7 +5184,7 @@
         <v>33</v>
       </c>
       <c r="J40" t="s">
-        <v>34</v>
+        <v>229</v>
       </c>
       <c r="K40" t="s">
         <v>35</v>
@@ -4899,7 +5199,7 @@
         <v>18499</v>
       </c>
       <c r="O40">
-        <v>195</v>
+        <v>27</v>
       </c>
       <c r="P40" t="s">
         <v>37</v>
@@ -4917,22 +5217,22 @@
         <v>0</v>
       </c>
       <c r="U40">
-        <v>195</v>
+        <v>27</v>
       </c>
       <c r="V40">
         <v>47.46</v>
       </c>
       <c r="W40" t="s">
-        <v>201</v>
+        <v>230</v>
       </c>
       <c r="X40" t="s">
-        <v>202</v>
+        <v>231</v>
       </c>
       <c r="Y40" t="s">
-        <v>145</v>
+        <v>232</v>
       </c>
       <c r="Z40" t="s">
-        <v>203</v>
+        <v>233</v>
       </c>
     </row>
     <row r="41" spans="1:26" x14ac:dyDescent="0.2">
@@ -4943,43 +5243,43 @@
         <v>46086</v>
       </c>
       <c r="C41" t="s">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="D41" t="s">
-        <v>28</v>
+        <v>168</v>
       </c>
       <c r="E41" t="s">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="F41" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="G41" t="s">
         <v>31</v>
       </c>
       <c r="H41" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="I41" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="J41" t="s">
-        <v>34</v>
+        <v>224</v>
       </c>
       <c r="K41" t="s">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="L41" t="s">
         <v>36</v>
       </c>
       <c r="M41">
-        <v>18525</v>
+        <v>37803</v>
       </c>
       <c r="N41">
-        <v>18499</v>
+        <v>37608</v>
       </c>
       <c r="O41">
-        <v>14</v>
+        <v>140</v>
       </c>
       <c r="P41" t="s">
         <v>37</v>
@@ -4997,22 +5297,22 @@
         <v>0</v>
       </c>
       <c r="U41">
-        <v>14</v>
+        <v>140</v>
       </c>
       <c r="V41">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W41" t="s">
-        <v>206</v>
+        <v>230</v>
       </c>
       <c r="X41" t="s">
-        <v>207</v>
+        <v>231</v>
       </c>
       <c r="Y41" t="s">
-        <v>127</v>
+        <v>232</v>
       </c>
       <c r="Z41" t="s">
-        <v>208</v>
+        <v>233</v>
       </c>
     </row>
     <row r="42" spans="1:26" x14ac:dyDescent="0.2">
@@ -5023,43 +5323,43 @@
         <v>46086</v>
       </c>
       <c r="C42" t="s">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="D42" t="s">
-        <v>28</v>
+        <v>168</v>
       </c>
       <c r="E42" t="s">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="F42" t="s">
-        <v>205</v>
+        <v>235</v>
       </c>
       <c r="G42" t="s">
         <v>31</v>
       </c>
       <c r="H42" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="I42" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="J42" t="s">
-        <v>108</v>
+        <v>171</v>
       </c>
       <c r="K42" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="L42" t="s">
         <v>36</v>
       </c>
       <c r="M42">
-        <v>37803</v>
+        <v>18525</v>
       </c>
       <c r="N42">
-        <v>37748</v>
+        <v>18499</v>
       </c>
       <c r="O42">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="P42" t="s">
         <v>37</v>
@@ -5077,22 +5377,22 @@
         <v>0</v>
       </c>
       <c r="U42">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="V42">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W42" t="s">
-        <v>206</v>
+        <v>236</v>
       </c>
       <c r="X42" t="s">
-        <v>207</v>
+        <v>237</v>
       </c>
       <c r="Y42" t="s">
-        <v>127</v>
+        <v>26</v>
       </c>
       <c r="Z42" t="s">
-        <v>208</v>
+        <v>238</v>
       </c>
     </row>
     <row r="43" spans="1:26" x14ac:dyDescent="0.2">
@@ -5103,43 +5403,43 @@
         <v>46086</v>
       </c>
       <c r="C43" t="s">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="D43" t="s">
-        <v>28</v>
+        <v>168</v>
       </c>
       <c r="E43" t="s">
-        <v>209</v>
+        <v>234</v>
       </c>
       <c r="F43" t="s">
-        <v>210</v>
+        <v>235</v>
       </c>
       <c r="G43" t="s">
         <v>31</v>
       </c>
       <c r="H43" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="I43" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="J43" t="s">
-        <v>34</v>
+        <v>224</v>
       </c>
       <c r="K43" t="s">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="L43" t="s">
         <v>36</v>
       </c>
       <c r="M43">
-        <v>18525</v>
+        <v>37803</v>
       </c>
       <c r="N43">
-        <v>18499</v>
+        <v>37608</v>
       </c>
       <c r="O43">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="P43" t="s">
         <v>37</v>
@@ -5157,22 +5457,22 @@
         <v>0</v>
       </c>
       <c r="U43">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="V43">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W43" t="s">
-        <v>211</v>
+        <v>236</v>
       </c>
       <c r="X43" t="s">
-        <v>212</v>
+        <v>237</v>
       </c>
       <c r="Y43" t="s">
-        <v>213</v>
+        <v>26</v>
       </c>
       <c r="Z43" t="s">
-        <v>214</v>
+        <v>238</v>
       </c>
     </row>
     <row r="44" spans="1:26" x14ac:dyDescent="0.2">
@@ -5183,43 +5483,43 @@
         <v>46086</v>
       </c>
       <c r="C44" t="s">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="D44" t="s">
-        <v>28</v>
+        <v>168</v>
       </c>
       <c r="E44" t="s">
-        <v>215</v>
+        <v>239</v>
       </c>
       <c r="F44" t="s">
-        <v>216</v>
+        <v>240</v>
       </c>
       <c r="G44" t="s">
         <v>31</v>
       </c>
       <c r="H44" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="I44" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="J44" t="s">
-        <v>108</v>
+        <v>171</v>
       </c>
       <c r="K44" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="L44" t="s">
         <v>36</v>
       </c>
       <c r="M44">
-        <v>37803</v>
+        <v>18525</v>
       </c>
       <c r="N44">
-        <v>37748</v>
+        <v>18499</v>
       </c>
       <c r="O44">
-        <v>140</v>
+        <v>36</v>
       </c>
       <c r="P44" t="s">
         <v>37</v>
@@ -5237,22 +5537,22 @@
         <v>0</v>
       </c>
       <c r="U44">
-        <v>140</v>
+        <v>36</v>
       </c>
       <c r="V44">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W44" t="s">
-        <v>217</v>
+        <v>241</v>
       </c>
       <c r="X44" t="s">
-        <v>218</v>
+        <v>158</v>
       </c>
       <c r="Y44" t="s">
-        <v>36</v>
+        <v>159</v>
       </c>
       <c r="Z44" t="s">
-        <v>219</v>
+        <v>160</v>
       </c>
     </row>
     <row r="45" spans="1:26" x14ac:dyDescent="0.2">
@@ -5263,31 +5563,31 @@
         <v>46086</v>
       </c>
       <c r="C45" t="s">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="D45" t="s">
-        <v>28</v>
+        <v>168</v>
       </c>
       <c r="E45" t="s">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="F45" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="G45" t="s">
         <v>31</v>
       </c>
       <c r="H45" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="I45" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="J45" t="s">
-        <v>108</v>
+        <v>224</v>
       </c>
       <c r="K45" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="L45" t="s">
         <v>36</v>
@@ -5296,10 +5596,10 @@
         <v>37803</v>
       </c>
       <c r="N45">
-        <v>37748</v>
+        <v>37608</v>
       </c>
       <c r="O45">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="P45" t="s">
         <v>37</v>
@@ -5317,22 +5617,22 @@
         <v>0</v>
       </c>
       <c r="U45">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="V45">
         <v>29.4</v>
       </c>
       <c r="W45" t="s">
-        <v>222</v>
+        <v>244</v>
       </c>
       <c r="X45" t="s">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="Y45" t="s">
-        <v>186</v>
+        <v>96</v>
       </c>
       <c r="Z45" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
     </row>
     <row r="46" spans="1:26" x14ac:dyDescent="0.2">
@@ -5343,43 +5643,43 @@
         <v>46086</v>
       </c>
       <c r="C46" t="s">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="D46" t="s">
-        <v>28</v>
+        <v>168</v>
       </c>
       <c r="E46" t="s">
-        <v>225</v>
+        <v>247</v>
       </c>
       <c r="F46" t="s">
-        <v>226</v>
+        <v>248</v>
       </c>
       <c r="G46" t="s">
         <v>31</v>
       </c>
       <c r="H46" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="I46" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="J46" t="s">
-        <v>108</v>
+        <v>171</v>
       </c>
       <c r="K46" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="L46" t="s">
         <v>36</v>
       </c>
       <c r="M46">
-        <v>37803</v>
+        <v>18525</v>
       </c>
       <c r="N46">
-        <v>37748</v>
+        <v>18499</v>
       </c>
       <c r="O46">
-        <v>210</v>
+        <v>65</v>
       </c>
       <c r="P46" t="s">
         <v>37</v>
@@ -5397,22 +5697,22 @@
         <v>0</v>
       </c>
       <c r="U46">
-        <v>210</v>
+        <v>65</v>
       </c>
       <c r="V46">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W46" t="s">
-        <v>227</v>
+        <v>249</v>
       </c>
       <c r="X46" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="Y46" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="Z46" t="s">
-        <v>230</v>
+        <v>252</v>
       </c>
     </row>
     <row r="47" spans="1:26" x14ac:dyDescent="0.2">
@@ -5423,40 +5723,40 @@
         <v>46086</v>
       </c>
       <c r="C47" t="s">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="D47" t="s">
-        <v>28</v>
+        <v>168</v>
       </c>
       <c r="E47" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="F47" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="G47" t="s">
         <v>31</v>
       </c>
       <c r="H47" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="I47" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="J47" t="s">
-        <v>107</v>
+        <v>223</v>
       </c>
       <c r="K47" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="L47" t="s">
         <v>36</v>
       </c>
       <c r="M47">
-        <v>12656</v>
+        <v>12600</v>
       </c>
       <c r="N47">
-        <v>12550</v>
+        <v>11150</v>
       </c>
       <c r="O47">
         <v>70</v>
@@ -5483,16 +5783,16 @@
         <v>36.86</v>
       </c>
       <c r="W47" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="X47" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="Y47" t="s">
-        <v>62</v>
+        <v>251</v>
       </c>
       <c r="Z47" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
     </row>
     <row r="48" spans="1:26" x14ac:dyDescent="0.2">
@@ -5503,31 +5803,31 @@
         <v>46086</v>
       </c>
       <c r="C48" t="s">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="D48" t="s">
-        <v>28</v>
+        <v>168</v>
       </c>
       <c r="E48" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="F48" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="G48" t="s">
         <v>31</v>
       </c>
       <c r="H48" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="I48" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="J48" t="s">
-        <v>108</v>
+        <v>224</v>
       </c>
       <c r="K48" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="L48" t="s">
         <v>36</v>
@@ -5536,10 +5836,10 @@
         <v>37803</v>
       </c>
       <c r="N48">
-        <v>37748</v>
+        <v>37608</v>
       </c>
       <c r="O48">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="P48" t="s">
         <v>37</v>
@@ -5557,22 +5857,22 @@
         <v>0</v>
       </c>
       <c r="U48">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="V48">
         <v>29.4</v>
       </c>
       <c r="W48" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="X48" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="Y48" t="s">
-        <v>62</v>
+        <v>251</v>
       </c>
       <c r="Z48" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
     </row>
     <row r="49" spans="1:26" x14ac:dyDescent="0.2">
@@ -5583,43 +5883,43 @@
         <v>46086</v>
       </c>
       <c r="C49" t="s">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="D49" t="s">
-        <v>28</v>
+        <v>168</v>
       </c>
       <c r="E49" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="F49" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="G49" t="s">
         <v>31</v>
       </c>
       <c r="H49" t="s">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="I49" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="J49" t="s">
-        <v>107</v>
+        <v>171</v>
       </c>
       <c r="K49" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="L49" t="s">
         <v>36</v>
       </c>
       <c r="M49">
-        <v>12656</v>
+        <v>18525</v>
       </c>
       <c r="N49">
-        <v>12550</v>
+        <v>18499</v>
       </c>
       <c r="O49">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="P49" t="s">
         <v>37</v>
@@ -5637,22 +5937,22 @@
         <v>0</v>
       </c>
       <c r="U49">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="V49">
-        <v>36.86</v>
+        <v>47.46</v>
       </c>
       <c r="W49" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="X49" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="Y49" t="s">
-        <v>240</v>
+        <v>40</v>
       </c>
       <c r="Z49" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
     </row>
     <row r="50" spans="1:26" x14ac:dyDescent="0.2">
@@ -5663,43 +5963,43 @@
         <v>46086</v>
       </c>
       <c r="C50" t="s">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="D50" t="s">
-        <v>28</v>
+        <v>168</v>
       </c>
       <c r="E50" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="F50" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="G50" t="s">
         <v>31</v>
       </c>
       <c r="H50" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="I50" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="J50" t="s">
-        <v>34</v>
+        <v>223</v>
       </c>
       <c r="K50" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="L50" t="s">
         <v>36</v>
       </c>
       <c r="M50">
-        <v>18525</v>
+        <v>12600</v>
       </c>
       <c r="N50">
-        <v>18499</v>
+        <v>11150</v>
       </c>
       <c r="O50">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="P50" t="s">
         <v>37</v>
@@ -5717,22 +6017,22 @@
         <v>0</v>
       </c>
       <c r="U50">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="V50">
-        <v>47.46</v>
+        <v>36.86</v>
       </c>
       <c r="W50" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="X50" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="Y50" t="s">
-        <v>246</v>
+        <v>40</v>
       </c>
       <c r="Z50" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
     </row>
     <row r="51" spans="1:26" x14ac:dyDescent="0.2">
@@ -5743,43 +6043,43 @@
         <v>46086</v>
       </c>
       <c r="C51" t="s">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="D51" t="s">
-        <v>28</v>
+        <v>168</v>
       </c>
       <c r="E51" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="F51" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="G51" t="s">
         <v>31</v>
       </c>
       <c r="H51" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="I51" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="J51" t="s">
-        <v>34</v>
+        <v>224</v>
       </c>
       <c r="K51" t="s">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="L51" t="s">
         <v>36</v>
       </c>
       <c r="M51">
-        <v>18525</v>
+        <v>37803</v>
       </c>
       <c r="N51">
-        <v>18499</v>
+        <v>37608</v>
       </c>
       <c r="O51">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="P51" t="s">
         <v>37</v>
@@ -5797,22 +6097,22 @@
         <v>0</v>
       </c>
       <c r="U51">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="V51">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W51" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="X51" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="Y51" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="Z51" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
     </row>
     <row r="52" spans="1:26" x14ac:dyDescent="0.2">
@@ -5823,43 +6123,43 @@
         <v>46086</v>
       </c>
       <c r="C52" t="s">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="D52" t="s">
-        <v>28</v>
+        <v>168</v>
       </c>
       <c r="E52" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="F52" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="G52" t="s">
         <v>31</v>
       </c>
       <c r="H52" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="I52" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="J52" t="s">
-        <v>107</v>
+        <v>223</v>
       </c>
       <c r="K52" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="L52" t="s">
         <v>36</v>
       </c>
       <c r="M52">
-        <v>12656</v>
+        <v>12600</v>
       </c>
       <c r="N52">
-        <v>12550</v>
+        <v>11150</v>
       </c>
       <c r="O52">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="P52" t="s">
         <v>37</v>
@@ -5877,22 +6177,22 @@
         <v>0</v>
       </c>
       <c r="U52">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="V52">
         <v>36.86</v>
       </c>
       <c r="W52" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="X52" t="s">
-        <v>251</v>
+        <v>130</v>
       </c>
       <c r="Y52" t="s">
-        <v>26</v>
+        <v>131</v>
       </c>
       <c r="Z52" t="s">
-        <v>252</v>
+        <v>132</v>
       </c>
     </row>
     <row r="53" spans="1:26" x14ac:dyDescent="0.2">
@@ -5903,43 +6203,43 @@
         <v>46086</v>
       </c>
       <c r="C53" t="s">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="D53" t="s">
-        <v>28</v>
+        <v>168</v>
       </c>
       <c r="E53" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="F53" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="G53" t="s">
         <v>31</v>
       </c>
       <c r="H53" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="I53" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="J53" t="s">
-        <v>108</v>
+        <v>171</v>
       </c>
       <c r="K53" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="L53" t="s">
         <v>36</v>
       </c>
       <c r="M53">
-        <v>37803</v>
+        <v>18525</v>
       </c>
       <c r="N53">
-        <v>37748</v>
+        <v>18499</v>
       </c>
       <c r="O53">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="P53" t="s">
         <v>37</v>
@@ -5957,22 +6257,22 @@
         <v>0</v>
       </c>
       <c r="U53">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="V53">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W53" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="X53" t="s">
-        <v>251</v>
+        <v>50</v>
       </c>
       <c r="Y53" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="Z53" t="s">
-        <v>252</v>
+        <v>52</v>
       </c>
     </row>
     <row r="54" spans="1:26" x14ac:dyDescent="0.2">
@@ -5980,46 +6280,46 @@
         <v>26</v>
       </c>
       <c r="B54" s="2">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="C54" t="s">
-        <v>253</v>
+        <v>167</v>
       </c>
       <c r="D54" t="s">
-        <v>254</v>
+        <v>168</v>
       </c>
       <c r="E54" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="F54" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G54" t="s">
         <v>31</v>
       </c>
       <c r="H54" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="I54" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="J54" t="s">
-        <v>257</v>
+        <v>224</v>
       </c>
       <c r="K54" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="L54" t="s">
         <v>36</v>
       </c>
       <c r="M54">
-        <v>1791</v>
+        <v>37803</v>
       </c>
       <c r="N54">
-        <v>1777</v>
+        <v>37608</v>
       </c>
       <c r="O54">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="P54" t="s">
         <v>37</v>
@@ -6037,22 +6337,22 @@
         <v>0</v>
       </c>
       <c r="U54">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="V54">
-        <v>57.33</v>
+        <v>29.4</v>
       </c>
       <c r="W54" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="X54" t="s">
-        <v>259</v>
+        <v>50</v>
       </c>
       <c r="Y54" t="s">
-        <v>260</v>
+        <v>51</v>
       </c>
       <c r="Z54" t="s">
-        <v>261</v>
+        <v>52</v>
       </c>
     </row>
     <row r="55" spans="1:26" x14ac:dyDescent="0.2">
@@ -6060,13 +6360,13 @@
         <v>26</v>
       </c>
       <c r="B55" s="2">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="C55" t="s">
-        <v>262</v>
+        <v>167</v>
       </c>
       <c r="D55" t="s">
-        <v>263</v>
+        <v>168</v>
       </c>
       <c r="E55" t="s">
         <v>264</v>
@@ -6078,28 +6378,28 @@
         <v>31</v>
       </c>
       <c r="H55" t="s">
+        <v>69</v>
+      </c>
+      <c r="I55" t="s">
+        <v>70</v>
+      </c>
+      <c r="J55" t="s">
+        <v>224</v>
+      </c>
+      <c r="K55" t="s">
         <v>72</v>
-      </c>
-      <c r="I55" t="s">
-        <v>73</v>
-      </c>
-      <c r="J55" t="s">
-        <v>37</v>
-      </c>
-      <c r="K55" t="s">
-        <v>75</v>
       </c>
       <c r="L55" t="s">
         <v>36</v>
       </c>
       <c r="M55">
-        <v>12656</v>
+        <v>37803</v>
       </c>
       <c r="N55">
-        <v>12550</v>
+        <v>37608</v>
       </c>
       <c r="O55">
-        <v>1400</v>
+        <v>30</v>
       </c>
       <c r="P55" t="s">
         <v>37</v>
@@ -6117,10 +6417,10 @@
         <v>0</v>
       </c>
       <c r="U55">
-        <v>1400</v>
+        <v>30</v>
       </c>
       <c r="V55">
-        <v>29.7</v>
+        <v>29.4</v>
       </c>
       <c r="W55" t="s">
         <v>266</v>
@@ -6129,7 +6429,7 @@
         <v>267</v>
       </c>
       <c r="Y55" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="Z55" t="s">
         <v>268</v>
@@ -6137,49 +6437,49 @@
     </row>
     <row r="56" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
+        <v>26</v>
+      </c>
+      <c r="B56" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C56" t="s">
+        <v>167</v>
+      </c>
+      <c r="D56" t="s">
+        <v>168</v>
+      </c>
+      <c r="E56" t="s">
         <v>269</v>
       </c>
-      <c r="B56" s="2">
-        <v>46084</v>
-      </c>
-      <c r="C56" t="s">
+      <c r="F56" t="s">
         <v>270</v>
-      </c>
-      <c r="D56" t="s">
-        <v>271</v>
-      </c>
-      <c r="E56" t="s">
-        <v>272</v>
-      </c>
-      <c r="F56" t="s">
-        <v>273</v>
       </c>
       <c r="G56" t="s">
         <v>31</v>
       </c>
       <c r="H56" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="I56" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="J56" t="s">
-        <v>274</v>
+        <v>223</v>
       </c>
       <c r="K56" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="L56" t="s">
         <v>36</v>
       </c>
       <c r="M56">
-        <v>1791</v>
+        <v>12600</v>
       </c>
       <c r="N56">
-        <v>1777</v>
+        <v>11150</v>
       </c>
       <c r="O56">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="P56" t="s">
         <v>37</v>
@@ -6197,22 +6497,22 @@
         <v>0</v>
       </c>
       <c r="U56">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="V56">
-        <v>57</v>
+        <v>36.86</v>
       </c>
       <c r="W56" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="X56" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="Y56" t="s">
-        <v>26</v>
+        <v>273</v>
       </c>
       <c r="Z56" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="57" spans="1:26" x14ac:dyDescent="0.2">
@@ -6220,46 +6520,46 @@
         <v>26</v>
       </c>
       <c r="B57" s="2">
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="C57" t="s">
-        <v>42</v>
+        <v>167</v>
       </c>
       <c r="D57" t="s">
-        <v>43</v>
+        <v>168</v>
       </c>
       <c r="E57" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="F57" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="G57" t="s">
         <v>31</v>
       </c>
       <c r="H57" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="I57" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="J57" t="s">
-        <v>37</v>
+        <v>224</v>
       </c>
       <c r="K57" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="L57" t="s">
         <v>36</v>
       </c>
       <c r="M57">
-        <v>1791</v>
+        <v>37803</v>
       </c>
       <c r="N57">
-        <v>1777</v>
+        <v>37608</v>
       </c>
       <c r="O57">
-        <v>6</v>
+        <v>140</v>
       </c>
       <c r="P57" t="s">
         <v>37</v>
@@ -6277,22 +6577,2022 @@
         <v>0</v>
       </c>
       <c r="U57">
+        <v>140</v>
+      </c>
+      <c r="V57">
+        <v>29.4</v>
+      </c>
+      <c r="W57" t="s">
+        <v>271</v>
+      </c>
+      <c r="X57" t="s">
+        <v>272</v>
+      </c>
+      <c r="Y57" t="s">
+        <v>273</v>
+      </c>
+      <c r="Z57" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="58" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>26</v>
+      </c>
+      <c r="B58" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C58" t="s">
+        <v>167</v>
+      </c>
+      <c r="D58" t="s">
+        <v>168</v>
+      </c>
+      <c r="E58" t="s">
+        <v>275</v>
+      </c>
+      <c r="F58" t="s">
+        <v>276</v>
+      </c>
+      <c r="G58" t="s">
+        <v>31</v>
+      </c>
+      <c r="H58" t="s">
+        <v>32</v>
+      </c>
+      <c r="I58" t="s">
+        <v>33</v>
+      </c>
+      <c r="J58" t="s">
+        <v>171</v>
+      </c>
+      <c r="K58" t="s">
+        <v>35</v>
+      </c>
+      <c r="L58" t="s">
+        <v>36</v>
+      </c>
+      <c r="M58">
+        <v>18525</v>
+      </c>
+      <c r="N58">
+        <v>18499</v>
+      </c>
+      <c r="O58">
+        <v>10</v>
+      </c>
+      <c r="P58" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q58">
+        <v>0</v>
+      </c>
+      <c r="R58">
+        <v>0</v>
+      </c>
+      <c r="S58">
+        <v>0</v>
+      </c>
+      <c r="T58">
+        <v>0</v>
+      </c>
+      <c r="U58">
+        <v>10</v>
+      </c>
+      <c r="V58">
+        <v>47.46</v>
+      </c>
+      <c r="W58" t="s">
+        <v>277</v>
+      </c>
+      <c r="X58" t="s">
+        <v>278</v>
+      </c>
+      <c r="Y58" t="s">
+        <v>279</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="59" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>26</v>
+      </c>
+      <c r="B59" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C59" t="s">
+        <v>167</v>
+      </c>
+      <c r="D59" t="s">
+        <v>168</v>
+      </c>
+      <c r="E59" t="s">
+        <v>275</v>
+      </c>
+      <c r="F59" t="s">
+        <v>276</v>
+      </c>
+      <c r="G59" t="s">
+        <v>31</v>
+      </c>
+      <c r="H59" t="s">
+        <v>69</v>
+      </c>
+      <c r="I59" t="s">
+        <v>70</v>
+      </c>
+      <c r="J59" t="s">
+        <v>224</v>
+      </c>
+      <c r="K59" t="s">
+        <v>72</v>
+      </c>
+      <c r="L59" t="s">
+        <v>36</v>
+      </c>
+      <c r="M59">
+        <v>37803</v>
+      </c>
+      <c r="N59">
+        <v>37608</v>
+      </c>
+      <c r="O59">
+        <v>70</v>
+      </c>
+      <c r="P59" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q59">
+        <v>0</v>
+      </c>
+      <c r="R59">
+        <v>0</v>
+      </c>
+      <c r="S59">
+        <v>0</v>
+      </c>
+      <c r="T59">
+        <v>0</v>
+      </c>
+      <c r="U59">
+        <v>70</v>
+      </c>
+      <c r="V59">
+        <v>29.4</v>
+      </c>
+      <c r="W59" t="s">
+        <v>277</v>
+      </c>
+      <c r="X59" t="s">
+        <v>278</v>
+      </c>
+      <c r="Y59" t="s">
+        <v>279</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="60" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>26</v>
+      </c>
+      <c r="B60" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C60" t="s">
+        <v>167</v>
+      </c>
+      <c r="D60" t="s">
+        <v>168</v>
+      </c>
+      <c r="E60" t="s">
+        <v>281</v>
+      </c>
+      <c r="F60" t="s">
+        <v>282</v>
+      </c>
+      <c r="G60" t="s">
+        <v>31</v>
+      </c>
+      <c r="H60" t="s">
+        <v>69</v>
+      </c>
+      <c r="I60" t="s">
+        <v>70</v>
+      </c>
+      <c r="J60" t="s">
+        <v>224</v>
+      </c>
+      <c r="K60" t="s">
+        <v>72</v>
+      </c>
+      <c r="L60" t="s">
+        <v>36</v>
+      </c>
+      <c r="M60">
+        <v>37803</v>
+      </c>
+      <c r="N60">
+        <v>37608</v>
+      </c>
+      <c r="O60">
+        <v>70</v>
+      </c>
+      <c r="P60" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q60">
+        <v>0</v>
+      </c>
+      <c r="R60">
+        <v>0</v>
+      </c>
+      <c r="S60">
+        <v>0</v>
+      </c>
+      <c r="T60">
+        <v>0</v>
+      </c>
+      <c r="U60">
+        <v>70</v>
+      </c>
+      <c r="V60">
+        <v>29.4</v>
+      </c>
+      <c r="W60" t="s">
+        <v>283</v>
+      </c>
+      <c r="X60" t="s">
+        <v>284</v>
+      </c>
+      <c r="Y60" t="s">
+        <v>285</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="61" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>26</v>
+      </c>
+      <c r="B61" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C61" t="s">
+        <v>167</v>
+      </c>
+      <c r="D61" t="s">
+        <v>168</v>
+      </c>
+      <c r="E61" t="s">
+        <v>287</v>
+      </c>
+      <c r="F61" t="s">
+        <v>288</v>
+      </c>
+      <c r="G61" t="s">
+        <v>31</v>
+      </c>
+      <c r="H61" t="s">
+        <v>32</v>
+      </c>
+      <c r="I61" t="s">
+        <v>33</v>
+      </c>
+      <c r="J61" t="s">
+        <v>171</v>
+      </c>
+      <c r="K61" t="s">
+        <v>35</v>
+      </c>
+      <c r="L61" t="s">
+        <v>36</v>
+      </c>
+      <c r="M61">
+        <v>18525</v>
+      </c>
+      <c r="N61">
+        <v>18499</v>
+      </c>
+      <c r="O61">
+        <v>14</v>
+      </c>
+      <c r="P61" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q61">
+        <v>0</v>
+      </c>
+      <c r="R61">
+        <v>0</v>
+      </c>
+      <c r="S61">
+        <v>0</v>
+      </c>
+      <c r="T61">
+        <v>0</v>
+      </c>
+      <c r="U61">
+        <v>14</v>
+      </c>
+      <c r="V61">
+        <v>47.46</v>
+      </c>
+      <c r="W61" t="s">
+        <v>289</v>
+      </c>
+      <c r="X61" t="s">
+        <v>290</v>
+      </c>
+      <c r="Y61" t="s">
+        <v>291</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="62" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>26</v>
+      </c>
+      <c r="B62" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C62" t="s">
+        <v>167</v>
+      </c>
+      <c r="D62" t="s">
+        <v>168</v>
+      </c>
+      <c r="E62" t="s">
+        <v>293</v>
+      </c>
+      <c r="F62" t="s">
+        <v>294</v>
+      </c>
+      <c r="G62" t="s">
+        <v>31</v>
+      </c>
+      <c r="H62" t="s">
+        <v>32</v>
+      </c>
+      <c r="I62" t="s">
+        <v>33</v>
+      </c>
+      <c r="J62" t="s">
+        <v>171</v>
+      </c>
+      <c r="K62" t="s">
+        <v>35</v>
+      </c>
+      <c r="L62" t="s">
+        <v>36</v>
+      </c>
+      <c r="M62">
+        <v>18525</v>
+      </c>
+      <c r="N62">
+        <v>18499</v>
+      </c>
+      <c r="O62">
+        <v>9</v>
+      </c>
+      <c r="P62" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q62">
+        <v>0</v>
+      </c>
+      <c r="R62">
+        <v>0</v>
+      </c>
+      <c r="S62">
+        <v>0</v>
+      </c>
+      <c r="T62">
+        <v>0</v>
+      </c>
+      <c r="U62">
+        <v>9</v>
+      </c>
+      <c r="V62">
+        <v>47.46</v>
+      </c>
+      <c r="W62" t="s">
+        <v>295</v>
+      </c>
+      <c r="X62" t="s">
+        <v>296</v>
+      </c>
+      <c r="Y62" t="s">
+        <v>195</v>
+      </c>
+      <c r="Z62" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="63" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>26</v>
+      </c>
+      <c r="B63" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C63" t="s">
+        <v>167</v>
+      </c>
+      <c r="D63" t="s">
+        <v>168</v>
+      </c>
+      <c r="E63" t="s">
+        <v>298</v>
+      </c>
+      <c r="F63" t="s">
+        <v>299</v>
+      </c>
+      <c r="G63" t="s">
+        <v>31</v>
+      </c>
+      <c r="H63" t="s">
+        <v>69</v>
+      </c>
+      <c r="I63" t="s">
+        <v>70</v>
+      </c>
+      <c r="J63" t="s">
+        <v>224</v>
+      </c>
+      <c r="K63" t="s">
+        <v>72</v>
+      </c>
+      <c r="L63" t="s">
+        <v>36</v>
+      </c>
+      <c r="M63">
+        <v>37803</v>
+      </c>
+      <c r="N63">
+        <v>37608</v>
+      </c>
+      <c r="O63">
+        <v>140</v>
+      </c>
+      <c r="P63" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q63">
+        <v>0</v>
+      </c>
+      <c r="R63">
+        <v>0</v>
+      </c>
+      <c r="S63">
+        <v>0</v>
+      </c>
+      <c r="T63">
+        <v>0</v>
+      </c>
+      <c r="U63">
+        <v>140</v>
+      </c>
+      <c r="V63">
+        <v>29.4</v>
+      </c>
+      <c r="W63" t="s">
+        <v>300</v>
+      </c>
+      <c r="X63" t="s">
+        <v>301</v>
+      </c>
+      <c r="Y63" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="64" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>26</v>
+      </c>
+      <c r="B64" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C64" t="s">
+        <v>167</v>
+      </c>
+      <c r="D64" t="s">
+        <v>168</v>
+      </c>
+      <c r="E64" t="s">
+        <v>303</v>
+      </c>
+      <c r="F64" t="s">
+        <v>304</v>
+      </c>
+      <c r="G64" t="s">
+        <v>31</v>
+      </c>
+      <c r="H64" t="s">
+        <v>150</v>
+      </c>
+      <c r="I64" t="s">
+        <v>151</v>
+      </c>
+      <c r="J64" t="s">
+        <v>305</v>
+      </c>
+      <c r="K64" t="s">
+        <v>153</v>
+      </c>
+      <c r="L64" t="s">
+        <v>36</v>
+      </c>
+      <c r="M64">
+        <v>1791</v>
+      </c>
+      <c r="N64">
+        <v>1745</v>
+      </c>
+      <c r="O64">
+        <v>8</v>
+      </c>
+      <c r="P64" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q64">
+        <v>0</v>
+      </c>
+      <c r="R64">
+        <v>0</v>
+      </c>
+      <c r="S64">
+        <v>0</v>
+      </c>
+      <c r="T64">
+        <v>0</v>
+      </c>
+      <c r="U64">
+        <v>8</v>
+      </c>
+      <c r="V64">
+        <v>57.33</v>
+      </c>
+      <c r="W64" t="s">
+        <v>306</v>
+      </c>
+      <c r="X64" t="s">
+        <v>307</v>
+      </c>
+      <c r="Y64" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="65" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>26</v>
+      </c>
+      <c r="B65" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C65" t="s">
+        <v>167</v>
+      </c>
+      <c r="D65" t="s">
+        <v>168</v>
+      </c>
+      <c r="E65" t="s">
+        <v>303</v>
+      </c>
+      <c r="F65" t="s">
+        <v>304</v>
+      </c>
+      <c r="G65" t="s">
+        <v>31</v>
+      </c>
+      <c r="H65" t="s">
+        <v>32</v>
+      </c>
+      <c r="I65" t="s">
+        <v>33</v>
+      </c>
+      <c r="J65" t="s">
+        <v>171</v>
+      </c>
+      <c r="K65" t="s">
+        <v>35</v>
+      </c>
+      <c r="L65" t="s">
+        <v>36</v>
+      </c>
+      <c r="M65">
+        <v>18525</v>
+      </c>
+      <c r="N65">
+        <v>18499</v>
+      </c>
+      <c r="O65">
+        <v>195</v>
+      </c>
+      <c r="P65" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q65">
+        <v>0</v>
+      </c>
+      <c r="R65">
+        <v>0</v>
+      </c>
+      <c r="S65">
+        <v>0</v>
+      </c>
+      <c r="T65">
+        <v>0</v>
+      </c>
+      <c r="U65">
+        <v>195</v>
+      </c>
+      <c r="V65">
+        <v>47.46</v>
+      </c>
+      <c r="W65" t="s">
+        <v>306</v>
+      </c>
+      <c r="X65" t="s">
+        <v>307</v>
+      </c>
+      <c r="Y65" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="66" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>26</v>
+      </c>
+      <c r="B66" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C66" t="s">
+        <v>167</v>
+      </c>
+      <c r="D66" t="s">
+        <v>168</v>
+      </c>
+      <c r="E66" t="s">
+        <v>309</v>
+      </c>
+      <c r="F66" t="s">
+        <v>310</v>
+      </c>
+      <c r="G66" t="s">
+        <v>31</v>
+      </c>
+      <c r="H66" t="s">
+        <v>32</v>
+      </c>
+      <c r="I66" t="s">
+        <v>33</v>
+      </c>
+      <c r="J66" t="s">
+        <v>171</v>
+      </c>
+      <c r="K66" t="s">
+        <v>35</v>
+      </c>
+      <c r="L66" t="s">
+        <v>36</v>
+      </c>
+      <c r="M66">
+        <v>18525</v>
+      </c>
+      <c r="N66">
+        <v>18499</v>
+      </c>
+      <c r="O66">
+        <v>14</v>
+      </c>
+      <c r="P66" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q66">
+        <v>0</v>
+      </c>
+      <c r="R66">
+        <v>0</v>
+      </c>
+      <c r="S66">
+        <v>0</v>
+      </c>
+      <c r="T66">
+        <v>0</v>
+      </c>
+      <c r="U66">
+        <v>14</v>
+      </c>
+      <c r="V66">
+        <v>47.46</v>
+      </c>
+      <c r="W66" t="s">
+        <v>311</v>
+      </c>
+      <c r="X66" t="s">
+        <v>312</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>159</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="67" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>26</v>
+      </c>
+      <c r="B67" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C67" t="s">
+        <v>167</v>
+      </c>
+      <c r="D67" t="s">
+        <v>168</v>
+      </c>
+      <c r="E67" t="s">
+        <v>309</v>
+      </c>
+      <c r="F67" t="s">
+        <v>310</v>
+      </c>
+      <c r="G67" t="s">
+        <v>31</v>
+      </c>
+      <c r="H67" t="s">
+        <v>69</v>
+      </c>
+      <c r="I67" t="s">
+        <v>70</v>
+      </c>
+      <c r="J67" t="s">
+        <v>224</v>
+      </c>
+      <c r="K67" t="s">
+        <v>72</v>
+      </c>
+      <c r="L67" t="s">
+        <v>36</v>
+      </c>
+      <c r="M67">
+        <v>37803</v>
+      </c>
+      <c r="N67">
+        <v>37608</v>
+      </c>
+      <c r="O67">
+        <v>70</v>
+      </c>
+      <c r="P67" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q67">
+        <v>0</v>
+      </c>
+      <c r="R67">
+        <v>0</v>
+      </c>
+      <c r="S67">
+        <v>0</v>
+      </c>
+      <c r="T67">
+        <v>0</v>
+      </c>
+      <c r="U67">
+        <v>70</v>
+      </c>
+      <c r="V67">
+        <v>29.4</v>
+      </c>
+      <c r="W67" t="s">
+        <v>311</v>
+      </c>
+      <c r="X67" t="s">
+        <v>312</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>159</v>
+      </c>
+      <c r="Z67" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="68" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>26</v>
+      </c>
+      <c r="B68" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C68" t="s">
+        <v>167</v>
+      </c>
+      <c r="D68" t="s">
+        <v>168</v>
+      </c>
+      <c r="E68" t="s">
+        <v>314</v>
+      </c>
+      <c r="F68" t="s">
+        <v>315</v>
+      </c>
+      <c r="G68" t="s">
+        <v>31</v>
+      </c>
+      <c r="H68" t="s">
+        <v>32</v>
+      </c>
+      <c r="I68" t="s">
+        <v>33</v>
+      </c>
+      <c r="J68" t="s">
+        <v>171</v>
+      </c>
+      <c r="K68" t="s">
+        <v>35</v>
+      </c>
+      <c r="L68" t="s">
+        <v>36</v>
+      </c>
+      <c r="M68">
+        <v>18525</v>
+      </c>
+      <c r="N68">
+        <v>18499</v>
+      </c>
+      <c r="O68">
+        <v>11</v>
+      </c>
+      <c r="P68" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q68">
+        <v>0</v>
+      </c>
+      <c r="R68">
+        <v>0</v>
+      </c>
+      <c r="S68">
+        <v>0</v>
+      </c>
+      <c r="T68">
+        <v>0</v>
+      </c>
+      <c r="U68">
+        <v>11</v>
+      </c>
+      <c r="V68">
+        <v>47.46</v>
+      </c>
+      <c r="W68" t="s">
+        <v>316</v>
+      </c>
+      <c r="X68" t="s">
+        <v>317</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z68" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="69" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>26</v>
+      </c>
+      <c r="B69" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C69" t="s">
+        <v>167</v>
+      </c>
+      <c r="D69" t="s">
+        <v>168</v>
+      </c>
+      <c r="E69" t="s">
+        <v>319</v>
+      </c>
+      <c r="F69" t="s">
+        <v>320</v>
+      </c>
+      <c r="G69" t="s">
+        <v>31</v>
+      </c>
+      <c r="H69" t="s">
+        <v>69</v>
+      </c>
+      <c r="I69" t="s">
+        <v>70</v>
+      </c>
+      <c r="J69" t="s">
+        <v>224</v>
+      </c>
+      <c r="K69" t="s">
+        <v>72</v>
+      </c>
+      <c r="L69" t="s">
+        <v>36</v>
+      </c>
+      <c r="M69">
+        <v>37803</v>
+      </c>
+      <c r="N69">
+        <v>37608</v>
+      </c>
+      <c r="O69">
+        <v>140</v>
+      </c>
+      <c r="P69" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q69">
+        <v>0</v>
+      </c>
+      <c r="R69">
+        <v>0</v>
+      </c>
+      <c r="S69">
+        <v>0</v>
+      </c>
+      <c r="T69">
+        <v>0</v>
+      </c>
+      <c r="U69">
+        <v>140</v>
+      </c>
+      <c r="V69">
+        <v>29.4</v>
+      </c>
+      <c r="W69" t="s">
+        <v>321</v>
+      </c>
+      <c r="X69" t="s">
+        <v>322</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z69" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="70" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>26</v>
+      </c>
+      <c r="B70" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C70" t="s">
+        <v>167</v>
+      </c>
+      <c r="D70" t="s">
+        <v>168</v>
+      </c>
+      <c r="E70" t="s">
+        <v>324</v>
+      </c>
+      <c r="F70" t="s">
+        <v>325</v>
+      </c>
+      <c r="G70" t="s">
+        <v>31</v>
+      </c>
+      <c r="H70" t="s">
+        <v>69</v>
+      </c>
+      <c r="I70" t="s">
+        <v>70</v>
+      </c>
+      <c r="J70" t="s">
+        <v>224</v>
+      </c>
+      <c r="K70" t="s">
+        <v>72</v>
+      </c>
+      <c r="L70" t="s">
+        <v>36</v>
+      </c>
+      <c r="M70">
+        <v>37803</v>
+      </c>
+      <c r="N70">
+        <v>37608</v>
+      </c>
+      <c r="O70">
+        <v>70</v>
+      </c>
+      <c r="P70" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q70">
+        <v>0</v>
+      </c>
+      <c r="R70">
+        <v>0</v>
+      </c>
+      <c r="S70">
+        <v>0</v>
+      </c>
+      <c r="T70">
+        <v>0</v>
+      </c>
+      <c r="U70">
+        <v>70</v>
+      </c>
+      <c r="V70">
+        <v>29.4</v>
+      </c>
+      <c r="W70" t="s">
+        <v>326</v>
+      </c>
+      <c r="X70" t="s">
+        <v>327</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>291</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="71" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>26</v>
+      </c>
+      <c r="B71" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C71" t="s">
+        <v>167</v>
+      </c>
+      <c r="D71" t="s">
+        <v>168</v>
+      </c>
+      <c r="E71" t="s">
+        <v>329</v>
+      </c>
+      <c r="F71" t="s">
+        <v>330</v>
+      </c>
+      <c r="G71" t="s">
+        <v>31</v>
+      </c>
+      <c r="H71" t="s">
+        <v>69</v>
+      </c>
+      <c r="I71" t="s">
+        <v>70</v>
+      </c>
+      <c r="J71" t="s">
+        <v>224</v>
+      </c>
+      <c r="K71" t="s">
+        <v>72</v>
+      </c>
+      <c r="L71" t="s">
+        <v>36</v>
+      </c>
+      <c r="M71">
+        <v>37803</v>
+      </c>
+      <c r="N71">
+        <v>37608</v>
+      </c>
+      <c r="O71">
+        <v>210</v>
+      </c>
+      <c r="P71" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q71">
+        <v>0</v>
+      </c>
+      <c r="R71">
+        <v>0</v>
+      </c>
+      <c r="S71">
+        <v>0</v>
+      </c>
+      <c r="T71">
+        <v>0</v>
+      </c>
+      <c r="U71">
+        <v>210</v>
+      </c>
+      <c r="V71">
+        <v>29.4</v>
+      </c>
+      <c r="W71" t="s">
+        <v>331</v>
+      </c>
+      <c r="X71" t="s">
+        <v>332</v>
+      </c>
+      <c r="Y71" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="72" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>26</v>
+      </c>
+      <c r="B72" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C72" t="s">
+        <v>167</v>
+      </c>
+      <c r="D72" t="s">
+        <v>168</v>
+      </c>
+      <c r="E72" t="s">
+        <v>334</v>
+      </c>
+      <c r="F72" t="s">
+        <v>335</v>
+      </c>
+      <c r="G72" t="s">
+        <v>31</v>
+      </c>
+      <c r="H72" t="s">
+        <v>57</v>
+      </c>
+      <c r="I72" t="s">
+        <v>58</v>
+      </c>
+      <c r="J72" t="s">
+        <v>223</v>
+      </c>
+      <c r="K72" t="s">
+        <v>59</v>
+      </c>
+      <c r="L72" t="s">
+        <v>36</v>
+      </c>
+      <c r="M72">
+        <v>12600</v>
+      </c>
+      <c r="N72">
+        <v>11150</v>
+      </c>
+      <c r="O72">
+        <v>70</v>
+      </c>
+      <c r="P72" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q72">
+        <v>0</v>
+      </c>
+      <c r="R72">
+        <v>0</v>
+      </c>
+      <c r="S72">
+        <v>0</v>
+      </c>
+      <c r="T72">
+        <v>0</v>
+      </c>
+      <c r="U72">
+        <v>70</v>
+      </c>
+      <c r="V72">
+        <v>36.86</v>
+      </c>
+      <c r="W72" t="s">
+        <v>336</v>
+      </c>
+      <c r="X72" t="s">
+        <v>337</v>
+      </c>
+      <c r="Y72" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z72" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="73" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>26</v>
+      </c>
+      <c r="B73" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C73" t="s">
+        <v>167</v>
+      </c>
+      <c r="D73" t="s">
+        <v>168</v>
+      </c>
+      <c r="E73" t="s">
+        <v>334</v>
+      </c>
+      <c r="F73" t="s">
+        <v>335</v>
+      </c>
+      <c r="G73" t="s">
+        <v>31</v>
+      </c>
+      <c r="H73" t="s">
+        <v>69</v>
+      </c>
+      <c r="I73" t="s">
+        <v>70</v>
+      </c>
+      <c r="J73" t="s">
+        <v>224</v>
+      </c>
+      <c r="K73" t="s">
+        <v>72</v>
+      </c>
+      <c r="L73" t="s">
+        <v>36</v>
+      </c>
+      <c r="M73">
+        <v>37803</v>
+      </c>
+      <c r="N73">
+        <v>37608</v>
+      </c>
+      <c r="O73">
+        <v>11</v>
+      </c>
+      <c r="P73" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q73">
+        <v>0</v>
+      </c>
+      <c r="R73">
+        <v>0</v>
+      </c>
+      <c r="S73">
+        <v>0</v>
+      </c>
+      <c r="T73">
+        <v>0</v>
+      </c>
+      <c r="U73">
+        <v>11</v>
+      </c>
+      <c r="V73">
+        <v>29.4</v>
+      </c>
+      <c r="W73" t="s">
+        <v>336</v>
+      </c>
+      <c r="X73" t="s">
+        <v>337</v>
+      </c>
+      <c r="Y73" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z73" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="74" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>26</v>
+      </c>
+      <c r="B74" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C74" t="s">
+        <v>167</v>
+      </c>
+      <c r="D74" t="s">
+        <v>168</v>
+      </c>
+      <c r="E74" t="s">
+        <v>339</v>
+      </c>
+      <c r="F74" t="s">
+        <v>340</v>
+      </c>
+      <c r="G74" t="s">
+        <v>31</v>
+      </c>
+      <c r="H74" t="s">
+        <v>57</v>
+      </c>
+      <c r="I74" t="s">
+        <v>58</v>
+      </c>
+      <c r="J74" t="s">
+        <v>223</v>
+      </c>
+      <c r="K74" t="s">
+        <v>59</v>
+      </c>
+      <c r="L74" t="s">
+        <v>36</v>
+      </c>
+      <c r="M74">
+        <v>12600</v>
+      </c>
+      <c r="N74">
+        <v>11150</v>
+      </c>
+      <c r="O74">
+        <v>70</v>
+      </c>
+      <c r="P74" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q74">
+        <v>0</v>
+      </c>
+      <c r="R74">
+        <v>0</v>
+      </c>
+      <c r="S74">
+        <v>0</v>
+      </c>
+      <c r="T74">
+        <v>0</v>
+      </c>
+      <c r="U74">
+        <v>70</v>
+      </c>
+      <c r="V74">
+        <v>36.86</v>
+      </c>
+      <c r="W74" t="s">
+        <v>341</v>
+      </c>
+      <c r="X74" t="s">
+        <v>342</v>
+      </c>
+      <c r="Y74" t="s">
+        <v>343</v>
+      </c>
+      <c r="Z74" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="75" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>26</v>
+      </c>
+      <c r="B75" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C75" t="s">
+        <v>167</v>
+      </c>
+      <c r="D75" t="s">
+        <v>168</v>
+      </c>
+      <c r="E75" t="s">
+        <v>345</v>
+      </c>
+      <c r="F75" t="s">
+        <v>346</v>
+      </c>
+      <c r="G75" t="s">
+        <v>31</v>
+      </c>
+      <c r="H75" t="s">
+        <v>32</v>
+      </c>
+      <c r="I75" t="s">
+        <v>33</v>
+      </c>
+      <c r="J75" t="s">
+        <v>171</v>
+      </c>
+      <c r="K75" t="s">
+        <v>35</v>
+      </c>
+      <c r="L75" t="s">
+        <v>36</v>
+      </c>
+      <c r="M75">
+        <v>18525</v>
+      </c>
+      <c r="N75">
+        <v>18499</v>
+      </c>
+      <c r="O75">
+        <v>70</v>
+      </c>
+      <c r="P75" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q75">
+        <v>0</v>
+      </c>
+      <c r="R75">
+        <v>0</v>
+      </c>
+      <c r="S75">
+        <v>0</v>
+      </c>
+      <c r="T75">
+        <v>0</v>
+      </c>
+      <c r="U75">
+        <v>70</v>
+      </c>
+      <c r="V75">
+        <v>47.46</v>
+      </c>
+      <c r="W75" t="s">
+        <v>347</v>
+      </c>
+      <c r="X75" t="s">
+        <v>348</v>
+      </c>
+      <c r="Y75" t="s">
+        <v>349</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="76" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>26</v>
+      </c>
+      <c r="B76" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C76" t="s">
+        <v>167</v>
+      </c>
+      <c r="D76" t="s">
+        <v>168</v>
+      </c>
+      <c r="E76" t="s">
+        <v>351</v>
+      </c>
+      <c r="F76" t="s">
+        <v>352</v>
+      </c>
+      <c r="G76" t="s">
+        <v>31</v>
+      </c>
+      <c r="H76" t="s">
+        <v>32</v>
+      </c>
+      <c r="I76" t="s">
+        <v>33</v>
+      </c>
+      <c r="J76" t="s">
+        <v>171</v>
+      </c>
+      <c r="K76" t="s">
+        <v>35</v>
+      </c>
+      <c r="L76" t="s">
+        <v>36</v>
+      </c>
+      <c r="M76">
+        <v>18525</v>
+      </c>
+      <c r="N76">
+        <v>18499</v>
+      </c>
+      <c r="O76">
+        <v>130</v>
+      </c>
+      <c r="P76" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q76">
+        <v>0</v>
+      </c>
+      <c r="R76">
+        <v>0</v>
+      </c>
+      <c r="S76">
+        <v>0</v>
+      </c>
+      <c r="T76">
+        <v>0</v>
+      </c>
+      <c r="U76">
+        <v>130</v>
+      </c>
+      <c r="V76">
+        <v>47.46</v>
+      </c>
+      <c r="W76" t="s">
+        <v>353</v>
+      </c>
+      <c r="X76" t="s">
+        <v>354</v>
+      </c>
+      <c r="Y76" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="77" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>26</v>
+      </c>
+      <c r="B77" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C77" t="s">
+        <v>167</v>
+      </c>
+      <c r="D77" t="s">
+        <v>168</v>
+      </c>
+      <c r="E77" t="s">
+        <v>351</v>
+      </c>
+      <c r="F77" t="s">
+        <v>352</v>
+      </c>
+      <c r="G77" t="s">
+        <v>31</v>
+      </c>
+      <c r="H77" t="s">
+        <v>57</v>
+      </c>
+      <c r="I77" t="s">
+        <v>58</v>
+      </c>
+      <c r="J77" t="s">
+        <v>223</v>
+      </c>
+      <c r="K77" t="s">
+        <v>59</v>
+      </c>
+      <c r="L77" t="s">
+        <v>36</v>
+      </c>
+      <c r="M77">
+        <v>12600</v>
+      </c>
+      <c r="N77">
+        <v>11150</v>
+      </c>
+      <c r="O77">
+        <v>51</v>
+      </c>
+      <c r="P77" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q77">
+        <v>0</v>
+      </c>
+      <c r="R77">
+        <v>0</v>
+      </c>
+      <c r="S77">
+        <v>0</v>
+      </c>
+      <c r="T77">
+        <v>0</v>
+      </c>
+      <c r="U77">
+        <v>51</v>
+      </c>
+      <c r="V77">
+        <v>36.86</v>
+      </c>
+      <c r="W77" t="s">
+        <v>353</v>
+      </c>
+      <c r="X77" t="s">
+        <v>354</v>
+      </c>
+      <c r="Y77" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z77" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="78" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>26</v>
+      </c>
+      <c r="B78" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C78" t="s">
+        <v>167</v>
+      </c>
+      <c r="D78" t="s">
+        <v>168</v>
+      </c>
+      <c r="E78" t="s">
+        <v>351</v>
+      </c>
+      <c r="F78" t="s">
+        <v>352</v>
+      </c>
+      <c r="G78" t="s">
+        <v>31</v>
+      </c>
+      <c r="H78" t="s">
+        <v>69</v>
+      </c>
+      <c r="I78" t="s">
+        <v>70</v>
+      </c>
+      <c r="J78" t="s">
+        <v>224</v>
+      </c>
+      <c r="K78" t="s">
+        <v>72</v>
+      </c>
+      <c r="L78" t="s">
+        <v>36</v>
+      </c>
+      <c r="M78">
+        <v>37803</v>
+      </c>
+      <c r="N78">
+        <v>37608</v>
+      </c>
+      <c r="O78">
+        <v>8</v>
+      </c>
+      <c r="P78" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q78">
+        <v>0</v>
+      </c>
+      <c r="R78">
+        <v>0</v>
+      </c>
+      <c r="S78">
+        <v>0</v>
+      </c>
+      <c r="T78">
+        <v>0</v>
+      </c>
+      <c r="U78">
+        <v>8</v>
+      </c>
+      <c r="V78">
+        <v>29.4</v>
+      </c>
+      <c r="W78" t="s">
+        <v>353</v>
+      </c>
+      <c r="X78" t="s">
+        <v>354</v>
+      </c>
+      <c r="Y78" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z78" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="79" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>26</v>
+      </c>
+      <c r="B79" s="2">
+        <v>46085</v>
+      </c>
+      <c r="C79" t="s">
+        <v>356</v>
+      </c>
+      <c r="D79" t="s">
+        <v>357</v>
+      </c>
+      <c r="E79" t="s">
+        <v>358</v>
+      </c>
+      <c r="F79" t="s">
+        <v>359</v>
+      </c>
+      <c r="G79" t="s">
+        <v>31</v>
+      </c>
+      <c r="H79" t="s">
+        <v>150</v>
+      </c>
+      <c r="I79" t="s">
+        <v>151</v>
+      </c>
+      <c r="J79" t="s">
+        <v>360</v>
+      </c>
+      <c r="K79" t="s">
+        <v>153</v>
+      </c>
+      <c r="L79" t="s">
+        <v>36</v>
+      </c>
+      <c r="M79">
+        <v>1791</v>
+      </c>
+      <c r="N79">
+        <v>1745</v>
+      </c>
+      <c r="O79">
+        <v>1</v>
+      </c>
+      <c r="P79">
+        <v>1</v>
+      </c>
+      <c r="Q79">
+        <v>0</v>
+      </c>
+      <c r="R79">
+        <v>0</v>
+      </c>
+      <c r="S79">
+        <v>0</v>
+      </c>
+      <c r="T79">
+        <v>0</v>
+      </c>
+      <c r="U79">
+        <v>0</v>
+      </c>
+      <c r="V79">
+        <v>57.33</v>
+      </c>
+      <c r="W79" t="s">
+        <v>361</v>
+      </c>
+      <c r="X79" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y79" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="80" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>26</v>
+      </c>
+      <c r="B80" s="2">
+        <v>46085</v>
+      </c>
+      <c r="C80" t="s">
+        <v>362</v>
+      </c>
+      <c r="D80" t="s">
+        <v>363</v>
+      </c>
+      <c r="E80" t="s">
+        <v>364</v>
+      </c>
+      <c r="F80" t="s">
+        <v>365</v>
+      </c>
+      <c r="G80" t="s">
+        <v>31</v>
+      </c>
+      <c r="H80" t="s">
+        <v>57</v>
+      </c>
+      <c r="I80" t="s">
+        <v>58</v>
+      </c>
+      <c r="J80" t="s">
+        <v>37</v>
+      </c>
+      <c r="K80" t="s">
+        <v>59</v>
+      </c>
+      <c r="L80" t="s">
+        <v>36</v>
+      </c>
+      <c r="M80">
+        <v>12600</v>
+      </c>
+      <c r="N80">
+        <v>11150</v>
+      </c>
+      <c r="O80">
+        <v>1400</v>
+      </c>
+      <c r="P80">
+        <v>1400</v>
+      </c>
+      <c r="Q80">
+        <v>0</v>
+      </c>
+      <c r="R80">
+        <v>0</v>
+      </c>
+      <c r="S80">
+        <v>0</v>
+      </c>
+      <c r="T80">
+        <v>0</v>
+      </c>
+      <c r="U80">
+        <v>0</v>
+      </c>
+      <c r="V80">
+        <v>29.7</v>
+      </c>
+      <c r="W80" t="s">
+        <v>366</v>
+      </c>
+      <c r="X80" t="s">
+        <v>367</v>
+      </c>
+      <c r="Y80" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z80" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="81" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>369</v>
+      </c>
+      <c r="B81" s="2">
+        <v>46084</v>
+      </c>
+      <c r="C81" t="s">
+        <v>370</v>
+      </c>
+      <c r="D81" t="s">
+        <v>371</v>
+      </c>
+      <c r="E81" t="s">
+        <v>372</v>
+      </c>
+      <c r="F81" t="s">
+        <v>373</v>
+      </c>
+      <c r="G81" t="s">
+        <v>31</v>
+      </c>
+      <c r="H81" t="s">
+        <v>150</v>
+      </c>
+      <c r="I81" t="s">
+        <v>151</v>
+      </c>
+      <c r="J81" t="s">
+        <v>374</v>
+      </c>
+      <c r="K81" t="s">
+        <v>153</v>
+      </c>
+      <c r="L81" t="s">
+        <v>36</v>
+      </c>
+      <c r="M81">
+        <v>1791</v>
+      </c>
+      <c r="N81">
+        <v>1745</v>
+      </c>
+      <c r="O81">
+        <v>3</v>
+      </c>
+      <c r="P81">
+        <v>3</v>
+      </c>
+      <c r="Q81">
+        <v>0</v>
+      </c>
+      <c r="R81">
+        <v>0</v>
+      </c>
+      <c r="S81">
+        <v>0</v>
+      </c>
+      <c r="T81">
+        <v>0</v>
+      </c>
+      <c r="U81">
+        <v>0</v>
+      </c>
+      <c r="V81">
+        <v>57</v>
+      </c>
+      <c r="W81" t="s">
+        <v>375</v>
+      </c>
+      <c r="X81" t="s">
+        <v>376</v>
+      </c>
+      <c r="Y81" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="82" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>26</v>
+      </c>
+      <c r="B82" s="2">
+        <v>46083</v>
+      </c>
+      <c r="C82" t="s">
+        <v>176</v>
+      </c>
+      <c r="D82" t="s">
+        <v>177</v>
+      </c>
+      <c r="E82" t="s">
+        <v>378</v>
+      </c>
+      <c r="F82" t="s">
+        <v>379</v>
+      </c>
+      <c r="G82" t="s">
+        <v>31</v>
+      </c>
+      <c r="H82" t="s">
+        <v>150</v>
+      </c>
+      <c r="I82" t="s">
+        <v>151</v>
+      </c>
+      <c r="J82" t="s">
+        <v>37</v>
+      </c>
+      <c r="K82" t="s">
+        <v>153</v>
+      </c>
+      <c r="L82" t="s">
+        <v>36</v>
+      </c>
+      <c r="M82">
+        <v>1791</v>
+      </c>
+      <c r="N82">
+        <v>1745</v>
+      </c>
+      <c r="O82">
         <v>6</v>
       </c>
-      <c r="V57">
+      <c r="P82">
+        <v>6</v>
+      </c>
+      <c r="Q82">
+        <v>0</v>
+      </c>
+      <c r="R82">
+        <v>0</v>
+      </c>
+      <c r="S82">
+        <v>0</v>
+      </c>
+      <c r="T82">
+        <v>0</v>
+      </c>
+      <c r="U82">
+        <v>0</v>
+      </c>
+      <c r="V82">
         <v>57.33</v>
       </c>
-      <c r="W57" t="s">
-        <v>49</v>
-      </c>
-      <c r="X57" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y57" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z57" t="s">
-        <v>51</v>
+      <c r="W82" t="s">
+        <v>180</v>
+      </c>
+      <c r="X82" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y82" t="s">
+        <v>174</v>
+      </c>
+      <c r="Z82" t="s">
+        <v>182</v>
       </c>
     </row>
   </sheetData>

--- a/data/searchresults.xlsx
+++ b/data/searchresults.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f0ae25cf28fa736a/Projects/BIAutomations/shipment-schedule/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{61969EF7-9912-4B44-8214-4F1B6AE3D726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{49B723FC-73E1-442E-BC2B-F33DAA3DEA1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0B368942-8F3B-44B2-8BD1-9F04935E3B49}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FADD182A-E14B-492A-A9D2-85503BF46181}"/>
   </bookViews>
   <sheets>
     <sheet name="OPTSensiMedicalSalesOpenOrderR" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1311" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="333">
   <si>
     <t>Division</t>
   </si>
@@ -103,6 +103,51 @@
     <t>MD</t>
   </si>
   <si>
+    <t>201044</t>
+  </si>
+  <si>
+    <t>HSIC : HENRY SCHEIN, INC. - MD 201044</t>
+  </si>
+  <si>
+    <t>SO153848</t>
+  </si>
+  <si>
+    <t>25630040</t>
+  </si>
+  <si>
+    <t>SENSI MEDICAL</t>
+  </si>
+  <si>
+    <t>7871800000</t>
+  </si>
+  <si>
+    <t>20164394C</t>
+  </si>
+  <si>
+    <t>1431501</t>
+  </si>
+  <si>
+    <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>3701 Litsey Road</t>
+  </si>
+  <si>
+    <t>Fort Worth</t>
+  </si>
+  <si>
+    <t>TX</t>
+  </si>
+  <si>
+    <t>76177</t>
+  </si>
+  <si>
     <t>201052</t>
   </si>
   <si>
@@ -115,9 +160,6 @@
     <t>36936661</t>
   </si>
   <si>
-    <t>SENSI MEDICAL</t>
-  </si>
-  <si>
     <t>V7871800000</t>
   </si>
   <si>
@@ -130,21 +172,12 @@
     <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
   </si>
   <si>
-    <t>CA</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
     <t>20710 HEMPSTEAD ROAD</t>
   </si>
   <si>
     <t>HOUSTON</t>
   </si>
   <si>
-    <t>TX</t>
-  </si>
-  <si>
     <t>77065</t>
   </si>
   <si>
@@ -472,18 +505,9 @@
     <t>60727</t>
   </si>
   <si>
-    <t>7871800000</t>
-  </si>
-  <si>
-    <t>20164394C</t>
-  </si>
-  <si>
     <t>48741800000</t>
   </si>
   <si>
-    <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
-  </si>
-  <si>
     <t>8313 WEST PIERCE STREET, SUITE 100</t>
   </si>
   <si>
@@ -550,369 +574,267 @@
     <t>43162</t>
   </si>
   <si>
-    <t>209304</t>
-  </si>
-  <si>
-    <t>RGH Enterprises, Inc. dba Cardinal Health At-Home 209304</t>
-  </si>
-  <si>
-    <t>SO153643</t>
-  </si>
-  <si>
-    <t>1042653452</t>
-  </si>
-  <si>
-    <t>1810 Summit Commerce Pkwy</t>
-  </si>
-  <si>
-    <t>Twinsburg</t>
-  </si>
-  <si>
-    <t>44087</t>
-  </si>
-  <si>
-    <t>202040</t>
-  </si>
-  <si>
-    <t>CHS : CONCORDANCE HEALTHCARE SOLUTIONS, LLC 202040</t>
-  </si>
-  <si>
-    <t>SO153650</t>
-  </si>
-  <si>
-    <t>3584739</t>
-  </si>
-  <si>
-    <t>354866</t>
-  </si>
-  <si>
-    <t>500 INDUSTRIAL PARK DRIVE</t>
-  </si>
-  <si>
-    <t>SHELBYVILLE</t>
-  </si>
-  <si>
-    <t>46176</t>
-  </si>
-  <si>
-    <t>SO153651</t>
-  </si>
-  <si>
-    <t>3584740</t>
-  </si>
-  <si>
-    <t>1473 MOUNTAIN ROAD</t>
-  </si>
-  <si>
-    <t>ANDERSONVILLE</t>
+    <t>SO153478</t>
+  </si>
+  <si>
+    <t>4519685454</t>
+  </si>
+  <si>
+    <t>21111 E. 36TH DRIVE</t>
+  </si>
+  <si>
+    <t>AURORA</t>
+  </si>
+  <si>
+    <t>CO</t>
+  </si>
+  <si>
+    <t>80011</t>
+  </si>
+  <si>
+    <t>SO153491</t>
+  </si>
+  <si>
+    <t>4519685466</t>
+  </si>
+  <si>
+    <t>2200 Cornerstone Parkway, Suite 100</t>
+  </si>
+  <si>
+    <t>Grayslake</t>
+  </si>
+  <si>
+    <t>IL</t>
+  </si>
+  <si>
+    <t>60030</t>
+  </si>
+  <si>
+    <t>O-T7871800002</t>
+  </si>
+  <si>
+    <t>O-T871800002</t>
+  </si>
+  <si>
+    <t>SO153498</t>
+  </si>
+  <si>
+    <t>4519685473</t>
+  </si>
+  <si>
+    <t>SO153506</t>
+  </si>
+  <si>
+    <t>4519685481</t>
+  </si>
+  <si>
+    <t>O-T787180000H</t>
+  </si>
+  <si>
+    <t>264 SOUTH 5750 WEST</t>
+  </si>
+  <si>
+    <t>SALT LAKE CITY</t>
+  </si>
+  <si>
+    <t>UT</t>
+  </si>
+  <si>
+    <t>84104</t>
+  </si>
+  <si>
+    <t>SO153510</t>
+  </si>
+  <si>
+    <t>4519685485</t>
+  </si>
+  <si>
+    <t>1390 Sparrows Point BLVD Suite 700</t>
+  </si>
+  <si>
+    <t>Edgemere</t>
+  </si>
+  <si>
+    <t>21219</t>
+  </si>
+  <si>
+    <t>SO153482</t>
+  </si>
+  <si>
+    <t>4519685457</t>
+  </si>
+  <si>
+    <t>1401 N. UNIVERSAL AVE.</t>
+  </si>
+  <si>
+    <t>SO153485</t>
+  </si>
+  <si>
+    <t>4519685460</t>
+  </si>
+  <si>
+    <t>13115 BROCKTON LANE N</t>
+  </si>
+  <si>
+    <t>ROGERS</t>
+  </si>
+  <si>
+    <t>55374</t>
+  </si>
+  <si>
+    <t>SO153497</t>
+  </si>
+  <si>
+    <t>4519685472</t>
+  </si>
+  <si>
+    <t>81 CAMPANELLI DRIVE</t>
+  </si>
+  <si>
+    <t>UXBRIDGE</t>
+  </si>
+  <si>
+    <t>MA</t>
+  </si>
+  <si>
+    <t>01569</t>
+  </si>
+  <si>
+    <t>SO153477</t>
+  </si>
+  <si>
+    <t>4519685453</t>
+  </si>
+  <si>
+    <t>1 MEDLINE DRIVE, SUITE 100</t>
+  </si>
+  <si>
+    <t>WILMER</t>
+  </si>
+  <si>
+    <t>75172</t>
+  </si>
+  <si>
+    <t>SO153489</t>
+  </si>
+  <si>
+    <t>4519685464</t>
+  </si>
+  <si>
+    <t>36445 VAN BORN ROAD</t>
+  </si>
+  <si>
+    <t>SO153502</t>
+  </si>
+  <si>
+    <t>4519685477</t>
+  </si>
+  <si>
+    <t>8787 W BUCKEYE ROAD</t>
+  </si>
+  <si>
+    <t>SO153483</t>
+  </si>
+  <si>
+    <t>4519685458</t>
+  </si>
+  <si>
+    <t>92 SOUTHEAST 223rd AVENUE</t>
+  </si>
+  <si>
+    <t>GRESHAM</t>
+  </si>
+  <si>
+    <t>97030</t>
+  </si>
+  <si>
+    <t>SO153484</t>
+  </si>
+  <si>
+    <t>4519685459</t>
+  </si>
+  <si>
+    <t>735 COUNTY ROAD 4 EAST</t>
+  </si>
+  <si>
+    <t>PRATTVILLE</t>
+  </si>
+  <si>
+    <t>AL</t>
+  </si>
+  <si>
+    <t>36067</t>
+  </si>
+  <si>
+    <t>SO153486</t>
+  </si>
+  <si>
+    <t>4519685461</t>
+  </si>
+  <si>
+    <t>1900 MEADOWVILLE TECHNOLOGY</t>
+  </si>
+  <si>
+    <t>CHESTER</t>
+  </si>
+  <si>
+    <t>VA</t>
+  </si>
+  <si>
+    <t>23834</t>
+  </si>
+  <si>
+    <t>SO153487</t>
+  </si>
+  <si>
+    <t>4519685462</t>
+  </si>
+  <si>
+    <t>500 SHARKEY DRIVE</t>
+  </si>
+  <si>
+    <t>MAUMELLE</t>
+  </si>
+  <si>
+    <t>AR</t>
+  </si>
+  <si>
+    <t>72113</t>
+  </si>
+  <si>
+    <t>SO153488</t>
+  </si>
+  <si>
+    <t>4519685463</t>
+  </si>
+  <si>
+    <t>1989 TRANSIT WAY</t>
+  </si>
+  <si>
+    <t>BROCKPORT</t>
+  </si>
+  <si>
+    <t>NY</t>
+  </si>
+  <si>
+    <t>14420</t>
+  </si>
+  <si>
+    <t>SO153490</t>
+  </si>
+  <si>
+    <t>4519685465</t>
+  </si>
+  <si>
+    <t>60 ATHLETES WAY</t>
+  </si>
+  <si>
+    <t>MOUNT JULIET</t>
   </si>
   <si>
     <t>TN</t>
   </si>
   <si>
-    <t>37705</t>
-  </si>
-  <si>
-    <t>SO153652</t>
-  </si>
-  <si>
-    <t>3584741</t>
-  </si>
-  <si>
-    <t>354864</t>
-  </si>
-  <si>
-    <t>3625 PARK CIRCLE DRIVE</t>
-  </si>
-  <si>
-    <t>KALAMAZOO</t>
-  </si>
-  <si>
-    <t>49048</t>
-  </si>
-  <si>
-    <t>ASV</t>
-  </si>
-  <si>
-    <t>107001</t>
-  </si>
-  <si>
-    <t>BOUND TREE MEDICAL, LLC 107001</t>
-  </si>
-  <si>
-    <t>SO153444</t>
-  </si>
-  <si>
-    <t>B1310223595-10</t>
-  </si>
-  <si>
-    <t>1033 COLLINS RD STE A</t>
-  </si>
-  <si>
-    <t>Greenwood</t>
-  </si>
-  <si>
-    <t>46143</t>
-  </si>
-  <si>
-    <t>SO153478</t>
-  </si>
-  <si>
-    <t>4519685454</t>
-  </si>
-  <si>
-    <t>21111 E. 36TH DRIVE</t>
-  </si>
-  <si>
-    <t>AURORA</t>
-  </si>
-  <si>
-    <t>CO</t>
-  </si>
-  <si>
-    <t>80011</t>
-  </si>
-  <si>
-    <t>SO153491</t>
-  </si>
-  <si>
-    <t>4519685466</t>
-  </si>
-  <si>
-    <t>2200 Cornerstone Parkway, Suite 100</t>
-  </si>
-  <si>
-    <t>Grayslake</t>
-  </si>
-  <si>
-    <t>IL</t>
-  </si>
-  <si>
-    <t>60030</t>
-  </si>
-  <si>
-    <t>O-T7871800002</t>
-  </si>
-  <si>
-    <t>O-T871800002</t>
-  </si>
-  <si>
-    <t>SO153498</t>
-  </si>
-  <si>
-    <t>4519685473</t>
-  </si>
-  <si>
-    <t>SO153506</t>
-  </si>
-  <si>
-    <t>4519685481</t>
-  </si>
-  <si>
-    <t>O-T787180000H</t>
-  </si>
-  <si>
-    <t>264 SOUTH 5750 WEST</t>
-  </si>
-  <si>
-    <t>SALT LAKE CITY</t>
-  </si>
-  <si>
-    <t>UT</t>
-  </si>
-  <si>
-    <t>84104</t>
-  </si>
-  <si>
-    <t>SO153510</t>
-  </si>
-  <si>
-    <t>4519685485</t>
-  </si>
-  <si>
-    <t>1390 Sparrows Point BLVD Suite 700</t>
-  </si>
-  <si>
-    <t>Edgemere</t>
-  </si>
-  <si>
-    <t>21219</t>
-  </si>
-  <si>
-    <t>SO153482</t>
-  </si>
-  <si>
-    <t>4519685457</t>
-  </si>
-  <si>
-    <t>1401 N. UNIVERSAL AVE.</t>
-  </si>
-  <si>
-    <t>SO153485</t>
-  </si>
-  <si>
-    <t>4519685460</t>
-  </si>
-  <si>
-    <t>13115 BROCKTON LANE N</t>
-  </si>
-  <si>
-    <t>ROGERS</t>
-  </si>
-  <si>
-    <t>55374</t>
-  </si>
-  <si>
-    <t>SO153497</t>
-  </si>
-  <si>
-    <t>4519685472</t>
-  </si>
-  <si>
-    <t>81 CAMPANELLI DRIVE</t>
-  </si>
-  <si>
-    <t>UXBRIDGE</t>
-  </si>
-  <si>
-    <t>MA</t>
-  </si>
-  <si>
-    <t>01569</t>
-  </si>
-  <si>
-    <t>SO153477</t>
-  </si>
-  <si>
-    <t>4519685453</t>
-  </si>
-  <si>
-    <t>1 MEDLINE DRIVE, SUITE 100</t>
-  </si>
-  <si>
-    <t>WILMER</t>
-  </si>
-  <si>
-    <t>75172</t>
-  </si>
-  <si>
-    <t>SO153489</t>
-  </si>
-  <si>
-    <t>4519685464</t>
-  </si>
-  <si>
-    <t>36445 VAN BORN ROAD</t>
-  </si>
-  <si>
-    <t>SO153502</t>
-  </si>
-  <si>
-    <t>4519685477</t>
-  </si>
-  <si>
-    <t>8787 W BUCKEYE ROAD</t>
-  </si>
-  <si>
-    <t>SO153483</t>
-  </si>
-  <si>
-    <t>4519685458</t>
-  </si>
-  <si>
-    <t>92 SOUTHEAST 223rd AVENUE</t>
-  </si>
-  <si>
-    <t>GRESHAM</t>
-  </si>
-  <si>
-    <t>97030</t>
-  </si>
-  <si>
-    <t>SO153484</t>
-  </si>
-  <si>
-    <t>4519685459</t>
-  </si>
-  <si>
-    <t>735 COUNTY ROAD 4 EAST</t>
-  </si>
-  <si>
-    <t>PRATTVILLE</t>
-  </si>
-  <si>
-    <t>AL</t>
-  </si>
-  <si>
-    <t>36067</t>
-  </si>
-  <si>
-    <t>SO153486</t>
-  </si>
-  <si>
-    <t>4519685461</t>
-  </si>
-  <si>
-    <t>1900 MEADOWVILLE TECHNOLOGY</t>
-  </si>
-  <si>
-    <t>CHESTER</t>
-  </si>
-  <si>
-    <t>VA</t>
-  </si>
-  <si>
-    <t>23834</t>
-  </si>
-  <si>
-    <t>SO153487</t>
-  </si>
-  <si>
-    <t>4519685462</t>
-  </si>
-  <si>
-    <t>500 SHARKEY DRIVE</t>
-  </si>
-  <si>
-    <t>MAUMELLE</t>
-  </si>
-  <si>
-    <t>AR</t>
-  </si>
-  <si>
-    <t>72113</t>
-  </si>
-  <si>
-    <t>SO153488</t>
-  </si>
-  <si>
-    <t>4519685463</t>
-  </si>
-  <si>
-    <t>1989 TRANSIT WAY</t>
-  </si>
-  <si>
-    <t>BROCKPORT</t>
-  </si>
-  <si>
-    <t>NY</t>
-  </si>
-  <si>
-    <t>14420</t>
-  </si>
-  <si>
-    <t>SO153490</t>
-  </si>
-  <si>
-    <t>4519685465</t>
-  </si>
-  <si>
-    <t>60 ATHLETES WAY</t>
-  </si>
-  <si>
-    <t>MOUNT JULIET</t>
-  </si>
-  <si>
     <t>37122</t>
   </si>
   <si>
@@ -1090,76 +1012,13 @@
     <t>21903</t>
   </si>
   <si>
-    <t>201044</t>
-  </si>
-  <si>
-    <t>HSIC : HENRY SCHEIN, INC. - MD 201044</t>
-  </si>
-  <si>
     <t>SO153373</t>
   </si>
   <si>
     <t>25605511</t>
   </si>
   <si>
-    <t>1431501</t>
-  </si>
-  <si>
     <t>8691 JESSE B SMITH COURT</t>
-  </si>
-  <si>
-    <t>209207</t>
-  </si>
-  <si>
-    <t>BANNER HEALTH 209207</t>
-  </si>
-  <si>
-    <t>SO153418</t>
-  </si>
-  <si>
-    <t>355546-0-101</t>
-  </si>
-  <si>
-    <t>7300 W DETROIT ST</t>
-  </si>
-  <si>
-    <t>Chandler</t>
-  </si>
-  <si>
-    <t>85226</t>
-  </si>
-  <si>
-    <t>OGS</t>
-  </si>
-  <si>
-    <t>301000</t>
-  </si>
-  <si>
-    <t>CAH-OGS : CARDINAL - OGS 301000</t>
-  </si>
-  <si>
-    <t>SO153295</t>
-  </si>
-  <si>
-    <t>4533257662</t>
-  </si>
-  <si>
-    <t>871800000B</t>
-  </si>
-  <si>
-    <t>7611 BRANDON WOODS BLVD</t>
-  </si>
-  <si>
-    <t>BALTIMORE</t>
-  </si>
-  <si>
-    <t>21226</t>
-  </si>
-  <si>
-    <t>SO153164</t>
-  </si>
-  <si>
-    <t>1042370490</t>
   </si>
 </sst>
 </file>
@@ -2031,8 +1890,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E77F3A3-7010-4EAD-87B8-02E76E752B7D}">
-  <dimension ref="A1:Z82"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B4A9030-943E-4D7A-82A8-12DD910A455E}">
+  <dimension ref="A1:Z74"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.2">
@@ -2120,7 +1979,7 @@
         <v>26</v>
       </c>
       <c r="B2" s="2">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="C2" t="s">
         <v>27</v>
@@ -2153,10 +2012,10 @@
         <v>36</v>
       </c>
       <c r="M2">
-        <v>18525</v>
+        <v>1746</v>
       </c>
       <c r="N2">
-        <v>18499</v>
+        <v>1633</v>
       </c>
       <c r="O2">
         <v>1</v>
@@ -2180,7 +2039,7 @@
         <v>1</v>
       </c>
       <c r="V2">
-        <v>47.46</v>
+        <v>57.33</v>
       </c>
       <c r="W2" t="s">
         <v>38</v>
@@ -2203,46 +2062,46 @@
         <v>46091</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="E3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G3" t="s">
         <v>31</v>
       </c>
       <c r="H3" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="I3" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="J3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="K3" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="L3" t="s">
         <v>36</v>
       </c>
       <c r="M3">
-        <v>18525</v>
+        <v>18591</v>
       </c>
       <c r="N3">
-        <v>18499</v>
+        <v>18428</v>
       </c>
       <c r="O3">
         <v>1</v>
       </c>
-      <c r="P3" t="s">
-        <v>37</v>
+      <c r="P3">
+        <v>1</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -2257,22 +2116,22 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3">
         <v>47.46</v>
       </c>
       <c r="W3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="X3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="Y3" t="s">
         <v>40</v>
       </c>
       <c r="Z3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.2">
@@ -2283,46 +2142,46 @@
         <v>46091</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="E4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G4" t="s">
         <v>31</v>
       </c>
       <c r="H4" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="I4" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="J4" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="K4" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="L4" t="s">
         <v>36</v>
       </c>
       <c r="M4">
-        <v>18525</v>
+        <v>18591</v>
       </c>
       <c r="N4">
-        <v>18499</v>
+        <v>18428</v>
       </c>
       <c r="O4">
         <v>1</v>
       </c>
-      <c r="P4" t="s">
-        <v>37</v>
+      <c r="P4">
+        <v>1</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -2337,22 +2196,22 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4">
         <v>47.46</v>
       </c>
       <c r="W4" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="X4" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="Y4" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="Z4" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.2">
@@ -2363,46 +2222,46 @@
         <v>46091</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G5" t="s">
         <v>31</v>
       </c>
       <c r="H5" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="I5" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="J5" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="K5" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="L5" t="s">
         <v>36</v>
       </c>
       <c r="M5">
-        <v>12600</v>
+        <v>18591</v>
       </c>
       <c r="N5">
-        <v>11150</v>
+        <v>18428</v>
       </c>
       <c r="O5">
         <v>1</v>
       </c>
-      <c r="P5" t="s">
-        <v>37</v>
+      <c r="P5">
+        <v>1</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -2417,10 +2276,10 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>36.86</v>
+        <v>47.46</v>
       </c>
       <c r="W5" t="s">
         <v>60</v>
@@ -2429,10 +2288,10 @@
         <v>61</v>
       </c>
       <c r="Y5" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="Z5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.2">
@@ -2443,43 +2302,43 @@
         <v>46091</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="E6" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F6" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G6" t="s">
         <v>31</v>
       </c>
       <c r="H6" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="I6" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="J6" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="K6" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="L6" t="s">
         <v>36</v>
       </c>
       <c r="M6">
-        <v>18525</v>
+        <v>11274</v>
       </c>
       <c r="N6">
-        <v>18499</v>
+        <v>10669</v>
       </c>
       <c r="O6">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="P6" t="s">
         <v>37</v>
@@ -2497,22 +2356,22 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="V6">
-        <v>47.46</v>
+        <v>36.86</v>
       </c>
       <c r="W6" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="X6" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Y6" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="Z6" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.2">
@@ -2523,46 +2382,46 @@
         <v>46091</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="E7" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="F7" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="G7" t="s">
         <v>31</v>
       </c>
       <c r="H7" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="I7" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="J7" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="K7" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="L7" t="s">
         <v>36</v>
       </c>
       <c r="M7">
-        <v>37803</v>
+        <v>18591</v>
       </c>
       <c r="N7">
-        <v>37608</v>
+        <v>18428</v>
       </c>
       <c r="O7">
-        <v>20</v>
-      </c>
-      <c r="P7" t="s">
-        <v>37</v>
+        <v>19</v>
+      </c>
+      <c r="P7">
+        <v>19</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -2577,22 +2436,22 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="V7">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W7" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="X7" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="Y7" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="Z7" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.2">
@@ -2603,46 +2462,46 @@
         <v>46091</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" t="s">
         <v>74</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>75</v>
-      </c>
-      <c r="F8" t="s">
-        <v>76</v>
       </c>
       <c r="G8" t="s">
         <v>31</v>
       </c>
       <c r="H8" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="I8" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="J8" t="s">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="K8" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="L8" t="s">
         <v>36</v>
       </c>
       <c r="M8">
-        <v>37803</v>
+        <v>37748</v>
       </c>
       <c r="N8">
-        <v>37608</v>
+        <v>35884</v>
       </c>
       <c r="O8">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="P8">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -2663,16 +2522,16 @@
         <v>29.4</v>
       </c>
       <c r="W8" t="s">
+        <v>76</v>
+      </c>
+      <c r="X8" t="s">
         <v>77</v>
       </c>
-      <c r="X8" t="s">
+      <c r="Y8" t="s">
         <v>78</v>
       </c>
-      <c r="Y8" t="s">
+      <c r="Z8" t="s">
         <v>79</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.2">
@@ -2683,46 +2542,46 @@
         <v>46091</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E9" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F9" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G9" t="s">
         <v>31</v>
       </c>
       <c r="H9" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="I9" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="J9" t="s">
         <v>37</v>
       </c>
       <c r="K9" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="L9" t="s">
         <v>36</v>
       </c>
       <c r="M9">
-        <v>37803</v>
+        <v>37748</v>
       </c>
       <c r="N9">
-        <v>37608</v>
+        <v>35884</v>
       </c>
       <c r="O9">
-        <v>791</v>
-      </c>
-      <c r="P9" t="s">
-        <v>37</v>
+        <v>140</v>
+      </c>
+      <c r="P9">
+        <v>140</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -2737,22 +2596,22 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>791</v>
+        <v>0</v>
       </c>
       <c r="V9">
         <v>29.4</v>
       </c>
       <c r="W9" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="X9" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Y9" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="Z9" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.2">
@@ -2763,76 +2622,76 @@
         <v>46091</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D10" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E10" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F10" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G10" t="s">
         <v>31</v>
       </c>
       <c r="H10" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="I10" t="s">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="J10" t="s">
-        <v>93</v>
+        <v>37</v>
       </c>
       <c r="K10" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="L10" t="s">
         <v>36</v>
       </c>
       <c r="M10">
-        <v>18525</v>
+        <v>37748</v>
       </c>
       <c r="N10">
-        <v>18499</v>
+        <v>35884</v>
       </c>
       <c r="O10">
+        <v>791</v>
+      </c>
+      <c r="P10">
+        <v>791</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>29.4</v>
+      </c>
+      <c r="W10" t="s">
+        <v>96</v>
+      </c>
+      <c r="X10" t="s">
         <v>97</v>
       </c>
-      <c r="P10" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>97</v>
-      </c>
-      <c r="V10">
-        <v>47.46</v>
-      </c>
-      <c r="W10" t="s">
-        <v>94</v>
-      </c>
-      <c r="X10" t="s">
-        <v>95</v>
-      </c>
       <c r="Y10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Z10" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.2">
@@ -2843,46 +2702,46 @@
         <v>46091</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D11" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="E11" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="F11" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="G11" t="s">
         <v>31</v>
       </c>
       <c r="H11" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="I11" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="J11" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="K11" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="L11" t="s">
         <v>36</v>
       </c>
       <c r="M11">
-        <v>37803</v>
+        <v>18591</v>
       </c>
       <c r="N11">
-        <v>37608</v>
+        <v>18428</v>
       </c>
       <c r="O11">
-        <v>80</v>
-      </c>
-      <c r="P11" t="s">
-        <v>37</v>
+        <v>97</v>
+      </c>
+      <c r="P11">
+        <v>97</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2897,22 +2756,22 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="V11">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W11" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="X11" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="Y11" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="Z11" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.2">
@@ -2923,46 +2782,46 @@
         <v>46091</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="E12" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F12" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G12" t="s">
         <v>31</v>
       </c>
       <c r="H12" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="I12" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="J12" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="K12" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="L12" t="s">
         <v>36</v>
       </c>
       <c r="M12">
-        <v>12600</v>
+        <v>37748</v>
       </c>
       <c r="N12">
-        <v>11150</v>
+        <v>35884</v>
       </c>
       <c r="O12">
-        <v>24</v>
-      </c>
-      <c r="P12" t="s">
-        <v>37</v>
+        <v>80</v>
+      </c>
+      <c r="P12">
+        <v>80</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2977,22 +2836,22 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>36.8598</v>
+        <v>29.4</v>
       </c>
       <c r="W12" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="X12" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="Y12" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="Z12" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.2">
@@ -3003,46 +2862,46 @@
         <v>46091</v>
       </c>
       <c r="C13" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="E13" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="F13" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="G13" t="s">
         <v>31</v>
       </c>
       <c r="H13" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="I13" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="J13" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="K13" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="L13" t="s">
         <v>36</v>
       </c>
       <c r="M13">
-        <v>18525</v>
+        <v>11274</v>
       </c>
       <c r="N13">
-        <v>18499</v>
+        <v>10669</v>
       </c>
       <c r="O13">
-        <v>1</v>
-      </c>
-      <c r="P13" t="s">
-        <v>37</v>
+        <v>24</v>
+      </c>
+      <c r="P13">
+        <v>24</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -3057,22 +2916,22 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13">
-        <v>47.46</v>
+        <v>36.8598</v>
       </c>
       <c r="W13" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="X13" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="Y13" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="Z13" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.2">
@@ -3083,46 +2942,46 @@
         <v>46091</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D14" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="E14" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="F14" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="G14" t="s">
         <v>31</v>
       </c>
       <c r="H14" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="I14" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="J14" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="K14" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="L14" t="s">
         <v>36</v>
       </c>
       <c r="M14">
-        <v>37803</v>
+        <v>18591</v>
       </c>
       <c r="N14">
-        <v>37608</v>
+        <v>18428</v>
       </c>
       <c r="O14">
-        <v>231</v>
-      </c>
-      <c r="P14" t="s">
-        <v>37</v>
+        <v>1</v>
+      </c>
+      <c r="P14">
+        <v>1</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -3137,22 +2996,22 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>231</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W14" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="X14" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="Y14" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="Z14" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.2">
@@ -3163,46 +3022,46 @@
         <v>46091</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="E15" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="F15" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G15" t="s">
         <v>31</v>
       </c>
       <c r="H15" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="I15" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="J15" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="K15" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="L15" t="s">
         <v>36</v>
       </c>
       <c r="M15">
-        <v>37803</v>
+        <v>37748</v>
       </c>
       <c r="N15">
-        <v>37608</v>
+        <v>35884</v>
       </c>
       <c r="O15">
-        <v>42</v>
-      </c>
-      <c r="P15" t="s">
-        <v>37</v>
+        <v>231</v>
+      </c>
+      <c r="P15">
+        <v>231</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -3217,22 +3076,22 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="V15">
         <v>29.4</v>
       </c>
       <c r="W15" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="X15" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="Y15" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="Z15" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.2">
@@ -3243,46 +3102,46 @@
         <v>46091</v>
       </c>
       <c r="C16" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="E16" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="F16" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="G16" t="s">
         <v>31</v>
       </c>
       <c r="H16" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="I16" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="J16" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="K16" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="L16" t="s">
         <v>36</v>
       </c>
       <c r="M16">
-        <v>12600</v>
+        <v>37748</v>
       </c>
       <c r="N16">
-        <v>11150</v>
+        <v>35884</v>
       </c>
       <c r="O16">
-        <v>274</v>
-      </c>
-      <c r="P16" t="s">
-        <v>37</v>
+        <v>42</v>
+      </c>
+      <c r="P16">
+        <v>42</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3297,22 +3156,22 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>274</v>
+        <v>0</v>
       </c>
       <c r="V16">
-        <v>36.8598</v>
+        <v>29.4</v>
       </c>
       <c r="W16" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="X16" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="Y16" t="s">
-        <v>79</v>
+        <v>121</v>
       </c>
       <c r="Z16" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.2">
@@ -3323,46 +3182,46 @@
         <v>46091</v>
       </c>
       <c r="C17" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D17" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="E17" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F17" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="G17" t="s">
         <v>31</v>
       </c>
       <c r="H17" t="s">
+        <v>68</v>
+      </c>
+      <c r="I17" t="s">
         <v>69</v>
       </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
+        <v>112</v>
+      </c>
+      <c r="K17" t="s">
         <v>70</v>
-      </c>
-      <c r="J17" t="s">
-        <v>98</v>
-      </c>
-      <c r="K17" t="s">
-        <v>72</v>
       </c>
       <c r="L17" t="s">
         <v>36</v>
       </c>
       <c r="M17">
-        <v>37803</v>
+        <v>11274</v>
       </c>
       <c r="N17">
-        <v>37608</v>
+        <v>10669</v>
       </c>
       <c r="O17">
-        <v>31</v>
-      </c>
-      <c r="P17" t="s">
-        <v>37</v>
+        <v>274</v>
+      </c>
+      <c r="P17">
+        <v>274</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3377,22 +3236,22 @@
         <v>0</v>
       </c>
       <c r="U17">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="V17">
-        <v>29.4</v>
+        <v>36.8598</v>
       </c>
       <c r="W17" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="X17" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="Y17" t="s">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="Z17" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.2">
@@ -3403,46 +3262,46 @@
         <v>46091</v>
       </c>
       <c r="C18" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D18" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="E18" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F18" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="G18" t="s">
         <v>31</v>
       </c>
       <c r="H18" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="I18" t="s">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="J18" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="K18" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="L18" t="s">
         <v>36</v>
       </c>
       <c r="M18">
-        <v>18525</v>
+        <v>37748</v>
       </c>
       <c r="N18">
-        <v>18499</v>
+        <v>35884</v>
       </c>
       <c r="O18">
-        <v>11</v>
-      </c>
-      <c r="P18" t="s">
-        <v>37</v>
+        <v>31</v>
+      </c>
+      <c r="P18">
+        <v>31</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3457,22 +3316,22 @@
         <v>0</v>
       </c>
       <c r="U18">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="V18">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W18" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="X18" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="Y18" t="s">
-        <v>104</v>
+        <v>26</v>
       </c>
       <c r="Z18" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.2">
@@ -3483,46 +3342,46 @@
         <v>46091</v>
       </c>
       <c r="C19" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D19" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="E19" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="F19" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="G19" t="s">
         <v>31</v>
       </c>
       <c r="H19" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="I19" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="J19" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="K19" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="L19" t="s">
         <v>36</v>
       </c>
       <c r="M19">
-        <v>18525</v>
+        <v>18591</v>
       </c>
       <c r="N19">
-        <v>18499</v>
+        <v>18428</v>
       </c>
       <c r="O19">
-        <v>23</v>
-      </c>
-      <c r="P19" t="s">
-        <v>37</v>
+        <v>11</v>
+      </c>
+      <c r="P19">
+        <v>11</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3537,22 +3396,22 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="V19">
         <v>47.46</v>
       </c>
       <c r="W19" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="X19" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="Y19" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="Z19" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.2">
@@ -3563,46 +3422,46 @@
         <v>46091</v>
       </c>
       <c r="C20" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D20" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="E20" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="F20" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="G20" t="s">
         <v>31</v>
       </c>
       <c r="H20" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="I20" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="J20" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="K20" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="L20" t="s">
         <v>36</v>
       </c>
       <c r="M20">
-        <v>37803</v>
+        <v>18591</v>
       </c>
       <c r="N20">
-        <v>37608</v>
+        <v>18428</v>
       </c>
       <c r="O20">
-        <v>158</v>
-      </c>
-      <c r="P20" t="s">
-        <v>37</v>
+        <v>23</v>
+      </c>
+      <c r="P20">
+        <v>23</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3617,22 +3476,22 @@
         <v>0</v>
       </c>
       <c r="U20">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="V20">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W20" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="X20" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="Y20" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="Z20" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.2">
@@ -3643,46 +3502,46 @@
         <v>46091</v>
       </c>
       <c r="C21" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D21" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="E21" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="F21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="G21" t="s">
         <v>31</v>
       </c>
       <c r="H21" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="I21" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="J21" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="K21" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="L21" t="s">
         <v>36</v>
       </c>
       <c r="M21">
-        <v>12600</v>
+        <v>37748</v>
       </c>
       <c r="N21">
-        <v>11150</v>
+        <v>35884</v>
       </c>
       <c r="O21">
-        <v>98</v>
-      </c>
-      <c r="P21" t="s">
-        <v>37</v>
+        <v>158</v>
+      </c>
+      <c r="P21">
+        <v>158</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3697,22 +3556,22 @@
         <v>0</v>
       </c>
       <c r="U21">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="V21">
-        <v>36.8598</v>
+        <v>29.4</v>
       </c>
       <c r="W21" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="X21" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="Y21" t="s">
-        <v>40</v>
+        <v>142</v>
       </c>
       <c r="Z21" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.2">
@@ -3723,46 +3582,46 @@
         <v>46091</v>
       </c>
       <c r="C22" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D22" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="E22" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="F22" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="G22" t="s">
         <v>31</v>
       </c>
       <c r="H22" t="s">
+        <v>68</v>
+      </c>
+      <c r="I22" t="s">
         <v>69</v>
       </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
+        <v>112</v>
+      </c>
+      <c r="K22" t="s">
         <v>70</v>
-      </c>
-      <c r="J22" t="s">
-        <v>98</v>
-      </c>
-      <c r="K22" t="s">
-        <v>72</v>
       </c>
       <c r="L22" t="s">
         <v>36</v>
       </c>
       <c r="M22">
-        <v>37803</v>
+        <v>11274</v>
       </c>
       <c r="N22">
-        <v>37608</v>
+        <v>10669</v>
       </c>
       <c r="O22">
-        <v>362</v>
-      </c>
-      <c r="P22" t="s">
-        <v>37</v>
+        <v>98</v>
+      </c>
+      <c r="P22">
+        <v>98</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -3777,22 +3636,22 @@
         <v>0</v>
       </c>
       <c r="U22">
-        <v>362</v>
+        <v>0</v>
       </c>
       <c r="V22">
-        <v>29.4</v>
+        <v>36.8598</v>
       </c>
       <c r="W22" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="X22" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="Y22" t="s">
-        <v>104</v>
+        <v>40</v>
       </c>
       <c r="Z22" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.2">
@@ -3803,46 +3662,46 @@
         <v>46091</v>
       </c>
       <c r="C23" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D23" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="E23" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="F23" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="G23" t="s">
         <v>31</v>
       </c>
       <c r="H23" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="I23" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="J23" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="K23" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="L23" t="s">
         <v>36</v>
       </c>
       <c r="M23">
-        <v>12600</v>
+        <v>37748</v>
       </c>
       <c r="N23">
-        <v>11150</v>
+        <v>35884</v>
       </c>
       <c r="O23">
-        <v>39</v>
-      </c>
-      <c r="P23" t="s">
-        <v>37</v>
+        <v>362</v>
+      </c>
+      <c r="P23">
+        <v>362</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -3857,22 +3716,22 @@
         <v>0</v>
       </c>
       <c r="U23">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="V23">
-        <v>36.8598</v>
+        <v>29.4</v>
       </c>
       <c r="W23" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="X23" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="Y23" t="s">
-        <v>67</v>
+        <v>115</v>
       </c>
       <c r="Z23" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.2">
@@ -3883,46 +3742,46 @@
         <v>46091</v>
       </c>
       <c r="C24" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D24" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="E24" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="F24" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="G24" t="s">
         <v>31</v>
       </c>
       <c r="H24" t="s">
-        <v>150</v>
+        <v>68</v>
       </c>
       <c r="I24" t="s">
-        <v>151</v>
+        <v>69</v>
       </c>
       <c r="J24" t="s">
-        <v>152</v>
+        <v>112</v>
       </c>
       <c r="K24" t="s">
-        <v>153</v>
+        <v>70</v>
       </c>
       <c r="L24" t="s">
         <v>36</v>
       </c>
       <c r="M24">
-        <v>1791</v>
+        <v>11274</v>
       </c>
       <c r="N24">
-        <v>1745</v>
+        <v>10669</v>
       </c>
       <c r="O24">
-        <v>112</v>
-      </c>
-      <c r="P24" t="s">
-        <v>37</v>
+        <v>39</v>
+      </c>
+      <c r="P24">
+        <v>39</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -3937,22 +3796,22 @@
         <v>0</v>
       </c>
       <c r="U24">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="V24">
-        <v>57.33</v>
+        <v>36.8598</v>
       </c>
       <c r="W24" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="X24" t="s">
-        <v>50</v>
+        <v>157</v>
       </c>
       <c r="Y24" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="Z24" t="s">
-        <v>52</v>
+        <v>158</v>
       </c>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.2">
@@ -3963,16 +3822,16 @@
         <v>46091</v>
       </c>
       <c r="C25" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D25" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="E25" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="F25" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="G25" t="s">
         <v>31</v>
@@ -3984,7 +3843,7 @@
         <v>33</v>
       </c>
       <c r="J25" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="K25" t="s">
         <v>35</v>
@@ -3993,16 +3852,16 @@
         <v>36</v>
       </c>
       <c r="M25">
-        <v>18525</v>
+        <v>1746</v>
       </c>
       <c r="N25">
-        <v>18499</v>
+        <v>1633</v>
       </c>
       <c r="O25">
-        <v>9</v>
-      </c>
-      <c r="P25" t="s">
-        <v>37</v>
+        <v>112</v>
+      </c>
+      <c r="P25">
+        <v>112</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4017,22 +3876,22 @@
         <v>0</v>
       </c>
       <c r="U25">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="V25">
-        <v>47.46</v>
+        <v>57.33</v>
       </c>
       <c r="W25" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="X25" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="Y25" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="Z25" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.2">
@@ -4043,46 +3902,46 @@
         <v>46091</v>
       </c>
       <c r="C26" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D26" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="E26" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="F26" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="G26" t="s">
         <v>31</v>
       </c>
       <c r="H26" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="I26" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="J26" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="K26" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="L26" t="s">
         <v>36</v>
       </c>
       <c r="M26">
-        <v>37803</v>
+        <v>18591</v>
       </c>
       <c r="N26">
-        <v>37608</v>
+        <v>18428</v>
       </c>
       <c r="O26">
         <v>9</v>
       </c>
-      <c r="P26" t="s">
-        <v>37</v>
+      <c r="P26">
+        <v>9</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4097,22 +3956,22 @@
         <v>0</v>
       </c>
       <c r="U26">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="V26">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W26" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="X26" t="s">
-        <v>158</v>
+        <v>61</v>
       </c>
       <c r="Y26" t="s">
-        <v>159</v>
+        <v>62</v>
       </c>
       <c r="Z26" t="s">
-        <v>160</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" spans="1:26" x14ac:dyDescent="0.2">
@@ -4123,46 +3982,46 @@
         <v>46091</v>
       </c>
       <c r="C27" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D27" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="E27" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F27" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G27" t="s">
         <v>31</v>
       </c>
       <c r="H27" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="I27" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="J27" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="K27" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="L27" t="s">
         <v>36</v>
       </c>
       <c r="M27">
-        <v>12600</v>
+        <v>37748</v>
       </c>
       <c r="N27">
-        <v>11150</v>
+        <v>35884</v>
       </c>
       <c r="O27">
-        <v>120</v>
-      </c>
-      <c r="P27" t="s">
-        <v>37</v>
+        <v>9</v>
+      </c>
+      <c r="P27">
+        <v>9</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4177,22 +4036,22 @@
         <v>0</v>
       </c>
       <c r="U27">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="V27">
-        <v>36.8598</v>
+        <v>29.4</v>
       </c>
       <c r="W27" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="X27" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Y27" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Z27" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="28" spans="1:26" x14ac:dyDescent="0.2">
@@ -4200,13 +4059,13 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="C28" t="s">
-        <v>167</v>
+        <v>100</v>
       </c>
       <c r="D28" t="s">
-        <v>168</v>
+        <v>101</v>
       </c>
       <c r="E28" t="s">
         <v>169</v>
@@ -4218,31 +4077,31 @@
         <v>31</v>
       </c>
       <c r="H28" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="I28" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="J28" t="s">
-        <v>171</v>
+        <v>112</v>
       </c>
       <c r="K28" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="L28" t="s">
         <v>36</v>
       </c>
       <c r="M28">
-        <v>18525</v>
+        <v>11274</v>
       </c>
       <c r="N28">
-        <v>18499</v>
+        <v>10669</v>
       </c>
       <c r="O28">
-        <v>80</v>
-      </c>
-      <c r="P28" t="s">
-        <v>37</v>
+        <v>120</v>
+      </c>
+      <c r="P28">
+        <v>120</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -4257,22 +4116,22 @@
         <v>0</v>
       </c>
       <c r="U28">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="V28">
-        <v>47.46</v>
+        <v>36.8598</v>
       </c>
       <c r="W28" t="s">
+        <v>171</v>
+      </c>
+      <c r="X28" t="s">
         <v>172</v>
       </c>
-      <c r="X28" t="s">
+      <c r="Y28" t="s">
         <v>173</v>
       </c>
-      <c r="Y28" t="s">
+      <c r="Z28" t="s">
         <v>174</v>
-      </c>
-      <c r="Z28" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.2">
@@ -4283,46 +4142,46 @@
         <v>46090</v>
       </c>
       <c r="C29" t="s">
+        <v>175</v>
+      </c>
+      <c r="D29" t="s">
         <v>176</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>177</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>178</v>
-      </c>
-      <c r="F29" t="s">
-        <v>179</v>
       </c>
       <c r="G29" t="s">
         <v>31</v>
       </c>
       <c r="H29" t="s">
-        <v>150</v>
+        <v>46</v>
       </c>
       <c r="I29" t="s">
-        <v>151</v>
+        <v>47</v>
       </c>
       <c r="J29" t="s">
-        <v>37</v>
+        <v>179</v>
       </c>
       <c r="K29" t="s">
-        <v>153</v>
+        <v>49</v>
       </c>
       <c r="L29" t="s">
         <v>36</v>
       </c>
       <c r="M29">
-        <v>1791</v>
+        <v>18591</v>
       </c>
       <c r="N29">
-        <v>1745</v>
+        <v>18428</v>
       </c>
       <c r="O29">
-        <v>28</v>
-      </c>
-      <c r="P29">
-        <v>28</v>
+        <v>80</v>
+      </c>
+      <c r="P29" t="s">
+        <v>37</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -4337,10 +4196,10 @@
         <v>0</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="V29">
-        <v>57.33</v>
+        <v>47.46</v>
       </c>
       <c r="W29" t="s">
         <v>180</v>
@@ -4349,10 +4208,10 @@
         <v>181</v>
       </c>
       <c r="Y29" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="Z29" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.2">
@@ -4360,49 +4219,49 @@
         <v>26</v>
       </c>
       <c r="B30" s="2">
-        <v>46090</v>
+        <v>46086</v>
       </c>
       <c r="C30" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="D30" t="s">
+        <v>176</v>
+      </c>
+      <c r="E30" t="s">
         <v>184</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>185</v>
-      </c>
-      <c r="F30" t="s">
-        <v>186</v>
       </c>
       <c r="G30" t="s">
         <v>31</v>
       </c>
       <c r="H30" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="I30" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="J30" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="K30" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="L30" t="s">
         <v>36</v>
       </c>
       <c r="M30">
-        <v>37803</v>
+        <v>18591</v>
       </c>
       <c r="N30">
-        <v>37608</v>
+        <v>18428</v>
       </c>
       <c r="O30">
-        <v>15</v>
-      </c>
-      <c r="P30">
-        <v>15</v>
+        <v>130</v>
+      </c>
+      <c r="P30" t="s">
+        <v>37</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -4417,22 +4276,22 @@
         <v>0</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="V30">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W30" t="s">
+        <v>186</v>
+      </c>
+      <c r="X30" t="s">
+        <v>187</v>
+      </c>
+      <c r="Y30" t="s">
         <v>188</v>
       </c>
-      <c r="X30" t="s">
+      <c r="Z30" t="s">
         <v>189</v>
-      </c>
-      <c r="Y30" t="s">
-        <v>87</v>
-      </c>
-      <c r="Z30" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.2">
@@ -4440,79 +4299,79 @@
         <v>26</v>
       </c>
       <c r="B31" s="2">
-        <v>46090</v>
+        <v>46086</v>
       </c>
       <c r="C31" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="D31" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="E31" t="s">
+        <v>190</v>
+      </c>
+      <c r="F31" t="s">
         <v>191</v>
-      </c>
-      <c r="F31" t="s">
-        <v>192</v>
       </c>
       <c r="G31" t="s">
         <v>31</v>
       </c>
       <c r="H31" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="I31" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="J31" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="K31" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="L31" t="s">
         <v>36</v>
       </c>
       <c r="M31">
-        <v>37803</v>
+        <v>18591</v>
       </c>
       <c r="N31">
-        <v>37608</v>
+        <v>18428</v>
       </c>
       <c r="O31">
-        <v>14</v>
-      </c>
-      <c r="P31">
-        <v>14</v>
+        <v>28</v>
+      </c>
+      <c r="P31" t="s">
+        <v>37</v>
       </c>
       <c r="Q31">
         <v>0</v>
       </c>
       <c r="R31">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="S31">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="T31">
         <v>0</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="V31">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W31" t="s">
+        <v>192</v>
+      </c>
+      <c r="X31" t="s">
         <v>193</v>
       </c>
-      <c r="X31" t="s">
+      <c r="Y31" t="s">
         <v>194</v>
       </c>
-      <c r="Y31" t="s">
+      <c r="Z31" t="s">
         <v>195</v>
-      </c>
-      <c r="Z31" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.2">
@@ -4520,49 +4379,49 @@
         <v>26</v>
       </c>
       <c r="B32" s="2">
-        <v>46090</v>
+        <v>46086</v>
       </c>
       <c r="C32" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="D32" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="E32" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="F32" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="G32" t="s">
         <v>31</v>
       </c>
       <c r="H32" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="I32" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="J32" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="K32" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="L32" t="s">
         <v>36</v>
       </c>
       <c r="M32">
-        <v>18525</v>
+        <v>11274</v>
       </c>
       <c r="N32">
-        <v>18499</v>
+        <v>10669</v>
       </c>
       <c r="O32">
-        <v>26</v>
-      </c>
-      <c r="P32">
-        <v>26</v>
+        <v>34</v>
+      </c>
+      <c r="P32" t="s">
+        <v>37</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -4577,22 +4436,22 @@
         <v>0</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="V32">
-        <v>47.46</v>
+        <v>36.86</v>
       </c>
       <c r="W32" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="X32" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="Y32" t="s">
-        <v>131</v>
+        <v>194</v>
       </c>
       <c r="Z32" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.2">
@@ -4600,49 +4459,49 @@
         <v>26</v>
       </c>
       <c r="B33" s="2">
-        <v>46090</v>
+        <v>46086</v>
       </c>
       <c r="C33" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="D33" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="E33" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="F33" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="G33" t="s">
         <v>31</v>
       </c>
       <c r="H33" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="I33" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="J33" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="K33" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="L33" t="s">
         <v>36</v>
       </c>
       <c r="M33">
-        <v>37803</v>
+        <v>37748</v>
       </c>
       <c r="N33">
-        <v>37608</v>
+        <v>35884</v>
       </c>
       <c r="O33">
-        <v>26</v>
-      </c>
-      <c r="P33">
-        <v>26</v>
+        <v>70</v>
+      </c>
+      <c r="P33" t="s">
+        <v>37</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -4657,72 +4516,72 @@
         <v>0</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="V33">
         <v>29.4</v>
       </c>
       <c r="W33" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="X33" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="Y33" t="s">
-        <v>131</v>
+        <v>194</v>
       </c>
       <c r="Z33" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>203</v>
+        <v>26</v>
       </c>
       <c r="B34" s="2">
         <v>46086</v>
       </c>
       <c r="C34" t="s">
-        <v>204</v>
+        <v>175</v>
       </c>
       <c r="D34" t="s">
-        <v>205</v>
+        <v>176</v>
       </c>
       <c r="E34" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="F34" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="G34" t="s">
         <v>31</v>
       </c>
       <c r="H34" t="s">
-        <v>150</v>
+        <v>46</v>
       </c>
       <c r="I34" t="s">
-        <v>151</v>
+        <v>47</v>
       </c>
       <c r="J34" t="s">
-        <v>37</v>
+        <v>179</v>
       </c>
       <c r="K34" t="s">
-        <v>153</v>
+        <v>49</v>
       </c>
       <c r="L34" t="s">
         <v>36</v>
       </c>
       <c r="M34">
-        <v>1791</v>
+        <v>18591</v>
       </c>
       <c r="N34">
-        <v>1745</v>
+        <v>18428</v>
       </c>
       <c r="O34">
-        <v>8</v>
-      </c>
-      <c r="P34">
-        <v>8</v>
+        <v>13</v>
+      </c>
+      <c r="P34" t="s">
+        <v>37</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -4737,22 +4596,22 @@
         <v>0</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="V34">
-        <v>57.33</v>
+        <v>47.46</v>
       </c>
       <c r="W34" t="s">
-        <v>208</v>
+        <v>180</v>
       </c>
       <c r="X34" t="s">
-        <v>209</v>
+        <v>181</v>
       </c>
       <c r="Y34" t="s">
-        <v>87</v>
+        <v>182</v>
       </c>
       <c r="Z34" t="s">
-        <v>210</v>
+        <v>183</v>
       </c>
     </row>
     <row r="35" spans="1:26" x14ac:dyDescent="0.2">
@@ -4763,43 +4622,43 @@
         <v>46086</v>
       </c>
       <c r="C35" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D35" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E35" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="F35" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="G35" t="s">
         <v>31</v>
       </c>
       <c r="H35" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="I35" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="J35" t="s">
-        <v>171</v>
+        <v>202</v>
       </c>
       <c r="K35" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="L35" t="s">
         <v>36</v>
       </c>
       <c r="M35">
-        <v>18525</v>
+        <v>18591</v>
       </c>
       <c r="N35">
-        <v>18499</v>
+        <v>18428</v>
       </c>
       <c r="O35">
-        <v>130</v>
+        <v>27</v>
       </c>
       <c r="P35" t="s">
         <v>37</v>
@@ -4817,22 +4676,22 @@
         <v>0</v>
       </c>
       <c r="U35">
-        <v>130</v>
+        <v>27</v>
       </c>
       <c r="V35">
         <v>47.46</v>
       </c>
       <c r="W35" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="X35" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="Y35" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="Z35" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
     </row>
     <row r="36" spans="1:26" x14ac:dyDescent="0.2">
@@ -4843,43 +4702,43 @@
         <v>46086</v>
       </c>
       <c r="C36" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D36" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E36" t="s">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="F36" t="s">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="G36" t="s">
         <v>31</v>
       </c>
       <c r="H36" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="I36" t="s">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="J36" t="s">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="K36" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="L36" t="s">
         <v>36</v>
       </c>
       <c r="M36">
-        <v>18525</v>
+        <v>37748</v>
       </c>
       <c r="N36">
-        <v>18499</v>
+        <v>35884</v>
       </c>
       <c r="O36">
-        <v>28</v>
+        <v>140</v>
       </c>
       <c r="P36" t="s">
         <v>37</v>
@@ -4897,22 +4756,22 @@
         <v>0</v>
       </c>
       <c r="U36">
-        <v>28</v>
+        <v>140</v>
       </c>
       <c r="V36">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W36" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="X36" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="Y36" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="Z36" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
     </row>
     <row r="37" spans="1:26" x14ac:dyDescent="0.2">
@@ -4923,43 +4782,43 @@
         <v>46086</v>
       </c>
       <c r="C37" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D37" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E37" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="F37" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="G37" t="s">
         <v>31</v>
       </c>
       <c r="H37" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="I37" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="J37" t="s">
-        <v>223</v>
+        <v>179</v>
       </c>
       <c r="K37" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="L37" t="s">
         <v>36</v>
       </c>
       <c r="M37">
-        <v>12600</v>
+        <v>18591</v>
       </c>
       <c r="N37">
-        <v>11150</v>
+        <v>18428</v>
       </c>
       <c r="O37">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="P37" t="s">
         <v>37</v>
@@ -4977,22 +4836,22 @@
         <v>0</v>
       </c>
       <c r="U37">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="V37">
-        <v>36.86</v>
+        <v>47.46</v>
       </c>
       <c r="W37" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="X37" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="Y37" t="s">
-        <v>221</v>
+        <v>26</v>
       </c>
       <c r="Z37" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
     </row>
     <row r="38" spans="1:26" x14ac:dyDescent="0.2">
@@ -5003,40 +4862,40 @@
         <v>46086</v>
       </c>
       <c r="C38" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D38" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E38" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="F38" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="G38" t="s">
         <v>31</v>
       </c>
       <c r="H38" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="I38" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="J38" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="K38" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="L38" t="s">
         <v>36</v>
       </c>
       <c r="M38">
-        <v>37803</v>
+        <v>37748</v>
       </c>
       <c r="N38">
-        <v>37608</v>
+        <v>35884</v>
       </c>
       <c r="O38">
         <v>70</v>
@@ -5063,16 +4922,16 @@
         <v>29.4</v>
       </c>
       <c r="W38" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="X38" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="Y38" t="s">
-        <v>221</v>
+        <v>26</v>
       </c>
       <c r="Z38" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
     </row>
     <row r="39" spans="1:26" x14ac:dyDescent="0.2">
@@ -5083,43 +4942,43 @@
         <v>46086</v>
       </c>
       <c r="C39" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D39" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E39" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="F39" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="G39" t="s">
         <v>31</v>
       </c>
       <c r="H39" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="I39" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="J39" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="K39" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="L39" t="s">
         <v>36</v>
       </c>
       <c r="M39">
-        <v>18525</v>
+        <v>18591</v>
       </c>
       <c r="N39">
-        <v>18499</v>
+        <v>18428</v>
       </c>
       <c r="O39">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="P39" t="s">
         <v>37</v>
@@ -5137,22 +4996,22 @@
         <v>0</v>
       </c>
       <c r="U39">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="V39">
         <v>47.46</v>
       </c>
       <c r="W39" t="s">
-        <v>172</v>
+        <v>214</v>
       </c>
       <c r="X39" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="Y39" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="Z39" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
     </row>
     <row r="40" spans="1:26" x14ac:dyDescent="0.2">
@@ -5163,43 +5022,43 @@
         <v>46086</v>
       </c>
       <c r="C40" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D40" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E40" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="F40" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="G40" t="s">
         <v>31</v>
       </c>
       <c r="H40" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="I40" t="s">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="J40" t="s">
-        <v>229</v>
+        <v>197</v>
       </c>
       <c r="K40" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="L40" t="s">
         <v>36</v>
       </c>
       <c r="M40">
-        <v>18525</v>
+        <v>37748</v>
       </c>
       <c r="N40">
-        <v>18499</v>
+        <v>35884</v>
       </c>
       <c r="O40">
-        <v>27</v>
+        <v>140</v>
       </c>
       <c r="P40" t="s">
         <v>37</v>
@@ -5217,22 +5076,22 @@
         <v>0</v>
       </c>
       <c r="U40">
-        <v>27</v>
+        <v>140</v>
       </c>
       <c r="V40">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W40" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="X40" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="Y40" t="s">
-        <v>232</v>
+        <v>107</v>
       </c>
       <c r="Z40" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
     </row>
     <row r="41" spans="1:26" x14ac:dyDescent="0.2">
@@ -5243,43 +5102,43 @@
         <v>46086</v>
       </c>
       <c r="C41" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D41" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E41" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="F41" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="G41" t="s">
         <v>31</v>
       </c>
       <c r="H41" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="I41" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="J41" t="s">
-        <v>224</v>
+        <v>179</v>
       </c>
       <c r="K41" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="L41" t="s">
         <v>36</v>
       </c>
       <c r="M41">
-        <v>37803</v>
+        <v>18591</v>
       </c>
       <c r="N41">
-        <v>37608</v>
+        <v>18428</v>
       </c>
       <c r="O41">
-        <v>140</v>
+        <v>65</v>
       </c>
       <c r="P41" t="s">
         <v>37</v>
@@ -5297,22 +5156,22 @@
         <v>0</v>
       </c>
       <c r="U41">
-        <v>140</v>
+        <v>65</v>
       </c>
       <c r="V41">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W41" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="X41" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="Y41" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="Z41" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
     </row>
     <row r="42" spans="1:26" x14ac:dyDescent="0.2">
@@ -5323,43 +5182,43 @@
         <v>46086</v>
       </c>
       <c r="C42" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D42" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E42" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="F42" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="G42" t="s">
         <v>31</v>
       </c>
       <c r="H42" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="I42" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="J42" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="K42" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="L42" t="s">
         <v>36</v>
       </c>
       <c r="M42">
-        <v>18525</v>
+        <v>11274</v>
       </c>
       <c r="N42">
-        <v>18499</v>
+        <v>10669</v>
       </c>
       <c r="O42">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="P42" t="s">
         <v>37</v>
@@ -5377,22 +5236,22 @@
         <v>0</v>
       </c>
       <c r="U42">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="V42">
-        <v>47.46</v>
+        <v>36.86</v>
       </c>
       <c r="W42" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="X42" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="Y42" t="s">
-        <v>26</v>
+        <v>224</v>
       </c>
       <c r="Z42" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
     </row>
     <row r="43" spans="1:26" x14ac:dyDescent="0.2">
@@ -5403,43 +5262,43 @@
         <v>46086</v>
       </c>
       <c r="C43" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D43" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E43" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="F43" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="G43" t="s">
         <v>31</v>
       </c>
       <c r="H43" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="I43" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="J43" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="K43" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="L43" t="s">
         <v>36</v>
       </c>
       <c r="M43">
-        <v>37803</v>
+        <v>37748</v>
       </c>
       <c r="N43">
-        <v>37608</v>
+        <v>35884</v>
       </c>
       <c r="O43">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="P43" t="s">
         <v>37</v>
@@ -5457,22 +5316,22 @@
         <v>0</v>
       </c>
       <c r="U43">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="V43">
         <v>29.4</v>
       </c>
       <c r="W43" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="X43" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="Y43" t="s">
-        <v>26</v>
+        <v>224</v>
       </c>
       <c r="Z43" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
     </row>
     <row r="44" spans="1:26" x14ac:dyDescent="0.2">
@@ -5483,43 +5342,43 @@
         <v>46086</v>
       </c>
       <c r="C44" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D44" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E44" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="F44" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="G44" t="s">
         <v>31</v>
       </c>
       <c r="H44" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="I44" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="J44" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="K44" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="L44" t="s">
         <v>36</v>
       </c>
       <c r="M44">
-        <v>18525</v>
+        <v>18591</v>
       </c>
       <c r="N44">
-        <v>18499</v>
+        <v>18428</v>
       </c>
       <c r="O44">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="P44" t="s">
         <v>37</v>
@@ -5537,22 +5396,22 @@
         <v>0</v>
       </c>
       <c r="U44">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="V44">
         <v>47.46</v>
       </c>
       <c r="W44" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="X44" t="s">
-        <v>158</v>
+        <v>229</v>
       </c>
       <c r="Y44" t="s">
-        <v>159</v>
+        <v>40</v>
       </c>
       <c r="Z44" t="s">
-        <v>160</v>
+        <v>230</v>
       </c>
     </row>
     <row r="45" spans="1:26" x14ac:dyDescent="0.2">
@@ -5563,43 +5422,43 @@
         <v>46086</v>
       </c>
       <c r="C45" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D45" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E45" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="F45" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="G45" t="s">
         <v>31</v>
       </c>
       <c r="H45" t="s">
+        <v>68</v>
+      </c>
+      <c r="I45" t="s">
         <v>69</v>
       </c>
-      <c r="I45" t="s">
+      <c r="J45" t="s">
+        <v>196</v>
+      </c>
+      <c r="K45" t="s">
         <v>70</v>
-      </c>
-      <c r="J45" t="s">
-        <v>224</v>
-      </c>
-      <c r="K45" t="s">
-        <v>72</v>
       </c>
       <c r="L45" t="s">
         <v>36</v>
       </c>
       <c r="M45">
-        <v>37803</v>
+        <v>11274</v>
       </c>
       <c r="N45">
-        <v>37608</v>
+        <v>10669</v>
       </c>
       <c r="O45">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="P45" t="s">
         <v>37</v>
@@ -5617,22 +5476,22 @@
         <v>0</v>
       </c>
       <c r="U45">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="V45">
-        <v>29.4</v>
+        <v>36.86</v>
       </c>
       <c r="W45" t="s">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="X45" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="Y45" t="s">
-        <v>96</v>
+        <v>40</v>
       </c>
       <c r="Z45" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
     </row>
     <row r="46" spans="1:26" x14ac:dyDescent="0.2">
@@ -5643,43 +5502,43 @@
         <v>46086</v>
       </c>
       <c r="C46" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D46" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E46" t="s">
-        <v>247</v>
+        <v>226</v>
       </c>
       <c r="F46" t="s">
-        <v>248</v>
+        <v>227</v>
       </c>
       <c r="G46" t="s">
         <v>31</v>
       </c>
       <c r="H46" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="I46" t="s">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="J46" t="s">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="K46" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="L46" t="s">
         <v>36</v>
       </c>
       <c r="M46">
-        <v>18525</v>
+        <v>37748</v>
       </c>
       <c r="N46">
-        <v>18499</v>
+        <v>35884</v>
       </c>
       <c r="O46">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="P46" t="s">
         <v>37</v>
@@ -5697,22 +5556,22 @@
         <v>0</v>
       </c>
       <c r="U46">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="V46">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W46" t="s">
-        <v>249</v>
+        <v>228</v>
       </c>
       <c r="X46" t="s">
-        <v>250</v>
+        <v>229</v>
       </c>
       <c r="Y46" t="s">
-        <v>251</v>
+        <v>40</v>
       </c>
       <c r="Z46" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
     </row>
     <row r="47" spans="1:26" x14ac:dyDescent="0.2">
@@ -5723,43 +5582,43 @@
         <v>46086</v>
       </c>
       <c r="C47" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D47" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E47" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="F47" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="G47" t="s">
         <v>31</v>
       </c>
       <c r="H47" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="I47" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="J47" t="s">
-        <v>223</v>
+        <v>196</v>
       </c>
       <c r="K47" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="L47" t="s">
         <v>36</v>
       </c>
       <c r="M47">
-        <v>12600</v>
+        <v>11274</v>
       </c>
       <c r="N47">
-        <v>11150</v>
+        <v>10669</v>
       </c>
       <c r="O47">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="P47" t="s">
         <v>37</v>
@@ -5777,22 +5636,22 @@
         <v>0</v>
       </c>
       <c r="U47">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="V47">
         <v>36.86</v>
       </c>
       <c r="W47" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="X47" t="s">
-        <v>250</v>
+        <v>141</v>
       </c>
       <c r="Y47" t="s">
-        <v>251</v>
+        <v>142</v>
       </c>
       <c r="Z47" t="s">
-        <v>252</v>
+        <v>143</v>
       </c>
     </row>
     <row r="48" spans="1:26" x14ac:dyDescent="0.2">
@@ -5803,43 +5662,43 @@
         <v>46086</v>
       </c>
       <c r="C48" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D48" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E48" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="F48" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="G48" t="s">
         <v>31</v>
       </c>
       <c r="H48" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="I48" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="J48" t="s">
-        <v>224</v>
+        <v>179</v>
       </c>
       <c r="K48" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="L48" t="s">
         <v>36</v>
       </c>
       <c r="M48">
-        <v>37803</v>
+        <v>18591</v>
       </c>
       <c r="N48">
-        <v>37608</v>
+        <v>18428</v>
       </c>
       <c r="O48">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="P48" t="s">
         <v>37</v>
@@ -5857,22 +5716,22 @@
         <v>0</v>
       </c>
       <c r="U48">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="V48">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W48" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="X48" t="s">
-        <v>250</v>
+        <v>61</v>
       </c>
       <c r="Y48" t="s">
-        <v>251</v>
+        <v>62</v>
       </c>
       <c r="Z48" t="s">
-        <v>252</v>
+        <v>63</v>
       </c>
     </row>
     <row r="49" spans="1:26" x14ac:dyDescent="0.2">
@@ -5883,43 +5742,43 @@
         <v>46086</v>
       </c>
       <c r="C49" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D49" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E49" t="s">
-        <v>253</v>
+        <v>234</v>
       </c>
       <c r="F49" t="s">
-        <v>254</v>
+        <v>235</v>
       </c>
       <c r="G49" t="s">
         <v>31</v>
       </c>
       <c r="H49" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="I49" t="s">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="J49" t="s">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="K49" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="L49" t="s">
         <v>36</v>
       </c>
       <c r="M49">
-        <v>18525</v>
+        <v>37748</v>
       </c>
       <c r="N49">
-        <v>18499</v>
+        <v>35884</v>
       </c>
       <c r="O49">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="P49" t="s">
         <v>37</v>
@@ -5937,22 +5796,22 @@
         <v>0</v>
       </c>
       <c r="U49">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="V49">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W49" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="X49" t="s">
-        <v>256</v>
+        <v>61</v>
       </c>
       <c r="Y49" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="Z49" t="s">
-        <v>257</v>
+        <v>63</v>
       </c>
     </row>
     <row r="50" spans="1:26" x14ac:dyDescent="0.2">
@@ -5963,43 +5822,43 @@
         <v>46086</v>
       </c>
       <c r="C50" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D50" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E50" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="F50" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="G50" t="s">
         <v>31</v>
       </c>
       <c r="H50" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="I50" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="J50" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="K50" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="L50" t="s">
         <v>36</v>
       </c>
       <c r="M50">
-        <v>12600</v>
+        <v>37748</v>
       </c>
       <c r="N50">
-        <v>11150</v>
+        <v>35884</v>
       </c>
       <c r="O50">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="P50" t="s">
         <v>37</v>
@@ -6017,22 +5876,22 @@
         <v>0</v>
       </c>
       <c r="U50">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="V50">
-        <v>36.86</v>
+        <v>29.4</v>
       </c>
       <c r="W50" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="X50" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="Y50" t="s">
-        <v>40</v>
+        <v>173</v>
       </c>
       <c r="Z50" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
     </row>
     <row r="51" spans="1:26" x14ac:dyDescent="0.2">
@@ -6043,43 +5902,43 @@
         <v>46086</v>
       </c>
       <c r="C51" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D51" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E51" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F51" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G51" t="s">
         <v>31</v>
       </c>
       <c r="H51" t="s">
+        <v>68</v>
+      </c>
+      <c r="I51" t="s">
         <v>69</v>
       </c>
-      <c r="I51" t="s">
+      <c r="J51" t="s">
+        <v>196</v>
+      </c>
+      <c r="K51" t="s">
         <v>70</v>
-      </c>
-      <c r="J51" t="s">
-        <v>224</v>
-      </c>
-      <c r="K51" t="s">
-        <v>72</v>
       </c>
       <c r="L51" t="s">
         <v>36</v>
       </c>
       <c r="M51">
-        <v>37803</v>
+        <v>11274</v>
       </c>
       <c r="N51">
-        <v>37608</v>
+        <v>10669</v>
       </c>
       <c r="O51">
-        <v>76</v>
+        <v>10</v>
       </c>
       <c r="P51" t="s">
         <v>37</v>
@@ -6097,22 +5956,22 @@
         <v>0</v>
       </c>
       <c r="U51">
-        <v>76</v>
+        <v>10</v>
       </c>
       <c r="V51">
-        <v>29.4</v>
+        <v>36.86</v>
       </c>
       <c r="W51" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="X51" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="Y51" t="s">
-        <v>40</v>
+        <v>246</v>
       </c>
       <c r="Z51" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
     </row>
     <row r="52" spans="1:26" x14ac:dyDescent="0.2">
@@ -6123,43 +5982,43 @@
         <v>46086</v>
       </c>
       <c r="C52" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D52" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E52" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="F52" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="G52" t="s">
         <v>31</v>
       </c>
       <c r="H52" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="I52" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="J52" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="K52" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="L52" t="s">
         <v>36</v>
       </c>
       <c r="M52">
-        <v>12600</v>
+        <v>37748</v>
       </c>
       <c r="N52">
-        <v>11150</v>
+        <v>35884</v>
       </c>
       <c r="O52">
-        <v>42</v>
+        <v>140</v>
       </c>
       <c r="P52" t="s">
         <v>37</v>
@@ -6177,22 +6036,22 @@
         <v>0</v>
       </c>
       <c r="U52">
-        <v>42</v>
+        <v>140</v>
       </c>
       <c r="V52">
-        <v>36.86</v>
+        <v>29.4</v>
       </c>
       <c r="W52" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="X52" t="s">
-        <v>130</v>
+        <v>245</v>
       </c>
       <c r="Y52" t="s">
-        <v>131</v>
+        <v>246</v>
       </c>
       <c r="Z52" t="s">
-        <v>132</v>
+        <v>247</v>
       </c>
     </row>
     <row r="53" spans="1:26" x14ac:dyDescent="0.2">
@@ -6203,43 +6062,43 @@
         <v>46086</v>
       </c>
       <c r="C53" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D53" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E53" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="F53" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="G53" t="s">
         <v>31</v>
       </c>
       <c r="H53" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="I53" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="J53" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="K53" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="L53" t="s">
         <v>36</v>
       </c>
       <c r="M53">
-        <v>18525</v>
+        <v>18591</v>
       </c>
       <c r="N53">
-        <v>18499</v>
+        <v>18428</v>
       </c>
       <c r="O53">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="P53" t="s">
         <v>37</v>
@@ -6257,22 +6116,22 @@
         <v>0</v>
       </c>
       <c r="U53">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="V53">
         <v>47.46</v>
       </c>
       <c r="W53" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="X53" t="s">
-        <v>50</v>
+        <v>251</v>
       </c>
       <c r="Y53" t="s">
-        <v>51</v>
+        <v>252</v>
       </c>
       <c r="Z53" t="s">
-        <v>52</v>
+        <v>253</v>
       </c>
     </row>
     <row r="54" spans="1:26" x14ac:dyDescent="0.2">
@@ -6283,43 +6142,43 @@
         <v>46086</v>
       </c>
       <c r="C54" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D54" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E54" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="F54" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="G54" t="s">
         <v>31</v>
       </c>
       <c r="H54" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="I54" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="J54" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="K54" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="L54" t="s">
         <v>36</v>
       </c>
       <c r="M54">
-        <v>37803</v>
+        <v>37748</v>
       </c>
       <c r="N54">
-        <v>37608</v>
+        <v>35884</v>
       </c>
       <c r="O54">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="P54" t="s">
         <v>37</v>
@@ -6337,22 +6196,22 @@
         <v>0</v>
       </c>
       <c r="U54">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="V54">
         <v>29.4</v>
       </c>
       <c r="W54" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="X54" t="s">
-        <v>50</v>
+        <v>251</v>
       </c>
       <c r="Y54" t="s">
-        <v>51</v>
+        <v>252</v>
       </c>
       <c r="Z54" t="s">
-        <v>52</v>
+        <v>253</v>
       </c>
     </row>
     <row r="55" spans="1:26" x14ac:dyDescent="0.2">
@@ -6363,43 +6222,43 @@
         <v>46086</v>
       </c>
       <c r="C55" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D55" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E55" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="F55" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="G55" t="s">
         <v>31</v>
       </c>
       <c r="H55" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="I55" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="J55" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="K55" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="L55" t="s">
         <v>36</v>
       </c>
       <c r="M55">
-        <v>37803</v>
+        <v>37748</v>
       </c>
       <c r="N55">
-        <v>37608</v>
+        <v>35884</v>
       </c>
       <c r="O55">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="P55" t="s">
         <v>37</v>
@@ -6417,22 +6276,22 @@
         <v>0</v>
       </c>
       <c r="U55">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="V55">
         <v>29.4</v>
       </c>
       <c r="W55" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="X55" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="Y55" t="s">
-        <v>165</v>
+        <v>258</v>
       </c>
       <c r="Z55" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
     </row>
     <row r="56" spans="1:26" x14ac:dyDescent="0.2">
@@ -6443,43 +6302,43 @@
         <v>46086</v>
       </c>
       <c r="C56" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D56" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E56" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="F56" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="G56" t="s">
         <v>31</v>
       </c>
       <c r="H56" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="I56" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="J56" t="s">
-        <v>223</v>
+        <v>179</v>
       </c>
       <c r="K56" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="L56" t="s">
         <v>36</v>
       </c>
       <c r="M56">
-        <v>12600</v>
+        <v>18591</v>
       </c>
       <c r="N56">
-        <v>11150</v>
+        <v>18428</v>
       </c>
       <c r="O56">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="P56" t="s">
         <v>37</v>
@@ -6497,22 +6356,22 @@
         <v>0</v>
       </c>
       <c r="U56">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="V56">
-        <v>36.86</v>
+        <v>47.46</v>
       </c>
       <c r="W56" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="X56" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="Y56" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="Z56" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
     </row>
     <row r="57" spans="1:26" x14ac:dyDescent="0.2">
@@ -6523,43 +6382,43 @@
         <v>46086</v>
       </c>
       <c r="C57" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D57" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E57" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="F57" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G57" t="s">
         <v>31</v>
       </c>
       <c r="H57" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="I57" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="J57" t="s">
-        <v>224</v>
+        <v>179</v>
       </c>
       <c r="K57" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="L57" t="s">
         <v>36</v>
       </c>
       <c r="M57">
-        <v>37803</v>
+        <v>18591</v>
       </c>
       <c r="N57">
-        <v>37608</v>
+        <v>18428</v>
       </c>
       <c r="O57">
-        <v>140</v>
+        <v>9</v>
       </c>
       <c r="P57" t="s">
         <v>37</v>
@@ -6577,22 +6436,22 @@
         <v>0</v>
       </c>
       <c r="U57">
-        <v>140</v>
+        <v>9</v>
       </c>
       <c r="V57">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W57" t="s">
+        <v>268</v>
+      </c>
+      <c r="X57" t="s">
+        <v>269</v>
+      </c>
+      <c r="Y57" t="s">
+        <v>270</v>
+      </c>
+      <c r="Z57" t="s">
         <v>271</v>
-      </c>
-      <c r="X57" t="s">
-        <v>272</v>
-      </c>
-      <c r="Y57" t="s">
-        <v>273</v>
-      </c>
-      <c r="Z57" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="58" spans="1:26" x14ac:dyDescent="0.2">
@@ -6603,43 +6462,43 @@
         <v>46086</v>
       </c>
       <c r="C58" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D58" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E58" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F58" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="G58" t="s">
         <v>31</v>
       </c>
       <c r="H58" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="I58" t="s">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="J58" t="s">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="K58" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="L58" t="s">
         <v>36</v>
       </c>
       <c r="M58">
-        <v>18525</v>
+        <v>37748</v>
       </c>
       <c r="N58">
-        <v>18499</v>
+        <v>35884</v>
       </c>
       <c r="O58">
-        <v>10</v>
+        <v>140</v>
       </c>
       <c r="P58" t="s">
         <v>37</v>
@@ -6657,22 +6516,22 @@
         <v>0</v>
       </c>
       <c r="U58">
-        <v>10</v>
+        <v>140</v>
       </c>
       <c r="V58">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W58" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="X58" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="Y58" t="s">
-        <v>279</v>
+        <v>36</v>
       </c>
       <c r="Z58" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="59" spans="1:26" x14ac:dyDescent="0.2">
@@ -6683,43 +6542,43 @@
         <v>46086</v>
       </c>
       <c r="C59" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D59" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E59" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F59" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="G59" t="s">
         <v>31</v>
       </c>
       <c r="H59" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="I59" t="s">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="J59" t="s">
-        <v>224</v>
+        <v>279</v>
       </c>
       <c r="K59" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="L59" t="s">
         <v>36</v>
       </c>
       <c r="M59">
-        <v>37803</v>
+        <v>1746</v>
       </c>
       <c r="N59">
-        <v>37608</v>
+        <v>1633</v>
       </c>
       <c r="O59">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="P59" t="s">
         <v>37</v>
@@ -6737,22 +6596,22 @@
         <v>0</v>
       </c>
       <c r="U59">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="V59">
-        <v>29.4</v>
+        <v>57.33</v>
       </c>
       <c r="W59" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="X59" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Y59" t="s">
-        <v>279</v>
+        <v>40</v>
       </c>
       <c r="Z59" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="60" spans="1:26" x14ac:dyDescent="0.2">
@@ -6763,43 +6622,43 @@
         <v>46086</v>
       </c>
       <c r="C60" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D60" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E60" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="F60" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="G60" t="s">
         <v>31</v>
       </c>
       <c r="H60" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="I60" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="J60" t="s">
-        <v>224</v>
+        <v>179</v>
       </c>
       <c r="K60" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="L60" t="s">
         <v>36</v>
       </c>
       <c r="M60">
-        <v>37803</v>
+        <v>18591</v>
       </c>
       <c r="N60">
-        <v>37608</v>
+        <v>18428</v>
       </c>
       <c r="O60">
-        <v>70</v>
+        <v>195</v>
       </c>
       <c r="P60" t="s">
         <v>37</v>
@@ -6817,22 +6676,22 @@
         <v>0</v>
       </c>
       <c r="U60">
-        <v>70</v>
+        <v>195</v>
       </c>
       <c r="V60">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W60" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="X60" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Y60" t="s">
-        <v>285</v>
+        <v>40</v>
       </c>
       <c r="Z60" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="61" spans="1:26" x14ac:dyDescent="0.2">
@@ -6843,40 +6702,40 @@
         <v>46086</v>
       </c>
       <c r="C61" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D61" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E61" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F61" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G61" t="s">
         <v>31</v>
       </c>
       <c r="H61" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="I61" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="J61" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="K61" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="L61" t="s">
         <v>36</v>
       </c>
       <c r="M61">
-        <v>18525</v>
+        <v>18591</v>
       </c>
       <c r="N61">
-        <v>18499</v>
+        <v>18428</v>
       </c>
       <c r="O61">
         <v>14</v>
@@ -6903,16 +6762,16 @@
         <v>47.46</v>
       </c>
       <c r="W61" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="X61" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="Y61" t="s">
-        <v>291</v>
+        <v>167</v>
       </c>
       <c r="Z61" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="62" spans="1:26" x14ac:dyDescent="0.2">
@@ -6923,43 +6782,43 @@
         <v>46086</v>
       </c>
       <c r="C62" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D62" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E62" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="F62" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="G62" t="s">
         <v>31</v>
       </c>
       <c r="H62" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="I62" t="s">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="J62" t="s">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="K62" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="L62" t="s">
         <v>36</v>
       </c>
       <c r="M62">
-        <v>18525</v>
+        <v>37748</v>
       </c>
       <c r="N62">
-        <v>18499</v>
+        <v>35884</v>
       </c>
       <c r="O62">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="P62" t="s">
         <v>37</v>
@@ -6977,22 +6836,22 @@
         <v>0</v>
       </c>
       <c r="U62">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="V62">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W62" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="X62" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="Y62" t="s">
-        <v>195</v>
+        <v>167</v>
       </c>
       <c r="Z62" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
     </row>
     <row r="63" spans="1:26" x14ac:dyDescent="0.2">
@@ -7003,43 +6862,43 @@
         <v>46086</v>
       </c>
       <c r="C63" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D63" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E63" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="F63" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="G63" t="s">
         <v>31</v>
       </c>
       <c r="H63" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="I63" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="J63" t="s">
-        <v>224</v>
+        <v>179</v>
       </c>
       <c r="K63" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="L63" t="s">
         <v>36</v>
       </c>
       <c r="M63">
-        <v>37803</v>
+        <v>18591</v>
       </c>
       <c r="N63">
-        <v>37608</v>
+        <v>18428</v>
       </c>
       <c r="O63">
-        <v>140</v>
+        <v>11</v>
       </c>
       <c r="P63" t="s">
         <v>37</v>
@@ -7057,22 +6916,22 @@
         <v>0</v>
       </c>
       <c r="U63">
-        <v>140</v>
+        <v>11</v>
       </c>
       <c r="V63">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W63" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="X63" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="Y63" t="s">
-        <v>36</v>
+        <v>121</v>
       </c>
       <c r="Z63" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
     </row>
     <row r="64" spans="1:26" x14ac:dyDescent="0.2">
@@ -7083,43 +6942,43 @@
         <v>46086</v>
       </c>
       <c r="C64" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D64" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E64" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="F64" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="G64" t="s">
         <v>31</v>
       </c>
       <c r="H64" t="s">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="I64" t="s">
-        <v>151</v>
+        <v>81</v>
       </c>
       <c r="J64" t="s">
-        <v>305</v>
+        <v>197</v>
       </c>
       <c r="K64" t="s">
-        <v>153</v>
+        <v>83</v>
       </c>
       <c r="L64" t="s">
         <v>36</v>
       </c>
       <c r="M64">
-        <v>1791</v>
+        <v>37748</v>
       </c>
       <c r="N64">
-        <v>1745</v>
+        <v>35884</v>
       </c>
       <c r="O64">
-        <v>8</v>
+        <v>140</v>
       </c>
       <c r="P64" t="s">
         <v>37</v>
@@ -7137,22 +6996,22 @@
         <v>0</v>
       </c>
       <c r="U64">
-        <v>8</v>
+        <v>140</v>
       </c>
       <c r="V64">
-        <v>57.33</v>
+        <v>29.4</v>
       </c>
       <c r="W64" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="X64" t="s">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="Y64" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="Z64" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
     </row>
     <row r="65" spans="1:26" x14ac:dyDescent="0.2">
@@ -7163,43 +7022,43 @@
         <v>46086</v>
       </c>
       <c r="C65" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D65" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E65" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="F65" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="G65" t="s">
         <v>31</v>
       </c>
       <c r="H65" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="I65" t="s">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="J65" t="s">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="K65" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="L65" t="s">
         <v>36</v>
       </c>
       <c r="M65">
-        <v>18525</v>
+        <v>37748</v>
       </c>
       <c r="N65">
-        <v>18499</v>
+        <v>35884</v>
       </c>
       <c r="O65">
-        <v>195</v>
+        <v>70</v>
       </c>
       <c r="P65" t="s">
         <v>37</v>
@@ -7217,22 +7076,22 @@
         <v>0</v>
       </c>
       <c r="U65">
-        <v>195</v>
+        <v>70</v>
       </c>
       <c r="V65">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W65" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="X65" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="Y65" t="s">
-        <v>40</v>
+        <v>264</v>
       </c>
       <c r="Z65" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="66" spans="1:26" x14ac:dyDescent="0.2">
@@ -7243,43 +7102,43 @@
         <v>46086</v>
       </c>
       <c r="C66" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D66" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E66" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="F66" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="G66" t="s">
         <v>31</v>
       </c>
       <c r="H66" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="I66" t="s">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="J66" t="s">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="K66" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="L66" t="s">
         <v>36</v>
       </c>
       <c r="M66">
-        <v>18525</v>
+        <v>37748</v>
       </c>
       <c r="N66">
-        <v>18499</v>
+        <v>35884</v>
       </c>
       <c r="O66">
-        <v>14</v>
+        <v>210</v>
       </c>
       <c r="P66" t="s">
         <v>37</v>
@@ -7297,22 +7156,22 @@
         <v>0</v>
       </c>
       <c r="U66">
-        <v>14</v>
+        <v>210</v>
       </c>
       <c r="V66">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W66" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="X66" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="Y66" t="s">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="Z66" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
     </row>
     <row r="67" spans="1:26" x14ac:dyDescent="0.2">
@@ -7323,40 +7182,40 @@
         <v>46086</v>
       </c>
       <c r="C67" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D67" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E67" t="s">
+        <v>308</v>
+      </c>
+      <c r="F67" t="s">
         <v>309</v>
-      </c>
-      <c r="F67" t="s">
-        <v>310</v>
       </c>
       <c r="G67" t="s">
         <v>31</v>
       </c>
       <c r="H67" t="s">
+        <v>68</v>
+      </c>
+      <c r="I67" t="s">
         <v>69</v>
       </c>
-      <c r="I67" t="s">
+      <c r="J67" t="s">
+        <v>196</v>
+      </c>
+      <c r="K67" t="s">
         <v>70</v>
-      </c>
-      <c r="J67" t="s">
-        <v>224</v>
-      </c>
-      <c r="K67" t="s">
-        <v>72</v>
       </c>
       <c r="L67" t="s">
         <v>36</v>
       </c>
       <c r="M67">
-        <v>37803</v>
+        <v>11274</v>
       </c>
       <c r="N67">
-        <v>37608</v>
+        <v>10669</v>
       </c>
       <c r="O67">
         <v>70</v>
@@ -7380,19 +7239,19 @@
         <v>70</v>
       </c>
       <c r="V67">
-        <v>29.4</v>
+        <v>36.86</v>
       </c>
       <c r="W67" t="s">
+        <v>310</v>
+      </c>
+      <c r="X67" t="s">
         <v>311</v>
       </c>
-      <c r="X67" t="s">
+      <c r="Y67" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z67" t="s">
         <v>312</v>
-      </c>
-      <c r="Y67" t="s">
-        <v>159</v>
-      </c>
-      <c r="Z67" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="68" spans="1:26" x14ac:dyDescent="0.2">
@@ -7403,40 +7262,40 @@
         <v>46086</v>
       </c>
       <c r="C68" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D68" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E68" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F68" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="G68" t="s">
         <v>31</v>
       </c>
       <c r="H68" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="I68" t="s">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="J68" t="s">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="K68" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="L68" t="s">
         <v>36</v>
       </c>
       <c r="M68">
-        <v>18525</v>
+        <v>37748</v>
       </c>
       <c r="N68">
-        <v>18499</v>
+        <v>35884</v>
       </c>
       <c r="O68">
         <v>11</v>
@@ -7460,19 +7319,19 @@
         <v>11</v>
       </c>
       <c r="V68">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W68" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="X68" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="Y68" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="Z68" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="69" spans="1:26" x14ac:dyDescent="0.2">
@@ -7483,43 +7342,43 @@
         <v>46086</v>
       </c>
       <c r="C69" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D69" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E69" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="F69" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="G69" t="s">
         <v>31</v>
       </c>
       <c r="H69" t="s">
+        <v>68</v>
+      </c>
+      <c r="I69" t="s">
         <v>69</v>
       </c>
-      <c r="I69" t="s">
+      <c r="J69" t="s">
+        <v>196</v>
+      </c>
+      <c r="K69" t="s">
         <v>70</v>
-      </c>
-      <c r="J69" t="s">
-        <v>224</v>
-      </c>
-      <c r="K69" t="s">
-        <v>72</v>
       </c>
       <c r="L69" t="s">
         <v>36</v>
       </c>
       <c r="M69">
-        <v>37803</v>
+        <v>11274</v>
       </c>
       <c r="N69">
-        <v>37608</v>
+        <v>10669</v>
       </c>
       <c r="O69">
-        <v>140</v>
+        <v>70</v>
       </c>
       <c r="P69" t="s">
         <v>37</v>
@@ -7537,22 +7396,22 @@
         <v>0</v>
       </c>
       <c r="U69">
-        <v>140</v>
+        <v>70</v>
       </c>
       <c r="V69">
-        <v>29.4</v>
+        <v>36.86</v>
       </c>
       <c r="W69" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="X69" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="Y69" t="s">
-        <v>36</v>
+        <v>317</v>
       </c>
       <c r="Z69" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
     </row>
     <row r="70" spans="1:26" x14ac:dyDescent="0.2">
@@ -7563,40 +7422,40 @@
         <v>46086</v>
       </c>
       <c r="C70" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D70" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E70" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F70" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="G70" t="s">
         <v>31</v>
       </c>
       <c r="H70" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="I70" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="J70" t="s">
-        <v>224</v>
+        <v>179</v>
       </c>
       <c r="K70" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="L70" t="s">
         <v>36</v>
       </c>
       <c r="M70">
-        <v>37803</v>
+        <v>18591</v>
       </c>
       <c r="N70">
-        <v>37608</v>
+        <v>18428</v>
       </c>
       <c r="O70">
         <v>70</v>
@@ -7620,19 +7479,19 @@
         <v>70</v>
       </c>
       <c r="V70">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W70" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="X70" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="Y70" t="s">
-        <v>291</v>
+        <v>323</v>
       </c>
       <c r="Z70" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
     </row>
     <row r="71" spans="1:26" x14ac:dyDescent="0.2">
@@ -7643,43 +7502,43 @@
         <v>46086</v>
       </c>
       <c r="C71" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D71" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E71" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="F71" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="G71" t="s">
         <v>31</v>
       </c>
       <c r="H71" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="I71" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="J71" t="s">
-        <v>224</v>
+        <v>179</v>
       </c>
       <c r="K71" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="L71" t="s">
         <v>36</v>
       </c>
       <c r="M71">
-        <v>37803</v>
+        <v>18591</v>
       </c>
       <c r="N71">
-        <v>37608</v>
+        <v>18428</v>
       </c>
       <c r="O71">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="P71" t="s">
         <v>37</v>
@@ -7697,22 +7556,22 @@
         <v>0</v>
       </c>
       <c r="U71">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="V71">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W71" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="X71" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="Y71" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="Z71" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
     </row>
     <row r="72" spans="1:26" x14ac:dyDescent="0.2">
@@ -7723,43 +7582,43 @@
         <v>46086</v>
       </c>
       <c r="C72" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D72" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E72" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="F72" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="G72" t="s">
         <v>31</v>
       </c>
       <c r="H72" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="I72" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="J72" t="s">
-        <v>223</v>
+        <v>196</v>
       </c>
       <c r="K72" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="L72" t="s">
         <v>36</v>
       </c>
       <c r="M72">
-        <v>12600</v>
+        <v>11274</v>
       </c>
       <c r="N72">
-        <v>11150</v>
+        <v>10669</v>
       </c>
       <c r="O72">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="P72" t="s">
         <v>37</v>
@@ -7777,22 +7636,22 @@
         <v>0</v>
       </c>
       <c r="U72">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="V72">
         <v>36.86</v>
       </c>
       <c r="W72" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="X72" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="Y72" t="s">
-        <v>87</v>
+        <v>26</v>
       </c>
       <c r="Z72" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
     </row>
     <row r="73" spans="1:26" x14ac:dyDescent="0.2">
@@ -7803,43 +7662,43 @@
         <v>46086</v>
       </c>
       <c r="C73" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D73" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E73" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="F73" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="G73" t="s">
         <v>31</v>
       </c>
       <c r="H73" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="I73" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="J73" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="K73" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="L73" t="s">
         <v>36</v>
       </c>
       <c r="M73">
-        <v>37803</v>
+        <v>37748</v>
       </c>
       <c r="N73">
-        <v>37608</v>
+        <v>35884</v>
       </c>
       <c r="O73">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="P73" t="s">
         <v>37</v>
@@ -7857,22 +7716,22 @@
         <v>0</v>
       </c>
       <c r="U73">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="V73">
         <v>29.4</v>
       </c>
       <c r="W73" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="X73" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="Y73" t="s">
-        <v>87</v>
+        <v>26</v>
       </c>
       <c r="Z73" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
     </row>
     <row r="74" spans="1:26" x14ac:dyDescent="0.2">
@@ -7880,719 +7739,79 @@
         <v>26</v>
       </c>
       <c r="B74" s="2">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="C74" t="s">
-        <v>167</v>
+        <v>27</v>
       </c>
       <c r="D74" t="s">
-        <v>168</v>
+        <v>28</v>
       </c>
       <c r="E74" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="F74" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="G74" t="s">
         <v>31</v>
       </c>
       <c r="H74" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="I74" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="J74" t="s">
-        <v>223</v>
+        <v>34</v>
       </c>
       <c r="K74" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="L74" t="s">
         <v>36</v>
       </c>
       <c r="M74">
-        <v>12600</v>
+        <v>1746</v>
       </c>
       <c r="N74">
-        <v>11150</v>
+        <v>1633</v>
       </c>
       <c r="O74">
-        <v>70</v>
-      </c>
-      <c r="P74" t="s">
-        <v>37</v>
+        <v>1</v>
+      </c>
+      <c r="P74">
+        <v>1</v>
       </c>
       <c r="Q74">
         <v>0</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T74">
         <v>0</v>
       </c>
       <c r="U74">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="V74">
-        <v>36.86</v>
+        <v>57.33</v>
       </c>
       <c r="W74" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="X74" t="s">
-        <v>342</v>
+        <v>114</v>
       </c>
       <c r="Y74" t="s">
-        <v>343</v>
+        <v>115</v>
       </c>
       <c r="Z74" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="75" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A75" t="s">
-        <v>26</v>
-      </c>
-      <c r="B75" s="2">
-        <v>46086</v>
-      </c>
-      <c r="C75" t="s">
-        <v>167</v>
-      </c>
-      <c r="D75" t="s">
-        <v>168</v>
-      </c>
-      <c r="E75" t="s">
-        <v>345</v>
-      </c>
-      <c r="F75" t="s">
-        <v>346</v>
-      </c>
-      <c r="G75" t="s">
-        <v>31</v>
-      </c>
-      <c r="H75" t="s">
-        <v>32</v>
-      </c>
-      <c r="I75" t="s">
-        <v>33</v>
-      </c>
-      <c r="J75" t="s">
-        <v>171</v>
-      </c>
-      <c r="K75" t="s">
-        <v>35</v>
-      </c>
-      <c r="L75" t="s">
-        <v>36</v>
-      </c>
-      <c r="M75">
-        <v>18525</v>
-      </c>
-      <c r="N75">
-        <v>18499</v>
-      </c>
-      <c r="O75">
-        <v>70</v>
-      </c>
-      <c r="P75" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q75">
-        <v>0</v>
-      </c>
-      <c r="R75">
-        <v>0</v>
-      </c>
-      <c r="S75">
-        <v>0</v>
-      </c>
-      <c r="T75">
-        <v>0</v>
-      </c>
-      <c r="U75">
-        <v>70</v>
-      </c>
-      <c r="V75">
-        <v>47.46</v>
-      </c>
-      <c r="W75" t="s">
-        <v>347</v>
-      </c>
-      <c r="X75" t="s">
-        <v>348</v>
-      </c>
-      <c r="Y75" t="s">
-        <v>349</v>
-      </c>
-      <c r="Z75" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="76" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A76" t="s">
-        <v>26</v>
-      </c>
-      <c r="B76" s="2">
-        <v>46086</v>
-      </c>
-      <c r="C76" t="s">
-        <v>167</v>
-      </c>
-      <c r="D76" t="s">
-        <v>168</v>
-      </c>
-      <c r="E76" t="s">
-        <v>351</v>
-      </c>
-      <c r="F76" t="s">
-        <v>352</v>
-      </c>
-      <c r="G76" t="s">
-        <v>31</v>
-      </c>
-      <c r="H76" t="s">
-        <v>32</v>
-      </c>
-      <c r="I76" t="s">
-        <v>33</v>
-      </c>
-      <c r="J76" t="s">
-        <v>171</v>
-      </c>
-      <c r="K76" t="s">
-        <v>35</v>
-      </c>
-      <c r="L76" t="s">
-        <v>36</v>
-      </c>
-      <c r="M76">
-        <v>18525</v>
-      </c>
-      <c r="N76">
-        <v>18499</v>
-      </c>
-      <c r="O76">
-        <v>130</v>
-      </c>
-      <c r="P76" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q76">
-        <v>0</v>
-      </c>
-      <c r="R76">
-        <v>0</v>
-      </c>
-      <c r="S76">
-        <v>0</v>
-      </c>
-      <c r="T76">
-        <v>0</v>
-      </c>
-      <c r="U76">
-        <v>130</v>
-      </c>
-      <c r="V76">
-        <v>47.46</v>
-      </c>
-      <c r="W76" t="s">
-        <v>353</v>
-      </c>
-      <c r="X76" t="s">
-        <v>354</v>
-      </c>
-      <c r="Y76" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z76" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="77" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A77" t="s">
-        <v>26</v>
-      </c>
-      <c r="B77" s="2">
-        <v>46086</v>
-      </c>
-      <c r="C77" t="s">
-        <v>167</v>
-      </c>
-      <c r="D77" t="s">
-        <v>168</v>
-      </c>
-      <c r="E77" t="s">
-        <v>351</v>
-      </c>
-      <c r="F77" t="s">
-        <v>352</v>
-      </c>
-      <c r="G77" t="s">
-        <v>31</v>
-      </c>
-      <c r="H77" t="s">
-        <v>57</v>
-      </c>
-      <c r="I77" t="s">
-        <v>58</v>
-      </c>
-      <c r="J77" t="s">
-        <v>223</v>
-      </c>
-      <c r="K77" t="s">
-        <v>59</v>
-      </c>
-      <c r="L77" t="s">
-        <v>36</v>
-      </c>
-      <c r="M77">
-        <v>12600</v>
-      </c>
-      <c r="N77">
-        <v>11150</v>
-      </c>
-      <c r="O77">
-        <v>51</v>
-      </c>
-      <c r="P77" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q77">
-        <v>0</v>
-      </c>
-      <c r="R77">
-        <v>0</v>
-      </c>
-      <c r="S77">
-        <v>0</v>
-      </c>
-      <c r="T77">
-        <v>0</v>
-      </c>
-      <c r="U77">
-        <v>51</v>
-      </c>
-      <c r="V77">
-        <v>36.86</v>
-      </c>
-      <c r="W77" t="s">
-        <v>353</v>
-      </c>
-      <c r="X77" t="s">
-        <v>354</v>
-      </c>
-      <c r="Y77" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z77" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="78" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A78" t="s">
-        <v>26</v>
-      </c>
-      <c r="B78" s="2">
-        <v>46086</v>
-      </c>
-      <c r="C78" t="s">
-        <v>167</v>
-      </c>
-      <c r="D78" t="s">
-        <v>168</v>
-      </c>
-      <c r="E78" t="s">
-        <v>351</v>
-      </c>
-      <c r="F78" t="s">
-        <v>352</v>
-      </c>
-      <c r="G78" t="s">
-        <v>31</v>
-      </c>
-      <c r="H78" t="s">
-        <v>69</v>
-      </c>
-      <c r="I78" t="s">
-        <v>70</v>
-      </c>
-      <c r="J78" t="s">
-        <v>224</v>
-      </c>
-      <c r="K78" t="s">
-        <v>72</v>
-      </c>
-      <c r="L78" t="s">
-        <v>36</v>
-      </c>
-      <c r="M78">
-        <v>37803</v>
-      </c>
-      <c r="N78">
-        <v>37608</v>
-      </c>
-      <c r="O78">
-        <v>8</v>
-      </c>
-      <c r="P78" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q78">
-        <v>0</v>
-      </c>
-      <c r="R78">
-        <v>0</v>
-      </c>
-      <c r="S78">
-        <v>0</v>
-      </c>
-      <c r="T78">
-        <v>0</v>
-      </c>
-      <c r="U78">
-        <v>8</v>
-      </c>
-      <c r="V78">
-        <v>29.4</v>
-      </c>
-      <c r="W78" t="s">
-        <v>353</v>
-      </c>
-      <c r="X78" t="s">
-        <v>354</v>
-      </c>
-      <c r="Y78" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z78" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="79" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A79" t="s">
-        <v>26</v>
-      </c>
-      <c r="B79" s="2">
-        <v>46085</v>
-      </c>
-      <c r="C79" t="s">
-        <v>356</v>
-      </c>
-      <c r="D79" t="s">
-        <v>357</v>
-      </c>
-      <c r="E79" t="s">
-        <v>358</v>
-      </c>
-      <c r="F79" t="s">
-        <v>359</v>
-      </c>
-      <c r="G79" t="s">
-        <v>31</v>
-      </c>
-      <c r="H79" t="s">
-        <v>150</v>
-      </c>
-      <c r="I79" t="s">
-        <v>151</v>
-      </c>
-      <c r="J79" t="s">
-        <v>360</v>
-      </c>
-      <c r="K79" t="s">
-        <v>153</v>
-      </c>
-      <c r="L79" t="s">
-        <v>36</v>
-      </c>
-      <c r="M79">
-        <v>1791</v>
-      </c>
-      <c r="N79">
-        <v>1745</v>
-      </c>
-      <c r="O79">
-        <v>1</v>
-      </c>
-      <c r="P79">
-        <v>1</v>
-      </c>
-      <c r="Q79">
-        <v>0</v>
-      </c>
-      <c r="R79">
-        <v>0</v>
-      </c>
-      <c r="S79">
-        <v>0</v>
-      </c>
-      <c r="T79">
-        <v>0</v>
-      </c>
-      <c r="U79">
-        <v>0</v>
-      </c>
-      <c r="V79">
-        <v>57.33</v>
-      </c>
-      <c r="W79" t="s">
-        <v>361</v>
-      </c>
-      <c r="X79" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y79" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z79" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="80" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A80" t="s">
-        <v>26</v>
-      </c>
-      <c r="B80" s="2">
-        <v>46085</v>
-      </c>
-      <c r="C80" t="s">
-        <v>362</v>
-      </c>
-      <c r="D80" t="s">
-        <v>363</v>
-      </c>
-      <c r="E80" t="s">
-        <v>364</v>
-      </c>
-      <c r="F80" t="s">
-        <v>365</v>
-      </c>
-      <c r="G80" t="s">
-        <v>31</v>
-      </c>
-      <c r="H80" t="s">
-        <v>57</v>
-      </c>
-      <c r="I80" t="s">
-        <v>58</v>
-      </c>
-      <c r="J80" t="s">
-        <v>37</v>
-      </c>
-      <c r="K80" t="s">
-        <v>59</v>
-      </c>
-      <c r="L80" t="s">
-        <v>36</v>
-      </c>
-      <c r="M80">
-        <v>12600</v>
-      </c>
-      <c r="N80">
-        <v>11150</v>
-      </c>
-      <c r="O80">
-        <v>1400</v>
-      </c>
-      <c r="P80">
-        <v>1400</v>
-      </c>
-      <c r="Q80">
-        <v>0</v>
-      </c>
-      <c r="R80">
-        <v>0</v>
-      </c>
-      <c r="S80">
-        <v>0</v>
-      </c>
-      <c r="T80">
-        <v>0</v>
-      </c>
-      <c r="U80">
-        <v>0</v>
-      </c>
-      <c r="V80">
-        <v>29.7</v>
-      </c>
-      <c r="W80" t="s">
-        <v>366</v>
-      </c>
-      <c r="X80" t="s">
-        <v>367</v>
-      </c>
-      <c r="Y80" t="s">
-        <v>51</v>
-      </c>
-      <c r="Z80" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="81" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A81" t="s">
-        <v>369</v>
-      </c>
-      <c r="B81" s="2">
-        <v>46084</v>
-      </c>
-      <c r="C81" t="s">
-        <v>370</v>
-      </c>
-      <c r="D81" t="s">
-        <v>371</v>
-      </c>
-      <c r="E81" t="s">
-        <v>372</v>
-      </c>
-      <c r="F81" t="s">
-        <v>373</v>
-      </c>
-      <c r="G81" t="s">
-        <v>31</v>
-      </c>
-      <c r="H81" t="s">
-        <v>150</v>
-      </c>
-      <c r="I81" t="s">
-        <v>151</v>
-      </c>
-      <c r="J81" t="s">
-        <v>374</v>
-      </c>
-      <c r="K81" t="s">
-        <v>153</v>
-      </c>
-      <c r="L81" t="s">
-        <v>36</v>
-      </c>
-      <c r="M81">
-        <v>1791</v>
-      </c>
-      <c r="N81">
-        <v>1745</v>
-      </c>
-      <c r="O81">
-        <v>3</v>
-      </c>
-      <c r="P81">
-        <v>3</v>
-      </c>
-      <c r="Q81">
-        <v>0</v>
-      </c>
-      <c r="R81">
-        <v>0</v>
-      </c>
-      <c r="S81">
-        <v>0</v>
-      </c>
-      <c r="T81">
-        <v>0</v>
-      </c>
-      <c r="U81">
-        <v>0</v>
-      </c>
-      <c r="V81">
-        <v>57</v>
-      </c>
-      <c r="W81" t="s">
-        <v>375</v>
-      </c>
-      <c r="X81" t="s">
-        <v>376</v>
-      </c>
-      <c r="Y81" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z81" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="82" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A82" t="s">
-        <v>26</v>
-      </c>
-      <c r="B82" s="2">
-        <v>46083</v>
-      </c>
-      <c r="C82" t="s">
-        <v>176</v>
-      </c>
-      <c r="D82" t="s">
-        <v>177</v>
-      </c>
-      <c r="E82" t="s">
-        <v>378</v>
-      </c>
-      <c r="F82" t="s">
-        <v>379</v>
-      </c>
-      <c r="G82" t="s">
-        <v>31</v>
-      </c>
-      <c r="H82" t="s">
-        <v>150</v>
-      </c>
-      <c r="I82" t="s">
-        <v>151</v>
-      </c>
-      <c r="J82" t="s">
-        <v>37</v>
-      </c>
-      <c r="K82" t="s">
-        <v>153</v>
-      </c>
-      <c r="L82" t="s">
-        <v>36</v>
-      </c>
-      <c r="M82">
-        <v>1791</v>
-      </c>
-      <c r="N82">
-        <v>1745</v>
-      </c>
-      <c r="O82">
-        <v>6</v>
-      </c>
-      <c r="P82">
-        <v>6</v>
-      </c>
-      <c r="Q82">
-        <v>0</v>
-      </c>
-      <c r="R82">
-        <v>0</v>
-      </c>
-      <c r="S82">
-        <v>0</v>
-      </c>
-      <c r="T82">
-        <v>0</v>
-      </c>
-      <c r="U82">
-        <v>0</v>
-      </c>
-      <c r="V82">
-        <v>57.33</v>
-      </c>
-      <c r="W82" t="s">
-        <v>180</v>
-      </c>
-      <c r="X82" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y82" t="s">
-        <v>174</v>
-      </c>
-      <c r="Z82" t="s">
-        <v>182</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/data/searchresults.xlsx
+++ b/data/searchresults.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f0ae25cf28fa736a/Projects/BIAutomations/shipment-schedule/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F10A70A-7723-48EF-A66A-71738EA4B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A2D82626-9ADA-470C-853A-00B4B9BF6E48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{48BBFA8D-9B83-4E36-9B43-62490879AC1B}"/>
+    <workbookView xWindow="4785" yWindow="1620" windowWidth="21600" windowHeight="11295" xr2:uid="{BAC8B229-39BB-4134-94FA-1E11BF2F8960}"/>
   </bookViews>
   <sheets>
     <sheet name="OPTSensiMedicalSalesOpenOrderR" sheetId="1" r:id="rId1"/>
@@ -2097,7 +2097,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C003B134-893F-42DF-8762-FC46CBAAE52D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CD22AA4-A119-45D6-8A72-DDE49C78076B}">
   <dimension ref="A1:Z116"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <sheetData>

--- a/data/searchresults.xlsx
+++ b/data/searchresults.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z44"/>
+  <dimension ref="A1:Z73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -559,26 +559,26 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>201052</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MCK : MCKESSON MEDICAL SURGICAL MD PC 201052</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SO154628</t>
+          <t>SO154855</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>36994536</t>
+          <t>4533295895</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -588,22 +588,22 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>7871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20164395C</t>
+          <t>20164396C</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1239964</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -612,17 +612,15 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>14262</v>
+        <v>15311</v>
       </c>
       <c r="N2" t="n">
-        <v>14005</v>
+        <v>15159</v>
       </c>
       <c r="O2" t="n">
-        <v>9</v>
-      </c>
-      <c r="P2" t="n">
-        <v>9</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
@@ -636,29 +634,29 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V2" t="n">
-        <v>36.86</v>
+        <v>47.46</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>3769 COMMERCE CENTER BLVD</t>
+          <t>Dixon, CA DC</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>BETHLEHEM</t>
+          <t>Dixon</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18015</t>
+          <t>95620</t>
         </is>
       </c>
     </row>
@@ -669,26 +667,26 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>201052</t>
+          <t>201001</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MCK : MCKESSON MEDICAL SURGICAL MD PC 201052</t>
+          <t>CAH : CARDINAL - MD DS 201001</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SO154633</t>
+          <t>SO154863</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>36994541</t>
+          <t>4231373081</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -698,22 +696,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>V7871800000</t>
+          <t>7871800002</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20164396C</t>
+          <t>20164395C</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1258911</t>
+          <t>7871800002</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -722,17 +720,15 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>15419</v>
+        <v>14145</v>
       </c>
       <c r="N3" t="n">
-        <v>15311</v>
+        <v>13553</v>
       </c>
       <c r="O3" t="n">
-        <v>5</v>
-      </c>
-      <c r="P3" t="n">
-        <v>5</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
@@ -746,29 +742,29 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V3" t="n">
-        <v>47.46</v>
+        <v>36.86</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>SEATTLE  #255</t>
+          <t>6441 MAIN ST</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>KENT</t>
+          <t>HOUSTON</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>WA</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>98032</t>
+          <t>770301502</t>
         </is>
       </c>
     </row>
@@ -779,26 +775,26 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>201052</t>
+          <t>202040</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MCK : MCKESSON MEDICAL SURGICAL MD PC 201052</t>
+          <t>CHS : CONCORDANCE HEALTHCARE SOLUTIONS, LLC 202040</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SO154633</t>
+          <t>SO154870</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>36994541</t>
+          <t>3591523</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -808,22 +804,22 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>V7871800002</t>
+          <t>7871800000</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20164397C</t>
+          <t>20164394C</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1258913</t>
+          <t>354861</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+          <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -832,16 +828,16 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>31433</v>
+        <v>4928</v>
       </c>
       <c r="N4" t="n">
-        <v>30547</v>
+        <v>4634</v>
       </c>
       <c r="O4" t="n">
-        <v>104</v>
+        <v>26</v>
       </c>
       <c r="P4" t="n">
-        <v>104</v>
+        <v>26</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -859,26 +855,26 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>29.4</v>
+        <v>57.33</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>SEATTLE  #255</t>
+          <t>60 DISTRIBUTION BOULEVARD</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>KENT</t>
+          <t>EDISON</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>WA</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>98032</t>
+          <t>08817</t>
         </is>
       </c>
     </row>
@@ -889,26 +885,26 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>201067</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SO154735</t>
+          <t>SO154908</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>16814</t>
+          <t>4519767997</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -928,7 +924,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>48741800002</t>
+          <t>O-T7871800002</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -942,13 +938,13 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>14262</v>
+        <v>14145</v>
       </c>
       <c r="N5" t="n">
-        <v>14005</v>
+        <v>13553</v>
       </c>
       <c r="O5" t="n">
-        <v>111</v>
+        <v>4</v>
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
@@ -964,29 +960,29 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>111</v>
+        <v>4</v>
       </c>
       <c r="V5" t="n">
-        <v>36.8598</v>
+        <v>36.86</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>7437 INDUSTRIAL BOULEVARD</t>
+          <t>735 COUNTY ROAD 4 EAST</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>ALLENTOWN</t>
+          <t>PRATTVILLE</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18106</t>
+          <t>36067</t>
         </is>
       </c>
     </row>
@@ -997,26 +993,26 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>201067</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SO154721</t>
+          <t>SO154908</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>04086</t>
+          <t>4519767997</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1026,22 +1022,22 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>V7871800000</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20164396C</t>
+          <t>20164397C</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>487471800000</t>
+          <t>O-T871800002</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1050,13 +1046,13 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>15419</v>
+        <v>30731</v>
       </c>
       <c r="N6" t="n">
-        <v>15311</v>
+        <v>29723</v>
       </c>
       <c r="O6" t="n">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="n">
@@ -1072,29 +1068,29 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="V6" t="n">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2151 COUNTY ROAD H2W</t>
+          <t>735 COUNTY ROAD 4 EAST</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>MOUNDS VIEW</t>
+          <t>PRATTVILLE</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>55112</t>
+          <t>36067</t>
         </is>
       </c>
     </row>
@@ -1105,26 +1101,26 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>201067</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SO154721</t>
+          <t>SO154909</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>04086</t>
+          <t>4519767998</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1144,7 +1140,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>487471800002</t>
+          <t>O-T871800002</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1158,13 +1154,13 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>31433</v>
+        <v>30731</v>
       </c>
       <c r="N7" t="n">
-        <v>30547</v>
+        <v>29723</v>
       </c>
       <c r="O7" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="n">
@@ -1180,19 +1176,19 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V7" t="n">
         <v>29.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2151 COUNTY ROAD H2W</t>
+          <t>13115 BROCKTON LANE N</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>MOUNDS VIEW</t>
+          <t>ROGERS</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1202,7 +1198,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>55112</t>
+          <t>55374</t>
         </is>
       </c>
     </row>
@@ -1213,26 +1209,26 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>201067</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SO154725</t>
+          <t>SO154911</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>05645</t>
+          <t>4519768000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1242,22 +1238,22 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>7871800000</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20164394C</t>
+          <t>20164397C</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>48741800000</t>
+          <t>O-T871800002</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1266,13 +1262,13 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>4928</v>
+        <v>30731</v>
       </c>
       <c r="N8" t="n">
-        <v>4928</v>
+        <v>29723</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="n">
@@ -1288,29 +1284,29 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="V8" t="n">
-        <v>57.33</v>
+        <v>29.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>202 COMMERCE BLVD.</t>
+          <t>500 SHARKEY DRIVE</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>KINGS MOUNTAIN</t>
+          <t>MAUMELLE</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>28086</t>
+          <t>72113</t>
         </is>
       </c>
     </row>
@@ -1321,26 +1317,26 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>201067</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SO154727</t>
+          <t>SO154917</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06858</t>
+          <t>4519768006</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1350,22 +1346,22 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>V7871800000</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20164396C</t>
+          <t>20164397C</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>487471800000</t>
+          <t>O-T871800002</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1374,13 +1370,13 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>15419</v>
+        <v>30731</v>
       </c>
       <c r="N9" t="n">
-        <v>15311</v>
+        <v>29723</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="n">
@@ -1396,29 +1392,29 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="V9" t="n">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>1805 NORTH LOOP 499 SUITE 130</t>
+          <t>1062 OLD DIXIE HIGHWAY</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>HARLINGEN</t>
+          <t>AUBURNDALE</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>78550</t>
+          <t>33823</t>
         </is>
       </c>
     </row>
@@ -1429,26 +1425,26 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>201067</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SO154730</t>
+          <t>SO154918</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>10054</t>
+          <t>4519768007</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1458,22 +1454,22 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7871800002</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20164395C</t>
+          <t>20164397C</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>48741800002</t>
+          <t>O-T871800002</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1482,13 +1478,13 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>14262</v>
+        <v>30731</v>
       </c>
       <c r="N10" t="n">
-        <v>14005</v>
+        <v>29723</v>
       </c>
       <c r="O10" t="n">
-        <v>42</v>
+        <v>140</v>
       </c>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="n">
@@ -1504,29 +1500,29 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>42</v>
+        <v>140</v>
       </c>
       <c r="V10" t="n">
-        <v>36.8598</v>
+        <v>29.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>8489 WESTSIDE INDUSTRIAL DRIVE</t>
+          <t>1960 W. MIRO WAY</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>JACKSONVILLE</t>
+          <t>RIALTO</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>32219</t>
+          <t>92376</t>
         </is>
       </c>
     </row>
@@ -1537,26 +1533,26 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>201067</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SO154730</t>
+          <t>SO154919</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>10054</t>
+          <t>4519768008</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1566,22 +1562,22 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>V7871800000</t>
+          <t>7871800000</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20164396C</t>
+          <t>20164394C</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>487471800000</t>
+          <t>O-T71800000</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+          <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1590,13 +1586,13 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>15419</v>
+        <v>4928</v>
       </c>
       <c r="N11" t="n">
-        <v>15311</v>
+        <v>4634</v>
       </c>
       <c r="O11" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="n">
@@ -1612,29 +1608,29 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="V11" t="n">
-        <v>47.46</v>
+        <v>57.33</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>8489 WESTSIDE INDUSTRIAL DRIVE</t>
+          <t>29895 US HWY 90 BUS</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>JACKSONVILLE</t>
+          <t>KATY</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>32219</t>
+          <t>77494</t>
         </is>
       </c>
     </row>
@@ -1645,26 +1641,26 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>201067</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SO154730</t>
+          <t>SO154919</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>10054</t>
+          <t>4519768008</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1674,22 +1670,22 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>V7871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20164397C</t>
+          <t>20164396C</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>487471800002</t>
+          <t>O-T7871800000</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1698,13 +1694,13 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>31433</v>
+        <v>15311</v>
       </c>
       <c r="N12" t="n">
-        <v>30547</v>
+        <v>15159</v>
       </c>
       <c r="O12" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="n">
@@ -1720,29 +1716,29 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="V12" t="n">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>8489 WESTSIDE INDUSTRIAL DRIVE</t>
+          <t>29895 US HWY 90 BUS</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>JACKSONVILLE</t>
+          <t>KATY</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>32219</t>
+          <t>77494</t>
         </is>
       </c>
     </row>
@@ -1753,26 +1749,26 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>201067</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SO154733</t>
+          <t>SO154920</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>15591</t>
+          <t>4519768009</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1782,22 +1778,22 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>V7871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20164397C</t>
+          <t>20164396C</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>487471800002</t>
+          <t>O-T7871800000</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1806,13 +1802,13 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>31433</v>
+        <v>15311</v>
       </c>
       <c r="N13" t="n">
-        <v>30547</v>
+        <v>15159</v>
       </c>
       <c r="O13" t="n">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="n">
@@ -1828,29 +1824,29 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="V13" t="n">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>326 U.S. HIGHWAY 49 SOUTH</t>
+          <t>5000 Premier Parkway, Suite 100</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>RICHLAND</t>
+          <t>Saint Peters</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>39218</t>
+          <t>63376</t>
         </is>
       </c>
     </row>
@@ -1861,26 +1857,26 @@
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>201067</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SO154743</t>
+          <t>SO154920</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>22732</t>
+          <t>4519768009</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1900,7 +1896,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>487471800002</t>
+          <t>O-T871800002</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1914,13 +1910,13 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>31433</v>
+        <v>30731</v>
       </c>
       <c r="N14" t="n">
-        <v>30547</v>
+        <v>29723</v>
       </c>
       <c r="O14" t="n">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="n">
@@ -1936,29 +1932,29 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="V14" t="n">
         <v>29.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>1425 MAGELLAN ROAD</t>
+          <t>5000 Premier Parkway, Suite 100</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>HANOVER</t>
+          <t>Saint Peters</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>21076</t>
+          <t>63376</t>
         </is>
       </c>
     </row>
@@ -1969,26 +1965,26 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>201067</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SO154745</t>
+          <t>SO154922</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>24198</t>
+          <t>4519768011</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2008,7 +2004,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>487471800000</t>
+          <t>O-T7871800000</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2022,13 +2018,13 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>15419</v>
+        <v>15311</v>
       </c>
       <c r="N15" t="n">
-        <v>15311</v>
+        <v>15159</v>
       </c>
       <c r="O15" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="n">
@@ -2044,29 +2040,29 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="V15" t="n">
         <v>47.46</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>14599 NW 8TH STREET</t>
+          <t>1040 ENTERPRISE PARKWAY</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>SUNRISE</t>
+          <t>WEST JEFFERSON</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>33325</t>
+          <t>43162</t>
         </is>
       </c>
     </row>
@@ -2077,26 +2073,26 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>201067</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SO154753</t>
+          <t>SO154922</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>35973</t>
+          <t>4519768011</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2116,7 +2112,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>48741800002</t>
+          <t>O-T7871800002</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2130,13 +2126,13 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>14262</v>
+        <v>14145</v>
       </c>
       <c r="N16" t="n">
-        <v>14005</v>
+        <v>13553</v>
       </c>
       <c r="O16" t="n">
-        <v>59</v>
+        <v>210</v>
       </c>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="n">
@@ -2152,19 +2148,19 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>59</v>
+        <v>210</v>
       </c>
       <c r="V16" t="n">
-        <v>36.8598</v>
+        <v>36.86</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>1160 MARQUETTE STREET</t>
+          <t>1040 ENTERPRISE PARKWAY</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>CLEVELAND</t>
+          <t>WEST JEFFERSON</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2174,7 +2170,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>44114</t>
+          <t>43162</t>
         </is>
       </c>
     </row>
@@ -2185,26 +2181,26 @@
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>201067</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SO154754</t>
+          <t>SO154922</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>38913</t>
+          <t>4519768011</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2214,22 +2210,22 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>V7871800000</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20164396C</t>
+          <t>20164397C</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>487471800000</t>
+          <t>O-T871800002</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2238,13 +2234,13 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>15419</v>
+        <v>30731</v>
       </c>
       <c r="N17" t="n">
-        <v>15311</v>
+        <v>29723</v>
       </c>
       <c r="O17" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="n">
@@ -2260,29 +2256,29 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="V17" t="n">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>36663 VAN BORN RD</t>
+          <t>1040 ENTERPRISE PARKWAY</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>ROMULUS</t>
+          <t>WEST JEFFERSON</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>48174</t>
+          <t>43162</t>
         </is>
       </c>
     </row>
@@ -2293,26 +2289,26 @@
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>201067</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SO154754</t>
+          <t>SO154924</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>38913</t>
+          <t>4519768013</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2332,7 +2328,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>487471800002</t>
+          <t>O-T871800002</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2346,13 +2342,13 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>31433</v>
+        <v>30731</v>
       </c>
       <c r="N18" t="n">
-        <v>30547</v>
+        <v>29723</v>
       </c>
       <c r="O18" t="n">
-        <v>184</v>
+        <v>140</v>
       </c>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="n">
@@ -2368,29 +2364,29 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>184</v>
+        <v>140</v>
       </c>
       <c r="V18" t="n">
         <v>29.4</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>36663 VAN BORN RD</t>
+          <t>5701 PROMONTORY PARKWAY</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>ROMULUS</t>
+          <t>TRACY</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>48174</t>
+          <t>95377</t>
         </is>
       </c>
     </row>
@@ -2401,26 +2397,26 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>201067</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SO154756</t>
+          <t>SO154931</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>40247</t>
+          <t>4519768020</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2430,22 +2426,22 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>7871800000</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20164394C</t>
+          <t>20164397C</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>48741800000</t>
+          <t>O-T871800002</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2454,13 +2450,13 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>4928</v>
+        <v>30731</v>
       </c>
       <c r="N19" t="n">
-        <v>4928</v>
+        <v>29723</v>
       </c>
       <c r="O19" t="n">
-        <v>87</v>
+        <v>210</v>
       </c>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="n">
@@ -2476,29 +2472,29 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>87</v>
+        <v>210</v>
       </c>
       <c r="V19" t="n">
-        <v>57.33</v>
+        <v>29.4</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>550 LAKESIDE PARKWAY</t>
+          <t>3770 HOGUM BAY RD. NE</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>FLOWER MOUND</t>
+          <t>LACEY</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>WA</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>75028</t>
+          <t>98516</t>
         </is>
       </c>
     </row>
@@ -2509,26 +2505,26 @@
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>201067</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SO154756</t>
+          <t>SO154933</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>40247</t>
+          <t>4519768022</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2548,7 +2544,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>48741800002</t>
+          <t>O-T7871800002</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2562,13 +2558,13 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>14262</v>
+        <v>14145</v>
       </c>
       <c r="N20" t="n">
-        <v>14005</v>
+        <v>13553</v>
       </c>
       <c r="O20" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="n">
@@ -2584,29 +2580,29 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="V20" t="n">
-        <v>36.8598</v>
+        <v>36.86</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>550 LAKESIDE PARKWAY</t>
+          <t>600 DERBY AVENUE</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>FLOWER MOUND</t>
+          <t>WEST HAVEN</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>75028</t>
+          <t>06516</t>
         </is>
       </c>
     </row>
@@ -2617,26 +2613,26 @@
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>201067</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SO154757</t>
+          <t>SO154902</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>40677</t>
+          <t>4519767991</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2646,22 +2642,22 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>V7871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20164397C</t>
+          <t>20164396C</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>487471800002</t>
+          <t>O-T7871800000</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2670,13 +2666,13 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>31433</v>
+        <v>15311</v>
       </c>
       <c r="N21" t="n">
-        <v>30547</v>
+        <v>15159</v>
       </c>
       <c r="O21" t="n">
-        <v>195</v>
+        <v>16</v>
       </c>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="n">
@@ -2692,29 +2688,29 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>195</v>
+        <v>16</v>
       </c>
       <c r="V21" t="n">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>4807 NE 63RD AVENUE</t>
+          <t>1 MEDLINE DRIVE, SUITE 100</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>GAINESVILLE</t>
+          <t>WILMER</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>32609</t>
+          <t>75172</t>
         </is>
       </c>
     </row>
@@ -2725,26 +2721,26 @@
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>201067</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SO154763</t>
+          <t>SO154902</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>60075</t>
+          <t>4519767991</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2764,7 +2760,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>48741800002</t>
+          <t>O-T7871800002</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2778,13 +2774,13 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>14262</v>
+        <v>14145</v>
       </c>
       <c r="N22" t="n">
-        <v>14005</v>
+        <v>13553</v>
       </c>
       <c r="O22" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="n">
@@ -2800,29 +2796,29 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="V22" t="n">
-        <v>36.8598</v>
+        <v>36.86</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>4301 W VALLEY HWY EAST</t>
+          <t>1 MEDLINE DRIVE, SUITE 100</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>SUMNER</t>
+          <t>WILMER</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>WA</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>98390</t>
+          <t>75172</t>
         </is>
       </c>
     </row>
@@ -2833,26 +2829,26 @@
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>201067</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SO154764</t>
+          <t>SO154902</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61288</t>
+          <t>4519767991</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2862,22 +2858,22 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>7871800000</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>20164394C</t>
+          <t>20164397C</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>48741800000</t>
+          <t>O-T871800002</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2886,13 +2882,13 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>4928</v>
+        <v>30731</v>
       </c>
       <c r="N23" t="n">
-        <v>4928</v>
+        <v>29723</v>
       </c>
       <c r="O23" t="n">
-        <v>179</v>
+        <v>48</v>
       </c>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="n">
@@ -2908,29 +2904,29 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>179</v>
+        <v>48</v>
       </c>
       <c r="V23" t="n">
-        <v>57.33</v>
+        <v>29.4</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>8313 WEST PIERCE STREET, SUITE 100</t>
+          <t>1 MEDLINE DRIVE, SUITE 100</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>TOLLESON</t>
+          <t>WILMER</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>85353</t>
+          <t>75172</t>
         </is>
       </c>
     </row>
@@ -2941,26 +2937,26 @@
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>201067</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SO154764</t>
+          <t>SO154906</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61288</t>
+          <t>4519767995</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2980,7 +2976,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>487471800000</t>
+          <t>O-T7871800000</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2994,13 +2990,13 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>15419</v>
+        <v>15311</v>
       </c>
       <c r="N24" t="n">
-        <v>15311</v>
+        <v>15159</v>
       </c>
       <c r="O24" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="n">
@@ -3016,29 +3012,29 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="V24" t="n">
         <v>47.46</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>8313 WEST PIERCE STREET, SUITE 100</t>
+          <t>1401 N. UNIVERSAL AVE.</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>TOLLESON</t>
+          <t>KANSAS CITY</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>85353</t>
+          <t>64120</t>
         </is>
       </c>
     </row>
@@ -3049,26 +3045,26 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>201067</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SO154769</t>
+          <t>SO154910</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>70270</t>
+          <t>4519767999</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3078,22 +3074,22 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>V7871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>20164397C</t>
+          <t>20164396C</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>487471800002</t>
+          <t>O-T7871800000</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -3102,13 +3098,13 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>31433</v>
+        <v>15311</v>
       </c>
       <c r="N25" t="n">
-        <v>30547</v>
+        <v>15159</v>
       </c>
       <c r="O25" t="n">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="n">
@@ -3124,29 +3120,29 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="V25" t="n">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>1880 NORTH CORRINGTON AVE</t>
+          <t>1900 MEADOWVILLE TECHNOLOGY</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>KANSAS CITY</t>
+          <t>CHESTER</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>64120</t>
+          <t>23834</t>
         </is>
       </c>
     </row>
@@ -3157,26 +3153,26 @@
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>201067</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SO154771</t>
+          <t>SO154910</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>79001</t>
+          <t>4519767999</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3186,22 +3182,22 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>7871800002</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>20164395C</t>
+          <t>20164397C</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>48741800002</t>
+          <t>O-T871800002</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3210,13 +3206,13 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>14262</v>
+        <v>30731</v>
       </c>
       <c r="N26" t="n">
-        <v>14005</v>
+        <v>29723</v>
       </c>
       <c r="O26" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="n">
@@ -3232,29 +3228,29 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="V26" t="n">
-        <v>36.8598</v>
+        <v>29.4</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>27695 S.W. 95th AVENUE</t>
+          <t>1900 MEADOWVILLE TECHNOLOGY</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>WILSONVILLE</t>
+          <t>CHESTER</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>97070</t>
+          <t>23834</t>
         </is>
       </c>
     </row>
@@ -3265,26 +3261,26 @@
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>46100</v>
+        <v>46107</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>209214</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VENTURE RESPIRATORY INC. 209214</t>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SO154426</t>
+          <t>SO154912</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>17823</t>
+          <t>4519768001</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3294,18 +3290,22 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>7871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>20164395C</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
+          <t>20164396C</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>O-T7871800000</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3314,17 +3314,15 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>14262</v>
+        <v>15311</v>
       </c>
       <c r="N27" t="n">
-        <v>14005</v>
+        <v>15159</v>
       </c>
       <c r="O27" t="n">
-        <v>140</v>
-      </c>
-      <c r="P27" t="n">
-        <v>140</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
@@ -3338,29 +3336,29 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V27" t="n">
-        <v>36.86</v>
+        <v>47.46</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>630 Herman Rd</t>
+          <t>1989 TRANSIT WAY</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>JACKSON</t>
+          <t>BROCKPORT</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>08527</t>
+          <t>14420</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3369,7 @@
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>46100</v>
+        <v>46107</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3385,12 +3383,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SO154447</t>
+          <t>SO154912</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>4519740417</t>
+          <t>4519768001</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3424,17 +3422,15 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>31433</v>
+        <v>30731</v>
       </c>
       <c r="N28" t="n">
-        <v>30547</v>
+        <v>29723</v>
       </c>
       <c r="O28" t="n">
-        <v>29</v>
-      </c>
-      <c r="P28" t="n">
-        <v>29</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="P28" t="inlineStr"/>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
@@ -3448,29 +3444,29 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="V28" t="n">
         <v>29.4</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>92 SOUTHEAST 223rd AVENUE</t>
+          <t>1989 TRANSIT WAY</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>GRESHAM</t>
+          <t>BROCKPORT</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>97030</t>
+          <t>14420</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3477,7 @@
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>46100</v>
+        <v>46107</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3495,12 +3491,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SO154452</t>
+          <t>SO154913</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>4519740423</t>
+          <t>4519768002</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3534,17 +3530,15 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>14262</v>
+        <v>14145</v>
       </c>
       <c r="N29" t="n">
-        <v>14005</v>
+        <v>13553</v>
       </c>
       <c r="O29" t="n">
-        <v>27</v>
-      </c>
-      <c r="P29" t="n">
-        <v>27</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="P29" t="inlineStr"/>
       <c r="Q29" t="n">
         <v>0</v>
       </c>
@@ -3558,7 +3552,7 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="V29" t="n">
         <v>36.86</v>
@@ -3591,7 +3585,7 @@
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>46100</v>
+        <v>46107</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3605,12 +3599,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SO154465</t>
+          <t>SO154914</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>4519740438</t>
+          <t>4519768003</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3620,22 +3614,22 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>V7871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>20164397C</t>
+          <t>20164396C</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>O-T871800002</t>
+          <t>O-T7871800000</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3644,53 +3638,51 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>31433</v>
+        <v>15311</v>
       </c>
       <c r="N30" t="n">
-        <v>30547</v>
+        <v>15159</v>
       </c>
       <c r="O30" t="n">
-        <v>4</v>
-      </c>
-      <c r="P30" t="n">
-        <v>4</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="P30" t="inlineStr"/>
       <c r="Q30" t="n">
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="V30" t="n">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>8787 W BUCKEYE ROAD</t>
+          <t>60 ATHLETES WAY</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>TOLLESON</t>
+          <t>MOUNT JULIET</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>85353</t>
+          <t>37122</t>
         </is>
       </c>
     </row>
@@ -3701,26 +3693,26 @@
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>46097</v>
+        <v>46107</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>201003</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CAH : CARDINAL - MD 201003</t>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SO154143</t>
+          <t>SO154914</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>4533277020</t>
+          <t>4519768003</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3740,7 +3732,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>V7871800002</t>
+          <t>O-T871800002</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3754,17 +3746,15 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>31433</v>
+        <v>30731</v>
       </c>
       <c r="N31" t="n">
-        <v>30547</v>
+        <v>29723</v>
       </c>
       <c r="O31" t="n">
-        <v>44</v>
-      </c>
-      <c r="P31" t="n">
-        <v>44</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="P31" t="inlineStr"/>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
@@ -3778,29 +3768,29 @@
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="V31" t="n">
         <v>29.4</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>1901 RAYMER AVENUE</t>
+          <t>60 ATHLETES WAY</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Fullerton</t>
+          <t>MOUNT JULIET</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>92833</t>
+          <t>37122</t>
         </is>
       </c>
     </row>
@@ -3811,7 +3801,7 @@
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>46093</v>
+        <v>46107</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3825,12 +3815,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SO154020</t>
+          <t>SO154915</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>4519714408</t>
+          <t>4519768004</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3840,22 +3830,22 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>7871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>20164395C</t>
+          <t>20164396C</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>O-T7871800002</t>
+          <t>O-T7871800000</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3864,17 +3854,15 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>14262</v>
+        <v>15311</v>
       </c>
       <c r="N32" t="n">
-        <v>14005</v>
+        <v>15159</v>
       </c>
       <c r="O32" t="n">
-        <v>39</v>
-      </c>
-      <c r="P32" t="n">
-        <v>39</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="P32" t="inlineStr"/>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
@@ -3888,29 +3876,29 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="V32" t="n">
-        <v>36.86</v>
+        <v>47.46</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>36445 VAN BORN ROAD</t>
+          <t>2200 Cornerstone Parkway, Suite 100</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>ROMULUS</t>
+          <t>Grayslake</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>48174</t>
+          <t>60030</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3909,7 @@
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>46093</v>
+        <v>46107</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3935,12 +3923,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SO154033</t>
+          <t>SO154915</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>4519714421</t>
+          <t>4519768004</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3950,22 +3938,22 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>V7871800000</t>
+          <t>7871800002</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20164396C</t>
+          <t>20164395C</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>O-T7871800000</t>
+          <t>O-T7871800002</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3974,53 +3962,51 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>15419</v>
+        <v>14145</v>
       </c>
       <c r="N33" t="n">
-        <v>15311</v>
+        <v>13553</v>
       </c>
       <c r="O33" t="n">
-        <v>18</v>
-      </c>
-      <c r="P33" t="n">
-        <v>18</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="P33" t="inlineStr"/>
       <c r="Q33" t="n">
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V33" t="n">
-        <v>47.46</v>
+        <v>36.86</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>8787 W BUCKEYE ROAD</t>
+          <t>2200 Cornerstone Parkway, Suite 100</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>TOLLESON</t>
+          <t>Grayslake</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>85353</t>
+          <t>60030</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4017,7 @@
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>46093</v>
+        <v>46107</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4045,12 +4031,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SO154033</t>
+          <t>SO154916</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>4519714421</t>
+          <t>4519768005</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4060,22 +4046,22 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>V7871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>20164397C</t>
+          <t>20164396C</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>O-T871800002</t>
+          <t>O-T7871800000</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -4084,53 +4070,51 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>31433</v>
+        <v>15311</v>
       </c>
       <c r="N34" t="n">
-        <v>30547</v>
+        <v>15159</v>
       </c>
       <c r="O34" t="n">
-        <v>54</v>
-      </c>
-      <c r="P34" t="n">
-        <v>54</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="P34" t="inlineStr"/>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="V34" t="n">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>8787 W BUCKEYE ROAD</t>
+          <t>1500 MEDLINE PLACE</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>TOLLESON</t>
+          <t>MC DONOUGH</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>85353</t>
+          <t>30253</t>
         </is>
       </c>
     </row>
@@ -4141,7 +4125,7 @@
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>46093</v>
+        <v>46107</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4155,12 +4139,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SO154038</t>
+          <t>SO154921</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>4519714426</t>
+          <t>4519768010</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4170,22 +4154,22 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>V7871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>20164397C</t>
+          <t>20164396C</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>O-T871800002</t>
+          <t>O-T7871800000</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -4194,53 +4178,51 @@
         </is>
       </c>
       <c r="M35" t="n">
-        <v>31433</v>
+        <v>15311</v>
       </c>
       <c r="N35" t="n">
-        <v>30547</v>
+        <v>15159</v>
       </c>
       <c r="O35" t="n">
-        <v>140</v>
-      </c>
-      <c r="P35" t="n">
-        <v>140</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="P35" t="inlineStr"/>
       <c r="Q35" t="n">
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="V35" t="n">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>3770 HOGUM BAY RD. NE</t>
+          <t>81 CAMPANELLI DRIVE</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>LACEY</t>
+          <t>UXBRIDGE</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>WA</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>98516</t>
+          <t>01569</t>
         </is>
       </c>
     </row>
@@ -4251,7 +4233,7 @@
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>46093</v>
+        <v>46107</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4265,12 +4247,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>SO154037</t>
+          <t>SO154921</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>4519714425</t>
+          <t>4519768010</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4280,22 +4262,22 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>V7871800000</t>
+          <t>7871800002</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>20164396C</t>
+          <t>20164395C</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>O-T787180000H</t>
+          <t>O-T7871800002</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -4304,17 +4286,15 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>15419</v>
+        <v>14145</v>
       </c>
       <c r="N36" t="n">
-        <v>15311</v>
+        <v>13553</v>
       </c>
       <c r="O36" t="n">
-        <v>27</v>
-      </c>
-      <c r="P36" t="n">
-        <v>27</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="P36" t="inlineStr"/>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
@@ -4328,29 +4308,29 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="V36" t="n">
-        <v>47.46</v>
+        <v>36.86</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>264 SOUTH 5750 WEST</t>
+          <t>81 CAMPANELLI DRIVE</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>SALT LAKE CITY</t>
+          <t>UXBRIDGE</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>UT</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>84104</t>
+          <t>01569</t>
         </is>
       </c>
     </row>
@@ -4361,7 +4341,7 @@
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>46093</v>
+        <v>46107</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4375,12 +4355,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SO154037</t>
+          <t>SO154921</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>4519714425</t>
+          <t>4519768010</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4414,17 +4394,15 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>31433</v>
+        <v>30731</v>
       </c>
       <c r="N37" t="n">
-        <v>30547</v>
+        <v>29723</v>
       </c>
       <c r="O37" t="n">
-        <v>210</v>
-      </c>
-      <c r="P37" t="n">
-        <v>210</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="P37" t="inlineStr"/>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
@@ -4438,29 +4416,29 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="V37" t="n">
         <v>29.4</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>264 SOUTH 5750 WEST</t>
+          <t>81 CAMPANELLI DRIVE</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>SALT LAKE CITY</t>
+          <t>UXBRIDGE</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>UT</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>84104</t>
+          <t>01569</t>
         </is>
       </c>
     </row>
@@ -4471,7 +4449,7 @@
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>46093</v>
+        <v>46107</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4485,12 +4463,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SO154014</t>
+          <t>SO154925</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>4519714402</t>
+          <t>4519768014</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4500,22 +4478,22 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>V7871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>20164397C</t>
+          <t>20164396C</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>O-T871800002</t>
+          <t>O-T7871800000</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4524,17 +4502,15 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>31433</v>
+        <v>15311</v>
       </c>
       <c r="N38" t="n">
-        <v>30547</v>
+        <v>15159</v>
       </c>
       <c r="O38" t="n">
-        <v>71</v>
-      </c>
-      <c r="P38" t="n">
-        <v>71</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="P38" t="inlineStr"/>
       <c r="Q38" t="n">
         <v>0</v>
       </c>
@@ -4548,29 +4524,29 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="V38" t="n">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>92 SOUTHEAST 223rd AVENUE</t>
+          <t>239 BELVIDERE ROAD</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>GRESHAM</t>
+          <t>PERRYVILLE</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>97030</t>
+          <t>21903</t>
         </is>
       </c>
     </row>
@@ -4581,7 +4557,7 @@
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>46086</v>
+        <v>46107</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4595,12 +4571,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SO153506</t>
+          <t>SO154925</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>4519685481</t>
+          <t>4519768014</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4610,22 +4586,22 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>V7871800000</t>
+          <t>7871800002</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>20164396C</t>
+          <t>20164395C</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>O-T787180000H</t>
+          <t>O-T7871800002</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4634,17 +4610,15 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>15419</v>
+        <v>14145</v>
       </c>
       <c r="N39" t="n">
-        <v>15311</v>
+        <v>13553</v>
       </c>
       <c r="O39" t="n">
-        <v>27</v>
-      </c>
-      <c r="P39" t="n">
-        <v>27</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="P39" t="inlineStr"/>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
@@ -4658,29 +4632,29 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="V39" t="n">
-        <v>47.46</v>
+        <v>36.86</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>264 SOUTH 5750 WEST</t>
+          <t>239 BELVIDERE ROAD</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>SALT LAKE CITY</t>
+          <t>PERRYVILLE</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>UT</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>84104</t>
+          <t>21903</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4665,7 @@
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>46086</v>
+        <v>46107</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4705,12 +4679,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SO153506</t>
+          <t>SO154925</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>4519685481</t>
+          <t>4519768014</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4744,17 +4718,15 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>31433</v>
+        <v>30731</v>
       </c>
       <c r="N40" t="n">
-        <v>30547</v>
+        <v>29723</v>
       </c>
       <c r="O40" t="n">
-        <v>140</v>
-      </c>
-      <c r="P40" t="n">
-        <v>140</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="P40" t="inlineStr"/>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
@@ -4768,29 +4740,29 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="V40" t="n">
         <v>29.4</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>264 SOUTH 5750 WEST</t>
+          <t>239 BELVIDERE ROAD</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>SALT LAKE CITY</t>
+          <t>PERRYVILLE</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>UT</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>84104</t>
+          <t>21903</t>
         </is>
       </c>
     </row>
@@ -4801,7 +4773,7 @@
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>46086</v>
+        <v>46107</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4815,12 +4787,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SO153489</t>
+          <t>SO154927</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>4519685464</t>
+          <t>4519768016</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -4830,22 +4802,22 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>7871800002</t>
+          <t>7871800000</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>20164395C</t>
+          <t>20164394C</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>O-T7871800002</t>
+          <t>O-T71800000</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+          <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4854,17 +4826,15 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>14262</v>
+        <v>4928</v>
       </c>
       <c r="N41" t="n">
-        <v>14005</v>
+        <v>4634</v>
       </c>
       <c r="O41" t="n">
-        <v>42</v>
-      </c>
-      <c r="P41" t="n">
-        <v>42</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="P41" t="inlineStr"/>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
@@ -4878,29 +4848,29 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="V41" t="n">
-        <v>36.86</v>
+        <v>57.33</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>36445 VAN BORN ROAD</t>
+          <t>494 State Route 416</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>ROMULUS</t>
+          <t>Montgomery</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>48174</t>
+          <t>12549</t>
         </is>
       </c>
     </row>
@@ -4911,7 +4881,7 @@
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>46086</v>
+        <v>46107</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4925,12 +4895,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SO153502</t>
+          <t>SO154927</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>4519685477</t>
+          <t>4519768016</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -4964,53 +4934,51 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>15419</v>
+        <v>15311</v>
       </c>
       <c r="N42" t="n">
-        <v>15311</v>
+        <v>15159</v>
       </c>
       <c r="O42" t="n">
-        <v>31</v>
-      </c>
-      <c r="P42" t="n">
-        <v>31</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="P42" t="inlineStr"/>
       <c r="Q42" t="n">
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="V42" t="n">
         <v>47.46</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>8787 W BUCKEYE ROAD</t>
+          <t>494 State Route 416</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>TOLLESON</t>
+          <t>Montgomery</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>85353</t>
+          <t>12549</t>
         </is>
       </c>
     </row>
@@ -5021,7 +4989,7 @@
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>46086</v>
+        <v>46107</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5035,12 +5003,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SO153502</t>
+          <t>SO154927</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>4519685477</t>
+          <t>4519768016</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -5050,22 +5018,22 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>V7871800002</t>
+          <t>7871800002</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>20164397C</t>
+          <t>20164395C</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>O-T871800002</t>
+          <t>O-T7871800002</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -5074,53 +5042,51 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>31433</v>
+        <v>14145</v>
       </c>
       <c r="N43" t="n">
-        <v>30547</v>
+        <v>13553</v>
       </c>
       <c r="O43" t="n">
-        <v>60</v>
-      </c>
-      <c r="P43" t="n">
-        <v>60</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="P43" t="inlineStr"/>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V43" t="n">
-        <v>29.4</v>
+        <v>36.86</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>8787 W BUCKEYE ROAD</t>
+          <t>494 State Route 416</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>TOLLESON</t>
+          <t>Montgomery</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>85353</t>
+          <t>12549</t>
         </is>
       </c>
     </row>
@@ -5131,7 +5097,7 @@
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>46086</v>
+        <v>46107</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5145,12 +5111,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SO153483</t>
+          <t>SO154927</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>4519685458</t>
+          <t>4519768016</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -5184,53 +5150,3229 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>31433</v>
+        <v>30731</v>
       </c>
       <c r="N44" t="n">
-        <v>30547</v>
+        <v>29723</v>
       </c>
       <c r="O44" t="n">
-        <v>30</v>
-      </c>
-      <c r="P44" t="n">
-        <v>30</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="P44" t="inlineStr"/>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="V44" t="n">
         <v>29.4</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
+          <t>494 State Route 416</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Montgomery</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>12549</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B45" s="1" t="n">
+        <v>46107</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>SO154930</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>4519768019</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>V7871800002</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>20164397C</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>O-T871800002</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>30731</v>
+      </c>
+      <c r="N45" t="n">
+        <v>29723</v>
+      </c>
+      <c r="O45" t="n">
+        <v>140</v>
+      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>140</v>
+      </c>
+      <c r="V45" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>264 SOUTH 5750 WEST</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>SALT LAKE CITY</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>84104</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B46" s="1" t="n">
+        <v>46107</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>SO154932</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>4519768021</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>V7871800002</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>20164397C</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O-T871800002</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>30731</v>
+      </c>
+      <c r="N46" t="n">
+        <v>29723</v>
+      </c>
+      <c r="O46" t="n">
+        <v>11</v>
+      </c>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>11</v>
+      </c>
+      <c r="V46" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>251 HILTON DRIVE</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>JEFFERSONVILLE</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>47130</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B47" s="1" t="n">
+        <v>46107</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>SO154907</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>4519767996</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>V7871800002</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>20164397C</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>O-T871800002</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
+        <v>30731</v>
+      </c>
+      <c r="N47" t="n">
+        <v>29723</v>
+      </c>
+      <c r="O47" t="n">
+        <v>70</v>
+      </c>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>70</v>
+      </c>
+      <c r="V47" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
           <t>92 SOUTHEAST 223rd AVENUE</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>GRESHAM</t>
         </is>
       </c>
-      <c r="Y44" t="inlineStr">
+      <c r="Y47" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
+      <c r="Z47" t="inlineStr">
         <is>
           <t>97030</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B48" s="1" t="n">
+        <v>46107</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>SO154926</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>4519768015</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>V7871800002</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>20164397C</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>O-T871800002</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M48" t="n">
+        <v>30731</v>
+      </c>
+      <c r="N48" t="n">
+        <v>29723</v>
+      </c>
+      <c r="O48" t="n">
+        <v>39</v>
+      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>39</v>
+      </c>
+      <c r="V48" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>8787 W BUCKEYE ROAD</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>TOLLESON</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>85353</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B49" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>201067</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>SO154735</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>16814</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>7871800002</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>20164395C</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>48741800002</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M49" t="n">
+        <v>14145</v>
+      </c>
+      <c r="N49" t="n">
+        <v>13553</v>
+      </c>
+      <c r="O49" t="n">
+        <v>111</v>
+      </c>
+      <c r="P49" t="n">
+        <v>111</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>36.8598</v>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>7437 INDUSTRIAL BOULEVARD</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>ALLENTOWN</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>18106</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B50" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>201067</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>SO154721</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>04086</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>V7871800000</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>20164396C</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>487471800000</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M50" t="n">
+        <v>15311</v>
+      </c>
+      <c r="N50" t="n">
+        <v>15159</v>
+      </c>
+      <c r="O50" t="n">
+        <v>57</v>
+      </c>
+      <c r="P50" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>47.46</v>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>2151 COUNTY ROAD H2W</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>MOUNDS VIEW</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>MN</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>55112</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B51" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>201067</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>SO154721</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>04086</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>V7871800002</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>20164397C</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>487471800002</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M51" t="n">
+        <v>30731</v>
+      </c>
+      <c r="N51" t="n">
+        <v>29723</v>
+      </c>
+      <c r="O51" t="n">
+        <v>72</v>
+      </c>
+      <c r="P51" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>2151 COUNTY ROAD H2W</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>MOUNDS VIEW</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>MN</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>55112</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B52" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>201067</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>SO154725</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>05645</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>7871800000</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>20164394C</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>48741800000</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
+        <v>4928</v>
+      </c>
+      <c r="N52" t="n">
+        <v>4634</v>
+      </c>
+      <c r="O52" t="n">
+        <v>2</v>
+      </c>
+      <c r="P52" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" t="n">
+        <v>57.33</v>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>202 COMMERCE BLVD.</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>KINGS MOUNTAIN</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>28086</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B53" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>201067</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>SO154727</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>06858</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>V7871800000</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>20164396C</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>487471800000</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M53" t="n">
+        <v>15311</v>
+      </c>
+      <c r="N53" t="n">
+        <v>15159</v>
+      </c>
+      <c r="O53" t="n">
+        <v>1</v>
+      </c>
+      <c r="P53" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>47.46</v>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>1805 NORTH LOOP 499 SUITE 130</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>HARLINGEN</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>78550</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B54" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>201067</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>SO154730</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>10054</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>7871800002</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>20164395C</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>48741800002</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M54" t="n">
+        <v>14145</v>
+      </c>
+      <c r="N54" t="n">
+        <v>13553</v>
+      </c>
+      <c r="O54" t="n">
+        <v>42</v>
+      </c>
+      <c r="P54" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" t="n">
+        <v>36.8598</v>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>8489 WESTSIDE INDUSTRIAL DRIVE</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>JACKSONVILLE</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>32219</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B55" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>201067</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>SO154730</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>10054</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>V7871800000</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>20164396C</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>487471800000</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M55" t="n">
+        <v>15311</v>
+      </c>
+      <c r="N55" t="n">
+        <v>15159</v>
+      </c>
+      <c r="O55" t="n">
+        <v>1</v>
+      </c>
+      <c r="P55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" t="n">
+        <v>47.46</v>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>8489 WESTSIDE INDUSTRIAL DRIVE</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>JACKSONVILLE</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>32219</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B56" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>201067</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>SO154730</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>10054</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>V7871800002</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>20164397C</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>487471800002</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M56" t="n">
+        <v>30731</v>
+      </c>
+      <c r="N56" t="n">
+        <v>29723</v>
+      </c>
+      <c r="O56" t="n">
+        <v>140</v>
+      </c>
+      <c r="P56" t="n">
+        <v>140</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>8489 WESTSIDE INDUSTRIAL DRIVE</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>JACKSONVILLE</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>32219</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B57" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>201067</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>SO154733</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>15591</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>V7871800002</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>20164397C</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>487471800002</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M57" t="n">
+        <v>30731</v>
+      </c>
+      <c r="N57" t="n">
+        <v>29723</v>
+      </c>
+      <c r="O57" t="n">
+        <v>87</v>
+      </c>
+      <c r="P57" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>326 U.S. HIGHWAY 49 SOUTH</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>RICHLAND</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>39218</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B58" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>201067</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>SO154743</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>22732</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>V7871800002</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>20164397C</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>487471800002</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M58" t="n">
+        <v>30731</v>
+      </c>
+      <c r="N58" t="n">
+        <v>29723</v>
+      </c>
+      <c r="O58" t="n">
+        <v>92</v>
+      </c>
+      <c r="P58" t="n">
+        <v>92</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>1425 MAGELLAN ROAD</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>HANOVER</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>21076</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B59" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>201067</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>SO154745</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>24198</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>V7871800000</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>20164396C</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>487471800000</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M59" t="n">
+        <v>15311</v>
+      </c>
+      <c r="N59" t="n">
+        <v>15159</v>
+      </c>
+      <c r="O59" t="n">
+        <v>11</v>
+      </c>
+      <c r="P59" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" t="n">
+        <v>47.46</v>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>14599 NW 8TH STREET</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>SUNRISE</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>33325</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B60" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>201067</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>SO154753</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>35973</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>7871800002</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>20164395C</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>48741800002</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M60" t="n">
+        <v>14145</v>
+      </c>
+      <c r="N60" t="n">
+        <v>13553</v>
+      </c>
+      <c r="O60" t="n">
+        <v>59</v>
+      </c>
+      <c r="P60" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" t="n">
+        <v>36.8598</v>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>1160 MARQUETTE STREET</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>CLEVELAND</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>44114</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B61" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>201067</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>SO154754</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>38913</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>V7871800000</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>20164396C</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>487471800000</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M61" t="n">
+        <v>15311</v>
+      </c>
+      <c r="N61" t="n">
+        <v>15159</v>
+      </c>
+      <c r="O61" t="n">
+        <v>49</v>
+      </c>
+      <c r="P61" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" t="n">
+        <v>47.46</v>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>36663 VAN BORN RD</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>ROMULUS</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>48174</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B62" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>201067</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>SO154754</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>38913</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>V7871800002</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>20164397C</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>487471800002</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M62" t="n">
+        <v>30731</v>
+      </c>
+      <c r="N62" t="n">
+        <v>29723</v>
+      </c>
+      <c r="O62" t="n">
+        <v>184</v>
+      </c>
+      <c r="P62" t="n">
+        <v>184</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>36663 VAN BORN RD</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>ROMULUS</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>48174</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B63" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>201067</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>SO154756</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>40247</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>7871800000</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>20164394C</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>48741800000</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M63" t="n">
+        <v>4928</v>
+      </c>
+      <c r="N63" t="n">
+        <v>4634</v>
+      </c>
+      <c r="O63" t="n">
+        <v>87</v>
+      </c>
+      <c r="P63" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" t="n">
+        <v>57.33</v>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>550 LAKESIDE PARKWAY</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>FLOWER MOUND</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>75028</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B64" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>201067</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>SO154756</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>40247</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>7871800002</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>20164395C</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>48741800002</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M64" t="n">
+        <v>14145</v>
+      </c>
+      <c r="N64" t="n">
+        <v>13553</v>
+      </c>
+      <c r="O64" t="n">
+        <v>102</v>
+      </c>
+      <c r="P64" t="n">
+        <v>102</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" t="n">
+        <v>36.8598</v>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>550 LAKESIDE PARKWAY</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>FLOWER MOUND</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>75028</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B65" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>201067</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>SO154757</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>40677</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>V7871800002</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>20164397C</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>487471800002</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M65" t="n">
+        <v>30731</v>
+      </c>
+      <c r="N65" t="n">
+        <v>29723</v>
+      </c>
+      <c r="O65" t="n">
+        <v>195</v>
+      </c>
+      <c r="P65" t="n">
+        <v>195</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>4807 NE 63RD AVENUE</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>GAINESVILLE</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>32609</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B66" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>201067</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>SO154763</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>60075</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>7871800002</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>20164395C</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>48741800002</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M66" t="n">
+        <v>14145</v>
+      </c>
+      <c r="N66" t="n">
+        <v>13553</v>
+      </c>
+      <c r="O66" t="n">
+        <v>18</v>
+      </c>
+      <c r="P66" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" t="n">
+        <v>36.8598</v>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>4301 W VALLEY HWY EAST</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>SUMNER</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>98390</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B67" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>201067</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>SO154764</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>61288</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>7871800000</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>20164394C</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>48741800000</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M67" t="n">
+        <v>4928</v>
+      </c>
+      <c r="N67" t="n">
+        <v>4634</v>
+      </c>
+      <c r="O67" t="n">
+        <v>179</v>
+      </c>
+      <c r="P67" t="n">
+        <v>179</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" t="n">
+        <v>57.33</v>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>8313 WEST PIERCE STREET, SUITE 100</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>TOLLESON</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>85353</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B68" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>201067</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>SO154764</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>61288</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>V7871800000</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>20164396C</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>487471800000</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M68" t="n">
+        <v>15311</v>
+      </c>
+      <c r="N68" t="n">
+        <v>15159</v>
+      </c>
+      <c r="O68" t="n">
+        <v>33</v>
+      </c>
+      <c r="P68" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" t="n">
+        <v>47.46</v>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>8313 WEST PIERCE STREET, SUITE 100</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>TOLLESON</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>85353</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B69" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>201067</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>SO154769</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>70270</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>V7871800002</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>20164397C</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>487471800002</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M69" t="n">
+        <v>30731</v>
+      </c>
+      <c r="N69" t="n">
+        <v>29723</v>
+      </c>
+      <c r="O69" t="n">
+        <v>54</v>
+      </c>
+      <c r="P69" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>1880 NORTH CORRINGTON AVE</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>KANSAS CITY</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>64120</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B70" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>201067</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>SO154771</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>79001</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>7871800002</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>20164395C</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>48741800002</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M70" t="n">
+        <v>14145</v>
+      </c>
+      <c r="N70" t="n">
+        <v>13553</v>
+      </c>
+      <c r="O70" t="n">
+        <v>120</v>
+      </c>
+      <c r="P70" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" t="n">
+        <v>36.8598</v>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>27695 S.W. 95th AVENUE</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>WILSONVILLE</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>97070</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B71" s="1" t="n">
+        <v>46100</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>209214</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VENTURE RESPIRATORY INC. 209214</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>SO154426</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>17823</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>7871800002</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>20164395C</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M71" t="n">
+        <v>14145</v>
+      </c>
+      <c r="N71" t="n">
+        <v>13553</v>
+      </c>
+      <c r="O71" t="n">
+        <v>140</v>
+      </c>
+      <c r="P71" t="n">
+        <v>140</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" t="n">
+        <v>36.86</v>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>630 Herman Rd</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>JACKSON</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>08527</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B72" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>201003</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>CAH : CARDINAL - MD 201003</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>SO154143</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>4533277020</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>V7871800002</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>20164397C</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>V7871800002</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M72" t="n">
+        <v>30731</v>
+      </c>
+      <c r="N72" t="n">
+        <v>29723</v>
+      </c>
+      <c r="O72" t="n">
+        <v>44</v>
+      </c>
+      <c r="P72" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>1901 RAYMER AVENUE</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Fullerton</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>92833</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B73" s="1" t="n">
+        <v>46093</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>SO154038</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>4519714426</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>V7871800002</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>20164397C</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>O-T871800002</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M73" t="n">
+        <v>30731</v>
+      </c>
+      <c r="N73" t="n">
+        <v>29723</v>
+      </c>
+      <c r="O73" t="n">
+        <v>140</v>
+      </c>
+      <c r="P73" t="n">
+        <v>140</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>140</v>
+      </c>
+      <c r="S73" t="n">
+        <v>140</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>3770 HOGUM BAY RD. NE</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>LACEY</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>98516</t>
         </is>
       </c>
     </row>

--- a/data/searchresults.xlsx
+++ b/data/searchresults.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z73"/>
+  <dimension ref="A1:Z63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -559,26 +559,26 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>201003</t>
+          <t>209198</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CAH : CARDINAL - MD 201003</t>
+          <t>PROGRESSIVE MEDICAL CONCEPTS, LLC 209198</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SO154855</t>
+          <t>SO154968</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>4533295895</t>
+          <t>BV4131-5863</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -588,22 +588,18 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>V7871800000</t>
+          <t>7871800000</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20164396C</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>V7871800000</t>
-        </is>
-      </c>
+          <t>20164394C</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+          <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -612,15 +608,17 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>15311</v>
+        <v>4928</v>
       </c>
       <c r="N2" t="n">
-        <v>15159</v>
+        <v>4501</v>
       </c>
       <c r="O2" t="n">
-        <v>5</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="P2" t="n">
+        <v>60</v>
+      </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
@@ -634,29 +632,29 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>47.46</v>
+        <v>57.33</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Dixon, CA DC</t>
+          <t>4210 ALTRURIA RD</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Dixon</t>
+          <t>BARTLETT</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>95620</t>
+          <t>38135</t>
         </is>
       </c>
     </row>
@@ -671,22 +669,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>201001</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CAH : CARDINAL - MD DS 201001</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SO154863</t>
+          <t>SO154855</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>4231373081</t>
+          <t>4533295895</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -696,22 +694,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>7871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20164395C</t>
+          <t>20164396C</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -720,13 +718,13 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>14145</v>
+        <v>15255</v>
       </c>
       <c r="N3" t="n">
-        <v>13553</v>
+        <v>14411</v>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
@@ -742,29 +740,29 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="V3" t="n">
-        <v>36.86</v>
+        <v>47.46</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>6441 MAIN ST</t>
+          <t>Dixon, CA DC</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>HOUSTON</t>
+          <t>Dixon</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>770301502</t>
+          <t>95620</t>
         </is>
       </c>
     </row>
@@ -779,22 +777,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>202040</t>
+          <t>201001</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CHS : CONCORDANCE HEALTHCARE SOLUTIONS, LLC 202040</t>
+          <t>CAH : CARDINAL - MD DS 201001</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SO154870</t>
+          <t>SO154863</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>3591523</t>
+          <t>4231373081</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -804,22 +802,22 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>7871800000</t>
+          <t>7871800002</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20164394C</t>
+          <t>20164395C</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>354861</t>
+          <t>7871800002</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -828,17 +826,15 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>4928</v>
+        <v>13622</v>
       </c>
       <c r="N4" t="n">
-        <v>4634</v>
+        <v>13025</v>
       </c>
       <c r="O4" t="n">
-        <v>26</v>
-      </c>
-      <c r="P4" t="n">
-        <v>26</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
@@ -852,29 +848,29 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V4" t="n">
-        <v>57.33</v>
+        <v>36.86</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>60 DISTRIBUTION BOULEVARD</t>
+          <t>6441 MAIN ST</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>EDISON</t>
+          <t>HOUSTON</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08817</t>
+          <t>770301502</t>
         </is>
       </c>
     </row>
@@ -889,22 +885,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>202040</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>CHS : CONCORDANCE HEALTHCARE SOLUTIONS, LLC 202040</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SO154908</t>
+          <t>SO154870</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>4519767997</t>
+          <t>3591523</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -914,22 +910,22 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>7871800002</t>
+          <t>7871800000</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20164395C</t>
+          <t>20164394C</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O-T7871800002</t>
+          <t>354861</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+          <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -938,15 +934,17 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>14145</v>
+        <v>4928</v>
       </c>
       <c r="N5" t="n">
-        <v>13553</v>
+        <v>4501</v>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="P5" t="n">
+        <v>26</v>
+      </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
@@ -960,29 +958,29 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>36.86</v>
+        <v>57.33</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>735 COUNTY ROAD 4 EAST</t>
+          <t>60 DISTRIBUTION BOULEVARD</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>PRATTVILLE</t>
+          <t>EDISON</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>36067</t>
+          <t>08817</t>
         </is>
       </c>
     </row>
@@ -1022,22 +1020,22 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>V7871800002</t>
+          <t>7871800002</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20164397C</t>
+          <t>20164395C</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O-T871800002</t>
+          <t>O-T7871800002</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1046,15 +1044,17 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>30731</v>
+        <v>13622</v>
       </c>
       <c r="N6" t="n">
-        <v>29723</v>
+        <v>13025</v>
       </c>
       <c r="O6" t="n">
-        <v>70</v>
-      </c>
-      <c r="P6" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="P6" t="n">
+        <v>4</v>
+      </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
@@ -1068,10 +1068,10 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>29.4</v>
+        <v>36.86</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1115,12 +1115,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SO154909</t>
+          <t>SO154908</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>4519767998</t>
+          <t>4519767997</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1154,15 +1154,17 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>30731</v>
+        <v>30390</v>
       </c>
       <c r="N7" t="n">
-        <v>29723</v>
+        <v>28188</v>
       </c>
       <c r="O7" t="n">
         <v>70</v>
       </c>
-      <c r="P7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>70</v>
+      </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
@@ -1176,29 +1178,29 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>29.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>13115 BROCKTON LANE N</t>
+          <t>735 COUNTY ROAD 4 EAST</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>ROGERS</t>
+          <t>PRATTVILLE</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>55374</t>
+          <t>36067</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1225,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SO154911</t>
+          <t>SO154909</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4519768000</t>
+          <t>4519767998</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1262,15 +1264,17 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>30731</v>
+        <v>30390</v>
       </c>
       <c r="N8" t="n">
-        <v>29723</v>
+        <v>28188</v>
       </c>
       <c r="O8" t="n">
         <v>70</v>
       </c>
-      <c r="P8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>70</v>
+      </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
@@ -1284,29 +1288,29 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>29.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>500 SHARKEY DRIVE</t>
+          <t>13115 BROCKTON LANE N</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>MAUMELLE</t>
+          <t>ROGERS</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>MN</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>72113</t>
+          <t>55374</t>
         </is>
       </c>
     </row>
@@ -1331,12 +1335,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SO154917</t>
+          <t>SO154911</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>4519768006</t>
+          <t>4519768000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1370,15 +1374,17 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>30731</v>
+        <v>30390</v>
       </c>
       <c r="N9" t="n">
-        <v>29723</v>
+        <v>28188</v>
       </c>
       <c r="O9" t="n">
-        <v>22</v>
-      </c>
-      <c r="P9" t="inlineStr"/>
+        <v>70</v>
+      </c>
+      <c r="P9" t="n">
+        <v>70</v>
+      </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
@@ -1392,29 +1398,29 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>29.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>1062 OLD DIXIE HIGHWAY</t>
+          <t>500 SHARKEY DRIVE</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>AUBURNDALE</t>
+          <t>MAUMELLE</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>33823</t>
+          <t>72113</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1445,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SO154918</t>
+          <t>SO154917</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4519768007</t>
+          <t>4519768006</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1478,15 +1484,17 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>30731</v>
+        <v>30390</v>
       </c>
       <c r="N10" t="n">
-        <v>29723</v>
+        <v>28188</v>
       </c>
       <c r="O10" t="n">
-        <v>140</v>
-      </c>
-      <c r="P10" t="inlineStr"/>
+        <v>22</v>
+      </c>
+      <c r="P10" t="n">
+        <v>22</v>
+      </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
@@ -1500,29 +1508,29 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>29.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>1960 W. MIRO WAY</t>
+          <t>1062 OLD DIXIE HIGHWAY</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>RIALTO</t>
+          <t>AUBURNDALE</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>92376</t>
+          <t>33823</t>
         </is>
       </c>
     </row>
@@ -1547,12 +1555,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SO154919</t>
+          <t>SO154918</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>4519768008</t>
+          <t>4519768007</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1562,22 +1570,22 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7871800000</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20164394C</t>
+          <t>20164397C</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O-T71800000</t>
+          <t>O-T871800002</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1586,15 +1594,17 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>4928</v>
+        <v>30390</v>
       </c>
       <c r="N11" t="n">
-        <v>4634</v>
+        <v>28188</v>
       </c>
       <c r="O11" t="n">
-        <v>8</v>
-      </c>
-      <c r="P11" t="inlineStr"/>
+        <v>140</v>
+      </c>
+      <c r="P11" t="n">
+        <v>140</v>
+      </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
@@ -1608,29 +1618,29 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>57.33</v>
+        <v>29.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>29895 US HWY 90 BUS</t>
+          <t>1960 W. MIRO WAY</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>KATY</t>
+          <t>RIALTO</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>77494</t>
+          <t>92376</t>
         </is>
       </c>
     </row>
@@ -1670,22 +1680,22 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>V7871800000</t>
+          <t>7871800000</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20164396C</t>
+          <t>20164394C</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O-T7871800000</t>
+          <t>O-T71800000</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+          <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1694,15 +1704,17 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>15311</v>
+        <v>4928</v>
       </c>
       <c r="N12" t="n">
-        <v>15159</v>
+        <v>4501</v>
       </c>
       <c r="O12" t="n">
-        <v>130</v>
-      </c>
-      <c r="P12" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="P12" t="n">
+        <v>8</v>
+      </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
@@ -1716,10 +1728,10 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>47.46</v>
+        <v>57.33</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1763,12 +1775,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SO154920</t>
+          <t>SO154919</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>4519768009</t>
+          <t>4519768008</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1802,15 +1814,17 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>15311</v>
+        <v>15255</v>
       </c>
       <c r="N13" t="n">
-        <v>15159</v>
+        <v>14411</v>
       </c>
       <c r="O13" t="n">
-        <v>20</v>
-      </c>
-      <c r="P13" t="inlineStr"/>
+        <v>130</v>
+      </c>
+      <c r="P13" t="n">
+        <v>130</v>
+      </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
@@ -1824,29 +1838,29 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
         <v>47.46</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>5000 Premier Parkway, Suite 100</t>
+          <t>29895 US HWY 90 BUS</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Saint Peters</t>
+          <t>KATY</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>63376</t>
+          <t>77494</t>
         </is>
       </c>
     </row>
@@ -1886,22 +1900,22 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>V7871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20164397C</t>
+          <t>20164396C</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>O-T871800002</t>
+          <t>O-T7871800000</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1910,15 +1924,17 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>30731</v>
+        <v>15255</v>
       </c>
       <c r="N14" t="n">
-        <v>29723</v>
+        <v>14411</v>
       </c>
       <c r="O14" t="n">
-        <v>70</v>
-      </c>
-      <c r="P14" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="P14" t="n">
+        <v>20</v>
+      </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
@@ -1932,10 +1948,10 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -1979,12 +1995,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SO154922</t>
+          <t>SO154920</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>4519768011</t>
+          <t>4519768009</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1994,22 +2010,22 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>V7871800000</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>20164396C</t>
+          <t>20164397C</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>O-T7871800000</t>
+          <t>O-T871800002</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2018,15 +2034,17 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>15311</v>
+        <v>30390</v>
       </c>
       <c r="N15" t="n">
-        <v>15159</v>
+        <v>28188</v>
       </c>
       <c r="O15" t="n">
-        <v>41</v>
-      </c>
-      <c r="P15" t="inlineStr"/>
+        <v>70</v>
+      </c>
+      <c r="P15" t="n">
+        <v>70</v>
+      </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
@@ -2040,29 +2058,29 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>1040 ENTERPRISE PARKWAY</t>
+          <t>5000 Premier Parkway, Suite 100</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>WEST JEFFERSON</t>
+          <t>Saint Peters</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>43162</t>
+          <t>63376</t>
         </is>
       </c>
     </row>
@@ -2102,22 +2120,22 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20164395C</t>
+          <t>20164396C</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>O-T7871800002</t>
+          <t>O-T7871800000</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2126,15 +2144,17 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>14145</v>
+        <v>15255</v>
       </c>
       <c r="N16" t="n">
-        <v>13553</v>
+        <v>14411</v>
       </c>
       <c r="O16" t="n">
-        <v>210</v>
-      </c>
-      <c r="P16" t="inlineStr"/>
+        <v>41</v>
+      </c>
+      <c r="P16" t="n">
+        <v>41</v>
+      </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
@@ -2148,10 +2168,10 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>36.86</v>
+        <v>47.46</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -2210,22 +2230,22 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>V7871800002</t>
+          <t>7871800002</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20164397C</t>
+          <t>20164395C</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>O-T871800002</t>
+          <t>O-T7871800002</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2234,15 +2254,17 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>30731</v>
+        <v>13622</v>
       </c>
       <c r="N17" t="n">
-        <v>29723</v>
+        <v>13025</v>
       </c>
       <c r="O17" t="n">
-        <v>43</v>
-      </c>
-      <c r="P17" t="inlineStr"/>
+        <v>210</v>
+      </c>
+      <c r="P17" t="n">
+        <v>210</v>
+      </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
@@ -2256,10 +2278,10 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>29.4</v>
+        <v>36.86</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -2303,12 +2325,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SO154924</t>
+          <t>SO154922</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>4519768013</t>
+          <t>4519768011</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2342,15 +2364,17 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>30731</v>
+        <v>30390</v>
       </c>
       <c r="N18" t="n">
-        <v>29723</v>
+        <v>28188</v>
       </c>
       <c r="O18" t="n">
-        <v>140</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="P18" t="n">
+        <v>43</v>
+      </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
@@ -2364,29 +2388,29 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>29.4</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>5701 PROMONTORY PARKWAY</t>
+          <t>1040 ENTERPRISE PARKWAY</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>TRACY</t>
+          <t>WEST JEFFERSON</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>95377</t>
+          <t>43162</t>
         </is>
       </c>
     </row>
@@ -2411,12 +2435,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SO154931</t>
+          <t>SO154924</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>4519768020</t>
+          <t>4519768013</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2450,15 +2474,17 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>30731</v>
+        <v>30390</v>
       </c>
       <c r="N19" t="n">
-        <v>29723</v>
+        <v>28188</v>
       </c>
       <c r="O19" t="n">
-        <v>210</v>
-      </c>
-      <c r="P19" t="inlineStr"/>
+        <v>140</v>
+      </c>
+      <c r="P19" t="n">
+        <v>140</v>
+      </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
@@ -2472,29 +2498,29 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>29.4</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>3770 HOGUM BAY RD. NE</t>
+          <t>5701 PROMONTORY PARKWAY</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>LACEY</t>
+          <t>TRACY</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>WA</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>98516</t>
+          <t>95377</t>
         </is>
       </c>
     </row>
@@ -2519,12 +2545,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SO154933</t>
+          <t>SO154931</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>4519768022</t>
+          <t>4519768020</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2534,22 +2560,22 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>7871800002</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20164395C</t>
+          <t>20164397C</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>O-T7871800002</t>
+          <t>O-T871800002</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2558,15 +2584,17 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>14145</v>
+        <v>30390</v>
       </c>
       <c r="N20" t="n">
-        <v>13553</v>
+        <v>28188</v>
       </c>
       <c r="O20" t="n">
-        <v>70</v>
-      </c>
-      <c r="P20" t="inlineStr"/>
+        <v>210</v>
+      </c>
+      <c r="P20" t="n">
+        <v>210</v>
+      </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
@@ -2580,29 +2608,29 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>36.86</v>
+        <v>29.4</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>600 DERBY AVENUE</t>
+          <t>3770 HOGUM BAY RD. NE</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>WEST HAVEN</t>
+          <t>LACEY</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>WA</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>06516</t>
+          <t>98516</t>
         </is>
       </c>
     </row>
@@ -2666,15 +2694,17 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>15311</v>
+        <v>15255</v>
       </c>
       <c r="N21" t="n">
-        <v>15159</v>
+        <v>14411</v>
       </c>
       <c r="O21" t="n">
         <v>16</v>
       </c>
-      <c r="P21" t="inlineStr"/>
+      <c r="P21" t="n">
+        <v>16</v>
+      </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
@@ -2688,7 +2718,7 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
         <v>47.46</v>
@@ -2774,15 +2804,17 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>14145</v>
+        <v>13622</v>
       </c>
       <c r="N22" t="n">
-        <v>13553</v>
+        <v>13025</v>
       </c>
       <c r="O22" t="n">
         <v>9</v>
       </c>
-      <c r="P22" t="inlineStr"/>
+      <c r="P22" t="n">
+        <v>9</v>
+      </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
@@ -2796,7 +2828,7 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
         <v>36.86</v>
@@ -2882,15 +2914,17 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>30731</v>
+        <v>30390</v>
       </c>
       <c r="N23" t="n">
-        <v>29723</v>
+        <v>28188</v>
       </c>
       <c r="O23" t="n">
         <v>48</v>
       </c>
-      <c r="P23" t="inlineStr"/>
+      <c r="P23" t="n">
+        <v>48</v>
+      </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
@@ -2904,7 +2938,7 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
         <v>29.4</v>
@@ -2990,15 +3024,17 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>15311</v>
+        <v>15255</v>
       </c>
       <c r="N24" t="n">
-        <v>15159</v>
+        <v>14411</v>
       </c>
       <c r="O24" t="n">
         <v>9</v>
       </c>
-      <c r="P24" t="inlineStr"/>
+      <c r="P24" t="n">
+        <v>9</v>
+      </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
@@ -3012,7 +3048,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
         <v>47.46</v>
@@ -3098,15 +3134,17 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>15311</v>
+        <v>15255</v>
       </c>
       <c r="N25" t="n">
-        <v>15159</v>
+        <v>14411</v>
       </c>
       <c r="O25" t="n">
         <v>15</v>
       </c>
-      <c r="P25" t="inlineStr"/>
+      <c r="P25" t="n">
+        <v>15</v>
+      </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
@@ -3120,7 +3158,7 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
         <v>47.46</v>
@@ -3206,15 +3244,17 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>30731</v>
+        <v>30390</v>
       </c>
       <c r="N26" t="n">
-        <v>29723</v>
+        <v>28188</v>
       </c>
       <c r="O26" t="n">
         <v>140</v>
       </c>
-      <c r="P26" t="inlineStr"/>
+      <c r="P26" t="n">
+        <v>140</v>
+      </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
@@ -3228,7 +3268,7 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
         <v>29.4</v>
@@ -3314,15 +3354,17 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>15311</v>
+        <v>15255</v>
       </c>
       <c r="N27" t="n">
-        <v>15159</v>
+        <v>14411</v>
       </c>
       <c r="O27" t="n">
         <v>7</v>
       </c>
-      <c r="P27" t="inlineStr"/>
+      <c r="P27" t="n">
+        <v>7</v>
+      </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
@@ -3336,7 +3378,7 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
         <v>47.46</v>
@@ -3422,15 +3464,17 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>30731</v>
+        <v>30390</v>
       </c>
       <c r="N28" t="n">
-        <v>29723</v>
+        <v>28188</v>
       </c>
       <c r="O28" t="n">
         <v>34</v>
       </c>
-      <c r="P28" t="inlineStr"/>
+      <c r="P28" t="n">
+        <v>34</v>
+      </c>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
@@ -3444,7 +3488,7 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
         <v>29.4</v>
@@ -3530,15 +3574,17 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>14145</v>
+        <v>13622</v>
       </c>
       <c r="N29" t="n">
-        <v>13553</v>
+        <v>13025</v>
       </c>
       <c r="O29" t="n">
         <v>40</v>
       </c>
-      <c r="P29" t="inlineStr"/>
+      <c r="P29" t="n">
+        <v>40</v>
+      </c>
       <c r="Q29" t="n">
         <v>0</v>
       </c>
@@ -3552,7 +3598,7 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
         <v>36.86</v>
@@ -3638,15 +3684,17 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>15311</v>
+        <v>15255</v>
       </c>
       <c r="N30" t="n">
-        <v>15159</v>
+        <v>14411</v>
       </c>
       <c r="O30" t="n">
         <v>9</v>
       </c>
-      <c r="P30" t="inlineStr"/>
+      <c r="P30" t="n">
+        <v>9</v>
+      </c>
       <c r="Q30" t="n">
         <v>0</v>
       </c>
@@ -3660,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
         <v>47.46</v>
@@ -3746,15 +3794,17 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>30731</v>
+        <v>30390</v>
       </c>
       <c r="N31" t="n">
-        <v>29723</v>
+        <v>28188</v>
       </c>
       <c r="O31" t="n">
         <v>70</v>
       </c>
-      <c r="P31" t="inlineStr"/>
+      <c r="P31" t="n">
+        <v>70</v>
+      </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
@@ -3768,7 +3818,7 @@
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
         <v>29.4</v>
@@ -3815,12 +3865,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SO154915</t>
+          <t>SO154916</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>4519768004</t>
+          <t>4519768005</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3854,15 +3904,17 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>15311</v>
+        <v>15255</v>
       </c>
       <c r="N32" t="n">
-        <v>15159</v>
+        <v>14411</v>
       </c>
       <c r="O32" t="n">
-        <v>45</v>
-      </c>
-      <c r="P32" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="P32" t="n">
+        <v>28</v>
+      </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
@@ -3876,29 +3928,29 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
         <v>47.46</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>2200 Cornerstone Parkway, Suite 100</t>
+          <t>1500 MEDLINE PLACE</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Grayslake</t>
+          <t>MC DONOUGH</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>60030</t>
+          <t>30253</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3975,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SO154915</t>
+          <t>SO154921</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>4519768004</t>
+          <t>4519768010</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3938,22 +3990,22 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>7871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20164395C</t>
+          <t>20164396C</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>O-T7871800002</t>
+          <t>O-T7871800000</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3962,15 +4014,17 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>14145</v>
+        <v>15255</v>
       </c>
       <c r="N33" t="n">
-        <v>13553</v>
+        <v>14411</v>
       </c>
       <c r="O33" t="n">
-        <v>5</v>
-      </c>
-      <c r="P33" t="inlineStr"/>
+        <v>195</v>
+      </c>
+      <c r="P33" t="n">
+        <v>195</v>
+      </c>
       <c r="Q33" t="n">
         <v>0</v>
       </c>
@@ -3984,29 +4038,29 @@
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>36.86</v>
+        <v>47.46</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>2200 Cornerstone Parkway, Suite 100</t>
+          <t>81 CAMPANELLI DRIVE</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Grayslake</t>
+          <t>UXBRIDGE</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>60030</t>
+          <t>01569</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4085,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SO154916</t>
+          <t>SO154921</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>4519768005</t>
+          <t>4519768010</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4046,22 +4100,22 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>V7871800000</t>
+          <t>7871800002</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>20164396C</t>
+          <t>20164395C</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>O-T7871800000</t>
+          <t>O-T7871800002</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -4070,15 +4124,17 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>15311</v>
+        <v>13622</v>
       </c>
       <c r="N34" t="n">
-        <v>15159</v>
+        <v>13025</v>
       </c>
       <c r="O34" t="n">
-        <v>28</v>
-      </c>
-      <c r="P34" t="inlineStr"/>
+        <v>140</v>
+      </c>
+      <c r="P34" t="n">
+        <v>140</v>
+      </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
@@ -4092,29 +4148,29 @@
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>47.46</v>
+        <v>36.86</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>1500 MEDLINE PLACE</t>
+          <t>81 CAMPANELLI DRIVE</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>MC DONOUGH</t>
+          <t>UXBRIDGE</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>30253</t>
+          <t>01569</t>
         </is>
       </c>
     </row>
@@ -4154,22 +4210,22 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>V7871800000</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>20164396C</t>
+          <t>20164397C</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>O-T7871800000</t>
+          <t>O-T871800002</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -4178,15 +4234,17 @@
         </is>
       </c>
       <c r="M35" t="n">
-        <v>15311</v>
+        <v>30390</v>
       </c>
       <c r="N35" t="n">
-        <v>15159</v>
+        <v>28188</v>
       </c>
       <c r="O35" t="n">
-        <v>195</v>
-      </c>
-      <c r="P35" t="inlineStr"/>
+        <v>31</v>
+      </c>
+      <c r="P35" t="n">
+        <v>31</v>
+      </c>
       <c r="Q35" t="n">
         <v>0</v>
       </c>
@@ -4200,10 +4258,10 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>195</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -4247,12 +4305,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>SO154921</t>
+          <t>SO154925</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>4519768010</t>
+          <t>4519768014</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4262,22 +4320,22 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>7871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>20164395C</t>
+          <t>20164396C</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>O-T7871800002</t>
+          <t>O-T7871800000</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -4286,15 +4344,17 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>14145</v>
+        <v>15255</v>
       </c>
       <c r="N36" t="n">
-        <v>13553</v>
+        <v>14411</v>
       </c>
       <c r="O36" t="n">
-        <v>140</v>
-      </c>
-      <c r="P36" t="inlineStr"/>
+        <v>195</v>
+      </c>
+      <c r="P36" t="n">
+        <v>195</v>
+      </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
@@ -4308,29 +4368,29 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>36.86</v>
+        <v>47.46</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>81 CAMPANELLI DRIVE</t>
+          <t>239 BELVIDERE ROAD</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>UXBRIDGE</t>
+          <t>PERRYVILLE</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>01569</t>
+          <t>21903</t>
         </is>
       </c>
     </row>
@@ -4355,12 +4415,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SO154921</t>
+          <t>SO154925</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>4519768010</t>
+          <t>4519768014</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4370,22 +4430,22 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>V7871800002</t>
+          <t>7871800002</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>20164397C</t>
+          <t>20164395C</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>O-T871800002</t>
+          <t>O-T7871800002</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -4394,15 +4454,17 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>30731</v>
+        <v>13622</v>
       </c>
       <c r="N37" t="n">
-        <v>29723</v>
+        <v>13025</v>
       </c>
       <c r="O37" t="n">
-        <v>31</v>
-      </c>
-      <c r="P37" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="P37" t="n">
+        <v>30</v>
+      </c>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
@@ -4416,29 +4478,29 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>29.4</v>
+        <v>36.86</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>81 CAMPANELLI DRIVE</t>
+          <t>239 BELVIDERE ROAD</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>UXBRIDGE</t>
+          <t>PERRYVILLE</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>01569</t>
+          <t>21903</t>
         </is>
       </c>
     </row>
@@ -4478,22 +4540,22 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>V7871800000</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>20164396C</t>
+          <t>20164397C</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>O-T7871800000</t>
+          <t>O-T871800002</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4502,15 +4564,17 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>15311</v>
+        <v>30390</v>
       </c>
       <c r="N38" t="n">
-        <v>15159</v>
+        <v>28188</v>
       </c>
       <c r="O38" t="n">
-        <v>195</v>
-      </c>
-      <c r="P38" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="P38" t="n">
+        <v>47</v>
+      </c>
       <c r="Q38" t="n">
         <v>0</v>
       </c>
@@ -4524,10 +4588,10 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>195</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
@@ -4571,12 +4635,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SO154925</t>
+          <t>SO154927</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>4519768014</t>
+          <t>4519768016</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4586,22 +4650,22 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>7871800002</t>
+          <t>7871800000</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>20164395C</t>
+          <t>20164394C</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>O-T7871800002</t>
+          <t>O-T71800000</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+          <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4610,15 +4674,17 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>14145</v>
+        <v>4928</v>
       </c>
       <c r="N39" t="n">
-        <v>13553</v>
+        <v>4501</v>
       </c>
       <c r="O39" t="n">
-        <v>30</v>
-      </c>
-      <c r="P39" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="P39" t="n">
+        <v>65</v>
+      </c>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
@@ -4632,29 +4698,29 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>36.86</v>
+        <v>57.33</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>239 BELVIDERE ROAD</t>
+          <t>494 State Route 416</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>PERRYVILLE</t>
+          <t>Montgomery</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>21903</t>
+          <t>12549</t>
         </is>
       </c>
     </row>
@@ -4679,12 +4745,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SO154925</t>
+          <t>SO154927</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>4519768014</t>
+          <t>4519768016</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4694,22 +4760,22 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>V7871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>20164397C</t>
+          <t>20164396C</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>O-T871800002</t>
+          <t>O-T7871800000</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4718,15 +4784,17 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>30731</v>
+        <v>15255</v>
       </c>
       <c r="N40" t="n">
-        <v>29723</v>
+        <v>14411</v>
       </c>
       <c r="O40" t="n">
-        <v>47</v>
-      </c>
-      <c r="P40" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="P40" t="n">
+        <v>28</v>
+      </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
@@ -4740,29 +4808,29 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>239 BELVIDERE ROAD</t>
+          <t>494 State Route 416</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>PERRYVILLE</t>
+          <t>Montgomery</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>21903</t>
+          <t>12549</t>
         </is>
       </c>
     </row>
@@ -4802,22 +4870,22 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>7871800000</t>
+          <t>7871800002</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>20164394C</t>
+          <t>20164395C</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>O-T71800000</t>
+          <t>O-T7871800002</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4826,15 +4894,17 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>4928</v>
+        <v>13622</v>
       </c>
       <c r="N41" t="n">
-        <v>4634</v>
+        <v>13025</v>
       </c>
       <c r="O41" t="n">
-        <v>65</v>
-      </c>
-      <c r="P41" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="P41" t="n">
+        <v>20</v>
+      </c>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
@@ -4848,10 +4918,10 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>57.33</v>
+        <v>36.86</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
@@ -4910,22 +4980,22 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>V7871800000</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>20164396C</t>
+          <t>20164397C</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>O-T7871800000</t>
+          <t>O-T871800002</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4934,15 +5004,17 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>15311</v>
+        <v>30390</v>
       </c>
       <c r="N42" t="n">
-        <v>15159</v>
+        <v>28188</v>
       </c>
       <c r="O42" t="n">
-        <v>28</v>
-      </c>
-      <c r="P42" t="inlineStr"/>
+        <v>70</v>
+      </c>
+      <c r="P42" t="n">
+        <v>70</v>
+      </c>
       <c r="Q42" t="n">
         <v>0</v>
       </c>
@@ -4956,10 +5028,10 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
@@ -5003,12 +5075,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SO154927</t>
+          <t>SO154930</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>4519768016</t>
+          <t>4519768019</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -5018,22 +5090,22 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>7871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>20164395C</t>
+          <t>20164396C</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>O-T7871800002</t>
+          <t>O-T787180000H</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -5042,15 +5114,17 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>14145</v>
+        <v>15255</v>
       </c>
       <c r="N43" t="n">
-        <v>13553</v>
+        <v>14411</v>
       </c>
       <c r="O43" t="n">
-        <v>20</v>
-      </c>
-      <c r="P43" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="P43" t="n">
+        <v>10</v>
+      </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
@@ -5064,29 +5138,29 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>36.86</v>
+        <v>47.46</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>494 State Route 416</t>
+          <t>264 SOUTH 5750 WEST</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Montgomery</t>
+          <t>SALT LAKE CITY</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>UT</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12549</t>
+          <t>84104</t>
         </is>
       </c>
     </row>
@@ -5111,12 +5185,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SO154927</t>
+          <t>SO154930</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>4519768016</t>
+          <t>4519768019</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -5150,15 +5224,17 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>30731</v>
+        <v>30390</v>
       </c>
       <c r="N44" t="n">
-        <v>29723</v>
+        <v>28188</v>
       </c>
       <c r="O44" t="n">
-        <v>70</v>
-      </c>
-      <c r="P44" t="inlineStr"/>
+        <v>140</v>
+      </c>
+      <c r="P44" t="n">
+        <v>140</v>
+      </c>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
@@ -5172,29 +5248,29 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
         <v>29.4</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>494 State Route 416</t>
+          <t>264 SOUTH 5750 WEST</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Montgomery</t>
+          <t>SALT LAKE CITY</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>UT</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12549</t>
+          <t>84104</t>
         </is>
       </c>
     </row>
@@ -5219,12 +5295,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>SO154930</t>
+          <t>SO154932</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>4519768019</t>
+          <t>4519768021</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -5258,15 +5334,17 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>30731</v>
+        <v>30390</v>
       </c>
       <c r="N45" t="n">
-        <v>29723</v>
+        <v>28188</v>
       </c>
       <c r="O45" t="n">
-        <v>140</v>
-      </c>
-      <c r="P45" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="P45" t="n">
+        <v>11</v>
+      </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
@@ -5280,29 +5358,29 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
         <v>29.4</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>264 SOUTH 5750 WEST</t>
+          <t>251 HILTON DRIVE</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>SALT LAKE CITY</t>
+          <t>JEFFERSONVILLE</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>UT</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>84104</t>
+          <t>47130</t>
         </is>
       </c>
     </row>
@@ -5327,12 +5405,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>SO154932</t>
+          <t>SO154907</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>4519768021</t>
+          <t>4519767996</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -5366,15 +5444,17 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>30731</v>
+        <v>30390</v>
       </c>
       <c r="N46" t="n">
-        <v>29723</v>
+        <v>28188</v>
       </c>
       <c r="O46" t="n">
-        <v>11</v>
-      </c>
-      <c r="P46" t="inlineStr"/>
+        <v>70</v>
+      </c>
+      <c r="P46" t="n">
+        <v>70</v>
+      </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
@@ -5388,29 +5468,29 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
         <v>29.4</v>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>251 HILTON DRIVE</t>
+          <t>92 SOUTHEAST 223rd AVENUE</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>JEFFERSONVILLE</t>
+          <t>GRESHAM</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>OR</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>47130</t>
+          <t>97030</t>
         </is>
       </c>
     </row>
@@ -5435,12 +5515,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>SO154907</t>
+          <t>SO154926</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>4519767996</t>
+          <t>4519768015</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -5474,15 +5554,17 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>30731</v>
+        <v>30390</v>
       </c>
       <c r="N47" t="n">
-        <v>29723</v>
+        <v>28188</v>
       </c>
       <c r="O47" t="n">
-        <v>70</v>
-      </c>
-      <c r="P47" t="inlineStr"/>
+        <v>39</v>
+      </c>
+      <c r="P47" t="n">
+        <v>39</v>
+      </c>
       <c r="Q47" t="n">
         <v>0</v>
       </c>
@@ -5496,29 +5578,29 @@
         <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
         <v>29.4</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>92 SOUTHEAST 223rd AVENUE</t>
+          <t>8787 W BUCKEYE ROAD</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>GRESHAM</t>
+          <t>TOLLESON</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>97030</t>
+          <t>85353</t>
         </is>
       </c>
     </row>
@@ -5529,26 +5611,26 @@
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>46107</v>
+        <v>46105</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>201067</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>SO154926</t>
+          <t>SO154721</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>4519768015</t>
+          <t>04086</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5558,22 +5640,22 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>V7871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>20164397C</t>
+          <t>20164396C</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>O-T871800002</t>
+          <t>487471800000</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -5582,15 +5664,17 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>30731</v>
+        <v>15255</v>
       </c>
       <c r="N48" t="n">
-        <v>29723</v>
+        <v>14411</v>
       </c>
       <c r="O48" t="n">
-        <v>39</v>
-      </c>
-      <c r="P48" t="inlineStr"/>
+        <v>57</v>
+      </c>
+      <c r="P48" t="n">
+        <v>57</v>
+      </c>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
@@ -5604,29 +5688,29 @@
         <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>8787 W BUCKEYE ROAD</t>
+          <t>2151 COUNTY ROAD H2W</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>TOLLESON</t>
+          <t>MOUNDS VIEW</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>MN</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>85353</t>
+          <t>55112</t>
         </is>
       </c>
     </row>
@@ -5651,12 +5735,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>SO154735</t>
+          <t>SO154721</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>16814</t>
+          <t>04086</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5666,22 +5750,22 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>7871800002</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>20164395C</t>
+          <t>20164397C</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>48741800002</t>
+          <t>487471800002</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5690,16 +5774,16 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>14145</v>
+        <v>30390</v>
       </c>
       <c r="N49" t="n">
-        <v>13553</v>
+        <v>28188</v>
       </c>
       <c r="O49" t="n">
-        <v>111</v>
+        <v>72</v>
       </c>
       <c r="P49" t="n">
-        <v>111</v>
+        <v>72</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -5717,26 +5801,26 @@
         <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>36.8598</v>
+        <v>29.4</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>7437 INDUSTRIAL BOULEVARD</t>
+          <t>2151 COUNTY ROAD H2W</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>ALLENTOWN</t>
+          <t>MOUNDS VIEW</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>MN</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18106</t>
+          <t>55112</t>
         </is>
       </c>
     </row>
@@ -5761,12 +5845,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>SO154721</t>
+          <t>SO154725</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>04086</t>
+          <t>05645</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5776,22 +5860,22 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>V7871800000</t>
+          <t>7871800000</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>20164396C</t>
+          <t>20164394C</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>487471800000</t>
+          <t>48741800000</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+          <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5800,16 +5884,16 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>15311</v>
+        <v>4928</v>
       </c>
       <c r="N50" t="n">
-        <v>15159</v>
+        <v>4501</v>
       </c>
       <c r="O50" t="n">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="P50" t="n">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -5827,26 +5911,26 @@
         <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>47.46</v>
+        <v>57.33</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>2151 COUNTY ROAD H2W</t>
+          <t>202 COMMERCE BLVD.</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>MOUNDS VIEW</t>
+          <t>KINGS MOUNTAIN</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>55112</t>
+          <t>28086</t>
         </is>
       </c>
     </row>
@@ -5871,12 +5955,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>SO154721</t>
+          <t>SO154727</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>04086</t>
+          <t>06858</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5886,22 +5970,22 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>V7871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>20164397C</t>
+          <t>20164396C</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>487471800002</t>
+          <t>487471800000</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5910,16 +5994,16 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>30731</v>
+        <v>15255</v>
       </c>
       <c r="N51" t="n">
-        <v>29723</v>
+        <v>14411</v>
       </c>
       <c r="O51" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="P51" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -5937,26 +6021,26 @@
         <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>2151 COUNTY ROAD H2W</t>
+          <t>1805 NORTH LOOP 499 SUITE 130</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>MOUNDS VIEW</t>
+          <t>HARLINGEN</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>55112</t>
+          <t>78550</t>
         </is>
       </c>
     </row>
@@ -5981,12 +6065,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>SO154725</t>
+          <t>SO154730</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>05645</t>
+          <t>10054</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5996,22 +6080,22 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>7871800000</t>
+          <t>7871800002</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>20164394C</t>
+          <t>20164395C</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>48741800000</t>
+          <t>48741800002</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -6020,16 +6104,16 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>4928</v>
+        <v>13622</v>
       </c>
       <c r="N52" t="n">
-        <v>4634</v>
+        <v>13025</v>
       </c>
       <c r="O52" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="P52" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -6047,26 +6131,26 @@
         <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>57.33</v>
+        <v>36.8598</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>202 COMMERCE BLVD.</t>
+          <t>8489 WESTSIDE INDUSTRIAL DRIVE</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>KINGS MOUNTAIN</t>
+          <t>JACKSONVILLE</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>28086</t>
+          <t>32219</t>
         </is>
       </c>
     </row>
@@ -6091,12 +6175,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>SO154727</t>
+          <t>SO154730</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>06858</t>
+          <t>10054</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -6130,10 +6214,10 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>15311</v>
+        <v>15255</v>
       </c>
       <c r="N53" t="n">
-        <v>15159</v>
+        <v>14411</v>
       </c>
       <c r="O53" t="n">
         <v>1</v>
@@ -6161,22 +6245,22 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>1805 NORTH LOOP 499 SUITE 130</t>
+          <t>8489 WESTSIDE INDUSTRIAL DRIVE</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>HARLINGEN</t>
+          <t>JACKSONVILLE</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>78550</t>
+          <t>32219</t>
         </is>
       </c>
     </row>
@@ -6216,22 +6300,22 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>7871800002</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>20164395C</t>
+          <t>20164397C</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>48741800002</t>
+          <t>487471800002</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -6240,16 +6324,16 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>14145</v>
+        <v>30390</v>
       </c>
       <c r="N54" t="n">
-        <v>13553</v>
+        <v>28188</v>
       </c>
       <c r="O54" t="n">
-        <v>42</v>
+        <v>140</v>
       </c>
       <c r="P54" t="n">
-        <v>42</v>
+        <v>140</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -6267,7 +6351,7 @@
         <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>36.8598</v>
+        <v>29.4</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
@@ -6311,12 +6395,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>SO154730</t>
+          <t>SO154733</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>10054</t>
+          <t>15591</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -6326,22 +6410,22 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>V7871800000</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>20164396C</t>
+          <t>20164397C</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>487471800000</t>
+          <t>487471800002</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -6350,25 +6434,25 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>15311</v>
+        <v>30390</v>
       </c>
       <c r="N55" t="n">
-        <v>15159</v>
+        <v>28188</v>
       </c>
       <c r="O55" t="n">
-        <v>1</v>
+        <v>87</v>
       </c>
       <c r="P55" t="n">
-        <v>1</v>
+        <v>87</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="T55" t="n">
         <v>0</v>
@@ -6377,26 +6461,26 @@
         <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>8489 WESTSIDE INDUSTRIAL DRIVE</t>
+          <t>326 U.S. HIGHWAY 49 SOUTH</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>JACKSONVILLE</t>
+          <t>RICHLAND</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>32219</t>
+          <t>39218</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6505,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>SO154730</t>
+          <t>SO154754</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>10054</t>
+          <t>38913</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -6436,22 +6520,22 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>V7871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>20164397C</t>
+          <t>20164396C</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>487471800002</t>
+          <t>487471800000</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -6460,16 +6544,16 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>30731</v>
+        <v>15255</v>
       </c>
       <c r="N56" t="n">
-        <v>29723</v>
+        <v>14411</v>
       </c>
       <c r="O56" t="n">
-        <v>140</v>
+        <v>49</v>
       </c>
       <c r="P56" t="n">
-        <v>140</v>
+        <v>49</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -6487,26 +6571,26 @@
         <v>0</v>
       </c>
       <c r="V56" t="n">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>8489 WESTSIDE INDUSTRIAL DRIVE</t>
+          <t>36663 VAN BORN RD</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>JACKSONVILLE</t>
+          <t>ROMULUS</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>32219</t>
+          <t>48174</t>
         </is>
       </c>
     </row>
@@ -6531,12 +6615,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>SO154733</t>
+          <t>SO154754</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>15591</t>
+          <t>38913</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -6570,16 +6654,16 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>30731</v>
+        <v>30390</v>
       </c>
       <c r="N57" t="n">
-        <v>29723</v>
+        <v>28188</v>
       </c>
       <c r="O57" t="n">
-        <v>87</v>
+        <v>184</v>
       </c>
       <c r="P57" t="n">
-        <v>87</v>
+        <v>184</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -6601,22 +6685,22 @@
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>326 U.S. HIGHWAY 49 SOUTH</t>
+          <t>36663 VAN BORN RD</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>RICHLAND</t>
+          <t>ROMULUS</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>39218</t>
+          <t>48174</t>
         </is>
       </c>
     </row>
@@ -6641,12 +6725,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>SO154743</t>
+          <t>SO154756</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>22732</t>
+          <t>40247</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -6656,22 +6740,22 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>V7871800002</t>
+          <t>7871800000</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>20164397C</t>
+          <t>20164394C</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>487471800002</t>
+          <t>48741800000</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+          <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -6680,16 +6764,16 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>30731</v>
+        <v>4928</v>
       </c>
       <c r="N58" t="n">
-        <v>29723</v>
+        <v>4501</v>
       </c>
       <c r="O58" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="P58" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -6707,26 +6791,26 @@
         <v>0</v>
       </c>
       <c r="V58" t="n">
-        <v>29.4</v>
+        <v>57.33</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>1425 MAGELLAN ROAD</t>
+          <t>550 LAKESIDE PARKWAY</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>HANOVER</t>
+          <t>FLOWER MOUND</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>21076</t>
+          <t>75028</t>
         </is>
       </c>
     </row>
@@ -6751,12 +6835,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>SO154745</t>
+          <t>SO154756</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>24198</t>
+          <t>40247</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -6766,22 +6850,22 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>V7871800000</t>
+          <t>7871800002</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>20164396C</t>
+          <t>20164395C</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>487471800000</t>
+          <t>48741800002</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -6790,16 +6874,16 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>15311</v>
+        <v>13622</v>
       </c>
       <c r="N59" t="n">
-        <v>15159</v>
+        <v>13025</v>
       </c>
       <c r="O59" t="n">
-        <v>11</v>
+        <v>102</v>
       </c>
       <c r="P59" t="n">
-        <v>11</v>
+        <v>102</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -6817,26 +6901,26 @@
         <v>0</v>
       </c>
       <c r="V59" t="n">
-        <v>47.46</v>
+        <v>36.8598</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>14599 NW 8TH STREET</t>
+          <t>550 LAKESIDE PARKWAY</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>SUNRISE</t>
+          <t>FLOWER MOUND</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>33325</t>
+          <t>75028</t>
         </is>
       </c>
     </row>
@@ -6861,12 +6945,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>SO154753</t>
+          <t>SO154764</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>35973</t>
+          <t>61288</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -6876,22 +6960,22 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>7871800002</t>
+          <t>7871800000</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>20164395C</t>
+          <t>20164394C</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>48741800002</t>
+          <t>48741800000</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+          <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6900,16 +6984,16 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>14145</v>
+        <v>4928</v>
       </c>
       <c r="N60" t="n">
-        <v>13553</v>
+        <v>4501</v>
       </c>
       <c r="O60" t="n">
-        <v>59</v>
+        <v>179</v>
       </c>
       <c r="P60" t="n">
-        <v>59</v>
+        <v>179</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -6927,26 +7011,26 @@
         <v>0</v>
       </c>
       <c r="V60" t="n">
-        <v>36.8598</v>
+        <v>57.33</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>1160 MARQUETTE STREET</t>
+          <t>8313 WEST PIERCE STREET, SUITE 100</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>CLEVELAND</t>
+          <t>TOLLESON</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>44114</t>
+          <t>85353</t>
         </is>
       </c>
     </row>
@@ -6971,12 +7055,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>SO154754</t>
+          <t>SO154764</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>38913</t>
+          <t>61288</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -7010,16 +7094,16 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>15311</v>
+        <v>15255</v>
       </c>
       <c r="N61" t="n">
-        <v>15159</v>
+        <v>14411</v>
       </c>
       <c r="O61" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="P61" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -7041,22 +7125,22 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>36663 VAN BORN RD</t>
+          <t>8313 WEST PIERCE STREET, SUITE 100</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>ROMULUS</t>
+          <t>TOLLESON</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>48174</t>
+          <t>85353</t>
         </is>
       </c>
     </row>
@@ -7067,26 +7151,26 @@
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>46105</v>
+        <v>46097</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>201067</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>SO154754</t>
+          <t>SO154143</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>38913</t>
+          <t>4533277020</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -7106,7 +7190,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>487471800002</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -7120,16 +7204,16 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>30731</v>
+        <v>30390</v>
       </c>
       <c r="N62" t="n">
-        <v>29723</v>
+        <v>28188</v>
       </c>
       <c r="O62" t="n">
-        <v>184</v>
+        <v>44</v>
       </c>
       <c r="P62" t="n">
-        <v>184</v>
+        <v>44</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -7151,22 +7235,22 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>36663 VAN BORN RD</t>
+          <t>1901 RAYMER AVENUE</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>ROMULUS</t>
+          <t>Fullerton</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>48174</t>
+          <t>92833</t>
         </is>
       </c>
     </row>
@@ -7177,26 +7261,26 @@
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>46105</v>
+        <v>46093</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>201067</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>SO154756</t>
+          <t>SO154038</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>40247</t>
+          <t>4519714426</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -7206,22 +7290,22 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>7871800000</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>20164394C</t>
+          <t>20164397C</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>48741800000</t>
+          <t>O-T871800002</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -7230,25 +7314,25 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>4928</v>
+        <v>30390</v>
       </c>
       <c r="N63" t="n">
-        <v>4634</v>
+        <v>28188</v>
       </c>
       <c r="O63" t="n">
-        <v>87</v>
+        <v>140</v>
       </c>
       <c r="P63" t="n">
-        <v>87</v>
+        <v>140</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="T63" t="n">
         <v>0</v>
@@ -7257,1120 +7341,24 @@
         <v>0</v>
       </c>
       <c r="V63" t="n">
-        <v>57.33</v>
+        <v>29.4</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>550 LAKESIDE PARKWAY</t>
+          <t>3770 HOGUM BAY RD. NE</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>FLOWER MOUND</t>
+          <t>LACEY</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>WA</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
-        <is>
-          <t>75028</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="B64" s="1" t="n">
-        <v>46105</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>201067</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>SO154756</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>40247</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>SENSI MEDICAL</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>7871800002</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>20164395C</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>48741800002</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="M64" t="n">
-        <v>14145</v>
-      </c>
-      <c r="N64" t="n">
-        <v>13553</v>
-      </c>
-      <c r="O64" t="n">
-        <v>102</v>
-      </c>
-      <c r="P64" t="n">
-        <v>102</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
-      <c r="R64" t="n">
-        <v>0</v>
-      </c>
-      <c r="S64" t="n">
-        <v>0</v>
-      </c>
-      <c r="T64" t="n">
-        <v>0</v>
-      </c>
-      <c r="U64" t="n">
-        <v>0</v>
-      </c>
-      <c r="V64" t="n">
-        <v>36.8598</v>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>550 LAKESIDE PARKWAY</t>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>FLOWER MOUND</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>TX</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>75028</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="B65" s="1" t="n">
-        <v>46105</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>201067</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>SO154757</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>40677</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>SENSI MEDICAL</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>V7871800002</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>20164397C</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>487471800002</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="M65" t="n">
-        <v>30731</v>
-      </c>
-      <c r="N65" t="n">
-        <v>29723</v>
-      </c>
-      <c r="O65" t="n">
-        <v>195</v>
-      </c>
-      <c r="P65" t="n">
-        <v>195</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" t="n">
-        <v>0</v>
-      </c>
-      <c r="S65" t="n">
-        <v>0</v>
-      </c>
-      <c r="T65" t="n">
-        <v>0</v>
-      </c>
-      <c r="U65" t="n">
-        <v>0</v>
-      </c>
-      <c r="V65" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>4807 NE 63RD AVENUE</t>
-        </is>
-      </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>GAINESVILLE</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>32609</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="B66" s="1" t="n">
-        <v>46105</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>201067</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>SO154763</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>60075</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>SENSI MEDICAL</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>7871800002</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>20164395C</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>48741800002</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="M66" t="n">
-        <v>14145</v>
-      </c>
-      <c r="N66" t="n">
-        <v>13553</v>
-      </c>
-      <c r="O66" t="n">
-        <v>18</v>
-      </c>
-      <c r="P66" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
-      <c r="R66" t="n">
-        <v>0</v>
-      </c>
-      <c r="S66" t="n">
-        <v>0</v>
-      </c>
-      <c r="T66" t="n">
-        <v>0</v>
-      </c>
-      <c r="U66" t="n">
-        <v>0</v>
-      </c>
-      <c r="V66" t="n">
-        <v>36.8598</v>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>4301 W VALLEY HWY EAST</t>
-        </is>
-      </c>
-      <c r="X66" t="inlineStr">
-        <is>
-          <t>SUMNER</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>WA</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>98390</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="B67" s="1" t="n">
-        <v>46105</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>201067</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>SO154764</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>61288</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>SENSI MEDICAL</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>7871800000</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>20164394C</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>48741800000</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="M67" t="n">
-        <v>4928</v>
-      </c>
-      <c r="N67" t="n">
-        <v>4634</v>
-      </c>
-      <c r="O67" t="n">
-        <v>179</v>
-      </c>
-      <c r="P67" t="n">
-        <v>179</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
-      <c r="R67" t="n">
-        <v>0</v>
-      </c>
-      <c r="S67" t="n">
-        <v>0</v>
-      </c>
-      <c r="T67" t="n">
-        <v>0</v>
-      </c>
-      <c r="U67" t="n">
-        <v>0</v>
-      </c>
-      <c r="V67" t="n">
-        <v>57.33</v>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>8313 WEST PIERCE STREET, SUITE 100</t>
-        </is>
-      </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t>TOLLESON</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>85353</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="B68" s="1" t="n">
-        <v>46105</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>201067</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>SO154764</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>61288</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>SENSI MEDICAL</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>V7871800000</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>20164396C</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>487471800000</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="M68" t="n">
-        <v>15311</v>
-      </c>
-      <c r="N68" t="n">
-        <v>15159</v>
-      </c>
-      <c r="O68" t="n">
-        <v>33</v>
-      </c>
-      <c r="P68" t="n">
-        <v>33</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
-      <c r="R68" t="n">
-        <v>0</v>
-      </c>
-      <c r="S68" t="n">
-        <v>0</v>
-      </c>
-      <c r="T68" t="n">
-        <v>0</v>
-      </c>
-      <c r="U68" t="n">
-        <v>0</v>
-      </c>
-      <c r="V68" t="n">
-        <v>47.46</v>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>8313 WEST PIERCE STREET, SUITE 100</t>
-        </is>
-      </c>
-      <c r="X68" t="inlineStr">
-        <is>
-          <t>TOLLESON</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>85353</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="B69" s="1" t="n">
-        <v>46105</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>201067</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>SO154769</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>70270</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>SENSI MEDICAL</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>V7871800002</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>20164397C</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>487471800002</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="M69" t="n">
-        <v>30731</v>
-      </c>
-      <c r="N69" t="n">
-        <v>29723</v>
-      </c>
-      <c r="O69" t="n">
-        <v>54</v>
-      </c>
-      <c r="P69" t="n">
-        <v>54</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
-      <c r="R69" t="n">
-        <v>0</v>
-      </c>
-      <c r="S69" t="n">
-        <v>0</v>
-      </c>
-      <c r="T69" t="n">
-        <v>0</v>
-      </c>
-      <c r="U69" t="n">
-        <v>0</v>
-      </c>
-      <c r="V69" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>1880 NORTH CORRINGTON AVE</t>
-        </is>
-      </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>KANSAS CITY</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>MO</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>64120</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="B70" s="1" t="n">
-        <v>46105</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>201067</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>SO154771</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>79001</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>SENSI MEDICAL</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>7871800002</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>20164395C</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>48741800002</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="M70" t="n">
-        <v>14145</v>
-      </c>
-      <c r="N70" t="n">
-        <v>13553</v>
-      </c>
-      <c r="O70" t="n">
-        <v>120</v>
-      </c>
-      <c r="P70" t="n">
-        <v>120</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
-      <c r="R70" t="n">
-        <v>0</v>
-      </c>
-      <c r="S70" t="n">
-        <v>0</v>
-      </c>
-      <c r="T70" t="n">
-        <v>0</v>
-      </c>
-      <c r="U70" t="n">
-        <v>0</v>
-      </c>
-      <c r="V70" t="n">
-        <v>36.8598</v>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>27695 S.W. 95th AVENUE</t>
-        </is>
-      </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>WILSONVILLE</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>OR</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>97070</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="B71" s="1" t="n">
-        <v>46100</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>209214</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>VENTURE RESPIRATORY INC. 209214</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>SO154426</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>17823</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>SENSI MEDICAL</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>7871800002</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>20164395C</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="M71" t="n">
-        <v>14145</v>
-      </c>
-      <c r="N71" t="n">
-        <v>13553</v>
-      </c>
-      <c r="O71" t="n">
-        <v>140</v>
-      </c>
-      <c r="P71" t="n">
-        <v>140</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
-      <c r="R71" t="n">
-        <v>0</v>
-      </c>
-      <c r="S71" t="n">
-        <v>0</v>
-      </c>
-      <c r="T71" t="n">
-        <v>0</v>
-      </c>
-      <c r="U71" t="n">
-        <v>0</v>
-      </c>
-      <c r="V71" t="n">
-        <v>36.86</v>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>630 Herman Rd</t>
-        </is>
-      </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>JACKSON</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>NJ</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>08527</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="B72" s="1" t="n">
-        <v>46097</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>201003</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>CAH : CARDINAL - MD 201003</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>SO154143</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>4533277020</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>SENSI MEDICAL</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>V7871800002</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>20164397C</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>V7871800002</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="M72" t="n">
-        <v>30731</v>
-      </c>
-      <c r="N72" t="n">
-        <v>29723</v>
-      </c>
-      <c r="O72" t="n">
-        <v>44</v>
-      </c>
-      <c r="P72" t="n">
-        <v>44</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
-      <c r="R72" t="n">
-        <v>0</v>
-      </c>
-      <c r="S72" t="n">
-        <v>0</v>
-      </c>
-      <c r="T72" t="n">
-        <v>0</v>
-      </c>
-      <c r="U72" t="n">
-        <v>0</v>
-      </c>
-      <c r="V72" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>1901 RAYMER AVENUE</t>
-        </is>
-      </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>Fullerton</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>92833</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="B73" s="1" t="n">
-        <v>46093</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>202033</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>SO154038</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>4519714426</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>SENSI MEDICAL</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>V7871800002</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>20164397C</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>O-T871800002</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="M73" t="n">
-        <v>30731</v>
-      </c>
-      <c r="N73" t="n">
-        <v>29723</v>
-      </c>
-      <c r="O73" t="n">
-        <v>140</v>
-      </c>
-      <c r="P73" t="n">
-        <v>140</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
-      <c r="R73" t="n">
-        <v>140</v>
-      </c>
-      <c r="S73" t="n">
-        <v>140</v>
-      </c>
-      <c r="T73" t="n">
-        <v>0</v>
-      </c>
-      <c r="U73" t="n">
-        <v>0</v>
-      </c>
-      <c r="V73" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>3770 HOGUM BAY RD. NE</t>
-        </is>
-      </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>LACEY</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>WA</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
         <is>
           <t>98516</t>
         </is>

--- a/data/searchresults.xlsx
+++ b/data/searchresults.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z63"/>
+  <dimension ref="A1:Z61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -555,30 +555,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>ASV</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>209198</t>
+          <t>107001</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PROGRESSIVE MEDICAL CONCEPTS, LLC 209198</t>
+          <t>BOUND TREE MEDICAL, LLC 107001</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SO154968</t>
+          <t>SO155003</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>BV4131-5863</t>
+          <t>B1310315831-10</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -608,16 +608,16 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>4928</v>
+        <v>4587</v>
       </c>
       <c r="N2" t="n">
-        <v>4501</v>
+        <v>4323</v>
       </c>
       <c r="O2" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="P2" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -639,22 +639,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>4210 ALTRURIA RD</t>
+          <t>1033 COLLINS RD STE A</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>BARTLETT</t>
+          <t>Greenwood</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>38135</t>
+          <t>46143</t>
         </is>
       </c>
     </row>
@@ -665,26 +665,26 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>201003</t>
+          <t>209304</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CAH : CARDINAL - MD 201003</t>
+          <t>RGH Enterprises, Inc. dba Cardinal Health At-Home 209304</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SO154855</t>
+          <t>SO155012</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>4533295895</t>
+          <t>1043459060</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -694,22 +694,18 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>V7871800000</t>
+          <t>7871800000</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20164396C</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>V7871800000</t>
-        </is>
-      </c>
+          <t>20164394C</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+          <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -718,15 +714,17 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>15255</v>
+        <v>4587</v>
       </c>
       <c r="N3" t="n">
-        <v>14411</v>
+        <v>4323</v>
       </c>
       <c r="O3" t="n">
-        <v>5</v>
-      </c>
-      <c r="P3" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="P3" t="n">
+        <v>16</v>
+      </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
@@ -740,29 +738,29 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>47.46</v>
+        <v>57.33</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Dixon, CA DC</t>
+          <t>4234 Surles Ct Suite 100</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Dixon</t>
+          <t>Durham</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>95620</t>
+          <t>27703</t>
         </is>
       </c>
     </row>
@@ -773,26 +771,26 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>201001</t>
+          <t>209304</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CAH : CARDINAL - MD DS 201001</t>
+          <t>RGH Enterprises, Inc. dba Cardinal Health At-Home 209304</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SO154863</t>
+          <t>SO155013</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>4231373081</t>
+          <t>1043459061</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -802,22 +800,18 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>7871800002</t>
+          <t>7871800000</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20164395C</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>7871800002</t>
-        </is>
-      </c>
+          <t>20164394C</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+          <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -826,15 +820,17 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>13622</v>
+        <v>4587</v>
       </c>
       <c r="N4" t="n">
-        <v>13025</v>
+        <v>4323</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
-      </c>
-      <c r="P4" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="P4" t="n">
+        <v>6</v>
+      </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
@@ -848,29 +844,29 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>36.86</v>
+        <v>57.33</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>6441 MAIN ST</t>
+          <t>1265 South River Road Suite 200</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>HOUSTON</t>
+          <t>Cranbury</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>770301502</t>
+          <t>08512</t>
         </is>
       </c>
     </row>
@@ -881,26 +877,26 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>202040</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CHS : CONCORDANCE HEALTHCARE SOLUTIONS, LLC 202040</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SO154870</t>
+          <t>SO155023</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>3591523</t>
+          <t>4533299552</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -910,22 +906,22 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>7871800000</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20164394C</t>
+          <t>20164397C</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>354861</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -934,16 +930,16 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>4928</v>
+        <v>28710</v>
       </c>
       <c r="N5" t="n">
-        <v>4501</v>
+        <v>27008</v>
       </c>
       <c r="O5" t="n">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="P5" t="n">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -961,26 +957,26 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>57.33</v>
+        <v>29.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>60 DISTRIBUTION BOULEVARD</t>
+          <t>3205 MERIDIAN PARKWAY</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>EDISON</t>
+          <t>WESTON</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08817</t>
+          <t>33331</t>
         </is>
       </c>
     </row>
@@ -991,26 +987,26 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SO154908</t>
+          <t>SO155025</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>4519767997</t>
+          <t>4533299554</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1020,22 +1016,22 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>7871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20164395C</t>
+          <t>20164396C</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O-T7871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1044,16 +1040,16 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>13622</v>
+        <v>14606</v>
       </c>
       <c r="N6" t="n">
-        <v>13025</v>
+        <v>13839</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="P6" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1071,26 +1067,26 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>36.86</v>
+        <v>47.46</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>735 COUNTY ROAD 4 EAST</t>
+          <t>22000 Alexander Road</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>PRATTVILLE</t>
+          <t>Walton Hills</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>36067</t>
+          <t>44146</t>
         </is>
       </c>
     </row>
@@ -1101,26 +1097,26 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SO154908</t>
+          <t>SO155025</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>4519767997</t>
+          <t>4533299554</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1140,7 +1136,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O-T871800002</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1154,16 +1150,16 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>30390</v>
+        <v>28710</v>
       </c>
       <c r="N7" t="n">
-        <v>28188</v>
+        <v>27008</v>
       </c>
       <c r="O7" t="n">
-        <v>70</v>
+        <v>230</v>
       </c>
       <c r="P7" t="n">
-        <v>70</v>
+        <v>230</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1185,22 +1181,22 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>735 COUNTY ROAD 4 EAST</t>
+          <t>22000 Alexander Road</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>PRATTVILLE</t>
+          <t>Walton Hills</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36067</t>
+          <t>44146</t>
         </is>
       </c>
     </row>
@@ -1211,26 +1207,26 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SO154909</t>
+          <t>SO155028</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4519767998</t>
+          <t>4533299557</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1240,22 +1236,22 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>V7871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20164397C</t>
+          <t>20164396C</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O-T871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1264,16 +1260,16 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>30390</v>
+        <v>14606</v>
       </c>
       <c r="N8" t="n">
-        <v>28188</v>
+        <v>13839</v>
       </c>
       <c r="O8" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="P8" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1291,26 +1287,26 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>13115 BROCKTON LANE N</t>
+          <t>11300 GLENWOOD STREET</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>ROGERS</t>
+          <t>OVERLAND PARK</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>KS</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>55374</t>
+          <t>66211</t>
         </is>
       </c>
     </row>
@@ -1321,26 +1317,26 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SO154911</t>
+          <t>SO155031</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>4519768000</t>
+          <t>4533299561</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1350,22 +1346,22 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>V7871800002</t>
+          <t>7871800002</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20164397C</t>
+          <t>20164395C</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O-T871800002</t>
+          <t>7871800002</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1374,16 +1370,16 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>30390</v>
+        <v>13099</v>
       </c>
       <c r="N9" t="n">
-        <v>28188</v>
+        <v>12533</v>
       </c>
       <c r="O9" t="n">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="P9" t="n">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1401,26 +1397,26 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>29.4</v>
+        <v>36.86</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>500 SHARKEY DRIVE</t>
+          <t>8440 CONCORD CENTER DR</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>MAUMELLE</t>
+          <t>ENGLEWOOD</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>72113</t>
+          <t>80112</t>
         </is>
       </c>
     </row>
@@ -1431,26 +1427,26 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SO154917</t>
+          <t>SO155032</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4519768006</t>
+          <t>4533299562</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1460,22 +1456,22 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>V7871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20164397C</t>
+          <t>20164396C</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O-T871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1484,16 +1480,16 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>30390</v>
+        <v>14606</v>
       </c>
       <c r="N10" t="n">
-        <v>28188</v>
+        <v>13839</v>
       </c>
       <c r="O10" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1511,26 +1507,26 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>1062 OLD DIXIE HIGHWAY</t>
+          <t>6710 26TH STREET EAST</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>AUBURNDALE</t>
+          <t>FIFE</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>WA</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>33823</t>
+          <t>98424</t>
         </is>
       </c>
     </row>
@@ -1541,26 +1537,26 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SO154918</t>
+          <t>SO155033</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>4519768007</t>
+          <t>4533299563</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1570,22 +1566,22 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>V7871800002</t>
+          <t>7871800000</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20164397C</t>
+          <t>20164394C</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O-T871800002</t>
+          <t>7871800000</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+          <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1594,16 +1590,16 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>30390</v>
+        <v>4587</v>
       </c>
       <c r="N11" t="n">
-        <v>28188</v>
+        <v>4323</v>
       </c>
       <c r="O11" t="n">
-        <v>140</v>
+        <v>54</v>
       </c>
       <c r="P11" t="n">
-        <v>140</v>
+        <v>54</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1621,26 +1617,26 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>29.4</v>
+        <v>57.33</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>1960 W. MIRO WAY</t>
+          <t>2222 S. STEARMAN DRIVE</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>RIALTO</t>
+          <t>CHANDLER</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>92376</t>
+          <t>85286</t>
         </is>
       </c>
     </row>
@@ -1651,26 +1647,26 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SO154919</t>
+          <t>SO155035</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>4519768008</t>
+          <t>4533299565</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1680,22 +1676,22 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7871800000</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20164394C</t>
+          <t>20164396C</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O-T71800000</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1704,16 +1700,16 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>4928</v>
+        <v>14606</v>
       </c>
       <c r="N12" t="n">
-        <v>4501</v>
+        <v>13839</v>
       </c>
       <c r="O12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="P12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1731,26 +1727,26 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>57.33</v>
+        <v>47.46</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>29895 US HWY 90 BUS</t>
+          <t>5532 SPELLMIRE DRIVE</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>KATY</t>
+          <t>CINCINNATI</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>77494</t>
+          <t>45246</t>
         </is>
       </c>
     </row>
@@ -1761,26 +1757,26 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SO154919</t>
+          <t>SO155035</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>4519768008</t>
+          <t>4533299565</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1790,22 +1786,22 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>V7871800000</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20164396C</t>
+          <t>20164397C</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>O-T7871800000</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1814,16 +1810,16 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>15255</v>
+        <v>28710</v>
       </c>
       <c r="N13" t="n">
-        <v>14411</v>
+        <v>27008</v>
       </c>
       <c r="O13" t="n">
-        <v>130</v>
+        <v>5</v>
       </c>
       <c r="P13" t="n">
-        <v>130</v>
+        <v>5</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1841,26 +1837,26 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>29895 US HWY 90 BUS</t>
+          <t>5532 SPELLMIRE DRIVE</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>KATY</t>
+          <t>CINCINNATI</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>77494</t>
+          <t>45246</t>
         </is>
       </c>
     </row>
@@ -1871,26 +1867,26 @@
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SO154920</t>
+          <t>SO155044</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>4519768009</t>
+          <t>4533299577</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1900,22 +1896,22 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>V7871800000</t>
+          <t>7871800000</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20164396C</t>
+          <t>20164394C</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>O-T7871800000</t>
+          <t>7871800000</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+          <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1924,16 +1920,16 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>15255</v>
+        <v>4587</v>
       </c>
       <c r="N14" t="n">
-        <v>14411</v>
+        <v>4323</v>
       </c>
       <c r="O14" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="P14" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -1951,26 +1947,26 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>47.46</v>
+        <v>57.33</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>5000 Premier Parkway, Suite 100</t>
+          <t>500 NEELYTOWN ROAD</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Saint Peters</t>
+          <t>MONTGOMERY</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>63376</t>
+          <t>12549</t>
         </is>
       </c>
     </row>
@@ -1981,26 +1977,26 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SO154920</t>
+          <t>SO155044</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>4519768009</t>
+          <t>4533299577</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2010,22 +2006,22 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>V7871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>20164397C</t>
+          <t>20164396C</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>O-T871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2034,16 +2030,16 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>30390</v>
+        <v>14606</v>
       </c>
       <c r="N15" t="n">
-        <v>28188</v>
+        <v>13839</v>
       </c>
       <c r="O15" t="n">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="P15" t="n">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2061,26 +2057,26 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>5000 Premier Parkway, Suite 100</t>
+          <t>500 NEELYTOWN ROAD</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Saint Peters</t>
+          <t>MONTGOMERY</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>63376</t>
+          <t>12549</t>
         </is>
       </c>
     </row>
@@ -2091,26 +2087,26 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SO154922</t>
+          <t>SO155018</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>4519768011</t>
+          <t>4533296391</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2120,22 +2116,22 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>V7871800000</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20164396C</t>
+          <t>20164397C</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>O-T7871800000</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2144,16 +2140,16 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>15255</v>
+        <v>28710</v>
       </c>
       <c r="N16" t="n">
-        <v>14411</v>
+        <v>27008</v>
       </c>
       <c r="O16" t="n">
-        <v>41</v>
+        <v>444</v>
       </c>
       <c r="P16" t="n">
-        <v>41</v>
+        <v>444</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2171,16 +2167,16 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>1040 ENTERPRISE PARKWAY</t>
+          <t>9756 Heartland Court</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>WEST JEFFERSON</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2190,7 +2186,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>43162</t>
+          <t>43217</t>
         </is>
       </c>
     </row>
@@ -2201,26 +2197,26 @@
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SO154922</t>
+          <t>SO155020</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>4519768011</t>
+          <t>4533299549</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2230,22 +2226,22 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7871800002</t>
+          <t>7871800000</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20164395C</t>
+          <t>20164394C</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>O-T7871800002</t>
+          <t>7871800000</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+          <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2254,16 +2250,16 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>13622</v>
+        <v>4587</v>
       </c>
       <c r="N17" t="n">
-        <v>13025</v>
+        <v>4323</v>
       </c>
       <c r="O17" t="n">
-        <v>210</v>
+        <v>25</v>
       </c>
       <c r="P17" t="n">
-        <v>210</v>
+        <v>25</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -2281,26 +2277,26 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>36.86</v>
+        <v>57.33</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>1040 ENTERPRISE PARKWAY</t>
+          <t>Edison, NJ DC</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>WEST JEFFERSON</t>
+          <t>Edison</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>43162</t>
+          <t>08837</t>
         </is>
       </c>
     </row>
@@ -2311,26 +2307,26 @@
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SO154922</t>
+          <t>SO155020</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>4519768011</t>
+          <t>4533299549</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2340,22 +2336,22 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>V7871800002</t>
+          <t>7871800002</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20164397C</t>
+          <t>20164395C</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>O-T871800002</t>
+          <t>7871800002</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2364,16 +2360,16 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>30390</v>
+        <v>13099</v>
       </c>
       <c r="N18" t="n">
-        <v>28188</v>
+        <v>12533</v>
       </c>
       <c r="O18" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="P18" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -2391,26 +2387,26 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>29.4</v>
+        <v>36.86</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>1040 ENTERPRISE PARKWAY</t>
+          <t>Edison, NJ DC</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>WEST JEFFERSON</t>
+          <t>Edison</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>43162</t>
+          <t>08837</t>
         </is>
       </c>
     </row>
@@ -2421,26 +2417,26 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SO154924</t>
+          <t>SO155021</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>4519768013</t>
+          <t>4533299550</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2450,22 +2446,22 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>V7871800002</t>
+          <t>7871800002</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20164397C</t>
+          <t>20164395C</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>O-T871800002</t>
+          <t>7871800002</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2474,16 +2470,16 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>30390</v>
+        <v>13099</v>
       </c>
       <c r="N19" t="n">
-        <v>28188</v>
+        <v>12533</v>
       </c>
       <c r="O19" t="n">
-        <v>140</v>
+        <v>167</v>
       </c>
       <c r="P19" t="n">
-        <v>140</v>
+        <v>167</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -2501,26 +2497,26 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>29.4</v>
+        <v>36.86</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>5701 PROMONTORY PARKWAY</t>
+          <t>80 Pine Hill Dr</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>TRACY</t>
+          <t>Boylston</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>95377</t>
+          <t>01505</t>
         </is>
       </c>
     </row>
@@ -2531,26 +2527,26 @@
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SO154931</t>
+          <t>SO155022</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>4519768020</t>
+          <t>4533299551</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2560,22 +2556,22 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>V7871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20164397C</t>
+          <t>20164396C</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>O-T871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2584,16 +2580,16 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>30390</v>
+        <v>14606</v>
       </c>
       <c r="N20" t="n">
-        <v>28188</v>
+        <v>13839</v>
       </c>
       <c r="O20" t="n">
-        <v>210</v>
+        <v>108</v>
       </c>
       <c r="P20" t="n">
-        <v>210</v>
+        <v>108</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -2611,26 +2607,26 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>3770 HOGUM BAY RD. NE</t>
+          <t>1761 SATELLITE BLVD</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>LACEY</t>
+          <t>BUFORD</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>WA</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>98516</t>
+          <t>30518</t>
         </is>
       </c>
     </row>
@@ -2641,26 +2637,26 @@
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SO154902</t>
+          <t>SO155022</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>4519767991</t>
+          <t>4533299551</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2670,22 +2666,22 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>V7871800000</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20164396C</t>
+          <t>20164397C</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>O-T7871800000</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2694,16 +2690,16 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>15255</v>
+        <v>28710</v>
       </c>
       <c r="N21" t="n">
-        <v>14411</v>
+        <v>27008</v>
       </c>
       <c r="O21" t="n">
-        <v>16</v>
+        <v>323</v>
       </c>
       <c r="P21" t="n">
-        <v>16</v>
+        <v>323</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -2721,26 +2717,26 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>1 MEDLINE DRIVE, SUITE 100</t>
+          <t>1761 SATELLITE BLVD</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>WILMER</t>
+          <t>BUFORD</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>75172</t>
+          <t>30518</t>
         </is>
       </c>
     </row>
@@ -2751,26 +2747,26 @@
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SO154902</t>
+          <t>SO155024</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>4519767991</t>
+          <t>4533299553</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2790,7 +2786,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>O-T7871800002</t>
+          <t>7871800002</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2804,16 +2800,16 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>13622</v>
+        <v>13099</v>
       </c>
       <c r="N22" t="n">
-        <v>13025</v>
+        <v>12533</v>
       </c>
       <c r="O22" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P22" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -2835,22 +2831,22 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>1 MEDLINE DRIVE, SUITE 100</t>
+          <t>8640 NAIL ROAD</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>WILMER</t>
+          <t>OLIVE BRANCH</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>75172</t>
+          <t>38654</t>
         </is>
       </c>
     </row>
@@ -2861,26 +2857,26 @@
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SO154902</t>
+          <t>SO155024</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>4519767991</t>
+          <t>4533299553</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2900,7 +2896,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>O-T871800002</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2914,16 +2910,16 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>30390</v>
+        <v>28710</v>
       </c>
       <c r="N23" t="n">
-        <v>28188</v>
+        <v>27008</v>
       </c>
       <c r="O23" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="P23" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -2945,22 +2941,22 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>1 MEDLINE DRIVE, SUITE 100</t>
+          <t>8640 NAIL ROAD</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>WILMER</t>
+          <t>OLIVE BRANCH</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>75172</t>
+          <t>38654</t>
         </is>
       </c>
     </row>
@@ -2971,26 +2967,26 @@
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SO154906</t>
+          <t>SO155026</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>4519767995</t>
+          <t>4533299555</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3010,7 +3006,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>O-T7871800000</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3024,16 +3020,16 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>15255</v>
+        <v>14606</v>
       </c>
       <c r="N24" t="n">
-        <v>14411</v>
+        <v>13839</v>
       </c>
       <c r="O24" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="P24" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -3055,12 +3051,12 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>1401 N. UNIVERSAL AVE.</t>
+          <t>13636 LAKEFRONT DRIVE</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>KANSAS CITY</t>
+          <t>EARTH CITY</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -3070,7 +3066,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>64120</t>
+          <t>63045</t>
         </is>
       </c>
     </row>
@@ -3081,26 +3077,26 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SO154910</t>
+          <t>SO155027</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>4519767999</t>
+          <t>4533299556</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3110,22 +3106,22 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>V7871800000</t>
+          <t>7871800000</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>20164396C</t>
+          <t>20164394C</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>O-T7871800000</t>
+          <t>7871800000</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+          <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -3134,16 +3130,16 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>15255</v>
+        <v>4587</v>
       </c>
       <c r="N25" t="n">
-        <v>14411</v>
+        <v>4323</v>
       </c>
       <c r="O25" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="P25" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -3161,26 +3157,26 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>47.46</v>
+        <v>57.33</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>1900 MEADOWVILLE TECHNOLOGY</t>
+          <t>2310A CENTER SQUARE ROAD</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>CHESTER</t>
+          <t>SWEDESBORO</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>VA</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>23834</t>
+          <t>08085</t>
         </is>
       </c>
     </row>
@@ -3191,26 +3187,26 @@
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SO154910</t>
+          <t>SO155027</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>4519767999</t>
+          <t>4533299556</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3220,22 +3216,22 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>V7871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>20164397C</t>
+          <t>20164396C</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>O-T871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3244,16 +3240,16 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>30390</v>
+        <v>14606</v>
       </c>
       <c r="N26" t="n">
-        <v>28188</v>
+        <v>13839</v>
       </c>
       <c r="O26" t="n">
-        <v>140</v>
+        <v>43</v>
       </c>
       <c r="P26" t="n">
-        <v>140</v>
+        <v>43</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -3271,26 +3267,26 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>1900 MEADOWVILLE TECHNOLOGY</t>
+          <t>2310A CENTER SQUARE ROAD</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>CHESTER</t>
+          <t>SWEDESBORO</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>VA</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>23834</t>
+          <t>08085</t>
         </is>
       </c>
     </row>
@@ -3301,26 +3297,26 @@
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SO154912</t>
+          <t>SO155030</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>4519768001</t>
+          <t>4533299560</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3330,22 +3326,22 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>V7871800000</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>20164396C</t>
+          <t>20164397C</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>O-T7871800000</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3354,16 +3350,16 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>15255</v>
+        <v>28710</v>
       </c>
       <c r="N27" t="n">
-        <v>14411</v>
+        <v>27008</v>
       </c>
       <c r="O27" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P27" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -3381,26 +3377,26 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>1989 TRANSIT WAY</t>
+          <t>151 NORTH PARK CENTRAL</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>BROCKPORT</t>
+          <t>HOUSTON</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14420</t>
+          <t>77073</t>
         </is>
       </c>
     </row>
@@ -3411,26 +3407,26 @@
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SO154912</t>
+          <t>SO155034</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>4519768001</t>
+          <t>4533299564</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3450,7 +3446,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>O-T871800002</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3464,16 +3460,16 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>30390</v>
+        <v>28710</v>
       </c>
       <c r="N28" t="n">
-        <v>28188</v>
+        <v>27008</v>
       </c>
       <c r="O28" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P28" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -3495,22 +3491,22 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>1989 TRANSIT WAY</t>
+          <t>1009 OPULE STREET</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>BROCKPORT</t>
+          <t>KAPOLEI</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>HI</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14420</t>
+          <t>96707</t>
         </is>
       </c>
     </row>
@@ -3521,26 +3517,26 @@
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SO154913</t>
+          <t>SO155036</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>4519768002</t>
+          <t>4533299566</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3560,7 +3556,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>O-T7871800002</t>
+          <t>7871800002</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3574,16 +3570,16 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>13622</v>
+        <v>13099</v>
       </c>
       <c r="N29" t="n">
-        <v>13025</v>
+        <v>12533</v>
       </c>
       <c r="O29" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="P29" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -3605,22 +3601,22 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>36445 VAN BORN ROAD</t>
+          <t>4551 EAST PHILADELPHIA ST</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>ROMULUS</t>
+          <t>ONTARIO</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>48174</t>
+          <t>91761</t>
         </is>
       </c>
     </row>
@@ -3631,26 +3627,26 @@
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SO154914</t>
+          <t>SO155036</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>4519768003</t>
+          <t>4533299566</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3660,22 +3656,22 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>V7871800000</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>20164396C</t>
+          <t>20164397C</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>O-T7871800000</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3684,16 +3680,16 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>15255</v>
+        <v>28710</v>
       </c>
       <c r="N30" t="n">
-        <v>14411</v>
+        <v>27008</v>
       </c>
       <c r="O30" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="P30" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -3711,26 +3707,26 @@
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>60 ATHLETES WAY</t>
+          <t>4551 EAST PHILADELPHIA ST</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>MOUNT JULIET</t>
+          <t>ONTARIO</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>37122</t>
+          <t>91761</t>
         </is>
       </c>
     </row>
@@ -3741,26 +3737,26 @@
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SO154914</t>
+          <t>SO155037</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>4519768003</t>
+          <t>4533299568</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3770,22 +3766,22 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>V7871800002</t>
+          <t>7871800002</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>20164397C</t>
+          <t>20164395C</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>O-T871800002</t>
+          <t>7871800002</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3794,16 +3790,16 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>30390</v>
+        <v>13099</v>
       </c>
       <c r="N31" t="n">
-        <v>28188</v>
+        <v>12533</v>
       </c>
       <c r="O31" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="P31" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -3821,26 +3817,26 @@
         <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>29.4</v>
+        <v>36.86</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>60 ATHLETES WAY</t>
+          <t>2101 WAUKEGAN ROAD</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>MOUNT JULIET</t>
+          <t>WAUKEGAN</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>37122</t>
+          <t>60085</t>
         </is>
       </c>
     </row>
@@ -3851,26 +3847,26 @@
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SO154916</t>
+          <t>SO155037</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>4519768005</t>
+          <t>4533299568</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3890,7 +3886,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>O-T7871800000</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3904,16 +3900,16 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>15255</v>
+        <v>14606</v>
       </c>
       <c r="N32" t="n">
-        <v>14411</v>
+        <v>13839</v>
       </c>
       <c r="O32" t="n">
-        <v>28</v>
+        <v>117</v>
       </c>
       <c r="P32" t="n">
-        <v>28</v>
+        <v>117</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -3935,22 +3931,22 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>1500 MEDLINE PLACE</t>
+          <t>2101 WAUKEGAN ROAD</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>MC DONOUGH</t>
+          <t>WAUKEGAN</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>30253</t>
+          <t>60085</t>
         </is>
       </c>
     </row>
@@ -3961,26 +3957,26 @@
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SO154921</t>
+          <t>SO155037</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>4519768010</t>
+          <t>4533299568</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3990,22 +3986,22 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>V7871800000</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20164396C</t>
+          <t>20164397C</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>O-T7871800000</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -4014,16 +4010,16 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>15255</v>
+        <v>28710</v>
       </c>
       <c r="N33" t="n">
-        <v>14411</v>
+        <v>27008</v>
       </c>
       <c r="O33" t="n">
-        <v>195</v>
+        <v>4</v>
       </c>
       <c r="P33" t="n">
-        <v>195</v>
+        <v>4</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -4041,26 +4037,26 @@
         <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>81 CAMPANELLI DRIVE</t>
+          <t>2101 WAUKEGAN ROAD</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>UXBRIDGE</t>
+          <t>WAUKEGAN</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>01569</t>
+          <t>60085</t>
         </is>
       </c>
     </row>
@@ -4071,26 +4067,26 @@
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SO154921</t>
+          <t>SO155038</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>4519768010</t>
+          <t>4533299571</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4100,22 +4096,22 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>7871800002</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>20164395C</t>
+          <t>20164397C</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>O-T7871800002</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -4124,16 +4120,16 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>13622</v>
+        <v>28710</v>
       </c>
       <c r="N34" t="n">
-        <v>13025</v>
+        <v>27008</v>
       </c>
       <c r="O34" t="n">
-        <v>140</v>
+        <v>12</v>
       </c>
       <c r="P34" t="n">
-        <v>140</v>
+        <v>12</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -4151,26 +4147,26 @@
         <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>36.86</v>
+        <v>29.4</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>81 CAMPANELLI DRIVE</t>
+          <t>9000 109TH AVENUE NORTH</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>UXBRIDGE</t>
+          <t>CHAMPLIN</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>MN</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>01569</t>
+          <t>55316</t>
         </is>
       </c>
     </row>
@@ -4181,26 +4177,26 @@
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SO154921</t>
+          <t>SO155039</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>4519768010</t>
+          <t>4533299572</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4210,22 +4206,22 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>V7871800002</t>
+          <t>7871800002</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>20164397C</t>
+          <t>20164395C</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>O-T871800002</t>
+          <t>7871800002</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -4234,16 +4230,16 @@
         </is>
       </c>
       <c r="M35" t="n">
-        <v>30390</v>
+        <v>13099</v>
       </c>
       <c r="N35" t="n">
-        <v>28188</v>
+        <v>12533</v>
       </c>
       <c r="O35" t="n">
-        <v>31</v>
+        <v>153</v>
       </c>
       <c r="P35" t="n">
-        <v>31</v>
+        <v>153</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -4261,26 +4257,26 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>29.4</v>
+        <v>36.86</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>81 CAMPANELLI DRIVE</t>
+          <t>3356 WALDEN AVENUE</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>UXBRIDGE</t>
+          <t>DEPEW</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>01569</t>
+          <t>14043</t>
         </is>
       </c>
     </row>
@@ -4291,26 +4287,26 @@
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>SO154925</t>
+          <t>SO155040</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>4519768014</t>
+          <t>4533299573</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4330,7 +4326,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>O-T7871800000</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -4344,16 +4340,16 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>15255</v>
+        <v>14606</v>
       </c>
       <c r="N36" t="n">
-        <v>14411</v>
+        <v>13839</v>
       </c>
       <c r="O36" t="n">
-        <v>195</v>
+        <v>65</v>
       </c>
       <c r="P36" t="n">
-        <v>195</v>
+        <v>65</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -4375,22 +4371,22 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>239 BELVIDERE ROAD</t>
+          <t>3950 VALLEY E INDUSTRIAL</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>PERRYVILLE</t>
+          <t>BIRMINGHAM</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>21903</t>
+          <t>35217</t>
         </is>
       </c>
     </row>
@@ -4401,26 +4397,26 @@
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SO154925</t>
+          <t>SO155040</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>4519768014</t>
+          <t>4533299573</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4430,22 +4426,22 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>7871800002</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>20164395C</t>
+          <t>20164397C</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>O-T7871800002</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -4454,16 +4450,16 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>13622</v>
+        <v>28710</v>
       </c>
       <c r="N37" t="n">
-        <v>13025</v>
+        <v>27008</v>
       </c>
       <c r="O37" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="P37" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -4481,26 +4477,26 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>36.86</v>
+        <v>29.4</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>239 BELVIDERE ROAD</t>
+          <t>3950 VALLEY E INDUSTRIAL</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>PERRYVILLE</t>
+          <t>BIRMINGHAM</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>21903</t>
+          <t>35217</t>
         </is>
       </c>
     </row>
@@ -4511,26 +4507,26 @@
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SO154925</t>
+          <t>SO155042</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>4519768014</t>
+          <t>4533299574</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4540,22 +4536,22 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>V7871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>20164397C</t>
+          <t>20164396C</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>O-T871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4564,16 +4560,16 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>30390</v>
+        <v>14606</v>
       </c>
       <c r="N38" t="n">
-        <v>28188</v>
+        <v>13839</v>
       </c>
       <c r="O38" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="P38" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -4591,16 +4587,16 @@
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>239 BELVIDERE ROAD</t>
+          <t>7611 BRANDON WOODS BLVD</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>PERRYVILLE</t>
+          <t>BALTIMORE</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -4610,7 +4606,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>21903</t>
+          <t>21226</t>
         </is>
       </c>
     </row>
@@ -4621,26 +4617,26 @@
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SO154927</t>
+          <t>SO155042</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>4519768016</t>
+          <t>4533299574</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4650,22 +4646,22 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>7871800000</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>20164394C</t>
+          <t>20164397C</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>O-T71800000</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4674,16 +4670,16 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>4928</v>
+        <v>28710</v>
       </c>
       <c r="N39" t="n">
-        <v>4501</v>
+        <v>27008</v>
       </c>
       <c r="O39" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="P39" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -4701,26 +4697,26 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>57.33</v>
+        <v>29.4</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>494 State Route 416</t>
+          <t>7611 BRANDON WOODS BLVD</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Montgomery</t>
+          <t>BALTIMORE</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12549</t>
+          <t>21226</t>
         </is>
       </c>
     </row>
@@ -4731,26 +4727,26 @@
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SO154927</t>
+          <t>SO155043</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>4519768016</t>
+          <t>4533299576</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4760,22 +4756,22 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>V7871800000</t>
+          <t>7871800002</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>20164396C</t>
+          <t>20164395C</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>O-T7871800000</t>
+          <t>7871800002</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4784,16 +4780,16 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>15255</v>
+        <v>13099</v>
       </c>
       <c r="N40" t="n">
-        <v>14411</v>
+        <v>12533</v>
       </c>
       <c r="O40" t="n">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="P40" t="n">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -4811,26 +4807,26 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>47.46</v>
+        <v>36.86</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>494 State Route 416</t>
+          <t>11210 N. MCKINLEY DRIVE</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Montgomery</t>
+          <t>TAMPA</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12549</t>
+          <t>33612</t>
         </is>
       </c>
     </row>
@@ -4841,26 +4837,26 @@
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SO154927</t>
+          <t>SO155019</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>4519768016</t>
+          <t>4533299548</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -4870,22 +4866,22 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>7871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>20164395C</t>
+          <t>20164396C</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>O-T7871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4894,16 +4890,16 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>13622</v>
+        <v>14606</v>
       </c>
       <c r="N41" t="n">
-        <v>13025</v>
+        <v>13839</v>
       </c>
       <c r="O41" t="n">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="P41" t="n">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -4921,26 +4917,26 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>36.86</v>
+        <v>47.46</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>494 State Route 416</t>
+          <t>9756 Heartland Court</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Montgomery</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12549</t>
+          <t>43217</t>
         </is>
       </c>
     </row>
@@ -4951,26 +4947,26 @@
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SO154927</t>
+          <t>SO155047</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>4519768016</t>
+          <t>4533299580</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -4980,22 +4976,22 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>V7871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>20164397C</t>
+          <t>20164396C</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>O-T871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -5004,16 +5000,16 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>30390</v>
+        <v>14606</v>
       </c>
       <c r="N42" t="n">
-        <v>28188</v>
+        <v>13839</v>
       </c>
       <c r="O42" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="P42" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -5031,26 +5027,26 @@
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>494 State Route 416</t>
+          <t>Ontario, CA DC</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Montgomery</t>
+          <t>Ontario</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12549</t>
+          <t>91761</t>
         </is>
       </c>
     </row>
@@ -5061,26 +5057,26 @@
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>202040</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>CHS : CONCORDANCE HEALTHCARE SOLUTIONS, LLC 202040</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SO154930</t>
+          <t>SO155066</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>4519768019</t>
+          <t>3592133</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -5090,22 +5086,22 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>V7871800000</t>
+          <t>7871800002</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>20164396C</t>
+          <t>20164395C</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>O-T787180000H</t>
+          <t>354862</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -5114,16 +5110,16 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>15255</v>
+        <v>13099</v>
       </c>
       <c r="N43" t="n">
-        <v>14411</v>
+        <v>12533</v>
       </c>
       <c r="O43" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P43" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -5141,26 +5137,26 @@
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>47.46</v>
+        <v>36.86</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>264 SOUTH 5750 WEST</t>
+          <t>1473 MOUNTAIN ROAD</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>SALT LAKE CITY</t>
+          <t>ANDERSONVILLE</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>UT</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>84104</t>
+          <t>37705</t>
         </is>
       </c>
     </row>
@@ -5171,26 +5167,26 @@
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>202040</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>CHS : CONCORDANCE HEALTHCARE SOLUTIONS, LLC 202040</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SO154930</t>
+          <t>SO155067</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>4519768019</t>
+          <t>3592134</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -5200,22 +5196,22 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>V7871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>20164397C</t>
+          <t>20164396C</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>O-T871800002</t>
+          <t>354864</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -5224,16 +5220,16 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>30390</v>
+        <v>14606</v>
       </c>
       <c r="N44" t="n">
-        <v>28188</v>
+        <v>13839</v>
       </c>
       <c r="O44" t="n">
-        <v>140</v>
+        <v>26</v>
       </c>
       <c r="P44" t="n">
-        <v>140</v>
+        <v>26</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -5251,26 +5247,26 @@
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>264 SOUTH 5750 WEST</t>
+          <t>3625 PARK CIRCLE DRIVE</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>SALT LAKE CITY</t>
+          <t>KALAMAZOO</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>UT</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>84104</t>
+          <t>49048</t>
         </is>
       </c>
     </row>
@@ -5281,26 +5277,26 @@
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>202040</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>CHS : CONCORDANCE HEALTHCARE SOLUTIONS, LLC 202040</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>SO154932</t>
+          <t>SO155068</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>4519768021</t>
+          <t>3592135</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -5310,22 +5306,22 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>V7871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>20164397C</t>
+          <t>20164396C</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>O-T871800002</t>
+          <t>354864</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -5334,16 +5330,16 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>30390</v>
+        <v>14606</v>
       </c>
       <c r="N45" t="n">
-        <v>28188</v>
+        <v>13839</v>
       </c>
       <c r="O45" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="P45" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -5361,26 +5357,26 @@
         <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>29.4</v>
+        <v>47.46</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>251 HILTON DRIVE</t>
+          <t>276 ENTERPRISE WAY</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>JEFFERSONVILLE</t>
+          <t>MOCKSVILLE</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>47130</t>
+          <t>27028</t>
         </is>
       </c>
     </row>
@@ -5391,26 +5387,26 @@
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>202040</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>CHS : CONCORDANCE HEALTHCARE SOLUTIONS, LLC 202040</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>SO154907</t>
+          <t>SO155069</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>4519767996</t>
+          <t>3592136</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -5420,22 +5416,22 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>V7871800002</t>
+          <t>7871800000</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>20164397C</t>
+          <t>20164394C</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>O-T871800002</t>
+          <t>354861</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+          <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -5444,16 +5440,16 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>30390</v>
+        <v>4587</v>
       </c>
       <c r="N46" t="n">
-        <v>28188</v>
+        <v>4323</v>
       </c>
       <c r="O46" t="n">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="P46" t="n">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -5471,26 +5467,26 @@
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>29.4</v>
+        <v>57.33</v>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>92 SOUTHEAST 223rd AVENUE</t>
+          <t>60 DISTRIBUTION BOULEVARD</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>GRESHAM</t>
+          <t>EDISON</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>97030</t>
+          <t>08817</t>
         </is>
       </c>
     </row>
@@ -5501,26 +5497,26 @@
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>209198</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>PROGRESSIVE MEDICAL CONCEPTS, LLC 209198</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>SO154926</t>
+          <t>SO154968</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>4519768015</t>
+          <t>BV4131-5863</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -5530,22 +5526,18 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>V7871800002</t>
+          <t>7871800000</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>20164397C</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>O-T871800002</t>
-        </is>
-      </c>
+          <t>20164394C</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+          <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -5554,16 +5546,16 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>30390</v>
+        <v>4587</v>
       </c>
       <c r="N47" t="n">
-        <v>28188</v>
+        <v>4323</v>
       </c>
       <c r="O47" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="P47" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -5581,26 +5573,26 @@
         <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>29.4</v>
+        <v>57.33</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>8787 W BUCKEYE ROAD</t>
+          <t>4210 ALTRURIA RD</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>TOLLESON</t>
+          <t>BARTLETT</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>85353</t>
+          <t>38135</t>
         </is>
       </c>
     </row>
@@ -5611,26 +5603,26 @@
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>201067</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>SO154721</t>
+          <t>SO154855</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>04086</t>
+          <t>4533295895</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5650,7 +5642,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>487471800000</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -5664,16 +5656,16 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>15255</v>
+        <v>14606</v>
       </c>
       <c r="N48" t="n">
-        <v>14411</v>
+        <v>13839</v>
       </c>
       <c r="O48" t="n">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="P48" t="n">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -5695,22 +5687,22 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>2151 COUNTY ROAD H2W</t>
+          <t>Dixon, CA DC</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>MOUNDS VIEW</t>
+          <t>Dixon</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>55112</t>
+          <t>95620</t>
         </is>
       </c>
     </row>
@@ -5721,26 +5713,26 @@
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>201067</t>
+          <t>201001</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+          <t>CAH : CARDINAL - MD DS 201001</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>SO154721</t>
+          <t>SO154863</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>04086</t>
+          <t>4231373081</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5750,22 +5742,22 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>V7871800002</t>
+          <t>7871800002</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>20164397C</t>
+          <t>20164395C</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>487471800002</t>
+          <t>7871800002</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5774,16 +5766,16 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>30390</v>
+        <v>13099</v>
       </c>
       <c r="N49" t="n">
-        <v>28188</v>
+        <v>12533</v>
       </c>
       <c r="O49" t="n">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="P49" t="n">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -5801,26 +5793,26 @@
         <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>29.4</v>
+        <v>36.86</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>2151 COUNTY ROAD H2W</t>
+          <t>6441 MAIN ST</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>MOUNDS VIEW</t>
+          <t>HOUSTON</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>55112</t>
+          <t>770301502</t>
         </is>
       </c>
     </row>
@@ -5831,26 +5823,26 @@
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>201067</t>
+          <t>202040</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+          <t>CHS : CONCORDANCE HEALTHCARE SOLUTIONS, LLC 202040</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>SO154725</t>
+          <t>SO154870</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>05645</t>
+          <t>3591523</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5870,7 +5862,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>48741800000</t>
+          <t>354861</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5884,16 +5876,16 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>4928</v>
+        <v>4587</v>
       </c>
       <c r="N50" t="n">
-        <v>4501</v>
+        <v>4323</v>
       </c>
       <c r="O50" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="P50" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -5915,22 +5907,22 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>202 COMMERCE BLVD.</t>
+          <t>60 DISTRIBUTION BOULEVARD</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>KINGS MOUNTAIN</t>
+          <t>EDISON</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>28086</t>
+          <t>08817</t>
         </is>
       </c>
     </row>
@@ -5941,26 +5933,26 @@
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>201067</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>SO154727</t>
+          <t>SO154908</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>06858</t>
+          <t>4519767997</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5970,22 +5962,22 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>V7871800000</t>
+          <t>7871800002</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>20164396C</t>
+          <t>20164395C</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>487471800000</t>
+          <t>O-T7871800002</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5994,16 +5986,16 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>15255</v>
+        <v>13099</v>
       </c>
       <c r="N51" t="n">
-        <v>14411</v>
+        <v>12533</v>
       </c>
       <c r="O51" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P51" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -6021,26 +6013,26 @@
         <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>47.46</v>
+        <v>36.86</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>1805 NORTH LOOP 499 SUITE 130</t>
+          <t>735 COUNTY ROAD 4 EAST</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>HARLINGEN</t>
+          <t>PRATTVILLE</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>78550</t>
+          <t>36067</t>
         </is>
       </c>
     </row>
@@ -6051,26 +6043,26 @@
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>201067</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>SO154730</t>
+          <t>SO154908</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>10054</t>
+          <t>4519767997</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -6080,22 +6072,22 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>7871800002</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>20164395C</t>
+          <t>20164397C</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>48741800002</t>
+          <t>O-T871800002</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -6104,16 +6096,16 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>13622</v>
+        <v>28710</v>
       </c>
       <c r="N52" t="n">
-        <v>13025</v>
+        <v>27008</v>
       </c>
       <c r="O52" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="P52" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -6131,26 +6123,26 @@
         <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>36.8598</v>
+        <v>29.4</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>8489 WESTSIDE INDUSTRIAL DRIVE</t>
+          <t>735 COUNTY ROAD 4 EAST</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>JACKSONVILLE</t>
+          <t>PRATTVILLE</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>32219</t>
+          <t>36067</t>
         </is>
       </c>
     </row>
@@ -6161,26 +6153,26 @@
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>201067</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>SO154730</t>
+          <t>SO154911</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>10054</t>
+          <t>4519768000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -6190,22 +6182,22 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>V7871800000</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>20164396C</t>
+          <t>20164397C</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>487471800000</t>
+          <t>O-T871800002</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -6214,25 +6206,25 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>15255</v>
+        <v>28710</v>
       </c>
       <c r="N53" t="n">
-        <v>14411</v>
+        <v>27008</v>
       </c>
       <c r="O53" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="P53" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="T53" t="n">
         <v>0</v>
@@ -6241,26 +6233,26 @@
         <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>8489 WESTSIDE INDUSTRIAL DRIVE</t>
+          <t>500 SHARKEY DRIVE</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>JACKSONVILLE</t>
+          <t>MAUMELLE</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>32219</t>
+          <t>72113</t>
         </is>
       </c>
     </row>
@@ -6271,26 +6263,26 @@
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>201067</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>SO154730</t>
+          <t>SO154918</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>10054</t>
+          <t>4519768007</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -6310,7 +6302,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>487471800002</t>
+          <t>O-T871800002</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -6324,10 +6316,10 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>30390</v>
+        <v>28710</v>
       </c>
       <c r="N54" t="n">
-        <v>28188</v>
+        <v>27008</v>
       </c>
       <c r="O54" t="n">
         <v>140</v>
@@ -6355,22 +6347,22 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>8489 WESTSIDE INDUSTRIAL DRIVE</t>
+          <t>1960 W. MIRO WAY</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>JACKSONVILLE</t>
+          <t>RIALTO</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>32219</t>
+          <t>92376</t>
         </is>
       </c>
     </row>
@@ -6381,26 +6373,26 @@
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>201067</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>SO154733</t>
+          <t>SO154913</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>15591</t>
+          <t>4519768002</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -6410,22 +6402,22 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>V7871800002</t>
+          <t>7871800002</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>20164397C</t>
+          <t>20164395C</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>487471800002</t>
+          <t>O-T7871800002</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -6434,25 +6426,25 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>30390</v>
+        <v>13099</v>
       </c>
       <c r="N55" t="n">
-        <v>28188</v>
+        <v>12533</v>
       </c>
       <c r="O55" t="n">
-        <v>87</v>
+        <v>40</v>
       </c>
       <c r="P55" t="n">
-        <v>87</v>
+        <v>40</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>87</v>
+        <v>40</v>
       </c>
       <c r="S55" t="n">
-        <v>87</v>
+        <v>40</v>
       </c>
       <c r="T55" t="n">
         <v>0</v>
@@ -6461,26 +6453,26 @@
         <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>29.4</v>
+        <v>36.86</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>326 U.S. HIGHWAY 49 SOUTH</t>
+          <t>36445 VAN BORN ROAD</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>RICHLAND</t>
+          <t>ROMULUS</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>39218</t>
+          <t>48174</t>
         </is>
       </c>
     </row>
@@ -6491,26 +6483,26 @@
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>201067</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>SO154754</t>
+          <t>SO154925</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>38913</t>
+          <t>4519768014</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -6530,7 +6522,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>487471800000</t>
+          <t>O-T7871800000</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -6544,16 +6536,16 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>15255</v>
+        <v>14606</v>
       </c>
       <c r="N56" t="n">
-        <v>14411</v>
+        <v>13839</v>
       </c>
       <c r="O56" t="n">
-        <v>49</v>
+        <v>195</v>
       </c>
       <c r="P56" t="n">
-        <v>49</v>
+        <v>195</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -6575,22 +6567,22 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>36663 VAN BORN RD</t>
+          <t>239 BELVIDERE ROAD</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>ROMULUS</t>
+          <t>PERRYVILLE</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>48174</t>
+          <t>21903</t>
         </is>
       </c>
     </row>
@@ -6601,26 +6593,26 @@
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>201067</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>SO154754</t>
+          <t>SO154925</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>38913</t>
+          <t>4519768014</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -6630,22 +6622,22 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>V7871800002</t>
+          <t>7871800002</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>20164397C</t>
+          <t>20164395C</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>487471800002</t>
+          <t>O-T7871800002</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -6654,16 +6646,16 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>30390</v>
+        <v>13099</v>
       </c>
       <c r="N57" t="n">
-        <v>28188</v>
+        <v>12533</v>
       </c>
       <c r="O57" t="n">
-        <v>184</v>
+        <v>30</v>
       </c>
       <c r="P57" t="n">
-        <v>184</v>
+        <v>30</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -6681,26 +6673,26 @@
         <v>0</v>
       </c>
       <c r="V57" t="n">
-        <v>29.4</v>
+        <v>36.86</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>36663 VAN BORN RD</t>
+          <t>239 BELVIDERE ROAD</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>ROMULUS</t>
+          <t>PERRYVILLE</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>48174</t>
+          <t>21903</t>
         </is>
       </c>
     </row>
@@ -6711,26 +6703,26 @@
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>201067</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>SO154756</t>
+          <t>SO154925</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>40247</t>
+          <t>4519768014</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -6740,22 +6732,22 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>7871800000</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>20164394C</t>
+          <t>20164397C</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>48741800000</t>
+          <t>O-T871800002</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -6764,16 +6756,16 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>4928</v>
+        <v>28710</v>
       </c>
       <c r="N58" t="n">
-        <v>4501</v>
+        <v>27008</v>
       </c>
       <c r="O58" t="n">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="P58" t="n">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -6791,26 +6783,26 @@
         <v>0</v>
       </c>
       <c r="V58" t="n">
-        <v>57.33</v>
+        <v>29.4</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>550 LAKESIDE PARKWAY</t>
+          <t>239 BELVIDERE ROAD</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>FLOWER MOUND</t>
+          <t>PERRYVILLE</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>75028</t>
+          <t>21903</t>
         </is>
       </c>
     </row>
@@ -6821,26 +6813,26 @@
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>201067</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>SO154756</t>
+          <t>SO154932</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>40247</t>
+          <t>4519768021</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -6850,22 +6842,22 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>7871800002</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>20164395C</t>
+          <t>20164397C</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>48741800002</t>
+          <t>O-T871800002</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -6874,16 +6866,16 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>13622</v>
+        <v>28710</v>
       </c>
       <c r="N59" t="n">
-        <v>13025</v>
+        <v>27008</v>
       </c>
       <c r="O59" t="n">
-        <v>102</v>
+        <v>11</v>
       </c>
       <c r="P59" t="n">
-        <v>102</v>
+        <v>11</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -6901,26 +6893,26 @@
         <v>0</v>
       </c>
       <c r="V59" t="n">
-        <v>36.8598</v>
+        <v>29.4</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>550 LAKESIDE PARKWAY</t>
+          <t>251 HILTON DRIVE</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>FLOWER MOUND</t>
+          <t>JEFFERSONVILLE</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>75028</t>
+          <t>47130</t>
         </is>
       </c>
     </row>
@@ -6931,26 +6923,26 @@
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>46105</v>
+        <v>46097</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>201067</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>SO154764</t>
+          <t>SO154143</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61288</t>
+          <t>4533277020</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -6960,22 +6952,22 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>7871800000</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>20164394C</t>
+          <t>20164397C</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>48741800000</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6984,16 +6976,16 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>4928</v>
+        <v>28710</v>
       </c>
       <c r="N60" t="n">
-        <v>4501</v>
+        <v>27008</v>
       </c>
       <c r="O60" t="n">
-        <v>179</v>
+        <v>44</v>
       </c>
       <c r="P60" t="n">
-        <v>179</v>
+        <v>44</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -7011,26 +7003,26 @@
         <v>0</v>
       </c>
       <c r="V60" t="n">
-        <v>57.33</v>
+        <v>29.4</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>8313 WEST PIERCE STREET, SUITE 100</t>
+          <t>1901 RAYMER AVENUE</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>TOLLESON</t>
+          <t>Fullerton</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>85353</t>
+          <t>92833</t>
         </is>
       </c>
     </row>
@@ -7041,26 +7033,26 @@
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>46105</v>
+        <v>46093</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>201067</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>OMI : OWENS &amp; MINOR - MD 201067</t>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>SO154764</t>
+          <t>SO154038</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61288</t>
+          <t>4519714426</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -7070,22 +7062,22 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>V7871800000</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>20164396C</t>
+          <t>20164397C</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>487471800000</t>
+          <t>O-T871800002</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -7094,25 +7086,25 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>15255</v>
+        <v>28710</v>
       </c>
       <c r="N61" t="n">
-        <v>14411</v>
+        <v>27008</v>
       </c>
       <c r="O61" t="n">
-        <v>33</v>
+        <v>140</v>
       </c>
       <c r="P61" t="n">
-        <v>33</v>
+        <v>140</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="S61" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="T61" t="n">
         <v>0</v>
@@ -7121,244 +7113,24 @@
         <v>0</v>
       </c>
       <c r="V61" t="n">
-        <v>47.46</v>
+        <v>29.4</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>8313 WEST PIERCE STREET, SUITE 100</t>
+          <t>3770 HOGUM BAY RD. NE</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>TOLLESON</t>
+          <t>LACEY</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>WA</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
-        <is>
-          <t>85353</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="B62" s="1" t="n">
-        <v>46097</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>201003</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>CAH : CARDINAL - MD 201003</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>SO154143</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>4533277020</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>SENSI MEDICAL</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>V7871800002</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>20164397C</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>V7871800002</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="M62" t="n">
-        <v>30390</v>
-      </c>
-      <c r="N62" t="n">
-        <v>28188</v>
-      </c>
-      <c r="O62" t="n">
-        <v>44</v>
-      </c>
-      <c r="P62" t="n">
-        <v>44</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" t="n">
-        <v>0</v>
-      </c>
-      <c r="T62" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>1901 RAYMER AVENUE</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>Fullerton</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>92833</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="B63" s="1" t="n">
-        <v>46093</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>202033</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>SO154038</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>4519714426</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>SENSI MEDICAL</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>V7871800002</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>20164397C</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>O-T871800002</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="M63" t="n">
-        <v>30390</v>
-      </c>
-      <c r="N63" t="n">
-        <v>28188</v>
-      </c>
-      <c r="O63" t="n">
-        <v>140</v>
-      </c>
-      <c r="P63" t="n">
-        <v>140</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
-      <c r="R63" t="n">
-        <v>140</v>
-      </c>
-      <c r="S63" t="n">
-        <v>140</v>
-      </c>
-      <c r="T63" t="n">
-        <v>0</v>
-      </c>
-      <c r="U63" t="n">
-        <v>0</v>
-      </c>
-      <c r="V63" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>3770 HOGUM BAY RD. NE</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>LACEY</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>WA</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
         <is>
           <t>98516</t>
         </is>

--- a/data/searchresults.xlsx
+++ b/data/searchresults.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:Z10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -559,26 +559,26 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>201052</t>
+          <t>208368-SENSI</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MCK : MCKESSON MEDICAL SURGICAL MD PC 201052</t>
+          <t>TWIN MED LLC 208368-SENSI</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SO155112</t>
+          <t>SO155252</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>37022811</t>
+          <t>TW747254-- Sensi</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -596,11 +596,7 @@
           <t>20164395C</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>1239964</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
@@ -615,12 +611,14 @@
         <v>12483</v>
       </c>
       <c r="N2" t="n">
-        <v>12483</v>
+        <v>12132</v>
       </c>
       <c r="O2" t="n">
-        <v>116</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
+        <v>70</v>
+      </c>
+      <c r="P2" t="n">
+        <v>70</v>
+      </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
@@ -634,29 +632,29 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
         <v>36.86</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>3769 COMMERCE CENTER BLVD</t>
+          <t>1263 HEIL QUAKER BLVD</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>BETHLEHEM</t>
+          <t>La Vergne</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18015</t>
+          <t>37086</t>
         </is>
       </c>
     </row>
@@ -667,26 +665,26 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>201052</t>
+          <t>208368-SENSI</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MCK : MCKESSON MEDICAL SURGICAL MD PC 201052</t>
+          <t>TWIN MED LLC 208368-SENSI</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SO155117</t>
+          <t>SO155254</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>37022816</t>
+          <t>TW747256- Sensi</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -696,22 +694,18 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>V7871800000</t>
+          <t>7871800002</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20164396C</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>1258911</t>
-        </is>
-      </c>
+          <t>20164395C</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -720,15 +714,17 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>13839</v>
+        <v>12483</v>
       </c>
       <c r="N3" t="n">
-        <v>13839</v>
+        <v>12132</v>
       </c>
       <c r="O3" t="n">
-        <v>6</v>
-      </c>
-      <c r="P3" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="P3" t="n">
+        <v>100</v>
+      </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
@@ -742,29 +738,29 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>47.46</v>
+        <v>36.86</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>SEATTLE  #255</t>
+          <t>1198 FEATHER WAY</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>KENT</t>
+          <t>Bethlehem</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>WA</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>98032</t>
+          <t>18015</t>
         </is>
       </c>
     </row>
@@ -775,26 +771,26 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>201052</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MCK : MCKESSON MEDICAL SURGICAL MD PC 201052</t>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SO155117</t>
+          <t>SO155287</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>37022816</t>
+          <t>4519788430</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -804,22 +800,22 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>V7871800002</t>
+          <t>7871800002</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20164397C</t>
+          <t>20164395C</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1258913</t>
+          <t>O-T7871800002</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -828,13 +824,13 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>27008</v>
+        <v>12483</v>
       </c>
       <c r="N4" t="n">
-        <v>27008</v>
+        <v>12132</v>
       </c>
       <c r="O4" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
@@ -850,29 +846,29 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="V4" t="n">
-        <v>29.4</v>
+        <v>36.86</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>SEATTLE  #255</t>
+          <t>1401 N. UNIVERSAL AVE.</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>KENT</t>
+          <t>KANSAS CITY</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>WA</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>98032</t>
+          <t>64120</t>
         </is>
       </c>
     </row>
@@ -883,26 +879,26 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>209249</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Medi-Rents &amp; Sales, Inc. 209249</t>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SO155186</t>
+          <t>SO155288</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>14027</t>
+          <t>4519788436</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -920,7 +916,11 @@
           <t>20164395C</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>O-T7871800002</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
@@ -935,10 +935,10 @@
         <v>12483</v>
       </c>
       <c r="N5" t="n">
-        <v>12483</v>
+        <v>12132</v>
       </c>
       <c r="O5" t="n">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
@@ -954,59 +954,59 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c r="V5" t="n">
         <v>36.86</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>9103 YELLOW BRICK RD</t>
+          <t>13115 BROCKTON LANE N</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Rosedale</t>
+          <t>ROGERS</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>MN</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>21237</t>
+          <t>55374</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ASV</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>108368</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>TWIN MED LLC 108368</t>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SO155190</t>
+          <t>SO155291</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>TW747254</t>
+          <t>4519788483</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1016,22 +1016,22 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>7871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20164395C</t>
+          <t>20164396C</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1004571</t>
+          <t>O-T7871800000</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1040,13 +1040,13 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>12483</v>
+        <v>13839</v>
       </c>
       <c r="N6" t="n">
-        <v>12483</v>
+        <v>13833</v>
       </c>
       <c r="O6" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="n">
@@ -1062,36 +1062,36 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="V6" t="n">
-        <v>36.86</v>
+        <v>47.46</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1263 HEIL QUAKER BLVD</t>
+          <t>3446 Highway 51 N, Suite 100</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>LA VERGNE</t>
+          <t>Southaven</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>37086-3516</t>
+          <t>38672</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ASV</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
@@ -1099,22 +1099,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>108368</t>
+          <t>201052</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>TWIN MED LLC 108368</t>
+          <t>MCK : MCKESSON MEDICAL SURGICAL MD PC 201052</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SO155192</t>
+          <t>SO155112</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>TW747256</t>
+          <t>37022811</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1004571</t>
+          <t>1239964</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1151,12 +1151,14 @@
         <v>12483</v>
       </c>
       <c r="N7" t="n">
-        <v>12483</v>
+        <v>12132</v>
       </c>
       <c r="O7" t="n">
-        <v>100</v>
-      </c>
-      <c r="P7" t="inlineStr"/>
+        <v>116</v>
+      </c>
+      <c r="P7" t="n">
+        <v>116</v>
+      </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
@@ -1170,14 +1172,14 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>36.86</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1198 FEATHER WAY</t>
+          <t>3769 COMMERCE CENTER BLVD</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1199,30 +1201,30 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ASV</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>107001</t>
+          <t>201052</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>BOUND TREE MEDICAL, LLC 107001</t>
+          <t>MCK : MCKESSON MEDICAL SURGICAL MD PC 201052</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SO155003</t>
+          <t>SO155117</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>B1310315831-10</t>
+          <t>37022816</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1232,18 +1234,22 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>7871800000</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20164394C</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>20164396C</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>1258911</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1252,16 +1258,16 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>4388</v>
+        <v>13839</v>
       </c>
       <c r="N8" t="n">
-        <v>4323</v>
+        <v>13833</v>
       </c>
       <c r="O8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1279,26 +1285,26 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>57.33</v>
+        <v>47.46</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>1033 COLLINS RD STE A</t>
+          <t>SEATTLE  #255</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Greenwood</t>
+          <t>KENT</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>WA</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>46143</t>
+          <t>98032</t>
         </is>
       </c>
     </row>
@@ -1309,26 +1315,26 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>209198</t>
+          <t>201052</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PROGRESSIVE MEDICAL CONCEPTS, LLC 209198</t>
+          <t>MCK : MCKESSON MEDICAL SURGICAL MD PC 201052</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SO154968</t>
+          <t>SO155117</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>BV4131-5863</t>
+          <t>37022816</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1338,18 +1344,22 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7871800000</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20164394C</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>20164397C</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>1258913</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1358,16 +1368,16 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>4388</v>
+        <v>27008</v>
       </c>
       <c r="N9" t="n">
-        <v>4323</v>
+        <v>26954</v>
       </c>
       <c r="O9" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="P9" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1385,26 +1395,132 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>57.33</v>
+        <v>29.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>4210 ALTRURIA RD</t>
+          <t>SEATTLE  #255</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>BARTLETT</t>
+          <t>KENT</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>WA</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>38135</t>
+          <t>98032</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>209249</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Medi-Rents &amp; Sales, Inc. 209249</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>SO155186</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>14027</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>7871800002</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20164395C</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>12483</v>
+      </c>
+      <c r="N10" t="n">
+        <v>12132</v>
+      </c>
+      <c r="O10" t="n">
+        <v>65</v>
+      </c>
+      <c r="P10" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>36.86</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>9103 YELLOW BRICK RD</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Rosedale</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>21237</t>
         </is>
       </c>
     </row>

--- a/data/searchresults.xlsx
+++ b/data/searchresults.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:Z58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -559,26 +559,26 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>208368-SENSI</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>TWIN MED LLC 208368-SENSI</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SO155252</t>
+          <t>SO155326</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>TW747254-- Sensi</t>
+          <t>4533306421</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -588,18 +588,22 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>7871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20164395C</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>20164396C</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>V7871800000</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -608,17 +612,15 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>12483</v>
+        <v>13839</v>
       </c>
       <c r="N2" t="n">
-        <v>12132</v>
+        <v>13833</v>
       </c>
       <c r="O2" t="n">
-        <v>70</v>
-      </c>
-      <c r="P2" t="n">
-        <v>70</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
@@ -632,29 +634,29 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V2" t="n">
-        <v>36.86</v>
+        <v>47.46</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>1263 HEIL QUAKER BLVD</t>
+          <t>Dixon, CA DC</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>La Vergne</t>
+          <t>Dixon</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>37086</t>
+          <t>95620</t>
         </is>
       </c>
     </row>
@@ -665,26 +667,26 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>208368-SENSI</t>
+          <t>201003</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>TWIN MED LLC 208368-SENSI</t>
+          <t>CAH : CARDINAL - MD 201003</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SO155254</t>
+          <t>SO155326</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>TW747256- Sensi</t>
+          <t>4533306421</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -694,18 +696,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>7871800002</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20164395C</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>20164397C</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>V7871800002</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -714,17 +720,15 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>12483</v>
+        <v>27008</v>
       </c>
       <c r="N3" t="n">
-        <v>12132</v>
+        <v>26954</v>
       </c>
       <c r="O3" t="n">
-        <v>100</v>
-      </c>
-      <c r="P3" t="n">
-        <v>100</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
@@ -738,59 +742,59 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="V3" t="n">
-        <v>36.86</v>
+        <v>29.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1198 FEATHER WAY</t>
+          <t>Dixon, CA DC</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Bethlehem</t>
+          <t>Dixon</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18015</t>
+          <t>95620</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>ASV</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>107001</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>BOUND TREE MEDICAL, LLC 107001</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SO155287</t>
+          <t>SO155336</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>4519788430</t>
+          <t>B0810340813-10</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -800,22 +804,18 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>7871800002</t>
+          <t>7871800000</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20164395C</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>O-T7871800002</t>
-        </is>
-      </c>
+          <t>20164394C</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+          <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -824,15 +824,17 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>12483</v>
+        <v>4323</v>
       </c>
       <c r="N4" t="n">
-        <v>12132</v>
+        <v>4322</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
-      <c r="P4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
@@ -846,29 +848,29 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>36.86</v>
+        <v>57.33</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>1401 N. UNIVERSAL AVE.</t>
+          <t>2619 Ignition Dr Ste 2</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>KANSAS CITY</t>
+          <t>Jacksonville</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>64120</t>
+          <t>32218</t>
         </is>
       </c>
     </row>
@@ -879,26 +881,26 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>209176</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+          <t>DISTRIBUTION COOPERATIVE, INC. 209176</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SO155288</t>
+          <t>SO155350</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>4519788436</t>
+          <t>58544</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -908,22 +910,18 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>7871800002</t>
+          <t>V7871800002</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20164395C</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>O-T7871800002</t>
-        </is>
-      </c>
+          <t>20164397C</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -932,13 +930,13 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>12483</v>
+        <v>27008</v>
       </c>
       <c r="N5" t="n">
-        <v>12132</v>
+        <v>26954</v>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
@@ -954,29 +952,29 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="V5" t="n">
-        <v>36.86</v>
+        <v>29.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>13115 BROCKTON LANE N</t>
+          <t>1281 HWY 155 S</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>ROGERS</t>
+          <t>MCDONOUGH</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>55374</t>
+          <t>30253</t>
         </is>
       </c>
     </row>
@@ -987,7 +985,7 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1001,12 +999,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SO155291</t>
+          <t>SO155362</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>4519788483</t>
+          <t>4519794763</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1016,22 +1014,22 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>V7871800000</t>
+          <t>7871800000</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20164396C</t>
+          <t>20164394C</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O-T7871800000</t>
+          <t>O-T71800000</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+          <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1040,13 +1038,13 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>13839</v>
+        <v>4323</v>
       </c>
       <c r="N6" t="n">
-        <v>13833</v>
+        <v>4322</v>
       </c>
       <c r="O6" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="n">
@@ -1062,29 +1060,29 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="V6" t="n">
-        <v>47.46</v>
+        <v>57.33</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3446 Highway 51 N, Suite 100</t>
+          <t>1 MEDLINE DRIVE, SUITE 100</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Southaven</t>
+          <t>WILMER</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>38672</t>
+          <t>75172</t>
         </is>
       </c>
     </row>
@@ -1095,26 +1093,26 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>201052</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MCK : MCKESSON MEDICAL SURGICAL MD PC 201052</t>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SO155112</t>
+          <t>SO155362</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>37022811</t>
+          <t>4519794763</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1124,22 +1122,22 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7871800002</t>
+          <t>V7871800000</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20164395C</t>
+          <t>20164396C</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1239964</t>
+          <t>O-T7871800000</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1148,17 +1146,15 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>12483</v>
+        <v>13839</v>
       </c>
       <c r="N7" t="n">
-        <v>12132</v>
+        <v>13833</v>
       </c>
       <c r="O7" t="n">
-        <v>116</v>
-      </c>
-      <c r="P7" t="n">
-        <v>116</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
@@ -1172,29 +1168,29 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="V7" t="n">
-        <v>36.86</v>
+        <v>47.46</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3769 COMMERCE CENTER BLVD</t>
+          <t>1 MEDLINE DRIVE, SUITE 100</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>BETHLEHEM</t>
+          <t>WILMER</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18015</t>
+          <t>75172</t>
         </is>
       </c>
     </row>
@@ -1205,26 +1201,26 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>201052</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MCK : MCKESSON MEDICAL SURGICAL MD PC 201052</t>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SO155117</t>
+          <t>SO155362</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>37022816</t>
+          <t>4519794763</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1234,22 +1230,22 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>V7871800000</t>
+          <t>7871800002</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20164396C</t>
+          <t>20164395C</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1258911</t>
+          <t>O-T7871800002</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1258,17 +1254,15 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>13839</v>
+        <v>12132</v>
       </c>
       <c r="N8" t="n">
-        <v>13833</v>
+        <v>12132</v>
       </c>
       <c r="O8" t="n">
-        <v>6</v>
-      </c>
-      <c r="P8" t="n">
-        <v>6</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
@@ -1282,29 +1276,29 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="V8" t="n">
-        <v>47.46</v>
+        <v>36.86</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>SEATTLE  #255</t>
+          <t>1 MEDLINE DRIVE, SUITE 100</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>KENT</t>
+          <t>WILMER</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>WA</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>98032</t>
+          <t>75172</t>
         </is>
       </c>
     </row>
@@ -1315,26 +1309,26 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>201052</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MCK : MCKESSON MEDICAL SURGICAL MD PC 201052</t>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SO155117</t>
+          <t>SO155362</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>37022816</t>
+          <t>4519794763</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1354,7 +1348,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1258913</t>
+          <t>O-T871800002</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1374,11 +1368,9 @@
         <v>26954</v>
       </c>
       <c r="O9" t="n">
-        <v>54</v>
-      </c>
-      <c r="P9" t="n">
-        <v>54</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
@@ -1392,29 +1384,29 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="V9" t="n">
         <v>29.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>SEATTLE  #255</t>
+          <t>1 MEDLINE DRIVE, SUITE 100</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>KENT</t>
+          <t>WILMER</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>WA</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>98032</t>
+          <t>75172</t>
         </is>
       </c>
     </row>
@@ -1425,102 +1417,5292 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>SO155369</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>4519794770</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>V7871800002</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20164397C</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>O-T871800002</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>27008</v>
+      </c>
+      <c r="N10" t="n">
+        <v>26954</v>
+      </c>
+      <c r="O10" t="n">
+        <v>70</v>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>70</v>
+      </c>
+      <c r="V10" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>13115 BROCKTON LANE N</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>ROGERS</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>MN</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>55374</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SO155372</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>4519794773</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>V7871800000</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20164396C</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O-T7871800000</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>13839</v>
+      </c>
+      <c r="N11" t="n">
+        <v>13833</v>
+      </c>
+      <c r="O11" t="n">
+        <v>27</v>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>27</v>
+      </c>
+      <c r="V11" t="n">
+        <v>47.46</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>1989 TRANSIT WAY</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>BROCKPORT</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14420</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SO155372</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>4519794773</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>V7871800002</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20164397C</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O-T871800002</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>27008</v>
+      </c>
+      <c r="N12" t="n">
+        <v>26954</v>
+      </c>
+      <c r="O12" t="n">
+        <v>64</v>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>64</v>
+      </c>
+      <c r="V12" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>1989 TRANSIT WAY</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>BROCKPORT</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14420</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>SO155374</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>4519794775</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>V7871800000</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20164396C</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O-T7871800000</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>13839</v>
+      </c>
+      <c r="N13" t="n">
+        <v>13833</v>
+      </c>
+      <c r="O13" t="n">
+        <v>12</v>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>12</v>
+      </c>
+      <c r="V13" t="n">
+        <v>47.46</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>60 ATHLETES WAY</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>MOUNT JULIET</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>37122</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>SO155374</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>4519794775</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>V7871800002</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20164397C</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O-T871800002</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>27008</v>
+      </c>
+      <c r="N14" t="n">
+        <v>26954</v>
+      </c>
+      <c r="O14" t="n">
+        <v>210</v>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>210</v>
+      </c>
+      <c r="V14" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>60 ATHLETES WAY</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>MOUNT JULIET</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>37122</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>SO155375</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>4519794776</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>V7871800000</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20164396C</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O-T7871800000</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>13839</v>
+      </c>
+      <c r="N15" t="n">
+        <v>13833</v>
+      </c>
+      <c r="O15" t="n">
+        <v>46</v>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>46</v>
+      </c>
+      <c r="V15" t="n">
+        <v>47.46</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>2200 Cornerstone Parkway, Suite 100</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Grayslake</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>60030</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>SO155375</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>4519794776</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>7871800002</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20164395C</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>O-T7871800002</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>12132</v>
+      </c>
+      <c r="N16" t="n">
+        <v>12132</v>
+      </c>
+      <c r="O16" t="n">
+        <v>77</v>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>77</v>
+      </c>
+      <c r="V16" t="n">
+        <v>36.86</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>2200 Cornerstone Parkway, Suite 100</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Grayslake</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>60030</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>SO155375</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>4519794776</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>V7871800002</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20164397C</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O-T871800002</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>27008</v>
+      </c>
+      <c r="N17" t="n">
+        <v>26954</v>
+      </c>
+      <c r="O17" t="n">
+        <v>140</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>140</v>
+      </c>
+      <c r="V17" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>2200 Cornerstone Parkway, Suite 100</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Grayslake</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>60030</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>SO155376</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>4519794777</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>V7871800000</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20164396C</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>O-T7871800000</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>13839</v>
+      </c>
+      <c r="N18" t="n">
+        <v>13833</v>
+      </c>
+      <c r="O18" t="n">
+        <v>27</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>27</v>
+      </c>
+      <c r="V18" t="n">
+        <v>47.46</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>1500 MEDLINE PLACE</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>MC DONOUGH</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>30253</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>SO155363</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>4519794764</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>V7871800000</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20164396C</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>O-T7871800000</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>13839</v>
+      </c>
+      <c r="N19" t="n">
+        <v>13833</v>
+      </c>
+      <c r="O19" t="n">
+        <v>65</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>65</v>
+      </c>
+      <c r="V19" t="n">
+        <v>47.46</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>21111 E. 36TH DRIVE</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>AURORA</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>80011</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>SO155366</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>4519794767</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>V7871800000</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20164396C</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>O-T7871800000</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>13839</v>
+      </c>
+      <c r="N20" t="n">
+        <v>13833</v>
+      </c>
+      <c r="O20" t="n">
+        <v>37</v>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>37</v>
+      </c>
+      <c r="V20" t="n">
+        <v>47.46</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>1401 N. UNIVERSAL AVE.</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>KANSAS CITY</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>64120</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>SO155366</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>4519794767</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>V7871800002</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>20164397C</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>O-T871800002</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>27008</v>
+      </c>
+      <c r="N21" t="n">
+        <v>26954</v>
+      </c>
+      <c r="O21" t="n">
+        <v>24</v>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>24</v>
+      </c>
+      <c r="V21" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>1401 N. UNIVERSAL AVE.</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>KANSAS CITY</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>64120</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>SO155367</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>4519794768</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>V7871800002</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>20164397C</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>O-T871800002</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>27008</v>
+      </c>
+      <c r="N22" t="n">
+        <v>26954</v>
+      </c>
+      <c r="O22" t="n">
+        <v>10</v>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>10</v>
+      </c>
+      <c r="V22" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>92 SOUTHEAST 223rd AVENUE</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>GRESHAM</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>97030</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>SO155368</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>4519794769</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>7871800002</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20164395C</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>O-T7871800002</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>12132</v>
+      </c>
+      <c r="N23" t="n">
+        <v>12132</v>
+      </c>
+      <c r="O23" t="n">
+        <v>12</v>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>12</v>
+      </c>
+      <c r="V23" t="n">
+        <v>36.86</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>735 COUNTY ROAD 4 EAST</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>PRATTVILLE</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>36067</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>SO155368</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>4519794769</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>V7871800002</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20164397C</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>O-T871800002</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>27008</v>
+      </c>
+      <c r="N24" t="n">
+        <v>26954</v>
+      </c>
+      <c r="O24" t="n">
+        <v>140</v>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>140</v>
+      </c>
+      <c r="V24" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>735 COUNTY ROAD 4 EAST</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>PRATTVILLE</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>36067</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>SO155370</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>4519794771</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>V7871800000</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20164396C</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>O-T7871800000</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>13839</v>
+      </c>
+      <c r="N25" t="n">
+        <v>13833</v>
+      </c>
+      <c r="O25" t="n">
+        <v>101</v>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>101</v>
+      </c>
+      <c r="V25" t="n">
+        <v>47.46</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>1900 MEADOWVILLE TECHNOLOGY</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>CHESTER</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>23834</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>SO155370</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>4519794771</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>V7871800002</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20164397C</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>O-T871800002</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>27008</v>
+      </c>
+      <c r="N26" t="n">
+        <v>26954</v>
+      </c>
+      <c r="O26" t="n">
+        <v>70</v>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>70</v>
+      </c>
+      <c r="V26" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>1900 MEADOWVILLE TECHNOLOGY</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>CHESTER</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>23834</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>SO155371</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>4519794772</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>V7871800000</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20164396C</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>O-T7871800000</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>13839</v>
+      </c>
+      <c r="N27" t="n">
+        <v>13833</v>
+      </c>
+      <c r="O27" t="n">
+        <v>7</v>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>7</v>
+      </c>
+      <c r="V27" t="n">
+        <v>47.46</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>500 SHARKEY DRIVE</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>MAUMELLE</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>72113</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>SO155371</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>4519794772</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>V7871800002</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>20164397C</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>O-T871800002</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>27008</v>
+      </c>
+      <c r="N28" t="n">
+        <v>26954</v>
+      </c>
+      <c r="O28" t="n">
+        <v>70</v>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>70</v>
+      </c>
+      <c r="V28" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>500 SHARKEY DRIVE</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>MAUMELLE</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>72113</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>SO155373</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>4519794774</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>7871800000</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20164394C</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>O-T71800000</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>4323</v>
+      </c>
+      <c r="N29" t="n">
+        <v>4322</v>
+      </c>
+      <c r="O29" t="n">
+        <v>5</v>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>5</v>
+      </c>
+      <c r="V29" t="n">
+        <v>57.33</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>36445 VAN BORN ROAD</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>ROMULUS</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>48174</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>SO155373</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>4519794774</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>7871800002</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>20164395C</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>O-T7871800002</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>12132</v>
+      </c>
+      <c r="N30" t="n">
+        <v>12132</v>
+      </c>
+      <c r="O30" t="n">
+        <v>56</v>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>56</v>
+      </c>
+      <c r="V30" t="n">
+        <v>36.86</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>36445 VAN BORN ROAD</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>ROMULUS</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>48174</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>SO155377</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>4519794778</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>V7871800002</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>20164397C</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>O-T871800002</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>27008</v>
+      </c>
+      <c r="N31" t="n">
+        <v>26954</v>
+      </c>
+      <c r="O31" t="n">
+        <v>13</v>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>13</v>
+      </c>
+      <c r="V31" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>1062 OLD DIXIE HIGHWAY</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>AUBURNDALE</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>33823</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>SO155378</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>4519794779</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>V7871800002</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>20164397C</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>O-T871800002</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>27008</v>
+      </c>
+      <c r="N32" t="n">
+        <v>26954</v>
+      </c>
+      <c r="O32" t="n">
+        <v>210</v>
+      </c>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>210</v>
+      </c>
+      <c r="V32" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>1960 W. MIRO WAY</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>RIALTO</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>92376</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>SO155379</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>4519794780</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>7871800000</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>20164394C</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>O-T71800000</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>7871800000: STERILE WATER FOR INHALATION USP 1000ML BAG 14/CASE</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>4323</v>
+      </c>
+      <c r="N33" t="n">
+        <v>4322</v>
+      </c>
+      <c r="O33" t="n">
+        <v>11</v>
+      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>11</v>
+      </c>
+      <c r="V33" t="n">
+        <v>57.33</v>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>29895 US HWY 90 BUS</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>KATY</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>77494</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>SO155379</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>4519794780</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>V7871800000</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>20164396C</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>O-T7871800000</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>13839</v>
+      </c>
+      <c r="N34" t="n">
+        <v>13833</v>
+      </c>
+      <c r="O34" t="n">
+        <v>130</v>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>130</v>
+      </c>
+      <c r="V34" t="n">
+        <v>47.46</v>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>29895 US HWY 90 BUS</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>KATY</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>77494</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>SO155380</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>4519794781</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>V7871800000</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>20164396C</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>O-T7871800000</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>13839</v>
+      </c>
+      <c r="N35" t="n">
+        <v>13833</v>
+      </c>
+      <c r="O35" t="n">
+        <v>19</v>
+      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>19</v>
+      </c>
+      <c r="V35" t="n">
+        <v>47.46</v>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>5000 Premier Parkway, Suite 100</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Saint Peters</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>63376</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>SO155380</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>4519794781</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>V7871800002</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>20164397C</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O-T871800002</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>27008</v>
+      </c>
+      <c r="N36" t="n">
+        <v>26954</v>
+      </c>
+      <c r="O36" t="n">
+        <v>70</v>
+      </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>70</v>
+      </c>
+      <c r="V36" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>5000 Premier Parkway, Suite 100</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Saint Peters</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>63376</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>SO155381</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>4519794782</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>V7871800002</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>20164397C</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>O-T871800002</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>27008</v>
+      </c>
+      <c r="N37" t="n">
+        <v>26954</v>
+      </c>
+      <c r="O37" t="n">
+        <v>27</v>
+      </c>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>27</v>
+      </c>
+      <c r="V37" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>81 CAMPANELLI DRIVE</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>UXBRIDGE</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>01569</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B38" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>SO155382</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>4519794783</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>V7871800000</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>20164396C</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O-T7871800000</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>13839</v>
+      </c>
+      <c r="N38" t="n">
+        <v>13833</v>
+      </c>
+      <c r="O38" t="n">
+        <v>26</v>
+      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>26</v>
+      </c>
+      <c r="V38" t="n">
+        <v>47.46</v>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>1040 ENTERPRISE PARKWAY</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>WEST JEFFERSON</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>43162</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B39" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>SO155382</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>4519794783</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>7871800002</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>20164395C</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>O-T7871800002</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>12132</v>
+      </c>
+      <c r="N39" t="n">
+        <v>12132</v>
+      </c>
+      <c r="O39" t="n">
+        <v>70</v>
+      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>70</v>
+      </c>
+      <c r="V39" t="n">
+        <v>36.86</v>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>1040 ENTERPRISE PARKWAY</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>WEST JEFFERSON</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>43162</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B40" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>SO155382</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>4519794783</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>V7871800002</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>20164397C</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>O-T871800002</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>27008</v>
+      </c>
+      <c r="N40" t="n">
+        <v>26954</v>
+      </c>
+      <c r="O40" t="n">
+        <v>27</v>
+      </c>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>27</v>
+      </c>
+      <c r="V40" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>1040 ENTERPRISE PARKWAY</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>WEST JEFFERSON</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>43162</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B41" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>SO155384</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>4519794785</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>V7871800002</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>20164397C</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>O-T871800002</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>27008</v>
+      </c>
+      <c r="N41" t="n">
+        <v>26954</v>
+      </c>
+      <c r="O41" t="n">
+        <v>70</v>
+      </c>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>70</v>
+      </c>
+      <c r="V41" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>5701 PROMONTORY PARKWAY</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>TRACY</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>95377</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>SO155385</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>4519794786</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>V7871800000</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>20164396C</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>O-T7871800000</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>13839</v>
+      </c>
+      <c r="N42" t="n">
+        <v>13833</v>
+      </c>
+      <c r="O42" t="n">
+        <v>130</v>
+      </c>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>130</v>
+      </c>
+      <c r="V42" t="n">
+        <v>47.46</v>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>239 BELVIDERE ROAD</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>PERRYVILLE</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>21903</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>SO155385</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>4519794786</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>7871800002</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>20164395C</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>O-T7871800002</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>12132</v>
+      </c>
+      <c r="N43" t="n">
+        <v>12132</v>
+      </c>
+      <c r="O43" t="n">
+        <v>28</v>
+      </c>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>28</v>
+      </c>
+      <c r="V43" t="n">
+        <v>36.86</v>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>239 BELVIDERE ROAD</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>PERRYVILLE</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>21903</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B44" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>SO155385</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>4519794786</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>V7871800002</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>20164397C</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>O-T871800002</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>27008</v>
+      </c>
+      <c r="N44" t="n">
+        <v>26954</v>
+      </c>
+      <c r="O44" t="n">
+        <v>47</v>
+      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>47</v>
+      </c>
+      <c r="V44" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>239 BELVIDERE ROAD</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>PERRYVILLE</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>21903</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B45" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>SO155386</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>4519794787</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>V7871800000</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>20164396C</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>O-T7871800000</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>13839</v>
+      </c>
+      <c r="N45" t="n">
+        <v>13833</v>
+      </c>
+      <c r="O45" t="n">
+        <v>16</v>
+      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>16</v>
+      </c>
+      <c r="V45" t="n">
+        <v>47.46</v>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>8787 W BUCKEYE ROAD</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>TOLLESON</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>85353</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B46" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>SO155386</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>4519794787</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>V7871800002</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>20164397C</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O-T871800002</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>27008</v>
+      </c>
+      <c r="N46" t="n">
+        <v>26954</v>
+      </c>
+      <c r="O46" t="n">
+        <v>46</v>
+      </c>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>46</v>
+      </c>
+      <c r="V46" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>8787 W BUCKEYE ROAD</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>TOLLESON</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>85353</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B47" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>SO155389</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>4519794790</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>V7871800002</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>20164397C</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>O-T871800002</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
+        <v>27008</v>
+      </c>
+      <c r="N47" t="n">
+        <v>26954</v>
+      </c>
+      <c r="O47" t="n">
+        <v>19</v>
+      </c>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>19</v>
+      </c>
+      <c r="V47" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>2100 Industrial Park Rd</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Hammond</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>70401</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B48" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>SO155387</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>4519794788</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>V7871800000</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>20164396C</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>O-T7871800000</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M48" t="n">
+        <v>13839</v>
+      </c>
+      <c r="N48" t="n">
+        <v>13833</v>
+      </c>
+      <c r="O48" t="n">
+        <v>23</v>
+      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>23</v>
+      </c>
+      <c r="V48" t="n">
+        <v>47.46</v>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>494 State Route 416</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Montgomery</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12549</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B49" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>SO155387</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>4519794788</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>7871800002</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>20164395C</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O-T7871800002</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M49" t="n">
+        <v>12132</v>
+      </c>
+      <c r="N49" t="n">
+        <v>12132</v>
+      </c>
+      <c r="O49" t="n">
+        <v>31</v>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>31</v>
+      </c>
+      <c r="V49" t="n">
+        <v>36.86</v>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>494 State Route 416</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Montgomery</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>12549</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B50" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>SO155390</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>4519794791</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>V7871800002</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>20164397C</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>O-T871800002</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M50" t="n">
+        <v>27008</v>
+      </c>
+      <c r="N50" t="n">
+        <v>26954</v>
+      </c>
+      <c r="O50" t="n">
+        <v>210</v>
+      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>210</v>
+      </c>
+      <c r="V50" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>264 SOUTH 5750 WEST</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>SALT LAKE CITY</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>84104</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B51" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>SO155391</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>4519794792</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>V7871800002</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>20164397C</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>O-T871800002</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M51" t="n">
+        <v>27008</v>
+      </c>
+      <c r="N51" t="n">
+        <v>26954</v>
+      </c>
+      <c r="O51" t="n">
+        <v>140</v>
+      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>140</v>
+      </c>
+      <c r="V51" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>3770 HOGUM BAY RD. NE</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>LACEY</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>98516</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B52" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>SO155392</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>4519794793</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>7871800002</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>20164395C</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>O-T7871800002</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
+        <v>12132</v>
+      </c>
+      <c r="N52" t="n">
+        <v>12132</v>
+      </c>
+      <c r="O52" t="n">
+        <v>140</v>
+      </c>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>140</v>
+      </c>
+      <c r="V52" t="n">
+        <v>36.86</v>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>251 HILTON DRIVE</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>JEFFERSONVILLE</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>47130</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B53" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>SO155394</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>4519794795</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>7871800002</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>20164395C</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>O-T7871800002</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M53" t="n">
+        <v>12132</v>
+      </c>
+      <c r="N53" t="n">
+        <v>12132</v>
+      </c>
+      <c r="O53" t="n">
+        <v>70</v>
+      </c>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>70</v>
+      </c>
+      <c r="V53" t="n">
+        <v>36.86</v>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>600 DERBY AVENUE</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>WEST HAVEN</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>06516</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B54" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>SO155287</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>4519788430</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>7871800002</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>20164395C</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>O-T7871800002</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M54" t="n">
+        <v>12132</v>
+      </c>
+      <c r="N54" t="n">
+        <v>12132</v>
+      </c>
+      <c r="O54" t="n">
+        <v>1</v>
+      </c>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
+      </c>
+      <c r="V54" t="n">
+        <v>36.86</v>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>1401 N. UNIVERSAL AVE.</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>KANSAS CITY</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>64120</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B55" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>SO155288</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>4519788436</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>7871800002</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>20164395C</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>O-T7871800002</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M55" t="n">
+        <v>12132</v>
+      </c>
+      <c r="N55" t="n">
+        <v>12132</v>
+      </c>
+      <c r="O55" t="n">
+        <v>4</v>
+      </c>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>4</v>
+      </c>
+      <c r="V55" t="n">
+        <v>36.86</v>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>13115 BROCKTON LANE N</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>ROGERS</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>MN</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>55374</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B56" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>202033</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>MEI : MEDLINE INDUSTRIES, INC. - MD 202033</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>SO155291</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>4519788483</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>V7871800000</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>20164396C</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>O-T7871800000</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M56" t="n">
+        <v>13839</v>
+      </c>
+      <c r="N56" t="n">
+        <v>13833</v>
+      </c>
+      <c r="O56" t="n">
+        <v>20</v>
+      </c>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>20</v>
+      </c>
+      <c r="V56" t="n">
+        <v>47.46</v>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>3446 Highway 51 N, Suite 100</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Southaven</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>38672</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B57" s="1" t="n">
         <v>46112</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>209249</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Medi-Rents &amp; Sales, Inc. 209249</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>SO155186</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>14027</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>201052</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>MCK : MCKESSON MEDICAL SURGICAL MD PC 201052</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>SO155117</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>37022816</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
         <is>
           <t>SENSI MEDICAL</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>7871800002</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20164395C</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>7871800002: STERILE WATER FOR INHALATION  USP 2000ML BAG 6/CASE</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>V7871800000</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>20164396C</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>1258911</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>V7871800000: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 1000ML BAG 14/CASE 1248/CTN</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="M10" t="n">
-        <v>12483</v>
-      </c>
-      <c r="N10" t="n">
-        <v>12132</v>
-      </c>
-      <c r="O10" t="n">
-        <v>65</v>
-      </c>
-      <c r="P10" t="n">
-        <v>65</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>36.86</v>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>9103 YELLOW BRICK RD</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>Rosedale</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
+      <c r="M57" t="n">
+        <v>13839</v>
+      </c>
+      <c r="N57" t="n">
+        <v>13833</v>
+      </c>
+      <c r="O57" t="n">
+        <v>6</v>
+      </c>
+      <c r="P57" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" t="n">
+        <v>47.46</v>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>SEATTLE  #255</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>KENT</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>98032</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>MD</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>21237</t>
+      <c r="B58" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>201052</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>MCK : MCKESSON MEDICAL SURGICAL MD PC 201052</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>SO155117</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>37022816</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>SENSI MEDICAL</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>V7871800002</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>20164397C</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>1258913</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>V7871800002: PRIVATE LABEL STERILE WATER FOR INHALATION  USP 2000ML  BAG 6/CASE 1400/CTN</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M58" t="n">
+        <v>27008</v>
+      </c>
+      <c r="N58" t="n">
+        <v>26954</v>
+      </c>
+      <c r="O58" t="n">
+        <v>54</v>
+      </c>
+      <c r="P58" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>SEATTLE  #255</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>KENT</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>98032</t>
         </is>
       </c>
     </row>

--- a/data/searchresults.xlsx
+++ b/data/searchresults.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OPTSensiMedicalSalesOpenOrderR" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OPTSensiMedicalSalesOpenOrderP" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/searchresults.xlsx
+++ b/data/searchresults.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OPTSensiMedicalSalesOpenOrderP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OPTSensiMedicalSalesOpenOrderR" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
